--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.303568532</v>
+        <v>1811.3036050799</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.28467152</v>
+        <v>652069.2978287641</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1084,10 +1084,10 @@
         <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371340839</v>
       </c>
       <c r="O17" t="n">
-        <v>90317.2541176477</v>
+        <v>90317.2540839297</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1396,10 +1396,10 @@
         <v>30</v>
       </c>
       <c r="N25" t="n">
-        <v>15403.520437158</v>
+        <v>15403.520494505</v>
       </c>
       <c r="O25" t="n">
-        <v>462105.61311474</v>
+        <v>462105.61483515</v>
       </c>
       <c r="P25" t="n">
         <v>33500</v>
@@ -2505,10 +2505,10 @@
         <v>175</v>
       </c>
       <c r="N50" t="n">
-        <v>28.165701357466</v>
+        <v>28.165681818182</v>
       </c>
       <c r="O50" t="n">
-        <v>4928.99773755655</v>
+        <v>4928.99431818185</v>
       </c>
       <c r="P50" t="n">
         <v>6800</v>
@@ -3350,10 +3350,10 @@
         <v>720</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0517240829</v>
+        <v>1098.0519160318</v>
       </c>
       <c r="O69" t="n">
-        <v>790597.241339688</v>
+        <v>790597.3795428959</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3670,10 +3670,10 @@
         <v>120</v>
       </c>
       <c r="N76" t="n">
-        <v>2033.5815122873</v>
+        <v>2033.5814772727</v>
       </c>
       <c r="O76" t="n">
-        <v>244029.781474476</v>
+        <v>244029.777272724</v>
       </c>
       <c r="P76" t="n">
         <v>4100</v>
@@ -3762,10 +3762,10 @@
         <v>3410</v>
       </c>
       <c r="N78" t="n">
-        <v>3158.8608104732</v>
+        <v>3158.8608123465</v>
       </c>
       <c r="O78" t="n">
-        <v>10771715.36371361</v>
+        <v>10771715.37010157</v>
       </c>
       <c r="P78" t="n">
         <v>5600</v>
@@ -3857,10 +3857,10 @@
         <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>3230.0679765396</v>
+        <v>3230.0679433681</v>
       </c>
       <c r="O80" t="n">
-        <v>193804.078592376</v>
+        <v>193804.076602086</v>
       </c>
       <c r="P80" t="n">
         <v>6200</v>
@@ -4234,10 +4234,10 @@
         <v>332</v>
       </c>
       <c r="N88" t="n">
-        <v>3594.2542925089</v>
+        <v>3594.2542686567</v>
       </c>
       <c r="O88" t="n">
-        <v>1193292.425112955</v>
+        <v>1193292.417194024</v>
       </c>
       <c r="P88" t="n">
         <v>6500</v>
@@ -4678,10 +4678,10 @@
         <v>280</v>
       </c>
       <c r="N98" t="n">
-        <v>1592.5679711276</v>
+        <v>1592.5679397781</v>
       </c>
       <c r="O98" t="n">
-        <v>445919.031915728</v>
+        <v>445919.023137868</v>
       </c>
       <c r="P98" t="n">
         <v>3900</v>
@@ -4986,10 +4986,10 @@
         <v>9</v>
       </c>
       <c r="N105" t="n">
-        <v>9635.7603030303</v>
+        <v>9635.760312500001</v>
       </c>
       <c r="O105" t="n">
-        <v>86721.8427272727</v>
+        <v>86721.84281250001</v>
       </c>
       <c r="P105" t="n">
         <v>12500</v>
@@ -5317,10 +5317,10 @@
         <v>748</v>
       </c>
       <c r="N112" t="n">
-        <v>1630.9228220183</v>
+        <v>1630.9228476208</v>
       </c>
       <c r="O112" t="n">
-        <v>1219930.270869688</v>
+        <v>1219930.290020358</v>
       </c>
       <c r="P112" t="n">
         <v>2500</v>
@@ -5363,10 +5363,10 @@
         <v>231</v>
       </c>
       <c r="N113" t="n">
-        <v>1550.1927548066</v>
+        <v>1550.1927793589</v>
       </c>
       <c r="O113" t="n">
-        <v>358094.5263603246</v>
+        <v>358094.5320319059</v>
       </c>
       <c r="P113" t="n">
         <v>2500</v>
@@ -5409,10 +5409,10 @@
         <v>168</v>
       </c>
       <c r="N114" t="n">
-        <v>1579.391452381</v>
+        <v>1579.3914319809</v>
       </c>
       <c r="O114" t="n">
-        <v>265337.764000008</v>
+        <v>265337.7605727912</v>
       </c>
       <c r="P114" t="n">
         <v>2900</v>
@@ -5455,10 +5455,10 @@
         <v>271</v>
       </c>
       <c r="N115" t="n">
-        <v>2403.5095333845</v>
+        <v>2403.5096714419</v>
       </c>
       <c r="O115" t="n">
-        <v>651351.0835471995</v>
+        <v>651351.1209607549</v>
       </c>
       <c r="P115" t="n">
         <v>3500</v>
@@ -5501,10 +5501,10 @@
         <v>56</v>
       </c>
       <c r="N116" t="n">
-        <v>2521.5499887387</v>
+        <v>2521.5498862344</v>
       </c>
       <c r="O116" t="n">
-        <v>141206.7993693672</v>
+        <v>141206.7936291264</v>
       </c>
       <c r="P116" t="n">
         <v>3900</v>
@@ -6289,10 +6289,10 @@
         <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>2029.8734883721</v>
+        <v>2029.8735277516</v>
       </c>
       <c r="O134" t="n">
-        <v>4059.7469767442</v>
+        <v>4059.7470555032</v>
       </c>
       <c r="P134" t="n">
         <v>3600</v>
@@ -6371,10 +6371,10 @@
         <v>141</v>
       </c>
       <c r="N136" t="n">
-        <v>2680.7397012195</v>
+        <v>2680.739700672</v>
       </c>
       <c r="O136" t="n">
-        <v>377984.2978719495</v>
+        <v>377984.297794752</v>
       </c>
       <c r="P136" t="n">
         <v>4900</v>
@@ -6663,10 +6663,10 @@
         <v>4</v>
       </c>
       <c r="N143" t="n">
-        <v>11562.038549223</v>
+        <v>11562.038545455</v>
       </c>
       <c r="O143" t="n">
-        <v>46248.154196892</v>
+        <v>46248.15418182</v>
       </c>
       <c r="P143" t="n">
         <v>18500</v>
@@ -7091,10 +7091,10 @@
         <v>26</v>
       </c>
       <c r="N153" t="n">
-        <v>2568.835631068</v>
+        <v>2568.8356026059</v>
       </c>
       <c r="O153" t="n">
-        <v>66789.726407768</v>
+        <v>66789.7256677534</v>
       </c>
       <c r="P153" t="n">
         <v>4500</v>
@@ -7178,10 +7178,10 @@
         <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>7969.9501638124</v>
+        <v>7969.9501643017</v>
       </c>
       <c r="O155" t="n">
-        <v>39849.750819062</v>
+        <v>39849.7508215085</v>
       </c>
       <c r="P155" t="n">
         <v>12900</v>
@@ -7764,10 +7764,10 @@
         <v>2</v>
       </c>
       <c r="N168" t="n">
-        <v>4163.1601333333</v>
+        <v>4254.3242335766</v>
       </c>
       <c r="O168" t="n">
-        <v>8326.3202666666</v>
+        <v>8508.6484671532</v>
       </c>
       <c r="P168" t="n">
         <v>6700</v>
@@ -7948,10 +7948,10 @@
         <v>155</v>
       </c>
       <c r="N172" t="n">
-        <v>5218.1704503582</v>
+        <v>5234.4433367983</v>
       </c>
       <c r="O172" t="n">
-        <v>808816.4198055209</v>
+        <v>811338.7172037365</v>
       </c>
       <c r="P172" t="n">
         <v>8500</v>
@@ -7994,10 +7994,10 @@
         <v>112</v>
       </c>
       <c r="N173" t="n">
-        <v>1595.0095763657</v>
+        <v>1595.0095696489</v>
       </c>
       <c r="O173" t="n">
-        <v>178641.0725529584</v>
+        <v>178641.0718006768</v>
       </c>
       <c r="P173" t="n">
         <v>2600</v>
@@ -8224,10 +8224,10 @@
         <v>158</v>
       </c>
       <c r="N178" t="n">
-        <v>1812.57</v>
+        <v>1821.7243939394</v>
       </c>
       <c r="O178" t="n">
-        <v>286386.06</v>
+        <v>287832.4542424252</v>
       </c>
       <c r="P178" t="n">
         <v>2900</v>
@@ -8696,10 +8696,10 @@
         <v>108</v>
       </c>
       <c r="N188" t="n">
-        <v>3903.7357803468</v>
+        <v>3903.7358031838</v>
       </c>
       <c r="O188" t="n">
-        <v>421603.4642774544</v>
+        <v>421603.4667438504</v>
       </c>
       <c r="P188" t="n">
         <v>7500</v>
@@ -9110,10 +9110,10 @@
         <v>344</v>
       </c>
       <c r="N197" t="n">
-        <v>17075.989526424</v>
+        <v>17075.98952512</v>
       </c>
       <c r="O197" t="n">
-        <v>5874140.397089856</v>
+        <v>5874140.39664128</v>
       </c>
       <c r="P197" t="n">
         <v>27500</v>
@@ -9340,10 +9340,10 @@
         <v>552</v>
       </c>
       <c r="N202" t="n">
-        <v>1516.0388206553</v>
+        <v>1516.0388192979</v>
       </c>
       <c r="O202" t="n">
-        <v>836853.4290017256</v>
+        <v>836853.4282524409</v>
       </c>
       <c r="P202" t="n">
         <v>2300</v>
@@ -9386,10 +9386,10 @@
         <v>432</v>
       </c>
       <c r="N203" t="n">
-        <v>2458.5136716147</v>
+        <v>2458.5136620146</v>
       </c>
       <c r="O203" t="n">
-        <v>1062077.90613755</v>
+        <v>1062077.901990307</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.3843686869</v>
+        <v>2079.3843256997</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.248484856</v>
+        <v>499052.2381679281</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>266</v>
       </c>
       <c r="N206" t="n">
-        <v>1803.0147280335</v>
+        <v>1803.0147949081</v>
       </c>
       <c r="O206" t="n">
-        <v>479601.917656911</v>
+        <v>479601.9354455546</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9570,10 +9570,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>3306.595599022</v>
+        <v>3306.5955223881</v>
       </c>
       <c r="O207" t="n">
-        <v>158716.588753056</v>
+        <v>158716.5850746288</v>
       </c>
       <c r="P207" t="n">
         <v>4900</v>
@@ -9616,10 +9616,10 @@
         <v>264</v>
       </c>
       <c r="N208" t="n">
-        <v>2122.1642044444</v>
+        <v>2122.1641906742</v>
       </c>
       <c r="O208" t="n">
-        <v>560251.3499733217</v>
+        <v>560251.3463379889</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7892625995</v>
+        <v>2108.7893319081</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.653814328</v>
+        <v>303665.6637947664</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.0840859599</v>
+        <v>2056.0840312319</v>
       </c>
       <c r="O210" t="n">
-        <v>592152.2167564513</v>
+        <v>592152.2009947873</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>3224.5675687104</v>
+        <v>3224.5675847458</v>
       </c>
       <c r="O211" t="n">
-        <v>696506.5948414464</v>
+        <v>696506.5983050928</v>
       </c>
       <c r="P211" t="n">
         <v>4500</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.9315593531</v>
+        <v>1655.9315412844</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.2890936928</v>
+        <v>476908.2838899072</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9846,10 +9846,10 @@
         <v>289</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.2740100137</v>
+        <v>1592.274090065</v>
       </c>
       <c r="O213" t="n">
-        <v>460167.1888939593</v>
+        <v>460167.212028785</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9936,10 +9936,10 @@
         <v>84</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9281444759</v>
+        <v>2311.9280428571</v>
       </c>
       <c r="O215" t="n">
-        <v>194201.9641359756</v>
+        <v>194201.9555999964</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -9982,10 +9982,10 @@
         <v>12</v>
       </c>
       <c r="N216" t="n">
-        <v>1906.1878571429</v>
+        <v>1906.1877678571</v>
       </c>
       <c r="O216" t="n">
-        <v>22874.2542857148</v>
+        <v>22874.2532142852</v>
       </c>
       <c r="P216" t="n">
         <v>2900</v>
@@ -10028,10 +10028,10 @@
         <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>2546.9861569689</v>
+        <v>2546.986027972</v>
       </c>
       <c r="O217" t="n">
-        <v>122255.3355345072</v>
+        <v>122255.329342656</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
@@ -10074,10 +10074,10 @@
         <v>600</v>
       </c>
       <c r="N218" t="n">
-        <v>1259.2741948888</v>
+        <v>1259.2742318172</v>
       </c>
       <c r="O218" t="n">
-        <v>755564.5169332799</v>
+        <v>755564.53909032</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -10251,10 +10251,10 @@
         <v>192</v>
       </c>
       <c r="N222" t="n">
-        <v>692.1519887834301</v>
+        <v>692.151995671</v>
       </c>
       <c r="O222" t="n">
-        <v>132893.1818464186</v>
+        <v>132893.183168832</v>
       </c>
       <c r="P222" t="n">
         <v>1200</v>
@@ -10726,10 +10726,10 @@
         <v>324</v>
       </c>
       <c r="N232" t="n">
-        <v>1530.4499206664</v>
+        <v>1530.4499206349</v>
       </c>
       <c r="O232" t="n">
-        <v>495865.7742959136</v>
+        <v>495865.7742857076</v>
       </c>
       <c r="P232" t="n">
         <v>2600</v>
@@ -11097,10 +11097,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>1690.8700087222</v>
+        <v>1690.8700087336</v>
       </c>
       <c r="O240" t="n">
-        <v>1690.8700087222</v>
+        <v>1690.8700087336</v>
       </c>
       <c r="P240" t="n">
         <v>3000</v>
@@ -11435,10 +11435,10 @@
         <v>2856</v>
       </c>
       <c r="N247" t="n">
-        <v>517.28707627294</v>
+        <v>517.28716412902</v>
       </c>
       <c r="O247" t="n">
-        <v>1477371.889835517</v>
+        <v>1477372.140752481</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11674,10 +11674,10 @@
         <v>630</v>
       </c>
       <c r="N252" t="n">
-        <v>3110.8438819661</v>
+        <v>3110.8436976288</v>
       </c>
       <c r="O252" t="n">
-        <v>1959831.645638643</v>
+        <v>1959831.529506144</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11902,10 +11902,10 @@
         <v>14016</v>
       </c>
       <c r="N257" t="n">
-        <v>703.79553851454</v>
+        <v>703.79553051727</v>
       </c>
       <c r="O257" t="n">
-        <v>9864398.267819792</v>
+        <v>9864398.155730056</v>
       </c>
       <c r="P257" t="n">
         <v>900</v>
@@ -11997,10 +11997,10 @@
         <v>172</v>
       </c>
       <c r="N259" t="n">
-        <v>3182.2510791367</v>
+        <v>3182.2510752688</v>
       </c>
       <c r="O259" t="n">
-        <v>547347.1856115124</v>
+        <v>547347.1849462336</v>
       </c>
       <c r="P259" t="n">
         <v>6900</v>
@@ -12181,10 +12181,10 @@
         <v>59</v>
       </c>
       <c r="N263" t="n">
-        <v>2501.3856451613</v>
+        <v>2501.3856275304</v>
       </c>
       <c r="O263" t="n">
-        <v>147581.7530645167</v>
+        <v>147581.7520242936</v>
       </c>
       <c r="P263" t="n">
         <v>4100</v>
@@ -13621,10 +13621,10 @@
         <v>1</v>
       </c>
       <c r="N293" t="n">
-        <v>3505.3803571429</v>
+        <v>3505.3803636364</v>
       </c>
       <c r="O293" t="n">
-        <v>3505.3803571429</v>
+        <v>3505.3803636364</v>
       </c>
       <c r="P293" t="n">
         <v>12900</v>
@@ -13759,10 +13759,10 @@
         <v>17</v>
       </c>
       <c r="N296" t="n">
-        <v>11866.99440678</v>
+        <v>11866.994561404</v>
       </c>
       <c r="O296" t="n">
-        <v>201738.90491526</v>
+        <v>201738.907543868</v>
       </c>
       <c r="P296" t="n">
         <v>55000</v>
@@ -17669,10 +17669,10 @@
         <v>8</v>
       </c>
       <c r="N377" t="n">
-        <v>7046.9398310097</v>
+        <v>7046.9398308668</v>
       </c>
       <c r="O377" t="n">
-        <v>56375.5186480776</v>
+        <v>56375.5186469344</v>
       </c>
       <c r="P377" t="n">
         <v>9900</v>
@@ -18352,10 +18352,10 @@
         <v>984</v>
       </c>
       <c r="N391" t="n">
-        <v>430.6099770247</v>
+        <v>430.60997670355</v>
       </c>
       <c r="O391" t="n">
-        <v>423720.2173923048</v>
+        <v>423720.2170762932</v>
       </c>
       <c r="P391" t="n">
         <v>2200</v>
@@ -18914,10 +18914,10 @@
         <v>42</v>
       </c>
       <c r="N403" t="n">
-        <v>1547.8820987654</v>
+        <v>1547.8821518987</v>
       </c>
       <c r="O403" t="n">
-        <v>65011.0481481468</v>
+        <v>65011.0503797454</v>
       </c>
       <c r="P403" t="n">
         <v>5500</v>
@@ -19016,10 +19016,10 @@
         <v>63</v>
       </c>
       <c r="N405" t="n">
-        <v>1757.3204971319</v>
+        <v>1757.320503876</v>
       </c>
       <c r="O405" t="n">
-        <v>110711.1913193097</v>
+        <v>110711.191744188</v>
       </c>
       <c r="P405" t="n">
         <v>2000</v>
@@ -21306,10 +21306,10 @@
         <v>38</v>
       </c>
       <c r="N455" t="n">
-        <v>1319.3608426966</v>
+        <v>1319.3608695652</v>
       </c>
       <c r="O455" t="n">
-        <v>50135.7120224708</v>
+        <v>50135.7130434776</v>
       </c>
       <c r="P455" t="n">
         <v>3500</v>
@@ -21694,10 +21694,10 @@
         <v>42</v>
       </c>
       <c r="N463" t="n">
-        <v>2432.1338016529</v>
+        <v>2432.1338655462</v>
       </c>
       <c r="O463" t="n">
-        <v>102149.6196694218</v>
+        <v>102149.6223529404</v>
       </c>
       <c r="P463" t="n">
         <v>4500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -7764,10 +7764,10 @@
         <v>2</v>
       </c>
       <c r="N168" t="n">
-        <v>4254.3242335766</v>
+        <v>4163.1601459854</v>
       </c>
       <c r="O168" t="n">
-        <v>8508.6484671532</v>
+        <v>8326.3202919708</v>
       </c>
       <c r="P168" t="n">
         <v>6700</v>
@@ -7948,10 +7948,10 @@
         <v>155</v>
       </c>
       <c r="N172" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O172" t="n">
-        <v>811338.7172037365</v>
+        <v>808816.4208939775</v>
       </c>
       <c r="P172" t="n">
         <v>8500</v>
@@ -8224,10 +8224,10 @@
         <v>158</v>
       </c>
       <c r="N178" t="n">
-        <v>1821.7243939394</v>
+        <v>1812.57</v>
       </c>
       <c r="O178" t="n">
-        <v>287832.4542424252</v>
+        <v>286386.06</v>
       </c>
       <c r="P178" t="n">
         <v>2900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3036050799</v>
+        <v>1811.3037351443</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.2978287641</v>
+        <v>652069.344651948</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2413.0011709602</v>
+        <v>2413.0011723329</v>
       </c>
       <c r="O18" t="n">
-        <v>4826.0023419204</v>
+        <v>4826.0023446658</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
         <v>3526.1</v>
       </c>
       <c r="O20" t="n">
-        <v>74048.09999999999</v>
+        <v>24682.7</v>
       </c>
       <c r="P20" t="n">
         <v>6300</v>
       </c>
       <c r="Q20" t="n">
-        <v>132300</v>
+        <v>44100</v>
       </c>
     </row>
     <row r="21">
@@ -3350,10 +3350,10 @@
         <v>720</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0519160318</v>
+        <v>1098.0523152957</v>
       </c>
       <c r="O69" t="n">
-        <v>790597.3795428959</v>
+        <v>790597.6670129041</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3670,10 +3670,10 @@
         <v>120</v>
       </c>
       <c r="N76" t="n">
-        <v>2033.5814772727</v>
+        <v>2033.5796673597</v>
       </c>
       <c r="O76" t="n">
-        <v>244029.777272724</v>
+        <v>244029.560083164</v>
       </c>
       <c r="P76" t="n">
         <v>4100</v>
@@ -3762,10 +3762,10 @@
         <v>3410</v>
       </c>
       <c r="N78" t="n">
-        <v>3158.8608123465</v>
+        <v>3158.860813208</v>
       </c>
       <c r="O78" t="n">
-        <v>10771715.37010157</v>
+        <v>10771715.37303928</v>
       </c>
       <c r="P78" t="n">
         <v>5600</v>
@@ -3808,10 +3808,10 @@
         <v>320</v>
       </c>
       <c r="N79" t="n">
-        <v>3841.6246596357</v>
+        <v>3841.6246641075</v>
       </c>
       <c r="O79" t="n">
-        <v>1229319.891083424</v>
+        <v>1229319.8925144</v>
       </c>
       <c r="P79" t="n">
         <v>6900</v>
@@ -3857,10 +3857,10 @@
         <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>3230.0679433681</v>
+        <v>3230.0678931298</v>
       </c>
       <c r="O80" t="n">
-        <v>193804.076602086</v>
+        <v>193804.073587788</v>
       </c>
       <c r="P80" t="n">
         <v>6200</v>
@@ -4093,10 +4093,10 @@
         <v>3</v>
       </c>
       <c r="N85" t="n">
-        <v>4967.81144</v>
+        <v>4967.8119354839</v>
       </c>
       <c r="O85" t="n">
-        <v>14903.43432</v>
+        <v>14903.4358064517</v>
       </c>
       <c r="P85" t="n">
         <v>7500</v>
@@ -4234,10 +4234,10 @@
         <v>332</v>
       </c>
       <c r="N88" t="n">
-        <v>3594.2542686567</v>
+        <v>3594.2542583732</v>
       </c>
       <c r="O88" t="n">
-        <v>1193292.417194024</v>
+        <v>1193292.413779903</v>
       </c>
       <c r="P88" t="n">
         <v>6500</v>
@@ -4417,10 +4417,10 @@
         <v>22</v>
       </c>
       <c r="N92" t="n">
-        <v>19098.750004659</v>
+        <v>19098.75000466</v>
       </c>
       <c r="O92" t="n">
-        <v>420172.500102498</v>
+        <v>420172.50010252</v>
       </c>
       <c r="P92" t="n">
         <v>15000</v>
@@ -4678,10 +4678,10 @@
         <v>280</v>
       </c>
       <c r="N98" t="n">
-        <v>1592.5679397781</v>
+        <v>1592.567877551</v>
       </c>
       <c r="O98" t="n">
-        <v>445919.023137868</v>
+        <v>445919.00571428</v>
       </c>
       <c r="P98" t="n">
         <v>3900</v>
@@ -4986,10 +4986,10 @@
         <v>9</v>
       </c>
       <c r="N105" t="n">
-        <v>9635.760312500001</v>
+        <v>9635.760317460299</v>
       </c>
       <c r="O105" t="n">
-        <v>86721.84281250001</v>
+        <v>86721.84285714269</v>
       </c>
       <c r="P105" t="n">
         <v>12500</v>
@@ -5317,10 +5317,10 @@
         <v>748</v>
       </c>
       <c r="N112" t="n">
-        <v>1630.9228476208</v>
+        <v>1630.9229073724</v>
       </c>
       <c r="O112" t="n">
-        <v>1219930.290020358</v>
+        <v>1219930.334714555</v>
       </c>
       <c r="P112" t="n">
         <v>2500</v>
@@ -5363,10 +5363,10 @@
         <v>231</v>
       </c>
       <c r="N113" t="n">
-        <v>1550.1927793589</v>
+        <v>1550.1928456407</v>
       </c>
       <c r="O113" t="n">
-        <v>358094.5320319059</v>
+        <v>358094.5473430017</v>
       </c>
       <c r="P113" t="n">
         <v>2500</v>
@@ -5409,10 +5409,10 @@
         <v>168</v>
       </c>
       <c r="N114" t="n">
-        <v>1579.3914319809</v>
+        <v>1579.3914114833</v>
       </c>
       <c r="O114" t="n">
-        <v>265337.7605727912</v>
+        <v>265337.7571291944</v>
       </c>
       <c r="P114" t="n">
         <v>2900</v>
@@ -5455,10 +5455,10 @@
         <v>271</v>
       </c>
       <c r="N115" t="n">
-        <v>2403.5096714419</v>
+        <v>2403.5097473321</v>
       </c>
       <c r="O115" t="n">
-        <v>651351.1209607549</v>
+        <v>651351.1415269991</v>
       </c>
       <c r="P115" t="n">
         <v>3500</v>
@@ -5501,10 +5501,10 @@
         <v>56</v>
       </c>
       <c r="N116" t="n">
-        <v>2521.5498862344</v>
+        <v>2521.5490111248</v>
       </c>
       <c r="O116" t="n">
-        <v>141206.7936291264</v>
+        <v>141206.7446229888</v>
       </c>
       <c r="P116" t="n">
         <v>3900</v>
@@ -5986,10 +5986,10 @@
         <v>5</v>
       </c>
       <c r="N127" t="n">
-        <v>6487.6411111111</v>
+        <v>6487.6416666667</v>
       </c>
       <c r="O127" t="n">
-        <v>32438.2055555555</v>
+        <v>32438.2083333335</v>
       </c>
       <c r="P127" t="n">
         <v>11900</v>
@@ -6371,10 +6371,10 @@
         <v>141</v>
       </c>
       <c r="N136" t="n">
-        <v>2680.739700672</v>
+        <v>2680.739700489</v>
       </c>
       <c r="O136" t="n">
-        <v>377984.297794752</v>
+        <v>377984.297768949</v>
       </c>
       <c r="P136" t="n">
         <v>4900</v>
@@ -6412,10 +6412,10 @@
         <v>402</v>
       </c>
       <c r="N137" t="n">
-        <v>880.32913152496</v>
+        <v>880.32918386061</v>
       </c>
       <c r="O137" t="n">
-        <v>353892.3108730339</v>
+        <v>353892.3319119652</v>
       </c>
       <c r="P137" t="n">
         <v>1200</v>
@@ -7764,10 +7764,10 @@
         <v>2</v>
       </c>
       <c r="N168" t="n">
-        <v>4163.1601459854</v>
+        <v>4163.1601515152</v>
       </c>
       <c r="O168" t="n">
-        <v>8326.3202919708</v>
+        <v>8326.320303030399</v>
       </c>
       <c r="P168" t="n">
         <v>6700</v>
@@ -7948,10 +7948,10 @@
         <v>155</v>
       </c>
       <c r="N172" t="n">
-        <v>5218.1704573805</v>
+        <v>5218.1704631579</v>
       </c>
       <c r="O172" t="n">
-        <v>808816.4208939775</v>
+        <v>808816.4217894744</v>
       </c>
       <c r="P172" t="n">
         <v>8500</v>
@@ -7994,10 +7994,10 @@
         <v>112</v>
       </c>
       <c r="N173" t="n">
-        <v>1595.0095696489</v>
+        <v>1595.009520202</v>
       </c>
       <c r="O173" t="n">
-        <v>178641.0718006768</v>
+        <v>178641.066262624</v>
       </c>
       <c r="P173" t="n">
         <v>2600</v>
@@ -9340,10 +9340,10 @@
         <v>552</v>
       </c>
       <c r="N202" t="n">
-        <v>1516.0388192979</v>
+        <v>1516.038818618</v>
       </c>
       <c r="O202" t="n">
-        <v>836853.4282524409</v>
+        <v>836853.427877136</v>
       </c>
       <c r="P202" t="n">
         <v>2300</v>
@@ -9386,10 +9386,10 @@
         <v>432</v>
       </c>
       <c r="N203" t="n">
-        <v>2458.5136620146</v>
+        <v>2458.5136155257</v>
       </c>
       <c r="O203" t="n">
-        <v>1062077.901990307</v>
+        <v>1062077.881907102</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9432,10 +9432,10 @@
         <v>144</v>
       </c>
       <c r="N204" t="n">
-        <v>1771.0915140845</v>
+        <v>1771.0914991182</v>
       </c>
       <c r="O204" t="n">
-        <v>255037.178028168</v>
+        <v>255037.1758730208</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.3843256997</v>
+        <v>2079.3842820513</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.2381679281</v>
+        <v>499052.227692312</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>266</v>
       </c>
       <c r="N206" t="n">
-        <v>1803.0147949081</v>
+        <v>1803.0148044218</v>
       </c>
       <c r="O206" t="n">
-        <v>479601.9354455546</v>
+        <v>479601.9379761988</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9570,10 +9570,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>3306.5955223881</v>
+        <v>3306.595494368</v>
       </c>
       <c r="O207" t="n">
-        <v>158716.5850746288</v>
+        <v>158716.583729664</v>
       </c>
       <c r="P207" t="n">
         <v>4900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7893319081</v>
+        <v>2108.7893820527</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.6637947664</v>
+        <v>303665.6710155888</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>3224.5675847458</v>
+        <v>3224.5676430401</v>
       </c>
       <c r="O211" t="n">
-        <v>696506.5983050928</v>
+        <v>696506.6108966616</v>
       </c>
       <c r="P211" t="n">
         <v>4500</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.9315412844</v>
+        <v>1655.9314708603</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.2838899072</v>
+        <v>476908.2636077664</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9846,10 +9846,10 @@
         <v>289</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.274090065</v>
+        <v>1592.2743101761</v>
       </c>
       <c r="O213" t="n">
-        <v>460167.212028785</v>
+        <v>460167.2756408929</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9936,10 +9936,10 @@
         <v>84</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9280428571</v>
+        <v>2311.9274887892</v>
       </c>
       <c r="O215" t="n">
-        <v>194201.9555999964</v>
+        <v>194201.9090582928</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -9982,10 +9982,10 @@
         <v>12</v>
       </c>
       <c r="N216" t="n">
-        <v>1906.1877678571</v>
+        <v>1906.1875409836</v>
       </c>
       <c r="O216" t="n">
-        <v>22874.2532142852</v>
+        <v>22874.2504918032</v>
       </c>
       <c r="P216" t="n">
         <v>2900</v>
@@ -10028,10 +10028,10 @@
         <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>2546.986027972</v>
+        <v>2546.985477707</v>
       </c>
       <c r="O217" t="n">
-        <v>122255.329342656</v>
+        <v>122255.302929936</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
@@ -10074,10 +10074,10 @@
         <v>600</v>
       </c>
       <c r="N218" t="n">
-        <v>1259.2742318172</v>
+        <v>1259.2742532126</v>
       </c>
       <c r="O218" t="n">
-        <v>755564.53909032</v>
+        <v>755564.5519275599</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -10251,10 +10251,10 @@
         <v>192</v>
       </c>
       <c r="N222" t="n">
-        <v>692.151995671</v>
+        <v>692.15200959024</v>
       </c>
       <c r="O222" t="n">
-        <v>132893.183168832</v>
+        <v>132893.1858413261</v>
       </c>
       <c r="P222" t="n">
         <v>1200</v>
@@ -10346,10 +10346,10 @@
         <v>2829</v>
       </c>
       <c r="N224" t="n">
-        <v>1955.2371193049</v>
+        <v>1955.2371191444</v>
       </c>
       <c r="O224" t="n">
-        <v>5531365.810513563</v>
+        <v>5531365.810059507</v>
       </c>
       <c r="P224" t="n">
         <v>3000</v>
@@ -11097,10 +11097,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>1690.8700087336</v>
+        <v>1690.8700087796</v>
       </c>
       <c r="O240" t="n">
-        <v>1690.8700087336</v>
+        <v>1690.8700087796</v>
       </c>
       <c r="P240" t="n">
         <v>3000</v>
@@ -11435,10 +11435,10 @@
         <v>2856</v>
       </c>
       <c r="N247" t="n">
-        <v>517.28716412902</v>
+        <v>517.28728171896</v>
       </c>
       <c r="O247" t="n">
-        <v>1477372.140752481</v>
+        <v>1477372.47658935</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11674,10 +11674,10 @@
         <v>630</v>
       </c>
       <c r="N252" t="n">
-        <v>3110.8436976288</v>
+        <v>3110.8435374771</v>
       </c>
       <c r="O252" t="n">
-        <v>1959831.529506144</v>
+        <v>1959831.428610573</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11902,10 +11902,10 @@
         <v>14016</v>
       </c>
       <c r="N257" t="n">
-        <v>703.79553051727</v>
+        <v>703.79547499887</v>
       </c>
       <c r="O257" t="n">
-        <v>9864398.155730056</v>
+        <v>9864397.377584161</v>
       </c>
       <c r="P257" t="n">
         <v>900</v>
@@ -12181,10 +12181,10 @@
         <v>59</v>
       </c>
       <c r="N263" t="n">
-        <v>2501.3856275304</v>
+        <v>2501.3856097561</v>
       </c>
       <c r="O263" t="n">
-        <v>147581.7520242936</v>
+        <v>147581.7509756099</v>
       </c>
       <c r="P263" t="n">
         <v>4100</v>
@@ -15647,10 +15647,10 @@
         <v>1000</v>
       </c>
       <c r="N335" t="n">
-        <v>1783.7988883868</v>
+        <v>1783.7988878843</v>
       </c>
       <c r="O335" t="n">
-        <v>1783798.8883868</v>
+        <v>1783798.8878843</v>
       </c>
       <c r="P335" t="n">
         <v>1500</v>
@@ -17669,10 +17669,10 @@
         <v>8</v>
       </c>
       <c r="N377" t="n">
-        <v>7046.9398308668</v>
+        <v>7046.939830831</v>
       </c>
       <c r="O377" t="n">
-        <v>56375.5186469344</v>
+        <v>56375.518646648</v>
       </c>
       <c r="P377" t="n">
         <v>9900</v>
@@ -19016,10 +19016,10 @@
         <v>63</v>
       </c>
       <c r="N405" t="n">
-        <v>1757.320503876</v>
+        <v>1757.3205078125</v>
       </c>
       <c r="O405" t="n">
-        <v>110711.191744188</v>
+        <v>110711.1919921875</v>
       </c>
       <c r="P405" t="n">
         <v>2000</v>
@@ -21403,10 +21403,10 @@
         <v>54</v>
       </c>
       <c r="N457" t="n">
-        <v>3088.1418644068</v>
+        <v>3088.1420689655</v>
       </c>
       <c r="O457" t="n">
-        <v>166759.6606779672</v>
+        <v>166759.671724137</v>
       </c>
       <c r="P457" t="n">
         <v>8500</v>
@@ -21694,10 +21694,10 @@
         <v>42</v>
       </c>
       <c r="N463" t="n">
-        <v>2432.1338655462</v>
+        <v>2432.1340350877</v>
       </c>
       <c r="O463" t="n">
-        <v>102149.6223529404</v>
+        <v>102149.6294736834</v>
       </c>
       <c r="P463" t="n">
         <v>4500</v>
@@ -22660,10 +22660,10 @@
         <v>20</v>
       </c>
       <c r="N484" t="n">
-        <v>7046.74</v>
+        <v>7046.7404347826</v>
       </c>
       <c r="O484" t="n">
-        <v>140934.8</v>
+        <v>140934.808695652</v>
       </c>
       <c r="P484" t="n">
         <v>22900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3037351443</v>
+        <v>1811.3037703513</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.344651948</v>
+        <v>652069.357326468</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -675,10 +675,10 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>27000</v>
+        <v>27225.941422594</v>
       </c>
       <c r="O7" t="n">
-        <v>324000</v>
+        <v>326711.297071128</v>
       </c>
       <c r="P7" t="n">
         <v>30000</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -711,19 +711,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
         <v>7306.61</v>
       </c>
       <c r="O8" t="n">
-        <v>94985.92999999999</v>
+        <v>14613.22</v>
       </c>
       <c r="P8" t="n">
         <v>12700</v>
       </c>
       <c r="Q8" t="n">
-        <v>165100</v>
+        <v>25400</v>
       </c>
     </row>
     <row r="9">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1042,19 +1042,19 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N16" t="n">
         <v>2812</v>
       </c>
       <c r="O16" t="n">
-        <v>36556</v>
+        <v>33744</v>
       </c>
       <c r="P16" t="n">
         <v>5000</v>
       </c>
       <c r="Q16" t="n">
-        <v>65000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="17">
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2413.0011723329</v>
+        <v>2421.5176470588</v>
       </c>
       <c r="O18" t="n">
-        <v>4826.0023446658</v>
+        <v>4843.0352941176</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -1162,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2474.7042715232</v>
+        <v>2487.0572046589</v>
       </c>
       <c r="O19" t="n">
-        <v>9898.8170860928</v>
+        <v>9948.2288186356</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
@@ -1357,10 +1357,10 @@
         <v>56</v>
       </c>
       <c r="N24" t="n">
-        <v>21333.69</v>
+        <v>21510.733070539</v>
       </c>
       <c r="O24" t="n">
-        <v>1194686.64</v>
+        <v>1204601.051950184</v>
       </c>
       <c r="P24" t="n">
         <v>30000</v>
@@ -1396,10 +1396,10 @@
         <v>30</v>
       </c>
       <c r="N25" t="n">
-        <v>15403.520494505</v>
+        <v>15403.520852273</v>
       </c>
       <c r="O25" t="n">
-        <v>462105.61483515</v>
+        <v>462105.62556819</v>
       </c>
       <c r="P25" t="n">
         <v>33500</v>
@@ -2321,10 +2321,10 @@
         <v>23</v>
       </c>
       <c r="N46" t="n">
-        <v>27000</v>
+        <v>27232.75862069</v>
       </c>
       <c r="O46" t="n">
-        <v>621000</v>
+        <v>626353.4482758701</v>
       </c>
       <c r="P46" t="n">
         <v>20000</v>
@@ -2597,10 +2597,10 @@
         <v>7</v>
       </c>
       <c r="N52" t="n">
-        <v>4878.2852688172</v>
+        <v>4878.2859036145</v>
       </c>
       <c r="O52" t="n">
-        <v>34147.9968817204</v>
+        <v>34148.0013253015</v>
       </c>
       <c r="P52" t="n">
         <v>13500</v>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2633,19 +2633,19 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="N53" t="n">
         <v>3667.11</v>
       </c>
       <c r="O53" t="n">
-        <v>132015.96</v>
+        <v>88010.64</v>
       </c>
       <c r="P53" t="n">
         <v>7300</v>
       </c>
       <c r="Q53" t="n">
-        <v>262800</v>
+        <v>175200</v>
       </c>
     </row>
     <row r="54">
@@ -2726,10 +2726,10 @@
         <v>10</v>
       </c>
       <c r="N55" t="n">
-        <v>2563.34</v>
+        <v>2576.9026455026</v>
       </c>
       <c r="O55" t="n">
-        <v>25633.4</v>
+        <v>25769.026455026</v>
       </c>
       <c r="P55" t="n">
         <v>4700</v>
@@ -2814,10 +2814,10 @@
         <v>12</v>
       </c>
       <c r="N57" t="n">
-        <v>11513.19</v>
+        <v>11705.0765</v>
       </c>
       <c r="O57" t="n">
-        <v>138158.28</v>
+        <v>140460.918</v>
       </c>
       <c r="P57" t="n">
         <v>17900</v>
@@ -3350,10 +3350,10 @@
         <v>720</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0523152957</v>
+        <v>1098.0525080824</v>
       </c>
       <c r="O69" t="n">
-        <v>790597.6670129041</v>
+        <v>790597.8058193279</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3670,10 +3670,10 @@
         <v>120</v>
       </c>
       <c r="N76" t="n">
-        <v>2033.5796673597</v>
+        <v>2033.5778733032</v>
       </c>
       <c r="O76" t="n">
-        <v>244029.560083164</v>
+        <v>244029.344796384</v>
       </c>
       <c r="P76" t="n">
         <v>4100</v>
@@ -3762,10 +3762,10 @@
         <v>3410</v>
       </c>
       <c r="N78" t="n">
-        <v>3158.860813208</v>
+        <v>3158.8608137572</v>
       </c>
       <c r="O78" t="n">
-        <v>10771715.37303928</v>
+        <v>10771715.37491205</v>
       </c>
       <c r="P78" t="n">
         <v>5600</v>
@@ -3808,10 +3808,10 @@
         <v>320</v>
       </c>
       <c r="N79" t="n">
-        <v>3841.6246641075</v>
+        <v>3841.6246911197</v>
       </c>
       <c r="O79" t="n">
-        <v>1229319.8925144</v>
+        <v>1229319.901158304</v>
       </c>
       <c r="P79" t="n">
         <v>6900</v>
@@ -3857,10 +3857,10 @@
         <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>3230.0678931298</v>
+        <v>3230.067792</v>
       </c>
       <c r="O80" t="n">
-        <v>193804.073587788</v>
+        <v>193804.06752</v>
       </c>
       <c r="P80" t="n">
         <v>6200</v>
@@ -3903,10 +3903,10 @@
         <v>514</v>
       </c>
       <c r="N81" t="n">
-        <v>2694.8235409253</v>
+        <v>2694.8235120643</v>
       </c>
       <c r="O81" t="n">
-        <v>1385139.300035604</v>
+        <v>1385139.28520105</v>
       </c>
       <c r="P81" t="n">
         <v>4900</v>
@@ -4093,10 +4093,10 @@
         <v>3</v>
       </c>
       <c r="N85" t="n">
-        <v>4967.8119354839</v>
+        <v>4967.814</v>
       </c>
       <c r="O85" t="n">
-        <v>14903.4358064517</v>
+        <v>14903.442</v>
       </c>
       <c r="P85" t="n">
         <v>7500</v>
@@ -4678,10 +4678,10 @@
         <v>280</v>
       </c>
       <c r="N98" t="n">
-        <v>1592.567877551</v>
+        <v>1592.567808681</v>
       </c>
       <c r="O98" t="n">
-        <v>445919.00571428</v>
+        <v>445918.98643068</v>
       </c>
       <c r="P98" t="n">
         <v>3900</v>
@@ -4986,10 +4986,10 @@
         <v>9</v>
       </c>
       <c r="N105" t="n">
-        <v>9635.760317460299</v>
+        <v>9635.7622222222</v>
       </c>
       <c r="O105" t="n">
-        <v>86721.84285714269</v>
+        <v>86721.8599999998</v>
       </c>
       <c r="P105" t="n">
         <v>12500</v>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -5268,19 +5268,19 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N111" t="n">
         <v>12754</v>
       </c>
       <c r="O111" t="n">
-        <v>535668</v>
+        <v>510160</v>
       </c>
       <c r="P111" t="n">
         <v>21500</v>
       </c>
       <c r="Q111" t="n">
-        <v>903000</v>
+        <v>860000</v>
       </c>
     </row>
     <row r="112">
@@ -5317,10 +5317,10 @@
         <v>748</v>
       </c>
       <c r="N112" t="n">
-        <v>1630.9229073724</v>
+        <v>1630.9229356747</v>
       </c>
       <c r="O112" t="n">
-        <v>1219930.334714555</v>
+        <v>1219930.355884676</v>
       </c>
       <c r="P112" t="n">
         <v>2500</v>
@@ -5363,10 +5363,10 @@
         <v>231</v>
       </c>
       <c r="N113" t="n">
-        <v>1550.1928456407</v>
+        <v>1550.192872291</v>
       </c>
       <c r="O113" t="n">
-        <v>358094.5473430017</v>
+        <v>358094.553499221</v>
       </c>
       <c r="P113" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>271</v>
       </c>
       <c r="N115" t="n">
-        <v>2403.5097473321</v>
+        <v>2403.5098964308</v>
       </c>
       <c r="O115" t="n">
-        <v>651351.1415269991</v>
+        <v>651351.1819327468</v>
       </c>
       <c r="P115" t="n">
         <v>3500</v>
@@ -5501,10 +5501,10 @@
         <v>56</v>
       </c>
       <c r="N116" t="n">
-        <v>2521.5490111248</v>
+        <v>2521.5486317136</v>
       </c>
       <c r="O116" t="n">
-        <v>141206.7446229888</v>
+        <v>141206.7233759616</v>
       </c>
       <c r="P116" t="n">
         <v>3900</v>
@@ -6289,10 +6289,10 @@
         <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>2029.8735277516</v>
+        <v>2029.8735344015</v>
       </c>
       <c r="O134" t="n">
-        <v>4059.7470555032</v>
+        <v>4059.747068803</v>
       </c>
       <c r="P134" t="n">
         <v>3600</v>
@@ -6412,10 +6412,10 @@
         <v>402</v>
       </c>
       <c r="N137" t="n">
-        <v>880.32918386061</v>
+        <v>880.32919651056</v>
       </c>
       <c r="O137" t="n">
-        <v>353892.3319119652</v>
+        <v>353892.3369972451</v>
       </c>
       <c r="P137" t="n">
         <v>1200</v>
@@ -7009,10 +7009,10 @@
         <v>16</v>
       </c>
       <c r="N151" t="n">
-        <v>26854</v>
+        <v>27226.972222222</v>
       </c>
       <c r="O151" t="n">
-        <v>429664</v>
+        <v>435631.555555552</v>
       </c>
       <c r="P151" t="n">
         <v>43900</v>
@@ -7764,10 +7764,10 @@
         <v>2</v>
       </c>
       <c r="N168" t="n">
-        <v>4163.1601515152</v>
+        <v>4163.16016</v>
       </c>
       <c r="O168" t="n">
-        <v>8326.320303030399</v>
+        <v>8326.320320000001</v>
       </c>
       <c r="P168" t="n">
         <v>6700</v>
@@ -7810,10 +7810,10 @@
         <v>35</v>
       </c>
       <c r="N169" t="n">
-        <v>8878.450000000001</v>
+        <v>9099.032608695699</v>
       </c>
       <c r="O169" t="n">
-        <v>310745.75</v>
+        <v>318466.1413043495</v>
       </c>
       <c r="P169" t="n">
         <v>14100</v>
@@ -7856,10 +7856,10 @@
         <v>61</v>
       </c>
       <c r="N170" t="n">
-        <v>2495.98</v>
+        <v>2498.7228351648</v>
       </c>
       <c r="O170" t="n">
-        <v>152254.78</v>
+        <v>152422.0929450528</v>
       </c>
       <c r="P170" t="n">
         <v>4100</v>
@@ -7948,10 +7948,10 @@
         <v>155</v>
       </c>
       <c r="N172" t="n">
-        <v>5218.1704631579</v>
+        <v>5218.1704646251</v>
       </c>
       <c r="O172" t="n">
-        <v>808816.4217894744</v>
+        <v>808816.4220168905</v>
       </c>
       <c r="P172" t="n">
         <v>8500</v>
@@ -7994,10 +7994,10 @@
         <v>112</v>
       </c>
       <c r="N173" t="n">
-        <v>1595.009520202</v>
+        <v>1595.0095153061</v>
       </c>
       <c r="O173" t="n">
-        <v>178641.066262624</v>
+        <v>178641.0657142832</v>
       </c>
       <c r="P173" t="n">
         <v>2600</v>
@@ -8086,10 +8086,10 @@
         <v>97</v>
       </c>
       <c r="N175" t="n">
-        <v>3965.02</v>
+        <v>3969.9272029703</v>
       </c>
       <c r="O175" t="n">
-        <v>384606.94</v>
+        <v>385082.9386881191</v>
       </c>
       <c r="P175" t="n">
         <v>6500</v>
@@ -8224,10 +8224,10 @@
         <v>158</v>
       </c>
       <c r="N178" t="n">
-        <v>1812.57</v>
+        <v>1817.3525065963</v>
       </c>
       <c r="O178" t="n">
-        <v>286386.06</v>
+        <v>287141.6960422154</v>
       </c>
       <c r="P178" t="n">
         <v>2900</v>
@@ -8696,10 +8696,10 @@
         <v>108</v>
       </c>
       <c r="N188" t="n">
-        <v>3903.7358031838</v>
+        <v>3903.7358605664</v>
       </c>
       <c r="O188" t="n">
-        <v>421603.4667438504</v>
+        <v>421603.4729411712</v>
       </c>
       <c r="P188" t="n">
         <v>7500</v>
@@ -8788,10 +8788,10 @@
         <v>153</v>
       </c>
       <c r="N190" t="n">
-        <v>13565</v>
+        <v>13585.460030166</v>
       </c>
       <c r="O190" t="n">
-        <v>2075445</v>
+        <v>2078575.384615398</v>
       </c>
       <c r="P190" t="n">
         <v>22500</v>
@@ -9248,10 +9248,10 @@
         <v>85</v>
       </c>
       <c r="N200" t="n">
-        <v>10713.21</v>
+        <v>10816.221634615</v>
       </c>
       <c r="O200" t="n">
-        <v>910622.85</v>
+        <v>919378.838942275</v>
       </c>
       <c r="P200" t="n">
         <v>20900</v>
@@ -9340,10 +9340,10 @@
         <v>552</v>
       </c>
       <c r="N202" t="n">
-        <v>1516.038818618</v>
+        <v>1516.0388180509</v>
       </c>
       <c r="O202" t="n">
-        <v>836853.427877136</v>
+        <v>836853.4275640969</v>
       </c>
       <c r="P202" t="n">
         <v>2300</v>
@@ -9386,10 +9386,10 @@
         <v>432</v>
       </c>
       <c r="N203" t="n">
-        <v>2458.5136155257</v>
+        <v>2458.5135821813</v>
       </c>
       <c r="O203" t="n">
-        <v>1062077.881907102</v>
+        <v>1062077.867502322</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9432,10 +9432,10 @@
         <v>144</v>
       </c>
       <c r="N204" t="n">
-        <v>1771.0914991182</v>
+        <v>1771.0914183976</v>
       </c>
       <c r="O204" t="n">
-        <v>255037.1758730208</v>
+        <v>255037.1642492544</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.3842820513</v>
+        <v>2079.384280218</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.227692312</v>
+        <v>499052.22725232</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>266</v>
       </c>
       <c r="N206" t="n">
-        <v>1803.0148044218</v>
+        <v>1803.0149016773</v>
       </c>
       <c r="O206" t="n">
-        <v>479601.9379761988</v>
+        <v>479601.9638461618</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9570,10 +9570,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>3306.595494368</v>
+        <v>3306.5954716981</v>
       </c>
       <c r="O207" t="n">
-        <v>158716.583729664</v>
+        <v>158716.5826415088</v>
       </c>
       <c r="P207" t="n">
         <v>4900</v>
@@ -9616,10 +9616,10 @@
         <v>264</v>
       </c>
       <c r="N208" t="n">
-        <v>2122.1641906742</v>
+        <v>2122.1641716329</v>
       </c>
       <c r="O208" t="n">
-        <v>560251.3463379889</v>
+        <v>560251.3413110856</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7893820527</v>
+        <v>2108.7895881384</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.6710155888</v>
+        <v>303665.7006919296</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.0840312319</v>
+        <v>2056.0839842611</v>
       </c>
       <c r="O210" t="n">
-        <v>592152.2009947873</v>
+        <v>592152.1874671967</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>3224.5676430401</v>
+        <v>3224.5678063672</v>
       </c>
       <c r="O211" t="n">
-        <v>696506.6108966616</v>
+        <v>696506.6461753151</v>
       </c>
       <c r="P211" t="n">
         <v>4500</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.9314708603</v>
+        <v>1655.9314682295</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.2636077664</v>
+        <v>476908.262850096</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9846,10 +9846,10 @@
         <v>289</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.2743101761</v>
+        <v>1592.2744517433</v>
       </c>
       <c r="O213" t="n">
-        <v>460167.2756408929</v>
+        <v>460167.3165538137</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9936,10 +9936,10 @@
         <v>84</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9274887892</v>
+        <v>2311.9273755656</v>
       </c>
       <c r="O215" t="n">
-        <v>194201.9090582928</v>
+        <v>194201.8995475104</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -9982,10 +9982,10 @@
         <v>12</v>
       </c>
       <c r="N216" t="n">
-        <v>1906.1875409836</v>
+        <v>1906.1874003466</v>
       </c>
       <c r="O216" t="n">
-        <v>22874.2504918032</v>
+        <v>22874.2488041592</v>
       </c>
       <c r="P216" t="n">
         <v>2900</v>
@@ -10028,10 +10028,10 @@
         <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>2546.985477707</v>
+        <v>2546.9854340836</v>
       </c>
       <c r="O217" t="n">
-        <v>122255.302929936</v>
+        <v>122255.3008360128</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
@@ -10074,10 +10074,10 @@
         <v>600</v>
       </c>
       <c r="N218" t="n">
-        <v>1259.2742532126</v>
+        <v>1259.2742585952</v>
       </c>
       <c r="O218" t="n">
-        <v>755564.5519275599</v>
+        <v>755564.5551571201</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -10115,10 +10115,10 @@
         <v>120</v>
       </c>
       <c r="N219" t="n">
-        <v>2842.2738983051</v>
+        <v>2842.2738509317</v>
       </c>
       <c r="O219" t="n">
-        <v>341072.867796612</v>
+        <v>341072.862111804</v>
       </c>
       <c r="P219" t="n">
         <v>4900</v>
@@ -10251,10 +10251,10 @@
         <v>192</v>
       </c>
       <c r="N222" t="n">
-        <v>692.15200959024</v>
+        <v>692.15203442189</v>
       </c>
       <c r="O222" t="n">
-        <v>132893.1858413261</v>
+        <v>132893.1906090029</v>
       </c>
       <c r="P222" t="n">
         <v>1200</v>
@@ -10346,10 +10346,10 @@
         <v>2829</v>
       </c>
       <c r="N224" t="n">
-        <v>1955.2371191444</v>
+        <v>1955.2371159315</v>
       </c>
       <c r="O224" t="n">
-        <v>5531365.810059507</v>
+        <v>5531365.800970213</v>
       </c>
       <c r="P224" t="n">
         <v>3000</v>
@@ -10726,10 +10726,10 @@
         <v>324</v>
       </c>
       <c r="N232" t="n">
-        <v>1530.4499206349</v>
+        <v>1530.4499204455</v>
       </c>
       <c r="O232" t="n">
-        <v>495865.7742857076</v>
+        <v>495865.774224342</v>
       </c>
       <c r="P232" t="n">
         <v>2600</v>
@@ -11097,10 +11097,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>1690.8700087796</v>
+        <v>1690.8700087835</v>
       </c>
       <c r="O240" t="n">
-        <v>1690.8700087796</v>
+        <v>1690.8700087835</v>
       </c>
       <c r="P240" t="n">
         <v>3000</v>
@@ -11435,10 +11435,10 @@
         <v>2856</v>
       </c>
       <c r="N247" t="n">
-        <v>517.28728171896</v>
+        <v>517.28742027978</v>
       </c>
       <c r="O247" t="n">
-        <v>1477372.47658935</v>
+        <v>1477372.872319052</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11674,10 +11674,10 @@
         <v>630</v>
       </c>
       <c r="N252" t="n">
-        <v>3110.8435374771</v>
+        <v>3110.8434146796</v>
       </c>
       <c r="O252" t="n">
-        <v>1959831.428610573</v>
+        <v>1959831.351248148</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11902,10 +11902,10 @@
         <v>14016</v>
       </c>
       <c r="N257" t="n">
-        <v>703.79547499887</v>
+        <v>703.79546441605</v>
       </c>
       <c r="O257" t="n">
-        <v>9864397.377584161</v>
+        <v>9864397.229255356</v>
       </c>
       <c r="P257" t="n">
         <v>900</v>
@@ -11997,10 +11997,10 @@
         <v>172</v>
       </c>
       <c r="N259" t="n">
-        <v>3182.2510752688</v>
+        <v>3182.2510791367</v>
       </c>
       <c r="O259" t="n">
-        <v>547347.1849462336</v>
+        <v>547347.1856115124</v>
       </c>
       <c r="P259" t="n">
         <v>6900</v>
@@ -12325,10 +12325,10 @@
         <v>3</v>
       </c>
       <c r="N266" t="n">
-        <v>7923.7</v>
+        <v>8330.0435897436</v>
       </c>
       <c r="O266" t="n">
-        <v>23771.1</v>
+        <v>24990.1307692308</v>
       </c>
       <c r="P266" t="n">
         <v>16600</v>
@@ -13192,10 +13192,10 @@
         <v>5</v>
       </c>
       <c r="N284" t="n">
-        <v>2832.1945945946</v>
+        <v>2870.9917808219</v>
       </c>
       <c r="O284" t="n">
-        <v>14160.972972973</v>
+        <v>14354.9589041095</v>
       </c>
       <c r="P284" t="n">
         <v>12900</v>
@@ -13621,10 +13621,10 @@
         <v>1</v>
       </c>
       <c r="N293" t="n">
-        <v>3505.3803636364</v>
+        <v>3505.3803703704</v>
       </c>
       <c r="O293" t="n">
-        <v>3505.3803636364</v>
+        <v>3505.3803703704</v>
       </c>
       <c r="P293" t="n">
         <v>12900</v>
@@ -13808,10 +13808,10 @@
         <v>49</v>
       </c>
       <c r="N297" t="n">
-        <v>10348.08</v>
+        <v>10459.349677419</v>
       </c>
       <c r="O297" t="n">
-        <v>507055.92</v>
+        <v>512508.1341935311</v>
       </c>
       <c r="P297" t="n">
         <v>16900</v>
@@ -13857,10 +13857,10 @@
         <v>8</v>
       </c>
       <c r="N298" t="n">
-        <v>9874.620000000001</v>
+        <v>10649.1</v>
       </c>
       <c r="O298" t="n">
-        <v>78996.96000000001</v>
+        <v>85192.8</v>
       </c>
       <c r="P298" t="n">
         <v>14700</v>
@@ -15021,10 +15021,10 @@
         <v>60</v>
       </c>
       <c r="N322" t="n">
-        <v>3067.0905325444</v>
+        <v>3067.0905341246</v>
       </c>
       <c r="O322" t="n">
-        <v>184025.431952664</v>
+        <v>184025.432047476</v>
       </c>
       <c r="P322" t="n">
         <v>7200</v>
@@ -15309,10 +15309,10 @@
         <v>74</v>
       </c>
       <c r="N328" t="n">
-        <v>4190.77</v>
+        <v>4360.6660810811</v>
       </c>
       <c r="O328" t="n">
-        <v>310116.98</v>
+        <v>322689.2900000014</v>
       </c>
       <c r="P328" t="n">
         <v>5900</v>
@@ -15938,10 +15938,10 @@
         <v>48</v>
       </c>
       <c r="N341" t="n">
-        <v>5876.81</v>
+        <v>6053.1143</v>
       </c>
       <c r="O341" t="n">
-        <v>282086.88</v>
+        <v>290549.4864</v>
       </c>
       <c r="P341" t="n">
         <v>22900</v>
@@ -17669,10 +17669,10 @@
         <v>8</v>
       </c>
       <c r="N377" t="n">
-        <v>7046.939830831</v>
+        <v>7046.9398307595</v>
       </c>
       <c r="O377" t="n">
-        <v>56375.518646648</v>
+        <v>56375.518646076</v>
       </c>
       <c r="P377" t="n">
         <v>9900</v>
@@ -17816,10 +17816,10 @@
         <v>8</v>
       </c>
       <c r="N380" t="n">
-        <v>14320.32952381</v>
+        <v>15827.732631579</v>
       </c>
       <c r="O380" t="n">
-        <v>114562.63619048</v>
+        <v>126621.861052632</v>
       </c>
       <c r="P380" t="n">
         <v>19900</v>
@@ -18242,7 +18242,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -18251,19 +18251,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="N389" t="n">
         <v>616.4</v>
       </c>
       <c r="O389" t="n">
-        <v>53010.4</v>
+        <v>40682.4</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
       </c>
       <c r="Q389" t="n">
-        <v>249400</v>
+        <v>191400</v>
       </c>
     </row>
     <row r="390">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>750</v>
+        <v>726</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -18398,19 +18398,19 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>750</v>
+        <v>726</v>
       </c>
       <c r="N392" t="n">
-        <v>465.8709058296</v>
+        <v>465.87091402715</v>
       </c>
       <c r="O392" t="n">
-        <v>349403.1793722</v>
+        <v>338222.2835837109</v>
       </c>
       <c r="P392" t="n">
         <v>2500</v>
       </c>
       <c r="Q392" t="n">
-        <v>1875000</v>
+        <v>1815000</v>
       </c>
     </row>
     <row r="393">
@@ -18725,10 +18725,10 @@
         <v>36</v>
       </c>
       <c r="N399" t="n">
-        <v>22951.705024752</v>
+        <v>23008.657146402</v>
       </c>
       <c r="O399" t="n">
-        <v>826261.380891072</v>
+        <v>828311.657270472</v>
       </c>
       <c r="P399" t="n">
         <v>37900</v>
@@ -19016,10 +19016,10 @@
         <v>63</v>
       </c>
       <c r="N405" t="n">
-        <v>1757.3205078125</v>
+        <v>1757.320513834</v>
       </c>
       <c r="O405" t="n">
-        <v>110711.1919921875</v>
+        <v>110711.192371542</v>
       </c>
       <c r="P405" t="n">
         <v>2000</v>
@@ -19338,10 +19338,10 @@
         <v>51</v>
       </c>
       <c r="N412" t="n">
-        <v>4518.3764814815</v>
+        <v>4518.3764150943</v>
       </c>
       <c r="O412" t="n">
-        <v>230437.2005555565</v>
+        <v>230437.1971698093</v>
       </c>
       <c r="P412" t="n">
         <v>11500</v>
@@ -19660,10 +19660,10 @@
         <v>1827</v>
       </c>
       <c r="N419" t="n">
-        <v>220.00897382472</v>
+        <v>220.00867896778</v>
       </c>
       <c r="O419" t="n">
-        <v>401956.3951777634</v>
+        <v>401955.8564741341</v>
       </c>
       <c r="P419" t="n">
         <v>260</v>
@@ -20478,10 +20478,10 @@
         <v>23</v>
       </c>
       <c r="N437" t="n">
-        <v>415.07</v>
+        <v>449.18534246575</v>
       </c>
       <c r="O437" t="n">
-        <v>9546.610000000001</v>
+        <v>10331.26287671225</v>
       </c>
       <c r="P437" t="n">
         <v>2900</v>
@@ -22418,7 +22418,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -22427,19 +22427,19 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N479" t="n">
         <v>753.98</v>
       </c>
       <c r="O479" t="n">
-        <v>60318.4</v>
+        <v>37699</v>
       </c>
       <c r="P479" t="n">
         <v>4000</v>
       </c>
       <c r="Q479" t="n">
-        <v>320000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="480">
@@ -22660,10 +22660,10 @@
         <v>20</v>
       </c>
       <c r="N484" t="n">
-        <v>7046.7404347826</v>
+        <v>7046.7409090909</v>
       </c>
       <c r="O484" t="n">
-        <v>140934.808695652</v>
+        <v>140934.818181818</v>
       </c>
       <c r="P484" t="n">
         <v>22900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -675,10 +675,10 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O7" t="n">
-        <v>326711.297071128</v>
+        <v>324000</v>
       </c>
       <c r="P7" t="n">
         <v>30000</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="O18" t="n">
-        <v>4843.0352941176</v>
+        <v>4826.0023529412</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -1162,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2487.0572046589</v>
+        <v>2474.7042429285</v>
       </c>
       <c r="O19" t="n">
-        <v>9948.2288186356</v>
+        <v>9898.816971714001</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
@@ -1357,10 +1357,10 @@
         <v>56</v>
       </c>
       <c r="N24" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O24" t="n">
-        <v>1204601.051950184</v>
+        <v>1194686.64</v>
       </c>
       <c r="P24" t="n">
         <v>30000</v>
@@ -2321,10 +2321,10 @@
         <v>23</v>
       </c>
       <c r="N46" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O46" t="n">
-        <v>626353.4482758701</v>
+        <v>621000</v>
       </c>
       <c r="P46" t="n">
         <v>20000</v>
@@ -2726,10 +2726,10 @@
         <v>10</v>
       </c>
       <c r="N55" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O55" t="n">
-        <v>25769.026455026</v>
+        <v>25633.4</v>
       </c>
       <c r="P55" t="n">
         <v>4700</v>
@@ -2814,10 +2814,10 @@
         <v>12</v>
       </c>
       <c r="N57" t="n">
-        <v>11705.0765</v>
+        <v>11513.19</v>
       </c>
       <c r="O57" t="n">
-        <v>140460.918</v>
+        <v>138158.28</v>
       </c>
       <c r="P57" t="n">
         <v>17900</v>
@@ -7009,10 +7009,10 @@
         <v>16</v>
       </c>
       <c r="N151" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O151" t="n">
-        <v>435631.555555552</v>
+        <v>429664</v>
       </c>
       <c r="P151" t="n">
         <v>43900</v>
@@ -7810,10 +7810,10 @@
         <v>35</v>
       </c>
       <c r="N169" t="n">
-        <v>9099.032608695699</v>
+        <v>8878.450000000001</v>
       </c>
       <c r="O169" t="n">
-        <v>318466.1413043495</v>
+        <v>310745.75</v>
       </c>
       <c r="P169" t="n">
         <v>14100</v>
@@ -7856,10 +7856,10 @@
         <v>61</v>
       </c>
       <c r="N170" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O170" t="n">
-        <v>152422.0929450528</v>
+        <v>152254.78</v>
       </c>
       <c r="P170" t="n">
         <v>4100</v>
@@ -8086,10 +8086,10 @@
         <v>97</v>
       </c>
       <c r="N175" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O175" t="n">
-        <v>385082.9386881191</v>
+        <v>384606.94</v>
       </c>
       <c r="P175" t="n">
         <v>6500</v>
@@ -8224,10 +8224,10 @@
         <v>158</v>
       </c>
       <c r="N178" t="n">
-        <v>1817.3525065963</v>
+        <v>1812.57</v>
       </c>
       <c r="O178" t="n">
-        <v>287141.6960422154</v>
+        <v>286386.06</v>
       </c>
       <c r="P178" t="n">
         <v>2900</v>
@@ -8788,10 +8788,10 @@
         <v>153</v>
       </c>
       <c r="N190" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O190" t="n">
-        <v>2078575.384615398</v>
+        <v>2075445</v>
       </c>
       <c r="P190" t="n">
         <v>22500</v>
@@ -9248,10 +9248,10 @@
         <v>85</v>
       </c>
       <c r="N200" t="n">
-        <v>10816.221634615</v>
+        <v>10713.21</v>
       </c>
       <c r="O200" t="n">
-        <v>919378.838942275</v>
+        <v>910622.85</v>
       </c>
       <c r="P200" t="n">
         <v>20900</v>
@@ -12325,10 +12325,10 @@
         <v>3</v>
       </c>
       <c r="N266" t="n">
-        <v>8330.0435897436</v>
+        <v>7923.7</v>
       </c>
       <c r="O266" t="n">
-        <v>24990.1307692308</v>
+        <v>23771.1</v>
       </c>
       <c r="P266" t="n">
         <v>16600</v>
@@ -13192,10 +13192,10 @@
         <v>5</v>
       </c>
       <c r="N284" t="n">
-        <v>2870.9917808219</v>
+        <v>2832.1946575342</v>
       </c>
       <c r="O284" t="n">
-        <v>14354.9589041095</v>
+        <v>14160.973287671</v>
       </c>
       <c r="P284" t="n">
         <v>12900</v>
@@ -13808,10 +13808,10 @@
         <v>49</v>
       </c>
       <c r="N297" t="n">
-        <v>10459.349677419</v>
+        <v>10348.08</v>
       </c>
       <c r="O297" t="n">
-        <v>512508.1341935311</v>
+        <v>507055.92</v>
       </c>
       <c r="P297" t="n">
         <v>16900</v>
@@ -13857,10 +13857,10 @@
         <v>8</v>
       </c>
       <c r="N298" t="n">
-        <v>10649.1</v>
+        <v>9874.620000000001</v>
       </c>
       <c r="O298" t="n">
-        <v>85192.8</v>
+        <v>78996.96000000001</v>
       </c>
       <c r="P298" t="n">
         <v>14700</v>
@@ -15309,10 +15309,10 @@
         <v>74</v>
       </c>
       <c r="N328" t="n">
-        <v>4360.6660810811</v>
+        <v>4190.77</v>
       </c>
       <c r="O328" t="n">
-        <v>322689.2900000014</v>
+        <v>310116.98</v>
       </c>
       <c r="P328" t="n">
         <v>5900</v>
@@ -15938,10 +15938,10 @@
         <v>48</v>
       </c>
       <c r="N341" t="n">
-        <v>6053.1143</v>
+        <v>5876.81</v>
       </c>
       <c r="O341" t="n">
-        <v>290549.4864</v>
+        <v>282086.88</v>
       </c>
       <c r="P341" t="n">
         <v>22900</v>
@@ -17816,10 +17816,10 @@
         <v>8</v>
       </c>
       <c r="N380" t="n">
-        <v>15827.732631579</v>
+        <v>14320.330526316</v>
       </c>
       <c r="O380" t="n">
-        <v>126621.861052632</v>
+        <v>114562.644210528</v>
       </c>
       <c r="P380" t="n">
         <v>19900</v>
@@ -18725,10 +18725,10 @@
         <v>36</v>
       </c>
       <c r="N399" t="n">
-        <v>23008.657146402</v>
+        <v>22951.705012407</v>
       </c>
       <c r="O399" t="n">
-        <v>828311.657270472</v>
+        <v>826261.3804466521</v>
       </c>
       <c r="P399" t="n">
         <v>37900</v>
@@ -20478,10 +20478,10 @@
         <v>23</v>
       </c>
       <c r="N437" t="n">
-        <v>449.18534246575</v>
+        <v>415.07</v>
       </c>
       <c r="O437" t="n">
-        <v>10331.26287671225</v>
+        <v>9546.610000000001</v>
       </c>
       <c r="P437" t="n">
         <v>2900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O6" t="n">
-        <v>653758.6632124321</v>
+        <v>652069.367875656</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -2726,10 +2726,10 @@
         <v>10</v>
       </c>
       <c r="N55" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O55" t="n">
-        <v>25977.011260054</v>
+        <v>25633.4</v>
       </c>
       <c r="P55" t="n">
         <v>4700</v>
@@ -3260,10 +3260,10 @@
         <v>164</v>
       </c>
       <c r="N67" t="n">
-        <v>3489.6196317829</v>
+        <v>3456.13</v>
       </c>
       <c r="O67" t="n">
-        <v>572297.6196123955</v>
+        <v>566805.3200000001</v>
       </c>
       <c r="P67" t="n">
         <v>5700</v>
@@ -3624,10 +3624,10 @@
         <v>1080</v>
       </c>
       <c r="N75" t="n">
-        <v>2588.3559055118</v>
+        <v>2582.2560787402</v>
       </c>
       <c r="O75" t="n">
-        <v>2795424.377952744</v>
+        <v>2788836.565039416</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3995,10 +3995,10 @@
         <v>150</v>
       </c>
       <c r="N83" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O83" t="n">
-        <v>1130794.110957</v>
+        <v>1126108.5</v>
       </c>
       <c r="P83" t="n">
         <v>13500</v>
@@ -4093,10 +4093,10 @@
         <v>20</v>
       </c>
       <c r="N85" t="n">
-        <v>8907.908396946599</v>
+        <v>8796</v>
       </c>
       <c r="O85" t="n">
-        <v>178158.167938932</v>
+        <v>175920</v>
       </c>
       <c r="P85" t="n">
         <v>14900</v>
@@ -4857,10 +4857,10 @@
         <v>152</v>
       </c>
       <c r="N102" t="n">
-        <v>3660.708</v>
+        <v>3655.96</v>
       </c>
       <c r="O102" t="n">
-        <v>556427.616</v>
+        <v>555705.92</v>
       </c>
       <c r="P102" t="n">
         <v>5500</v>
@@ -6381,10 +6381,10 @@
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O136" t="n">
-        <v>4071.5602909796</v>
+        <v>4059.7472744908</v>
       </c>
       <c r="P136" t="n">
         <v>3600</v>
@@ -6755,10 +6755,10 @@
         <v>4</v>
       </c>
       <c r="N145" t="n">
-        <v>11652.839895288</v>
+        <v>11562.038534031</v>
       </c>
       <c r="O145" t="n">
-        <v>46611.359581152</v>
+        <v>46248.154136124</v>
       </c>
       <c r="P145" t="n">
         <v>18500</v>
@@ -7856,10 +7856,10 @@
         <v>2</v>
       </c>
       <c r="N170" t="n">
-        <v>4265.5329508197</v>
+        <v>4163.1601639344</v>
       </c>
       <c r="O170" t="n">
-        <v>8531.0659016394</v>
+        <v>8326.3203278688</v>
       </c>
       <c r="P170" t="n">
         <v>6700</v>
@@ -9478,10 +9478,10 @@
         <v>144</v>
       </c>
       <c r="N205" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O205" t="n">
-        <v>258726.6696564144</v>
+        <v>255037.144882464</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>
@@ -9524,10 +9524,10 @@
         <v>240</v>
       </c>
       <c r="N206" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O206" t="n">
-        <v>502930.868393784</v>
+        <v>499052.213471496</v>
       </c>
       <c r="P206" t="n">
         <v>2900</v>
@@ -9570,10 +9570,10 @@
         <v>266</v>
       </c>
       <c r="N207" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O207" t="n">
-        <v>486372.8189352816</v>
+        <v>479601.9860882306</v>
       </c>
       <c r="P207" t="n">
         <v>2500</v>
@@ -9662,10 +9662,10 @@
         <v>264</v>
       </c>
       <c r="N209" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O209" t="n">
-        <v>564295.2575278127</v>
+        <v>560251.3269654048</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9800,10 +9800,10 @@
         <v>216</v>
       </c>
       <c r="N212" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O212" t="n">
-        <v>707616.1894904713</v>
+        <v>696506.6730704472</v>
       </c>
       <c r="P212" t="n">
         <v>4500</v>
@@ -9936,10 +9936,10 @@
         <v>44</v>
       </c>
       <c r="N215" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O215" t="n">
-        <v>238241.3715</v>
+        <v>235300.12</v>
       </c>
       <c r="P215" t="n">
         <v>9500</v>
@@ -11241,10 +11241,10 @@
         <v>-2</v>
       </c>
       <c r="N243" t="n">
-        <v>2483.1635416667</v>
+        <v>2270.3210416667</v>
       </c>
       <c r="O243" t="n">
-        <v>-4966.3270833334</v>
+        <v>-4540.6420833334</v>
       </c>
       <c r="P243" t="n">
         <v>3900</v>
@@ -11948,10 +11948,10 @@
         <v>13440</v>
       </c>
       <c r="N258" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O258" t="n">
-        <v>9464151.711304283</v>
+        <v>9459010.911304416</v>
       </c>
       <c r="P258" t="n">
         <v>900</v>
@@ -12043,10 +12043,10 @@
         <v>172</v>
       </c>
       <c r="N260" t="n">
-        <v>3216.9665454545</v>
+        <v>3182.2510909091</v>
       </c>
       <c r="O260" t="n">
-        <v>553318.245818174</v>
+        <v>547347.1876363652</v>
       </c>
       <c r="P260" t="n">
         <v>6900</v>
@@ -17277,10 +17277,10 @@
         <v>496</v>
       </c>
       <c r="N369" t="n">
-        <v>713.93197013211</v>
+        <v>711.48</v>
       </c>
       <c r="O369" t="n">
-        <v>354110.2571855265</v>
+        <v>352894.08</v>
       </c>
       <c r="P369" t="n">
         <v>2500</v>
@@ -18814,10 +18814,10 @@
         <v>159</v>
       </c>
       <c r="N401" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O401" t="n">
-        <v>112432.3709412655</v>
+        <v>112178.9539156622</v>
       </c>
       <c r="P401" t="n">
         <v>1500</v>
@@ -20838,10 +20838,10 @@
         <v>58</v>
       </c>
       <c r="N445" t="n">
-        <v>614.59626373626</v>
+        <v>576.58</v>
       </c>
       <c r="O445" t="n">
-        <v>35646.58329670308</v>
+        <v>33441.64</v>
       </c>
       <c r="P445" t="n">
         <v>5900</v>
@@ -21737,10 +21737,10 @@
         <v>235</v>
       </c>
       <c r="N464" t="n">
-        <v>229.9076771366</v>
+        <v>227.41596785975</v>
       </c>
       <c r="O464" t="n">
-        <v>54028.304127101</v>
+        <v>53442.75244704125</v>
       </c>
       <c r="P464" t="n">
         <v>1200</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3037996546</v>
+        <v>1811.3039621792</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.367875656</v>
+        <v>652069.426384512</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -756,10 +756,10 @@
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>7588.3739393939</v>
+        <v>7588.3731034483</v>
       </c>
       <c r="O9" t="n">
-        <v>45530.2436363634</v>
+        <v>45530.2386206898</v>
       </c>
       <c r="P9" t="n">
         <v>14900</v>
@@ -1084,10 +1084,10 @@
         <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O17" t="n">
-        <v>90317.2540501795</v>
+        <v>90317.25398257331</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2413.0011764706</v>
+        <v>2413.0010330579</v>
       </c>
       <c r="O18" t="n">
-        <v>4826.0023529412</v>
+        <v>4826.0020661158</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -2505,10 +2505,10 @@
         <v>175</v>
       </c>
       <c r="N50" t="n">
-        <v>28.165681818182</v>
+        <v>28.165642201835</v>
       </c>
       <c r="O50" t="n">
-        <v>4928.99431818185</v>
+        <v>4928.987385321125</v>
       </c>
       <c r="P50" t="n">
         <v>6800</v>
@@ -3088,10 +3088,10 @@
         <v>92</v>
       </c>
       <c r="N63" t="n">
-        <v>732.63410958904</v>
+        <v>732.63413793103</v>
       </c>
       <c r="O63" t="n">
-        <v>67402.33808219168</v>
+        <v>67402.34068965475</v>
       </c>
       <c r="P63" t="n">
         <v>6200</v>
@@ -3178,10 +3178,10 @@
         <v>33</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101595359</v>
+        <v>4937.3101601164</v>
       </c>
       <c r="O65" t="n">
-        <v>162931.2352646847</v>
+        <v>162931.2352838412</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3350,10 +3350,10 @@
         <v>432</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0527732407</v>
+        <v>1098.0529624405</v>
       </c>
       <c r="O69" t="n">
-        <v>474358.7980399824</v>
+        <v>474358.879774296</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3618,22 +3618,22 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M75" t="n">
-        <v>1080</v>
+        <v>1044</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2560787402</v>
+        <v>2582.2560663507</v>
       </c>
       <c r="O75" t="n">
-        <v>2788836.565039416</v>
+        <v>2695875.333270131</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
       </c>
       <c r="Q75" t="n">
-        <v>4860000</v>
+        <v>4698000</v>
       </c>
     </row>
     <row r="76">
@@ -3716,10 +3716,10 @@
         <v>120</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.5763768116</v>
+        <v>2033.5756109726</v>
       </c>
       <c r="O77" t="n">
-        <v>244029.165217392</v>
+        <v>244029.073316712</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
@@ -3756,22 +3756,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M78" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N78" t="n">
         <v>5503.85</v>
       </c>
       <c r="O78" t="n">
-        <v>165115.5</v>
+        <v>99069.3</v>
       </c>
       <c r="P78" t="n">
         <v>9500</v>
       </c>
       <c r="Q78" t="n">
-        <v>285000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="79">
@@ -4280,10 +4280,10 @@
         <v>332</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.2542480527</v>
+        <v>3594.2542307692</v>
       </c>
       <c r="O89" t="n">
-        <v>1193292.410353496</v>
+        <v>1193292.404615375</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4637,10 +4637,10 @@
         <v>317</v>
       </c>
       <c r="N97" t="n">
-        <v>4372.2107862617</v>
+        <v>4372.2107863175</v>
       </c>
       <c r="O97" t="n">
-        <v>1385990.819244959</v>
+        <v>1385990.819262647</v>
       </c>
       <c r="P97" t="n">
         <v>7500</v>
@@ -4770,10 +4770,10 @@
         <v>280</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.5677691978</v>
+        <v>1592.5677332171</v>
       </c>
       <c r="O100" t="n">
-        <v>445918.975375384</v>
+        <v>445918.9653007881</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
@@ -5409,10 +5409,10 @@
         <v>748</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9229788882</v>
+        <v>1630.9230192383</v>
       </c>
       <c r="O114" t="n">
-        <v>1219930.388208374</v>
+        <v>1219930.418390248</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>231</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.1929105882</v>
+        <v>1550.19293615</v>
       </c>
       <c r="O115" t="n">
-        <v>358094.5623458742</v>
+        <v>358094.56825065</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
@@ -5501,10 +5501,10 @@
         <v>168</v>
       </c>
       <c r="N116" t="n">
-        <v>1579.3913493976</v>
+        <v>1579.3910696517</v>
       </c>
       <c r="O116" t="n">
-        <v>265337.7466987968</v>
+        <v>265337.6997014856</v>
       </c>
       <c r="P116" t="n">
         <v>2900</v>
@@ -5547,10 +5547,10 @@
         <v>271</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5099727039</v>
+        <v>2403.5100306848</v>
       </c>
       <c r="O117" t="n">
-        <v>651351.2026027569</v>
+        <v>651351.2183155807</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5483026316</v>
+        <v>2521.5479047619</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.7049473696</v>
+        <v>141206.6826666664</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -5683,10 +5683,10 @@
         <v>50</v>
       </c>
       <c r="N120" t="n">
-        <v>1830.7565306122</v>
+        <v>1830.7564583333</v>
       </c>
       <c r="O120" t="n">
-        <v>91537.82653061001</v>
+        <v>91537.822916665</v>
       </c>
       <c r="P120" t="n">
         <v>3150</v>
@@ -6463,10 +6463,10 @@
         <v>141</v>
       </c>
       <c r="N138" t="n">
-        <v>2680.739700489</v>
+        <v>2680.7396999388</v>
       </c>
       <c r="O138" t="n">
-        <v>377984.297768949</v>
+        <v>377984.2976913708</v>
       </c>
       <c r="P138" t="n">
         <v>4900</v>
@@ -6504,10 +6504,10 @@
         <v>402</v>
       </c>
       <c r="N139" t="n">
-        <v>880.32923254206</v>
+        <v>880.32929682061</v>
       </c>
       <c r="O139" t="n">
-        <v>353892.3514819081</v>
+        <v>353892.3773218852</v>
       </c>
       <c r="P139" t="n">
         <v>1200</v>
@@ -7270,10 +7270,10 @@
         <v>5</v>
       </c>
       <c r="N157" t="n">
-        <v>7969.9501643017</v>
+        <v>7969.950164794</v>
       </c>
       <c r="O157" t="n">
-        <v>39849.7508215085</v>
+        <v>39849.75082397</v>
       </c>
       <c r="P157" t="n">
         <v>12900</v>
@@ -7574,22 +7574,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M164" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="N164" t="n">
         <v>2634.61</v>
       </c>
       <c r="O164" t="n">
-        <v>305614.76</v>
+        <v>226576.46</v>
       </c>
       <c r="P164" t="n">
         <v>4200</v>
       </c>
       <c r="Q164" t="n">
-        <v>487200</v>
+        <v>361200</v>
       </c>
     </row>
     <row r="165">
@@ -7666,22 +7666,22 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M166" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="N166" t="n">
         <v>4690.64</v>
       </c>
       <c r="O166" t="n">
-        <v>136028.56</v>
+        <v>42215.76</v>
       </c>
       <c r="P166" t="n">
         <v>7500</v>
       </c>
       <c r="Q166" t="n">
-        <v>217500</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="167">
@@ -7712,22 +7712,22 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M167" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N167" t="n">
         <v>5410.72</v>
       </c>
       <c r="O167" t="n">
-        <v>270536</v>
+        <v>162321.6</v>
       </c>
       <c r="P167" t="n">
         <v>8700</v>
       </c>
       <c r="Q167" t="n">
-        <v>435000</v>
+        <v>261000</v>
       </c>
     </row>
     <row r="168">
@@ -7758,22 +7758,22 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M168" t="n">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N168" t="n">
         <v>10911.29</v>
       </c>
       <c r="O168" t="n">
-        <v>2411395.09</v>
+        <v>2345927.35</v>
       </c>
       <c r="P168" t="n">
         <v>17400</v>
       </c>
       <c r="Q168" t="n">
-        <v>3845400</v>
+        <v>3741000</v>
       </c>
     </row>
     <row r="169">
@@ -7856,10 +7856,10 @@
         <v>2</v>
       </c>
       <c r="N170" t="n">
-        <v>4163.1601639344</v>
+        <v>4163.1601724138</v>
       </c>
       <c r="O170" t="n">
-        <v>8326.3203278688</v>
+        <v>8326.3203448276</v>
       </c>
       <c r="P170" t="n">
         <v>6700</v>
@@ -8034,22 +8034,22 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M174" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N174" t="n">
-        <v>5218.1704756757</v>
+        <v>5218.1704867257</v>
       </c>
       <c r="O174" t="n">
-        <v>808816.4237297334</v>
+        <v>793161.9139823065</v>
       </c>
       <c r="P174" t="n">
         <v>8500</v>
       </c>
       <c r="Q174" t="n">
-        <v>1317500</v>
+        <v>1292000</v>
       </c>
     </row>
     <row r="175">
@@ -8086,10 +8086,10 @@
         <v>112</v>
       </c>
       <c r="N175" t="n">
-        <v>1595.0095090439</v>
+        <v>1595.0094973545</v>
       </c>
       <c r="O175" t="n">
-        <v>178641.0650129168</v>
+        <v>178641.063703704</v>
       </c>
       <c r="P175" t="n">
         <v>2600</v>
@@ -9386,10 +9386,10 @@
         <v>552</v>
       </c>
       <c r="N203" t="n">
-        <v>1516.0388166875</v>
+        <v>1516.0388137227</v>
       </c>
       <c r="O203" t="n">
-        <v>836853.4268115</v>
+        <v>836853.4251749305</v>
       </c>
       <c r="P203" t="n">
         <v>2300</v>
@@ -9432,10 +9432,10 @@
         <v>432</v>
       </c>
       <c r="N204" t="n">
-        <v>2458.5134637046</v>
+        <v>2458.5134514107</v>
       </c>
       <c r="O204" t="n">
-        <v>1062077.816320387</v>
+        <v>1062077.811009422</v>
       </c>
       <c r="P204" t="n">
         <v>3500</v>
@@ -9570,10 +9570,10 @@
         <v>266</v>
       </c>
       <c r="N207" t="n">
-        <v>1803.0149852941</v>
+        <v>1803.0149867608</v>
       </c>
       <c r="O207" t="n">
-        <v>479601.9860882306</v>
+        <v>479601.9864783728</v>
       </c>
       <c r="P207" t="n">
         <v>2500</v>
@@ -9708,10 +9708,10 @@
         <v>144</v>
       </c>
       <c r="N210" t="n">
-        <v>2108.7897270195</v>
+        <v>2108.7897651007</v>
       </c>
       <c r="O210" t="n">
-        <v>303665.720690808</v>
+        <v>303665.7261745008</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>288</v>
       </c>
       <c r="N211" t="n">
-        <v>2056.0839525344</v>
+        <v>2056.0838952972</v>
       </c>
       <c r="O211" t="n">
-        <v>592152.1783299071</v>
+        <v>592152.1618455936</v>
       </c>
       <c r="P211" t="n">
         <v>2900</v>
@@ -9800,10 +9800,10 @@
         <v>216</v>
       </c>
       <c r="N212" t="n">
-        <v>3224.5679308817</v>
+        <v>3224.5679626335</v>
       </c>
       <c r="O212" t="n">
-        <v>696506.6730704472</v>
+        <v>696506.6799288359</v>
       </c>
       <c r="P212" t="n">
         <v>4500</v>
@@ -9846,10 +9846,10 @@
         <v>288</v>
       </c>
       <c r="N213" t="n">
-        <v>1655.9314259144</v>
+        <v>1655.93135625</v>
       </c>
       <c r="O213" t="n">
-        <v>476908.2506633472</v>
+        <v>476908.2306</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9892,10 +9892,10 @@
         <v>289</v>
       </c>
       <c r="N214" t="n">
-        <v>1592.2745718734</v>
+        <v>1592.2746762208</v>
       </c>
       <c r="O214" t="n">
-        <v>460167.3512714126</v>
+        <v>460167.3814278112</v>
       </c>
       <c r="P214" t="n">
         <v>2500</v>
@@ -9982,10 +9982,10 @@
         <v>84</v>
       </c>
       <c r="N216" t="n">
-        <v>2311.9273755656</v>
+        <v>2311.9269828927</v>
       </c>
       <c r="O216" t="n">
-        <v>194201.8995475104</v>
+        <v>194201.8665629868</v>
       </c>
       <c r="P216" t="n">
         <v>3500</v>
@@ -10028,10 +10028,10 @@
         <v>12</v>
       </c>
       <c r="N217" t="n">
-        <v>1906.1870703125</v>
+        <v>1906.1869325153</v>
       </c>
       <c r="O217" t="n">
-        <v>22874.24484375</v>
+        <v>22874.2431901836</v>
       </c>
       <c r="P217" t="n">
         <v>2900</v>
@@ -10074,10 +10074,10 @@
         <v>48</v>
       </c>
       <c r="N218" t="n">
-        <v>2546.9853442623</v>
+        <v>2546.9852428811</v>
       </c>
       <c r="O218" t="n">
-        <v>122255.2965245904</v>
+        <v>122255.2916582928</v>
       </c>
       <c r="P218" t="n">
         <v>3900</v>
@@ -10120,10 +10120,10 @@
         <v>600</v>
       </c>
       <c r="N219" t="n">
-        <v>1259.274396777</v>
+        <v>1259.2744102228</v>
       </c>
       <c r="O219" t="n">
-        <v>755564.6380662</v>
+        <v>755564.64613368</v>
       </c>
       <c r="P219" t="n">
         <v>1900</v>
@@ -10161,10 +10161,10 @@
         <v>120</v>
       </c>
       <c r="N220" t="n">
-        <v>2842.2738221529</v>
+        <v>2842.2737931034</v>
       </c>
       <c r="O220" t="n">
-        <v>341072.858658348</v>
+        <v>341072.855172408</v>
       </c>
       <c r="P220" t="n">
         <v>4900</v>
@@ -10297,10 +10297,10 @@
         <v>192</v>
       </c>
       <c r="N223" t="n">
-        <v>692.1520380194499</v>
+        <v>692.15204525288</v>
       </c>
       <c r="O223" t="n">
-        <v>132893.1912997344</v>
+        <v>132893.192688553</v>
       </c>
       <c r="P223" t="n">
         <v>1200</v>
@@ -11241,10 +11241,10 @@
         <v>-2</v>
       </c>
       <c r="N243" t="n">
-        <v>2270.3210416667</v>
+        <v>2270.3210752688</v>
       </c>
       <c r="O243" t="n">
-        <v>-4540.6420833334</v>
+        <v>-4540.6421505376</v>
       </c>
       <c r="P243" t="n">
         <v>3900</v>
@@ -11481,10 +11481,10 @@
         <v>2280</v>
       </c>
       <c r="N248" t="n">
-        <v>517.28747614462</v>
+        <v>517.28760395334</v>
       </c>
       <c r="O248" t="n">
-        <v>1179415.445609733</v>
+        <v>1179415.737013615</v>
       </c>
       <c r="P248" t="n">
         <v>900</v>
@@ -11720,10 +11720,10 @@
         <v>504</v>
       </c>
       <c r="N253" t="n">
-        <v>3110.8433414956</v>
+        <v>3110.843282022</v>
       </c>
       <c r="O253" t="n">
-        <v>1567865.044113782</v>
+        <v>1567865.014139088</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -11948,10 +11948,10 @@
         <v>13440</v>
       </c>
       <c r="N258" t="n">
-        <v>703.79545471015</v>
+        <v>703.79543678174</v>
       </c>
       <c r="O258" t="n">
-        <v>9459010.911304416</v>
+        <v>9459010.670346586</v>
       </c>
       <c r="P258" t="n">
         <v>900</v>
@@ -12227,10 +12227,10 @@
         <v>59</v>
       </c>
       <c r="N264" t="n">
-        <v>2501.3854811715</v>
+        <v>2501.3854621849</v>
       </c>
       <c r="O264" t="n">
-        <v>147581.7433891185</v>
+        <v>147581.7422689091</v>
       </c>
       <c r="P264" t="n">
         <v>4100</v>
@@ -14099,10 +14099,10 @@
         <v>5</v>
       </c>
       <c r="N303" t="n">
-        <v>12448.353125</v>
+        <v>12448.353225806</v>
       </c>
       <c r="O303" t="n">
-        <v>62241.765625</v>
+        <v>62241.76612903</v>
       </c>
       <c r="P303" t="n">
         <v>22900</v>
@@ -15647,10 +15647,10 @@
         <v>1000</v>
       </c>
       <c r="N335" t="n">
-        <v>1783.7988878843</v>
+        <v>1783.7988868778</v>
       </c>
       <c r="O335" t="n">
-        <v>1783798.8878843</v>
+        <v>1783798.8868778</v>
       </c>
       <c r="P335" t="n">
         <v>1500</v>
@@ -17620,10 +17620,10 @@
         <v>8</v>
       </c>
       <c r="N376" t="n">
-        <v>7046.9398305803</v>
+        <v>7046.9398302567</v>
       </c>
       <c r="O376" t="n">
-        <v>56375.5186446424</v>
+        <v>56375.5186420536</v>
       </c>
       <c r="P376" t="n">
         <v>9900</v>
@@ -18058,10 +18058,10 @@
         <v>11</v>
       </c>
       <c r="N385" t="n">
-        <v>366.39981132075</v>
+        <v>366.39980582524</v>
       </c>
       <c r="O385" t="n">
-        <v>4030.39792452825</v>
+        <v>4030.39786407764</v>
       </c>
       <c r="P385" t="n">
         <v>2900</v>
@@ -18352,10 +18352,10 @@
         <v>726</v>
       </c>
       <c r="N391" t="n">
-        <v>465.87091651543</v>
+        <v>465.87093087558</v>
       </c>
       <c r="O391" t="n">
-        <v>338222.2853902022</v>
+        <v>338222.295815671</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -18529,22 +18529,22 @@
         <v>0</v>
       </c>
       <c r="L395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N395" t="n">
         <v>1297.52</v>
       </c>
       <c r="O395" t="n">
-        <v>168677.6</v>
+        <v>167380.08</v>
       </c>
       <c r="P395" t="n">
         <v>1800</v>
       </c>
       <c r="Q395" t="n">
-        <v>234000</v>
+        <v>232200</v>
       </c>
     </row>
     <row r="396">
@@ -18676,10 +18676,10 @@
         <v>36</v>
       </c>
       <c r="N398" t="n">
-        <v>22951.705012407</v>
+        <v>22951.704981273</v>
       </c>
       <c r="O398" t="n">
-        <v>826261.3804466521</v>
+        <v>826261.379325828</v>
       </c>
       <c r="P398" t="n">
         <v>37900</v>
@@ -18865,10 +18865,10 @@
         <v>42</v>
       </c>
       <c r="N402" t="n">
-        <v>1547.8822666667</v>
+        <v>1547.8823611111</v>
       </c>
       <c r="O402" t="n">
-        <v>65011.0552000014</v>
+        <v>65011.0591666662</v>
       </c>
       <c r="P402" t="n">
         <v>5500</v>
@@ -18967,10 +18967,10 @@
         <v>63</v>
       </c>
       <c r="N404" t="n">
-        <v>1757.320515873</v>
+        <v>1757.3205179283</v>
       </c>
       <c r="O404" t="n">
-        <v>110711.192499999</v>
+        <v>110711.1926294829</v>
       </c>
       <c r="P404" t="n">
         <v>2000</v>
@@ -22657,10 +22657,10 @@
         <v>21</v>
       </c>
       <c r="N484" t="n">
-        <v>10009.170833333</v>
+        <v>10009.170869565</v>
       </c>
       <c r="O484" t="n">
-        <v>210192.587499993</v>
+        <v>210192.588260865</v>
       </c>
       <c r="P484" t="n">
         <v>22900</v>
@@ -23025,10 +23025,10 @@
         <v>32</v>
       </c>
       <c r="N492" t="n">
-        <v>4158.2963157895</v>
+        <v>4158.2962162162</v>
       </c>
       <c r="O492" t="n">
-        <v>133065.482105264</v>
+        <v>133065.4789189184</v>
       </c>
       <c r="P492" t="n">
         <v>13800</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -3612,13 +3612,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>1080</v>
+        <v>1044</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>1044</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>18</v>
@@ -7568,13 +7568,13 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>86</v>
@@ -7660,13 +7660,13 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
         <v>9</v>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>30</v>
@@ -7752,13 +7752,13 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
         <v>215</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
         <v>152</v>
@@ -18523,13 +18523,13 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
       </c>
       <c r="L395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M395" t="n">
         <v>129</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3039621792</v>
+        <v>1811.3040256176</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.426384512</v>
+        <v>652069.4492223361</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1162,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2474.7042429285</v>
+        <v>2474.7042140468</v>
       </c>
       <c r="O19" t="n">
-        <v>9898.816971714001</v>
+        <v>9898.816856187201</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
@@ -3350,10 +3350,10 @@
         <v>432</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0529624405</v>
+        <v>1098.053336357</v>
       </c>
       <c r="O69" t="n">
-        <v>474358.879774296</v>
+        <v>474359.041306224</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3618,22 +3618,22 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M75" t="n">
-        <v>1044</v>
+        <v>1008</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2560663507</v>
+        <v>2582.256064019</v>
       </c>
       <c r="O75" t="n">
-        <v>2695875.333270131</v>
+        <v>2602914.112531152</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
       </c>
       <c r="Q75" t="n">
-        <v>4698000</v>
+        <v>4536000</v>
       </c>
     </row>
     <row r="76">
@@ -3710,22 +3710,22 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M77" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.5756109726</v>
+        <v>2033.574464752</v>
       </c>
       <c r="O77" t="n">
-        <v>244029.073316712</v>
+        <v>97611.57430809599</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
       </c>
       <c r="Q77" t="n">
-        <v>492000</v>
+        <v>196800</v>
       </c>
     </row>
     <row r="78">
@@ -3949,10 +3949,10 @@
         <v>514</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.8235120643</v>
+        <v>2694.8234975369</v>
       </c>
       <c r="O82" t="n">
-        <v>1385139.28520105</v>
+        <v>1385139.277733967</v>
       </c>
       <c r="P82" t="n">
         <v>4900</v>
@@ -4320,22 +4320,22 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378867925</v>
+        <v>14822.378867257</v>
       </c>
       <c r="O90" t="n">
-        <v>4268845.1139624</v>
+        <v>4179910.840566474</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
       </c>
       <c r="Q90" t="n">
-        <v>7171200</v>
+        <v>7021800</v>
       </c>
     </row>
     <row r="91">
@@ -4770,10 +4770,10 @@
         <v>280</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.5677332171</v>
+        <v>1592.567707231</v>
       </c>
       <c r="O100" t="n">
-        <v>445918.9653007881</v>
+        <v>445918.95802468</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
@@ -5409,10 +5409,10 @@
         <v>748</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9230192383</v>
+        <v>1630.9230407276</v>
       </c>
       <c r="O114" t="n">
-        <v>1219930.418390248</v>
+        <v>1219930.434464245</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>231</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.19293615</v>
+        <v>1550.1929579149</v>
       </c>
       <c r="O115" t="n">
-        <v>358094.56825065</v>
+        <v>358094.5732783419</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
@@ -5547,10 +5547,10 @@
         <v>271</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5100306848</v>
+        <v>2403.5100778841</v>
       </c>
       <c r="O117" t="n">
-        <v>651351.2183155807</v>
+        <v>651351.2311065912</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5479047619</v>
+        <v>2521.5475490196</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.6826666664</v>
+        <v>141206.6627450976</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -6381,10 +6381,10 @@
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>2029.8736372454</v>
+        <v>2029.8736443149</v>
       </c>
       <c r="O136" t="n">
-        <v>4059.7472744908</v>
+        <v>4059.7472886298</v>
       </c>
       <c r="P136" t="n">
         <v>3600</v>
@@ -6504,10 +6504,10 @@
         <v>402</v>
       </c>
       <c r="N139" t="n">
-        <v>880.32929682061</v>
+        <v>880.32931844615</v>
       </c>
       <c r="O139" t="n">
-        <v>353892.3773218852</v>
+        <v>353892.3860153523</v>
       </c>
       <c r="P139" t="n">
         <v>1200</v>
@@ -7620,22 +7620,22 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M165" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N165" t="n">
         <v>5569.98</v>
       </c>
       <c r="O165" t="n">
-        <v>300778.92</v>
+        <v>189379.32</v>
       </c>
       <c r="P165" t="n">
         <v>8900</v>
       </c>
       <c r="Q165" t="n">
-        <v>480600</v>
+        <v>302600</v>
       </c>
     </row>
     <row r="166">
@@ -7755,25 +7755,25 @@
         <v>215</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="N168" t="n">
         <v>10911.29</v>
       </c>
       <c r="O168" t="n">
-        <v>2345927.35</v>
+        <v>2465951.54</v>
       </c>
       <c r="P168" t="n">
         <v>17400</v>
       </c>
       <c r="Q168" t="n">
-        <v>3741000</v>
+        <v>3932400</v>
       </c>
     </row>
     <row r="169">
@@ -7804,22 +7804,22 @@
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M169" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="N169" t="n">
         <v>2112.96</v>
       </c>
       <c r="O169" t="n">
-        <v>86631.36</v>
+        <v>44372.16</v>
       </c>
       <c r="P169" t="n">
         <v>3500</v>
       </c>
       <c r="Q169" t="n">
-        <v>143500</v>
+        <v>73500</v>
       </c>
     </row>
     <row r="170">
@@ -7850,22 +7850,22 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
         <v>4163.1601724138</v>
       </c>
       <c r="O170" t="n">
-        <v>8326.3203448276</v>
+        <v>0</v>
       </c>
       <c r="P170" t="n">
         <v>6700</v>
       </c>
       <c r="Q170" t="n">
-        <v>13400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -7942,22 +7942,22 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M172" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="N172" t="n">
         <v>2495.98</v>
       </c>
       <c r="O172" t="n">
-        <v>152254.78</v>
+        <v>102335.18</v>
       </c>
       <c r="P172" t="n">
         <v>4100</v>
       </c>
       <c r="Q172" t="n">
-        <v>250100</v>
+        <v>168100</v>
       </c>
     </row>
     <row r="173">
@@ -7988,22 +7988,22 @@
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M173" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="N173" t="n">
         <v>3254.49</v>
       </c>
       <c r="O173" t="n">
-        <v>292904.1</v>
+        <v>227814.3</v>
       </c>
       <c r="P173" t="n">
         <v>5200</v>
       </c>
       <c r="Q173" t="n">
-        <v>468000</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="174">
@@ -8034,22 +8034,22 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M174" t="n">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="N174" t="n">
-        <v>5218.1704867257</v>
+        <v>5218.170490524</v>
       </c>
       <c r="O174" t="n">
-        <v>793161.9139823065</v>
+        <v>584435.094938688</v>
       </c>
       <c r="P174" t="n">
         <v>8500</v>
       </c>
       <c r="Q174" t="n">
-        <v>1292000</v>
+        <v>952000</v>
       </c>
     </row>
     <row r="175">
@@ -8086,10 +8086,10 @@
         <v>112</v>
       </c>
       <c r="N175" t="n">
-        <v>1595.0094973545</v>
+        <v>1595.0094864865</v>
       </c>
       <c r="O175" t="n">
-        <v>178641.063703704</v>
+        <v>178641.062486488</v>
       </c>
       <c r="P175" t="n">
         <v>2600</v>
@@ -8126,22 +8126,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M176" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="N176" t="n">
         <v>4227.77</v>
       </c>
       <c r="O176" t="n">
-        <v>321310.52</v>
+        <v>279032.82</v>
       </c>
       <c r="P176" t="n">
         <v>6900</v>
       </c>
       <c r="Q176" t="n">
-        <v>524400</v>
+        <v>455400</v>
       </c>
     </row>
     <row r="177">
@@ -8310,22 +8310,22 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M180" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="N180" t="n">
         <v>1812.57</v>
       </c>
       <c r="O180" t="n">
-        <v>286386.06</v>
+        <v>250134.66</v>
       </c>
       <c r="P180" t="n">
         <v>2900</v>
       </c>
       <c r="Q180" t="n">
-        <v>458200</v>
+        <v>400200</v>
       </c>
     </row>
     <row r="181">
@@ -9156,10 +9156,10 @@
         <v>344</v>
       </c>
       <c r="N198" t="n">
-        <v>17075.98952512</v>
+        <v>17075.989524793</v>
       </c>
       <c r="O198" t="n">
-        <v>5874140.39664128</v>
+        <v>5874140.396528792</v>
       </c>
       <c r="P198" t="n">
         <v>27500</v>
@@ -9386,10 +9386,10 @@
         <v>552</v>
       </c>
       <c r="N203" t="n">
-        <v>1516.0388137227</v>
+        <v>1516.0388131508</v>
       </c>
       <c r="O203" t="n">
-        <v>836853.4251749305</v>
+        <v>836853.4248592416</v>
       </c>
       <c r="P203" t="n">
         <v>2300</v>
@@ -9478,10 +9478,10 @@
         <v>144</v>
       </c>
       <c r="N205" t="n">
-        <v>1771.091283906</v>
+        <v>1771.0912628399</v>
       </c>
       <c r="O205" t="n">
-        <v>255037.144882464</v>
+        <v>255037.1418489456</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>
@@ -9524,10 +9524,10 @@
         <v>240</v>
       </c>
       <c r="N206" t="n">
-        <v>2079.3842227979</v>
+        <v>2079.3842209265</v>
       </c>
       <c r="O206" t="n">
-        <v>499052.213471496</v>
+        <v>499052.21302236</v>
       </c>
       <c r="P206" t="n">
         <v>2900</v>
@@ -9570,10 +9570,10 @@
         <v>266</v>
       </c>
       <c r="N207" t="n">
-        <v>1803.0149867608</v>
+        <v>1803.0149882284</v>
       </c>
       <c r="O207" t="n">
-        <v>479601.9864783728</v>
+        <v>479601.9868687544</v>
       </c>
       <c r="P207" t="n">
         <v>2500</v>
@@ -9616,10 +9616,10 @@
         <v>48</v>
       </c>
       <c r="N208" t="n">
-        <v>3306.5954602774</v>
+        <v>3306.5954545455</v>
       </c>
       <c r="O208" t="n">
-        <v>158716.5820933152</v>
+        <v>158716.581818184</v>
       </c>
       <c r="P208" t="n">
         <v>4900</v>
@@ -9662,10 +9662,10 @@
         <v>264</v>
       </c>
       <c r="N209" t="n">
-        <v>2122.1641172932</v>
+        <v>2122.1641155235</v>
       </c>
       <c r="O209" t="n">
-        <v>560251.3269654048</v>
+        <v>560251.326498204</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>144</v>
       </c>
       <c r="N210" t="n">
-        <v>2108.7897651007</v>
+        <v>2108.7897869955</v>
       </c>
       <c r="O210" t="n">
-        <v>303665.7261745008</v>
+        <v>303665.729327352</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>288</v>
       </c>
       <c r="N211" t="n">
-        <v>2056.0838952972</v>
+        <v>2056.0838880663</v>
       </c>
       <c r="O211" t="n">
-        <v>592152.1618455936</v>
+        <v>592152.1597630944</v>
       </c>
       <c r="P211" t="n">
         <v>2900</v>
@@ -9846,10 +9846,10 @@
         <v>288</v>
       </c>
       <c r="N213" t="n">
-        <v>1655.93135625</v>
+        <v>1655.931342723</v>
       </c>
       <c r="O213" t="n">
-        <v>476908.2306</v>
+        <v>476908.226704224</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9892,10 +9892,10 @@
         <v>289</v>
       </c>
       <c r="N214" t="n">
-        <v>1592.2746762208</v>
+        <v>1592.2747647377</v>
       </c>
       <c r="O214" t="n">
-        <v>460167.3814278112</v>
+        <v>460167.4070091953</v>
       </c>
       <c r="P214" t="n">
         <v>2500</v>
@@ -9982,10 +9982,10 @@
         <v>84</v>
       </c>
       <c r="N216" t="n">
-        <v>2311.9269828927</v>
+        <v>2311.9267563291</v>
       </c>
       <c r="O216" t="n">
-        <v>194201.8665629868</v>
+        <v>194201.8475316444</v>
       </c>
       <c r="P216" t="n">
         <v>3500</v>
@@ -10028,10 +10028,10 @@
         <v>12</v>
       </c>
       <c r="N217" t="n">
-        <v>1906.1869325153</v>
+        <v>1906.1867602592</v>
       </c>
       <c r="O217" t="n">
-        <v>22874.2431901836</v>
+        <v>22874.2411231104</v>
       </c>
       <c r="P217" t="n">
         <v>2900</v>
@@ -10074,10 +10074,10 @@
         <v>48</v>
       </c>
       <c r="N218" t="n">
-        <v>2546.9852428811</v>
+        <v>2546.9851864407</v>
       </c>
       <c r="O218" t="n">
-        <v>122255.2916582928</v>
+        <v>122255.2889491536</v>
       </c>
       <c r="P218" t="n">
         <v>3900</v>
@@ -10120,10 +10120,10 @@
         <v>600</v>
       </c>
       <c r="N219" t="n">
-        <v>1259.2744102228</v>
+        <v>1259.2744140796</v>
       </c>
       <c r="O219" t="n">
-        <v>755564.64613368</v>
+        <v>755564.64844776</v>
       </c>
       <c r="P219" t="n">
         <v>1900</v>
@@ -10297,10 +10297,10 @@
         <v>192</v>
       </c>
       <c r="N223" t="n">
-        <v>692.15204525288</v>
+        <v>692.15205253785</v>
       </c>
       <c r="O223" t="n">
-        <v>132893.192688553</v>
+        <v>132893.1940872672</v>
       </c>
       <c r="P223" t="n">
         <v>1200</v>
@@ -10438,10 +10438,10 @@
         <v>2761</v>
       </c>
       <c r="N226" t="n">
-        <v>1185.3195720165</v>
+        <v>1185.3195716639</v>
       </c>
       <c r="O226" t="n">
-        <v>3272667.338337556</v>
+        <v>3272667.337364028</v>
       </c>
       <c r="P226" t="n">
         <v>1900</v>
@@ -11143,10 +11143,10 @@
         <v>1</v>
       </c>
       <c r="N241" t="n">
-        <v>1690.8700088067</v>
+        <v>1690.8700088574</v>
       </c>
       <c r="O241" t="n">
-        <v>1690.8700088067</v>
+        <v>1690.8700088574</v>
       </c>
       <c r="P241" t="n">
         <v>3000</v>
@@ -11481,10 +11481,10 @@
         <v>2280</v>
       </c>
       <c r="N248" t="n">
-        <v>517.28760395334</v>
+        <v>517.28764753291</v>
       </c>
       <c r="O248" t="n">
-        <v>1179415.737013615</v>
+        <v>1179415.836375035</v>
       </c>
       <c r="P248" t="n">
         <v>900</v>
@@ -11720,10 +11720,10 @@
         <v>504</v>
       </c>
       <c r="N253" t="n">
-        <v>3110.843282022</v>
+        <v>3110.8431677619</v>
       </c>
       <c r="O253" t="n">
-        <v>1567865.014139088</v>
+        <v>1567864.956551998</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -11948,10 +11948,10 @@
         <v>13440</v>
       </c>
       <c r="N258" t="n">
-        <v>703.79543678174</v>
+        <v>703.79542528945</v>
       </c>
       <c r="O258" t="n">
-        <v>9459010.670346586</v>
+        <v>9459010.515890209</v>
       </c>
       <c r="P258" t="n">
         <v>900</v>
@@ -12043,10 +12043,10 @@
         <v>172</v>
       </c>
       <c r="N260" t="n">
-        <v>3182.2510909091</v>
+        <v>3182.2510928962</v>
       </c>
       <c r="O260" t="n">
-        <v>547347.1876363652</v>
+        <v>547347.1879781464</v>
       </c>
       <c r="P260" t="n">
         <v>6900</v>
@@ -12227,10 +12227,10 @@
         <v>59</v>
       </c>
       <c r="N264" t="n">
-        <v>2501.3854621849</v>
+        <v>2501.385443038</v>
       </c>
       <c r="O264" t="n">
-        <v>147581.7422689091</v>
+        <v>147581.741139242</v>
       </c>
       <c r="P264" t="n">
         <v>4100</v>
@@ -12855,10 +12855,10 @@
         <v>71</v>
       </c>
       <c r="N277" t="n">
-        <v>2098.4047922438</v>
+        <v>2098.4048459384</v>
       </c>
       <c r="O277" t="n">
-        <v>148986.7402493098</v>
+        <v>148986.7440616264</v>
       </c>
       <c r="P277" t="n">
         <v>9500</v>
@@ -18676,10 +18676,10 @@
         <v>36</v>
       </c>
       <c r="N398" t="n">
-        <v>22951.704981273</v>
+        <v>22951.704968711</v>
       </c>
       <c r="O398" t="n">
-        <v>826261.379325828</v>
+        <v>826261.3788735961</v>
       </c>
       <c r="P398" t="n">
         <v>37900</v>
@@ -18865,10 +18865,10 @@
         <v>42</v>
       </c>
       <c r="N402" t="n">
-        <v>1547.8823611111</v>
+        <v>1547.8824285714</v>
       </c>
       <c r="O402" t="n">
-        <v>65011.0591666662</v>
+        <v>65011.0619999988</v>
       </c>
       <c r="P402" t="n">
         <v>5500</v>
@@ -19611,10 +19611,10 @@
         <v>1827</v>
       </c>
       <c r="N418" t="n">
-        <v>220.00867896778</v>
+        <v>220.00852554547</v>
       </c>
       <c r="O418" t="n">
-        <v>401955.8564741341</v>
+        <v>401955.5761715737</v>
       </c>
       <c r="P418" t="n">
         <v>260</v>
@@ -21257,10 +21257,10 @@
         <v>38</v>
       </c>
       <c r="N454" t="n">
-        <v>1319.3608695652</v>
+        <v>1319.360872093</v>
       </c>
       <c r="O454" t="n">
-        <v>50135.7130434776</v>
+        <v>50135.713139534</v>
       </c>
       <c r="P454" t="n">
         <v>3500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -556,10 +556,10 @@
         <v>280</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27043.062200957</v>
       </c>
       <c r="O4" t="n">
-        <v>7560000</v>
+        <v>7572057.41626796</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3040256176</v>
+        <v>1811.3041548631</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.4492223361</v>
+        <v>652069.495750716</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -967,10 +967,10 @@
         <v>99</v>
       </c>
       <c r="N14" t="n">
-        <v>27000</v>
+        <v>27064.133016627</v>
       </c>
       <c r="O14" t="n">
-        <v>2673000</v>
+        <v>2679349.168646073</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
@@ -1084,10 +1084,10 @@
         <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8371296771</v>
+        <v>3926.8371267317</v>
       </c>
       <c r="O17" t="n">
-        <v>90317.25398257331</v>
+        <v>90317.25391482911</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1357,10 +1357,10 @@
         <v>56</v>
       </c>
       <c r="N24" t="n">
-        <v>21333.69</v>
+        <v>21423.327352941</v>
       </c>
       <c r="O24" t="n">
-        <v>1194686.64</v>
+        <v>1199706.331764696</v>
       </c>
       <c r="P24" t="n">
         <v>30000</v>
@@ -2413,10 +2413,10 @@
         <v>166</v>
       </c>
       <c r="N48" t="n">
-        <v>580.36602666667</v>
+        <v>580.36600536193</v>
       </c>
       <c r="O48" t="n">
-        <v>96340.76042666721</v>
+        <v>96340.75689008037</v>
       </c>
       <c r="P48" t="n">
         <v>6800</v>
@@ -2459,10 +2459,10 @@
         <v>117</v>
       </c>
       <c r="N49" t="n">
-        <v>538.40029962547</v>
+        <v>538.40033834586</v>
       </c>
       <c r="O49" t="n">
-        <v>62992.83505617999</v>
+        <v>62992.83958646561</v>
       </c>
       <c r="P49" t="n">
         <v>6800</v>
@@ -2505,10 +2505,10 @@
         <v>175</v>
       </c>
       <c r="N50" t="n">
-        <v>28.165642201835</v>
+        <v>28.165601851852</v>
       </c>
       <c r="O50" t="n">
-        <v>4928.987385321125</v>
+        <v>4928.9803240741</v>
       </c>
       <c r="P50" t="n">
         <v>6800</v>
@@ -3178,10 +3178,10 @@
         <v>33</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101601164</v>
+        <v>4937.3101603499</v>
       </c>
       <c r="O65" t="n">
-        <v>162931.2352838412</v>
+        <v>162931.2352915467</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3350,10 +3350,10 @@
         <v>432</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.053336357</v>
+        <v>1098.0535004591</v>
       </c>
       <c r="O69" t="n">
-        <v>474359.041306224</v>
+        <v>474359.1121983312</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3529,10 +3529,10 @@
         <v>11</v>
       </c>
       <c r="N73" t="n">
-        <v>17207.41</v>
+        <v>17261.351724138</v>
       </c>
       <c r="O73" t="n">
-        <v>189281.51</v>
+        <v>189874.868965518</v>
       </c>
       <c r="P73" t="n">
         <v>20000</v>
@@ -3618,22 +3618,22 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M75" t="n">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.256064019</v>
+        <v>2582.2560562265</v>
       </c>
       <c r="O75" t="n">
-        <v>2602914.112531152</v>
+        <v>2509952.886652158</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
       </c>
       <c r="Q75" t="n">
-        <v>4536000</v>
+        <v>4374000</v>
       </c>
     </row>
     <row r="76">
@@ -3716,10 +3716,10 @@
         <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.574464752</v>
+        <v>2033.573495935</v>
       </c>
       <c r="O77" t="n">
-        <v>97611.57430809599</v>
+        <v>97611.52780488</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
@@ -3808,10 +3808,10 @@
         <v>3410</v>
       </c>
       <c r="N79" t="n">
-        <v>3158.8608137572</v>
+        <v>3158.860813875</v>
       </c>
       <c r="O79" t="n">
-        <v>10771715.37491205</v>
+        <v>10771715.37531375</v>
       </c>
       <c r="P79" t="n">
         <v>5600</v>
@@ -3854,10 +3854,10 @@
         <v>320</v>
       </c>
       <c r="N80" t="n">
-        <v>3841.6246911197</v>
+        <v>3841.6247184466</v>
       </c>
       <c r="O80" t="n">
-        <v>1229319.901158304</v>
+        <v>1229319.909902912</v>
       </c>
       <c r="P80" t="n">
         <v>6900</v>
@@ -3903,10 +3903,10 @@
         <v>60</v>
       </c>
       <c r="N81" t="n">
-        <v>3230.0677597403</v>
+        <v>3230.067752443</v>
       </c>
       <c r="O81" t="n">
-        <v>193804.065584418</v>
+        <v>193804.06514658</v>
       </c>
       <c r="P81" t="n">
         <v>6200</v>
@@ -3949,10 +3949,10 @@
         <v>514</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.8234975369</v>
+        <v>2694.8234682861</v>
       </c>
       <c r="O82" t="n">
-        <v>1385139.277733967</v>
+        <v>1385139.262699055</v>
       </c>
       <c r="P82" t="n">
         <v>4900</v>
@@ -4280,10 +4280,10 @@
         <v>332</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.2542307692</v>
+        <v>3594.254188862</v>
       </c>
       <c r="O89" t="n">
-        <v>1193292.404615375</v>
+        <v>1193292.390702184</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4637,10 +4637,10 @@
         <v>317</v>
       </c>
       <c r="N97" t="n">
-        <v>4372.2107863175</v>
+        <v>4372.2107866525</v>
       </c>
       <c r="O97" t="n">
-        <v>1385990.819262647</v>
+        <v>1385990.819368843</v>
       </c>
       <c r="P97" t="n">
         <v>7500</v>
@@ -4764,22 +4764,22 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M100" t="n">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.567707231</v>
+        <v>1592.5676712942</v>
       </c>
       <c r="O100" t="n">
-        <v>445918.95802468</v>
+        <v>388586.5117957848</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
       </c>
       <c r="Q100" t="n">
-        <v>1092000</v>
+        <v>951600</v>
       </c>
     </row>
     <row r="101">
@@ -5403,22 +5403,22 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M114" t="n">
-        <v>748</v>
+        <v>636</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9230407276</v>
+        <v>1630.9230521929</v>
       </c>
       <c r="O114" t="n">
-        <v>1219930.434464245</v>
+        <v>1037267.061194684</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
       </c>
       <c r="Q114" t="n">
-        <v>1870000</v>
+        <v>1590000</v>
       </c>
     </row>
     <row r="115">
@@ -5449,22 +5449,22 @@
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="M115" t="n">
-        <v>231</v>
+        <v>23</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.1929579149</v>
+        <v>1550.1930031561</v>
       </c>
       <c r="O115" t="n">
-        <v>358094.5732783419</v>
+        <v>35654.4390725903</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
       </c>
       <c r="Q115" t="n">
-        <v>577500</v>
+        <v>57500</v>
       </c>
     </row>
     <row r="116">
@@ -5501,10 +5501,10 @@
         <v>168</v>
       </c>
       <c r="N116" t="n">
-        <v>1579.3910696517</v>
+        <v>1579.3910473815</v>
       </c>
       <c r="O116" t="n">
-        <v>265337.6997014856</v>
+        <v>265337.695960092</v>
       </c>
       <c r="P116" t="n">
         <v>2900</v>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M117" t="n">
-        <v>271</v>
+        <v>171</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5100778841</v>
+        <v>2403.5101337902</v>
       </c>
       <c r="O117" t="n">
-        <v>651351.2311065912</v>
+        <v>411000.2328781242</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
       </c>
       <c r="Q117" t="n">
-        <v>948500</v>
+        <v>598500</v>
       </c>
     </row>
     <row r="118">
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5475490196</v>
+        <v>2521.5468491124</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.6627450976</v>
+        <v>141206.6235502944</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -5683,10 +5683,10 @@
         <v>50</v>
       </c>
       <c r="N120" t="n">
-        <v>1830.7564583333</v>
+        <v>1830.7563675214</v>
       </c>
       <c r="O120" t="n">
-        <v>91537.822916665</v>
+        <v>91537.81837607</v>
       </c>
       <c r="P120" t="n">
         <v>3150</v>
@@ -6294,10 +6294,10 @@
         <v>128</v>
       </c>
       <c r="N134" t="n">
-        <v>5449.5304477612</v>
+        <v>5449.5304580153</v>
       </c>
       <c r="O134" t="n">
-        <v>697539.8973134336</v>
+        <v>697539.8986259584</v>
       </c>
       <c r="P134" t="n">
         <v>6200</v>
@@ -6381,10 +6381,10 @@
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>2029.8736443149</v>
+        <v>2029.8736460865</v>
       </c>
       <c r="O136" t="n">
-        <v>4059.7472886298</v>
+        <v>4059.747292173</v>
       </c>
       <c r="P136" t="n">
         <v>3600</v>
@@ -6504,10 +6504,10 @@
         <v>402</v>
       </c>
       <c r="N139" t="n">
-        <v>880.32931844615</v>
+        <v>880.32932278334</v>
       </c>
       <c r="O139" t="n">
-        <v>353892.3860153523</v>
+        <v>353892.3877589027</v>
       </c>
       <c r="P139" t="n">
         <v>1200</v>
@@ -6755,10 +6755,10 @@
         <v>4</v>
       </c>
       <c r="N145" t="n">
-        <v>11562.038534031</v>
+        <v>11562.038530184</v>
       </c>
       <c r="O145" t="n">
-        <v>46248.154136124</v>
+        <v>46248.154120736</v>
       </c>
       <c r="P145" t="n">
         <v>18500</v>
@@ -7439,10 +7439,10 @@
         <v>21</v>
       </c>
       <c r="N161" t="n">
-        <v>12981.59</v>
+        <v>13028.454945848</v>
       </c>
       <c r="O161" t="n">
-        <v>272613.39</v>
+        <v>273597.553862808</v>
       </c>
       <c r="P161" t="n">
         <v>21900</v>
@@ -7994,10 +7994,10 @@
         <v>112</v>
       </c>
       <c r="N173" t="n">
-        <v>5218.170490524</v>
+        <v>5218.1704988662</v>
       </c>
       <c r="O173" t="n">
-        <v>584435.094938688</v>
+        <v>584435.0958730144</v>
       </c>
       <c r="P173" t="n">
         <v>8500</v>
@@ -8040,10 +8040,10 @@
         <v>112</v>
       </c>
       <c r="N174" t="n">
-        <v>1595.0094864865</v>
+        <v>1595.0094843962</v>
       </c>
       <c r="O174" t="n">
-        <v>178641.062486488</v>
+        <v>178641.0622523744</v>
       </c>
       <c r="P174" t="n">
         <v>2600</v>
@@ -9110,10 +9110,10 @@
         <v>344</v>
       </c>
       <c r="N197" t="n">
-        <v>17075.989524793</v>
+        <v>17075.989524138</v>
       </c>
       <c r="O197" t="n">
-        <v>5874140.396528792</v>
+        <v>5874140.396303472</v>
       </c>
       <c r="P197" t="n">
         <v>27500</v>
@@ -9340,10 +9340,10 @@
         <v>552</v>
       </c>
       <c r="N202" t="n">
-        <v>1516.0388131508</v>
+        <v>1516.0388129219</v>
       </c>
       <c r="O202" t="n">
-        <v>836853.4248592416</v>
+        <v>836853.4247328888</v>
       </c>
       <c r="P202" t="n">
         <v>2300</v>
@@ -9386,10 +9386,10 @@
         <v>432</v>
       </c>
       <c r="N203" t="n">
-        <v>2458.5134514107</v>
+        <v>2458.5134452463</v>
       </c>
       <c r="O203" t="n">
-        <v>1062077.811009422</v>
+        <v>1062077.808346401</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.3842209265</v>
+        <v>2079.3842077922</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.21302236</v>
+        <v>499052.209870128</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9570,10 +9570,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>3306.5954545455</v>
+        <v>3306.595443038</v>
       </c>
       <c r="O207" t="n">
-        <v>158716.581818184</v>
+        <v>158716.581265824</v>
       </c>
       <c r="P207" t="n">
         <v>4900</v>
@@ -9616,10 +9616,10 @@
         <v>264</v>
       </c>
       <c r="N208" t="n">
-        <v>2122.1641155235</v>
+        <v>2122.1641066586</v>
       </c>
       <c r="O208" t="n">
-        <v>560251.326498204</v>
+        <v>560251.3241578704</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7897869955</v>
+        <v>2108.7898867497</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.729327352</v>
+        <v>303665.7436919568</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.0838880663</v>
+        <v>2056.692917654</v>
       </c>
       <c r="O210" t="n">
-        <v>592152.1597630944</v>
+        <v>592327.560284352</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>3224.5679626335</v>
+        <v>3224.5679768271</v>
       </c>
       <c r="O211" t="n">
-        <v>696506.6799288359</v>
+        <v>696506.6829946537</v>
       </c>
       <c r="P211" t="n">
         <v>4500</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.931342723</v>
+        <v>1655.9313291536</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.226704224</v>
+        <v>476908.2227962368</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9840,22 +9840,22 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M213" t="n">
-        <v>289</v>
+        <v>97</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.2747647377</v>
+        <v>1592.2748727876</v>
       </c>
       <c r="O213" t="n">
-        <v>460167.4070091953</v>
+        <v>154450.6626603972</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
       </c>
       <c r="Q213" t="n">
-        <v>722500</v>
+        <v>242500</v>
       </c>
     </row>
     <row r="214">
@@ -9930,22 +9930,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M215" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9267563291</v>
+        <v>2311.9264781906</v>
       </c>
       <c r="O215" t="n">
-        <v>194201.8475316444</v>
+        <v>83229.35321486159</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
       </c>
       <c r="Q215" t="n">
-        <v>294000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="216">
@@ -9982,10 +9982,10 @@
         <v>12</v>
       </c>
       <c r="N216" t="n">
-        <v>1906.1867602592</v>
+        <v>1906.1867105263</v>
       </c>
       <c r="O216" t="n">
-        <v>22874.2411231104</v>
+        <v>22874.2405263156</v>
       </c>
       <c r="P216" t="n">
         <v>2900</v>
@@ -10028,10 +10028,10 @@
         <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>2546.9851864407</v>
+        <v>2546.9851535836</v>
       </c>
       <c r="O217" t="n">
-        <v>122255.2889491536</v>
+        <v>122255.2873720128</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
@@ -10074,10 +10074,10 @@
         <v>600</v>
       </c>
       <c r="N218" t="n">
-        <v>1259.2744140796</v>
+        <v>1259.2744160105</v>
       </c>
       <c r="O218" t="n">
-        <v>755564.64844776</v>
+        <v>755564.6496063001</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -10115,10 +10115,10 @@
         <v>120</v>
       </c>
       <c r="N219" t="n">
-        <v>2842.2737931034</v>
+        <v>2842.2737735849</v>
       </c>
       <c r="O219" t="n">
-        <v>341072.855172408</v>
+        <v>341072.852830188</v>
       </c>
       <c r="P219" t="n">
         <v>4900</v>
@@ -10726,10 +10726,10 @@
         <v>324</v>
       </c>
       <c r="N232" t="n">
-        <v>1530.4499204455</v>
+        <v>1530.4499204138</v>
       </c>
       <c r="O232" t="n">
-        <v>495865.774224342</v>
+        <v>495865.7742140712</v>
       </c>
       <c r="P232" t="n">
         <v>2600</v>
@@ -11097,10 +11097,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>1690.8700088574</v>
+        <v>1690.8700089286</v>
       </c>
       <c r="O240" t="n">
-        <v>1690.8700088574</v>
+        <v>1690.8700089286</v>
       </c>
       <c r="P240" t="n">
         <v>3000</v>
@@ -11195,10 +11195,10 @@
         <v>-2</v>
       </c>
       <c r="N242" t="n">
-        <v>2270.3210752688</v>
+        <v>2270.3211494253</v>
       </c>
       <c r="O242" t="n">
-        <v>-4540.6421505376</v>
+        <v>-4540.6422988506</v>
       </c>
       <c r="P242" t="n">
         <v>3900</v>
@@ -11435,10 +11435,10 @@
         <v>2280</v>
       </c>
       <c r="N247" t="n">
-        <v>517.28764753291</v>
+        <v>517.28774146762</v>
       </c>
       <c r="O247" t="n">
-        <v>1179415.836375035</v>
+        <v>1179416.050546173</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11674,10 +11674,10 @@
         <v>504</v>
       </c>
       <c r="N252" t="n">
-        <v>3110.8431677619</v>
+        <v>3110.8430699863</v>
       </c>
       <c r="O252" t="n">
-        <v>1567864.956551998</v>
+        <v>1567864.907273095</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11902,10 +11902,10 @@
         <v>13440</v>
       </c>
       <c r="N257" t="n">
-        <v>703.79542528945</v>
+        <v>703.79541200942</v>
       </c>
       <c r="O257" t="n">
-        <v>9459010.515890209</v>
+        <v>9459010.337406605</v>
       </c>
       <c r="P257" t="n">
         <v>900</v>
@@ -11942,22 +11942,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M258" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N258" t="n">
         <v>34615.38</v>
       </c>
       <c r="O258" t="n">
-        <v>276923.04</v>
+        <v>138461.52</v>
       </c>
       <c r="P258" t="n">
         <v>45000</v>
       </c>
       <c r="Q258" t="n">
-        <v>360000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="259">
@@ -11997,10 +11997,10 @@
         <v>172</v>
       </c>
       <c r="N259" t="n">
-        <v>3182.2510928962</v>
+        <v>3182.2511009174</v>
       </c>
       <c r="O259" t="n">
-        <v>547347.1879781464</v>
+        <v>547347.1893577928</v>
       </c>
       <c r="P259" t="n">
         <v>6900</v>
@@ -12809,10 +12809,10 @@
         <v>71</v>
       </c>
       <c r="N276" t="n">
-        <v>2098.4048459384</v>
+        <v>2098.4048595506</v>
       </c>
       <c r="O276" t="n">
-        <v>148986.7440616264</v>
+        <v>148986.7450280926</v>
       </c>
       <c r="P276" t="n">
         <v>9500</v>
@@ -14053,10 +14053,10 @@
         <v>5</v>
       </c>
       <c r="N302" t="n">
-        <v>12448.353225806</v>
+        <v>12448.353333333</v>
       </c>
       <c r="O302" t="n">
-        <v>62241.76612903</v>
+        <v>62241.766666665</v>
       </c>
       <c r="P302" t="n">
         <v>22900</v>
@@ -18355,10 +18355,10 @@
         <v>455</v>
       </c>
       <c r="N391" t="n">
-        <v>315.02675450763</v>
+        <v>315.02678272981</v>
       </c>
       <c r="O391" t="n">
-        <v>143337.1733009717</v>
+        <v>143337.1861420636</v>
       </c>
       <c r="P391" t="n">
         <v>2200</v>
@@ -18921,10 +18921,10 @@
         <v>63</v>
       </c>
       <c r="N403" t="n">
-        <v>1757.3205179283</v>
+        <v>1757.3205295316</v>
       </c>
       <c r="O403" t="n">
-        <v>110711.1926294829</v>
+        <v>110711.1933604908</v>
       </c>
       <c r="P403" t="n">
         <v>2000</v>
@@ -19565,10 +19565,10 @@
         <v>1827</v>
       </c>
       <c r="N417" t="n">
-        <v>220.00852554547</v>
+        <v>220.00820587826</v>
       </c>
       <c r="O417" t="n">
-        <v>401955.5761715737</v>
+        <v>401954.992139581</v>
       </c>
       <c r="P417" t="n">
         <v>260</v>
@@ -20291,10 +20291,10 @@
         <v>3</v>
       </c>
       <c r="N433" t="n">
-        <v>21664.37125</v>
+        <v>21664.371428571</v>
       </c>
       <c r="O433" t="n">
-        <v>64993.11375</v>
+        <v>64993.114285713</v>
       </c>
       <c r="P433" t="n">
         <v>30000</v>
@@ -21211,10 +21211,10 @@
         <v>38</v>
       </c>
       <c r="N453" t="n">
-        <v>1319.360872093</v>
+        <v>1319.3608797654</v>
       </c>
       <c r="O453" t="n">
-        <v>50135.713139534</v>
+        <v>50135.71343108521</v>
       </c>
       <c r="P453" t="n">
         <v>3500</v>
@@ -21599,10 +21599,10 @@
         <v>42</v>
       </c>
       <c r="N461" t="n">
-        <v>2432.1340350877</v>
+        <v>2432.1341071429</v>
       </c>
       <c r="O461" t="n">
-        <v>102149.6294736834</v>
+        <v>102149.6325000018</v>
       </c>
       <c r="P461" t="n">
         <v>4500</v>
@@ -22559,22 +22559,22 @@
         <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M482" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.7409090909</v>
+        <v>7046.7426315789</v>
       </c>
       <c r="O482" t="n">
-        <v>140934.818181818</v>
+        <v>98654.3968421046</v>
       </c>
       <c r="P482" t="n">
         <v>22900</v>
       </c>
       <c r="Q482" t="n">
-        <v>458000</v>
+        <v>320600</v>
       </c>
     </row>
     <row r="483">
@@ -22847,10 +22847,10 @@
         <v>819000</v>
       </c>
       <c r="P488" t="n">
-        <v>6500</v>
+        <v>5500</v>
       </c>
       <c r="Q488" t="n">
-        <v>1170000</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="489">

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>280</v>
       </c>
       <c r="N4" t="n">
-        <v>27043.062200957</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>7572057.41626796</v>
+        <v>7560000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -967,10 +967,10 @@
         <v>99</v>
       </c>
       <c r="N14" t="n">
-        <v>27064.133016627</v>
+        <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>2679349.168646073</v>
+        <v>2673000</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
@@ -1357,10 +1357,10 @@
         <v>56</v>
       </c>
       <c r="N24" t="n">
-        <v>21423.327352941</v>
+        <v>21333.69</v>
       </c>
       <c r="O24" t="n">
-        <v>1199706.331764696</v>
+        <v>1194686.64</v>
       </c>
       <c r="P24" t="n">
         <v>30000</v>
@@ -3529,10 +3529,10 @@
         <v>11</v>
       </c>
       <c r="N73" t="n">
-        <v>17261.351724138</v>
+        <v>17207.41</v>
       </c>
       <c r="O73" t="n">
-        <v>189874.868965518</v>
+        <v>189281.51</v>
       </c>
       <c r="P73" t="n">
         <v>20000</v>
@@ -3612,13 +3612,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>972</v>
@@ -4758,13 +4758,13 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>244</v>
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>748</v>
+        <v>636</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
         <v>636</v>
@@ -5443,13 +5443,13 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>231</v>
+        <v>23</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
         <v>23</v>
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>271</v>
+        <v>171</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
         <v>171</v>
@@ -7439,10 +7439,10 @@
         <v>21</v>
       </c>
       <c r="N161" t="n">
-        <v>13028.454945848</v>
+        <v>12981.59</v>
       </c>
       <c r="O161" t="n">
-        <v>273597.553862808</v>
+        <v>272613.39</v>
       </c>
       <c r="P161" t="n">
         <v>21900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.692917654</v>
+        <v>2056.0838862559</v>
       </c>
       <c r="O210" t="n">
-        <v>592327.560284352</v>
+        <v>592152.1592416991</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9834,13 +9834,13 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>289</v>
+        <v>97</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
         <v>97</v>
@@ -9924,13 +9924,13 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
         <v>36</v>
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
         <v>4</v>
@@ -22553,13 +22553,13 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M482" t="n">
         <v>14</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3041548631</v>
+        <v>1811.3043052838</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.495750716</v>
+        <v>652069.549902168</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2413.0010330579</v>
+        <v>2413.001059322</v>
       </c>
       <c r="O18" t="n">
-        <v>4826.0020661158</v>
+        <v>4826.002118644</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -2367,10 +2367,10 @@
         <v>122</v>
       </c>
       <c r="N47" t="n">
-        <v>427.91890410959</v>
+        <v>430.87006896552</v>
       </c>
       <c r="O47" t="n">
-        <v>52206.10630136998</v>
+        <v>52566.14841379344</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
@@ -2459,10 +2459,10 @@
         <v>117</v>
       </c>
       <c r="N49" t="n">
-        <v>538.40033834586</v>
+        <v>542.47912878788</v>
       </c>
       <c r="O49" t="n">
-        <v>62992.83958646561</v>
+        <v>63470.05806818196</v>
       </c>
       <c r="P49" t="n">
         <v>6800</v>
@@ -2499,22 +2499,22 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="N50" t="n">
-        <v>28.165601851852</v>
+        <v>28.165539906103</v>
       </c>
       <c r="O50" t="n">
-        <v>4928.9803240741</v>
+        <v>4647.314084506995</v>
       </c>
       <c r="P50" t="n">
         <v>6800</v>
       </c>
       <c r="Q50" t="n">
-        <v>1190000</v>
+        <v>1122000</v>
       </c>
     </row>
     <row r="51">
@@ -3178,10 +3178,10 @@
         <v>33</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101603499</v>
+        <v>4937.3101608187</v>
       </c>
       <c r="O65" t="n">
-        <v>162931.2352915467</v>
+        <v>162931.2353070171</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3350,10 +3350,10 @@
         <v>432</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0535004591</v>
+        <v>1098.0541801698</v>
       </c>
       <c r="O69" t="n">
-        <v>474359.1121983312</v>
+        <v>474359.4058333536</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3624,10 +3624,10 @@
         <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2560562265</v>
+        <v>2582.2560231583</v>
       </c>
       <c r="O75" t="n">
-        <v>2509952.886652158</v>
+        <v>2509952.854509868</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3664,22 +3664,22 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="N76" t="n">
-        <v>5216.8959875629</v>
+        <v>5216.8959762435</v>
       </c>
       <c r="O76" t="n">
-        <v>7512330.222090576</v>
+        <v>7501896.413838153</v>
       </c>
       <c r="P76" t="n">
         <v>8500</v>
       </c>
       <c r="Q76" t="n">
-        <v>12240000</v>
+        <v>12223000</v>
       </c>
     </row>
     <row r="77">
@@ -3716,10 +3716,10 @@
         <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.573495935</v>
+        <v>2033.5693416928</v>
       </c>
       <c r="O77" t="n">
-        <v>97611.52780488</v>
+        <v>97611.3284012544</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
@@ -3808,10 +3808,10 @@
         <v>3410</v>
       </c>
       <c r="N79" t="n">
-        <v>3158.860813875</v>
+        <v>3158.8608143857</v>
       </c>
       <c r="O79" t="n">
-        <v>10771715.37531375</v>
+        <v>10771715.37705524</v>
       </c>
       <c r="P79" t="n">
         <v>5600</v>
@@ -3949,10 +3949,10 @@
         <v>514</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.8234682861</v>
+        <v>2694.8234624043</v>
       </c>
       <c r="O82" t="n">
-        <v>1385139.262699055</v>
+        <v>1385139.25967581</v>
       </c>
       <c r="P82" t="n">
         <v>4900</v>
@@ -4280,10 +4280,10 @@
         <v>332</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.254188862</v>
+        <v>3594.2541747573</v>
       </c>
       <c r="O89" t="n">
-        <v>1193292.390702184</v>
+        <v>1193292.386019424</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4326,10 +4326,10 @@
         <v>282</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378867257</v>
+        <v>14822.378864577</v>
       </c>
       <c r="O90" t="n">
-        <v>4179910.840566474</v>
+        <v>4179910.839810714</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -4637,10 +4637,10 @@
         <v>317</v>
       </c>
       <c r="N97" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="O97" t="n">
-        <v>1385990.819368843</v>
+        <v>1385990.819457381</v>
       </c>
       <c r="P97" t="n">
         <v>7500</v>
@@ -4770,10 +4770,10 @@
         <v>244</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.5676712942</v>
+        <v>1592.5675881262</v>
       </c>
       <c r="O100" t="n">
-        <v>388586.5117957848</v>
+        <v>388586.4915027928</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
@@ -5172,22 +5172,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M109" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N109" t="n">
         <v>11921.4</v>
       </c>
       <c r="O109" t="n">
-        <v>739126.7999999999</v>
+        <v>631834.2</v>
       </c>
       <c r="P109" t="n">
         <v>19900</v>
       </c>
       <c r="Q109" t="n">
-        <v>1233800</v>
+        <v>1054700</v>
       </c>
     </row>
     <row r="110">
@@ -5409,10 +5409,10 @@
         <v>636</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9230521929</v>
+        <v>1630.9231064431</v>
       </c>
       <c r="O114" t="n">
-        <v>1037267.061194684</v>
+        <v>1037267.095697812</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>23</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.1930031561</v>
+        <v>1550.1930735465</v>
       </c>
       <c r="O115" t="n">
-        <v>35654.4390725903</v>
+        <v>35654.4406915695</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
@@ -5547,10 +5547,10 @@
         <v>171</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5101337902</v>
+        <v>2403.5102087442</v>
       </c>
       <c r="O117" t="n">
-        <v>411000.2328781242</v>
+        <v>411000.2456952582</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5468491124</v>
+        <v>2521.5455211726</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.6235502944</v>
+        <v>141206.5491856656</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -6288,22 +6288,22 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M134" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="N134" t="n">
-        <v>5449.5304580153</v>
+        <v>5449.53048</v>
       </c>
       <c r="O134" t="n">
-        <v>697539.8986259584</v>
+        <v>561301.6394400001</v>
       </c>
       <c r="P134" t="n">
         <v>6200</v>
       </c>
       <c r="Q134" t="n">
-        <v>793600</v>
+        <v>638600</v>
       </c>
     </row>
     <row r="135">
@@ -6381,10 +6381,10 @@
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>2029.8736460865</v>
+        <v>2029.8736549708</v>
       </c>
       <c r="O136" t="n">
-        <v>4059.747292173</v>
+        <v>4059.7473099416</v>
       </c>
       <c r="P136" t="n">
         <v>3600</v>
@@ -6504,10 +6504,10 @@
         <v>402</v>
       </c>
       <c r="N139" t="n">
-        <v>880.32932278334</v>
+        <v>880.32933581916</v>
       </c>
       <c r="O139" t="n">
-        <v>353892.3877589027</v>
+        <v>353892.3929993023</v>
       </c>
       <c r="P139" t="n">
         <v>1200</v>
@@ -6926,22 +6926,22 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M149" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="N149" t="n">
         <v>4793.53</v>
       </c>
       <c r="O149" t="n">
-        <v>431417.7</v>
+        <v>364308.28</v>
       </c>
       <c r="P149" t="n">
         <v>7900</v>
       </c>
       <c r="Q149" t="n">
-        <v>711000</v>
+        <v>600400</v>
       </c>
     </row>
     <row r="150">
@@ -7183,10 +7183,10 @@
         <v>26</v>
       </c>
       <c r="N155" t="n">
-        <v>2568.8356026059</v>
+        <v>2568.8355</v>
       </c>
       <c r="O155" t="n">
-        <v>66789.7256677534</v>
+        <v>66789.723</v>
       </c>
       <c r="P155" t="n">
         <v>4500</v>
@@ -7270,10 +7270,10 @@
         <v>5</v>
       </c>
       <c r="N157" t="n">
-        <v>7969.950164794</v>
+        <v>7969.9501649175</v>
       </c>
       <c r="O157" t="n">
-        <v>39849.75082397</v>
+        <v>39849.7508245875</v>
       </c>
       <c r="P157" t="n">
         <v>12900</v>
@@ -7994,10 +7994,10 @@
         <v>112</v>
       </c>
       <c r="N173" t="n">
-        <v>5218.1704988662</v>
+        <v>5218.1705022831</v>
       </c>
       <c r="O173" t="n">
-        <v>584435.0958730144</v>
+        <v>584435.0962557072</v>
       </c>
       <c r="P173" t="n">
         <v>8500</v>
@@ -8040,10 +8040,10 @@
         <v>112</v>
       </c>
       <c r="N174" t="n">
-        <v>1595.0094843962</v>
+        <v>1595.0094808743</v>
       </c>
       <c r="O174" t="n">
-        <v>178641.0622523744</v>
+        <v>178641.0618579216</v>
       </c>
       <c r="P174" t="n">
         <v>2600</v>
@@ -9110,10 +9110,10 @@
         <v>344</v>
       </c>
       <c r="N197" t="n">
-        <v>17075.989524138</v>
+        <v>17075.98952381</v>
       </c>
       <c r="O197" t="n">
-        <v>5874140.396303472</v>
+        <v>5874140.39619064</v>
       </c>
       <c r="P197" t="n">
         <v>27500</v>
@@ -9386,10 +9386,10 @@
         <v>432</v>
       </c>
       <c r="N203" t="n">
-        <v>2458.5134452463</v>
+        <v>2458.5134204724</v>
       </c>
       <c r="O203" t="n">
-        <v>1062077.808346401</v>
+        <v>1062077.797644077</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.3842077922</v>
+        <v>2079.384205911</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.209870128</v>
+        <v>499052.2094186401</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>266</v>
       </c>
       <c r="N206" t="n">
-        <v>1803.0149882284</v>
+        <v>1803.0150073855</v>
       </c>
       <c r="O206" t="n">
-        <v>479601.9868687544</v>
+        <v>479601.991964543</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9570,10 +9570,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>3306.595443038</v>
+        <v>3306.5954372624</v>
       </c>
       <c r="O207" t="n">
-        <v>158716.581265824</v>
+        <v>158716.5809885952</v>
       </c>
       <c r="P207" t="n">
         <v>4900</v>
@@ -9616,10 +9616,10 @@
         <v>264</v>
       </c>
       <c r="N208" t="n">
-        <v>2122.1641066586</v>
+        <v>2122.1640959855</v>
       </c>
       <c r="O208" t="n">
-        <v>560251.3241578704</v>
+        <v>560251.321340172</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7898867497</v>
+        <v>2108.7899091941</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.7436919568</v>
+        <v>303665.7469239504</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.0838862559</v>
+        <v>2056.083871734</v>
       </c>
       <c r="O210" t="n">
-        <v>592152.1592416991</v>
+        <v>592152.155059392</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>3224.5679768271</v>
+        <v>3224.5680666967</v>
       </c>
       <c r="O211" t="n">
-        <v>696506.6829946537</v>
+        <v>696506.7024064872</v>
       </c>
       <c r="P211" t="n">
         <v>4500</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.9313291536</v>
+        <v>1655.9312964128</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.2227962368</v>
+        <v>476908.2133668864</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9846,10 +9846,10 @@
         <v>97</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.2748727876</v>
+        <v>1592.2752659892</v>
       </c>
       <c r="O213" t="n">
-        <v>154450.6626603972</v>
+        <v>154450.7008009524</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9890,10 +9890,10 @@
         <v>44</v>
       </c>
       <c r="N214" t="n">
-        <v>5347.73</v>
+        <v>5370.4862978723</v>
       </c>
       <c r="O214" t="n">
-        <v>235300.12</v>
+        <v>236301.3971063812</v>
       </c>
       <c r="P214" t="n">
         <v>9500</v>
@@ -9936,10 +9936,10 @@
         <v>36</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9264781906</v>
+        <v>2311.9257410562</v>
       </c>
       <c r="O215" t="n">
-        <v>83229.35321486159</v>
+        <v>83229.32667802319</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -9982,10 +9982,10 @@
         <v>12</v>
       </c>
       <c r="N216" t="n">
-        <v>1906.1867105263</v>
+        <v>1906.1864705882</v>
       </c>
       <c r="O216" t="n">
-        <v>22874.2405263156</v>
+        <v>22874.2376470584</v>
       </c>
       <c r="P216" t="n">
         <v>2900</v>
@@ -10074,10 +10074,10 @@
         <v>600</v>
       </c>
       <c r="N218" t="n">
-        <v>1259.2744160105</v>
+        <v>1259.2744247206</v>
       </c>
       <c r="O218" t="n">
-        <v>755564.6496063001</v>
+        <v>755564.6548323601</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -10251,10 +10251,10 @@
         <v>192</v>
       </c>
       <c r="N222" t="n">
-        <v>692.15205253785</v>
+        <v>692.15206356312</v>
       </c>
       <c r="O222" t="n">
-        <v>132893.1940872672</v>
+        <v>132893.196204119</v>
       </c>
       <c r="P222" t="n">
         <v>1200</v>
@@ -11435,10 +11435,10 @@
         <v>2280</v>
       </c>
       <c r="N247" t="n">
-        <v>517.28774146762</v>
+        <v>517.2878865955601</v>
       </c>
       <c r="O247" t="n">
-        <v>1179416.050546173</v>
+        <v>1179416.381437877</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11481,10 +11481,10 @@
         <v>65</v>
       </c>
       <c r="N248" t="n">
-        <v>2571.14</v>
+        <v>2639.7037333333</v>
       </c>
       <c r="O248" t="n">
-        <v>167124.1</v>
+        <v>171580.7426666645</v>
       </c>
       <c r="P248" t="n">
         <v>6900</v>
@@ -11674,10 +11674,10 @@
         <v>504</v>
       </c>
       <c r="N252" t="n">
-        <v>3110.8430699863</v>
+        <v>3110.8429819337</v>
       </c>
       <c r="O252" t="n">
-        <v>1567864.907273095</v>
+        <v>1567864.862894585</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11896,22 +11896,22 @@
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M257" t="n">
-        <v>13440</v>
+        <v>13152</v>
       </c>
       <c r="N257" t="n">
-        <v>703.79541200942</v>
+        <v>703.79538564105</v>
       </c>
       <c r="O257" t="n">
-        <v>9459010.337406605</v>
+        <v>9256316.911951089</v>
       </c>
       <c r="P257" t="n">
         <v>900</v>
       </c>
       <c r="Q257" t="n">
-        <v>12096000</v>
+        <v>11836800</v>
       </c>
     </row>
     <row r="258">
@@ -12181,10 +12181,10 @@
         <v>59</v>
       </c>
       <c r="N263" t="n">
-        <v>2501.385443038</v>
+        <v>2501.3854237288</v>
       </c>
       <c r="O263" t="n">
-        <v>147581.741139242</v>
+        <v>147581.7399999992</v>
       </c>
       <c r="P263" t="n">
         <v>4100</v>
@@ -12809,10 +12809,10 @@
         <v>71</v>
       </c>
       <c r="N276" t="n">
-        <v>2098.4048595506</v>
+        <v>2098.4049008499</v>
       </c>
       <c r="O276" t="n">
-        <v>148986.7450280926</v>
+        <v>148986.7479603429</v>
       </c>
       <c r="P276" t="n">
         <v>9500</v>
@@ -13192,10 +13192,10 @@
         <v>5</v>
       </c>
       <c r="N284" t="n">
-        <v>2832.1946575342</v>
+        <v>2832.1948571429</v>
       </c>
       <c r="O284" t="n">
-        <v>14160.973287671</v>
+        <v>14160.9742857145</v>
       </c>
       <c r="P284" t="n">
         <v>12900</v>
@@ -14053,10 +14053,10 @@
         <v>5</v>
       </c>
       <c r="N302" t="n">
-        <v>12448.353333333</v>
+        <v>12448.353571429</v>
       </c>
       <c r="O302" t="n">
-        <v>62241.766666665</v>
+        <v>62241.76785714499</v>
       </c>
       <c r="P302" t="n">
         <v>22900</v>
@@ -15021,10 +15021,10 @@
         <v>60</v>
       </c>
       <c r="N322" t="n">
-        <v>3067.0905341246</v>
+        <v>3067.0905389222</v>
       </c>
       <c r="O322" t="n">
-        <v>184025.432047476</v>
+        <v>184025.432335332</v>
       </c>
       <c r="P322" t="n">
         <v>7200</v>
@@ -15263,10 +15263,10 @@
         <v>74</v>
       </c>
       <c r="N327" t="n">
-        <v>4190.77</v>
+        <v>4205.0243197279</v>
       </c>
       <c r="O327" t="n">
-        <v>310116.98</v>
+        <v>311171.7996598646</v>
       </c>
       <c r="P327" t="n">
         <v>5900</v>
@@ -15312,10 +15312,10 @@
         <v>264</v>
       </c>
       <c r="N328" t="n">
-        <v>3499.72</v>
+        <v>3508.0033609467</v>
       </c>
       <c r="O328" t="n">
-        <v>923926.08</v>
+        <v>926112.8872899289</v>
       </c>
       <c r="P328" t="n">
         <v>6900</v>
@@ -15601,10 +15601,10 @@
         <v>1000</v>
       </c>
       <c r="N334" t="n">
-        <v>1783.7988868778</v>
+        <v>1783.7988843537</v>
       </c>
       <c r="O334" t="n">
-        <v>1783798.8868778</v>
+        <v>1783798.8843537</v>
       </c>
       <c r="P334" t="n">
         <v>1500</v>
@@ -15941,10 +15941,10 @@
         <v>1</v>
       </c>
       <c r="N341" t="n">
-        <v>10737.526727273</v>
+        <v>10737.526666667</v>
       </c>
       <c r="O341" t="n">
-        <v>10737.526727273</v>
+        <v>10737.526666667</v>
       </c>
       <c r="P341" t="n">
         <v>18900</v>
@@ -17427,10 +17427,10 @@
         <v>50</v>
       </c>
       <c r="N372" t="n">
-        <v>1934.77</v>
+        <v>1942.8822431866</v>
       </c>
       <c r="O372" t="n">
-        <v>96738.5</v>
+        <v>97144.11215932999</v>
       </c>
       <c r="P372" t="n">
         <v>8900</v>
@@ -17574,10 +17574,10 @@
         <v>8</v>
       </c>
       <c r="N375" t="n">
-        <v>7046.9398302567</v>
+        <v>7046.9398299681</v>
       </c>
       <c r="O375" t="n">
-        <v>56375.5186420536</v>
+        <v>56375.5186397448</v>
       </c>
       <c r="P375" t="n">
         <v>9900</v>
@@ -17623,10 +17623,10 @@
         <v>2</v>
       </c>
       <c r="N376" t="n">
-        <v>26378.027272727</v>
+        <v>26378.027</v>
       </c>
       <c r="O376" t="n">
-        <v>52756.054545454</v>
+        <v>52756.054</v>
       </c>
       <c r="P376" t="n">
         <v>36500</v>
@@ -17914,10 +17914,10 @@
         <v>526</v>
       </c>
       <c r="N382" t="n">
-        <v>641.78</v>
+        <v>642.25894029851</v>
       </c>
       <c r="O382" t="n">
-        <v>337576.28</v>
+        <v>337828.2025970162</v>
       </c>
       <c r="P382" t="n">
         <v>2500</v>
@@ -18355,10 +18355,10 @@
         <v>455</v>
       </c>
       <c r="N391" t="n">
-        <v>315.02678272981</v>
+        <v>315.02679218968</v>
       </c>
       <c r="O391" t="n">
-        <v>143337.1861420636</v>
+        <v>143337.1904463044</v>
       </c>
       <c r="P391" t="n">
         <v>2200</v>
@@ -18624,22 +18624,22 @@
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M397" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N397" t="n">
         <v>22951.704968711</v>
       </c>
       <c r="O397" t="n">
-        <v>826261.3788735961</v>
+        <v>688551.14906133</v>
       </c>
       <c r="P397" t="n">
         <v>37900</v>
       </c>
       <c r="Q397" t="n">
-        <v>1364400</v>
+        <v>1137000</v>
       </c>
     </row>
     <row r="398">
@@ -18921,10 +18921,10 @@
         <v>63</v>
       </c>
       <c r="N403" t="n">
-        <v>1757.3205295316</v>
+        <v>1757.3205360825</v>
       </c>
       <c r="O403" t="n">
-        <v>110711.1933604908</v>
+        <v>110711.1937731975</v>
       </c>
       <c r="P403" t="n">
         <v>2000</v>
@@ -20153,10 +20153,10 @@
         <v>3</v>
       </c>
       <c r="N430" t="n">
-        <v>9855.0382758621</v>
+        <v>9855.0381481481</v>
       </c>
       <c r="O430" t="n">
-        <v>29565.1148275863</v>
+        <v>29565.1144444443</v>
       </c>
       <c r="P430" t="n">
         <v>15500</v>
@@ -20889,10 +20889,10 @@
         <v>250</v>
       </c>
       <c r="N446" t="n">
-        <v>1236.3</v>
+        <v>1242.6076530612</v>
       </c>
       <c r="O446" t="n">
-        <v>309075</v>
+        <v>310651.9132653</v>
       </c>
       <c r="P446" t="n">
         <v>2300</v>
@@ -21399,22 +21399,22 @@
         <v>0</v>
       </c>
       <c r="L457" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M457" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="N457" t="n">
         <v>571.87</v>
       </c>
       <c r="O457" t="n">
-        <v>92642.94</v>
+        <v>86924.24000000001</v>
       </c>
       <c r="P457" t="n">
         <v>2500</v>
       </c>
       <c r="Q457" t="n">
-        <v>405000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="458">
@@ -21691,10 +21691,10 @@
         <v>235</v>
       </c>
       <c r="N463" t="n">
-        <v>227.41596785975</v>
+        <v>227.41597222222</v>
       </c>
       <c r="O463" t="n">
-        <v>53442.75244704125</v>
+        <v>53442.7534722217</v>
       </c>
       <c r="P463" t="n">
         <v>1200</v>
@@ -22565,10 +22565,10 @@
         <v>14</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.7426315789</v>
+        <v>7046.7433333333</v>
       </c>
       <c r="O482" t="n">
-        <v>98654.3968421046</v>
+        <v>98654.4066666662</v>
       </c>
       <c r="P482" t="n">
         <v>22900</v>
@@ -22611,10 +22611,10 @@
         <v>21</v>
       </c>
       <c r="N483" t="n">
-        <v>10009.170869565</v>
+        <v>10009.170909091</v>
       </c>
       <c r="O483" t="n">
-        <v>210192.588260865</v>
+        <v>210192.589090911</v>
       </c>
       <c r="P483" t="n">
         <v>22900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2367,10 +2367,10 @@
         <v>122</v>
       </c>
       <c r="N47" t="n">
-        <v>430.87006896552</v>
+        <v>427.91889655172</v>
       </c>
       <c r="O47" t="n">
-        <v>52566.14841379344</v>
+        <v>52206.10537930984</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
@@ -2459,10 +2459,10 @@
         <v>117</v>
       </c>
       <c r="N49" t="n">
-        <v>542.47912878788</v>
+        <v>538.40041666667</v>
       </c>
       <c r="O49" t="n">
-        <v>63470.05806818196</v>
+        <v>62992.84875000039</v>
       </c>
       <c r="P49" t="n">
         <v>6800</v>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>165</v>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>1438</v>
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
         <v>53</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
         <v>103</v>
@@ -6920,13 +6920,13 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
         <v>76</v>
@@ -9890,10 +9890,10 @@
         <v>44</v>
       </c>
       <c r="N214" t="n">
-        <v>5370.4862978723</v>
+        <v>5347.73</v>
       </c>
       <c r="O214" t="n">
-        <v>236301.3971063812</v>
+        <v>235300.12</v>
       </c>
       <c r="P214" t="n">
         <v>9500</v>
@@ -11481,10 +11481,10 @@
         <v>65</v>
       </c>
       <c r="N248" t="n">
-        <v>2639.7037333333</v>
+        <v>2571.14</v>
       </c>
       <c r="O248" t="n">
-        <v>171580.7426666645</v>
+        <v>167124.1</v>
       </c>
       <c r="P248" t="n">
         <v>6900</v>
@@ -11890,13 +11890,13 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>13440</v>
+        <v>13152</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
         <v>13152</v>
@@ -15263,10 +15263,10 @@
         <v>74</v>
       </c>
       <c r="N327" t="n">
-        <v>4205.0243197279</v>
+        <v>4190.77</v>
       </c>
       <c r="O327" t="n">
-        <v>311171.7996598646</v>
+        <v>310116.98</v>
       </c>
       <c r="P327" t="n">
         <v>5900</v>
@@ -15312,10 +15312,10 @@
         <v>264</v>
       </c>
       <c r="N328" t="n">
-        <v>3508.0033609467</v>
+        <v>3499.72</v>
       </c>
       <c r="O328" t="n">
-        <v>926112.8872899289</v>
+        <v>923926.08</v>
       </c>
       <c r="P328" t="n">
         <v>6900</v>
@@ -17427,10 +17427,10 @@
         <v>50</v>
       </c>
       <c r="N372" t="n">
-        <v>1942.8822431866</v>
+        <v>1934.77</v>
       </c>
       <c r="O372" t="n">
-        <v>97144.11215932999</v>
+        <v>96738.5</v>
       </c>
       <c r="P372" t="n">
         <v>8900</v>
@@ -17914,10 +17914,10 @@
         <v>526</v>
       </c>
       <c r="N382" t="n">
-        <v>642.25894029851</v>
+        <v>641.78</v>
       </c>
       <c r="O382" t="n">
-        <v>337828.2025970162</v>
+        <v>337576.28</v>
       </c>
       <c r="P382" t="n">
         <v>2500</v>
@@ -18618,13 +18618,13 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M397" t="n">
         <v>30</v>
@@ -20889,10 +20889,10 @@
         <v>250</v>
       </c>
       <c r="N446" t="n">
-        <v>1242.6076530612</v>
+        <v>1236.3</v>
       </c>
       <c r="O446" t="n">
-        <v>310651.9132653</v>
+        <v>309075</v>
       </c>
       <c r="P446" t="n">
         <v>2300</v>
@@ -21393,13 +21393,13 @@
         </is>
       </c>
       <c r="J457" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="K457" t="n">
         <v>0</v>
       </c>
       <c r="L457" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M457" t="n">
         <v>152</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3043052838</v>
+        <v>1811.3044243338</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.549902168</v>
+        <v>652069.592760168</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1084,10 +1084,10 @@
         <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O17" t="n">
-        <v>90317.25391482911</v>
+        <v>90317.2538469446</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -2367,10 +2367,10 @@
         <v>122</v>
       </c>
       <c r="N47" t="n">
-        <v>427.91889655172</v>
+        <v>427.91888111888</v>
       </c>
       <c r="O47" t="n">
-        <v>52206.10537930984</v>
+        <v>52206.10349650336</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
@@ -3344,22 +3344,22 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M69" t="n">
-        <v>432</v>
+        <v>144</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0541801698</v>
+        <v>1098.0548595108</v>
       </c>
       <c r="O69" t="n">
-        <v>474359.4058333536</v>
+        <v>158119.8997695552</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
       </c>
       <c r="Q69" t="n">
-        <v>648000</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="70">
@@ -3670,10 +3670,10 @@
         <v>1438</v>
       </c>
       <c r="N76" t="n">
-        <v>5216.8959762435</v>
+        <v>5216.8959678619</v>
       </c>
       <c r="O76" t="n">
-        <v>7501896.413838153</v>
+        <v>7501896.401785413</v>
       </c>
       <c r="P76" t="n">
         <v>8500</v>
@@ -3716,10 +3716,10 @@
         <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.5693416928</v>
+        <v>2033.5682467532</v>
       </c>
       <c r="O77" t="n">
-        <v>97611.3284012544</v>
+        <v>97611.2758441536</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
@@ -3808,10 +3808,10 @@
         <v>3410</v>
       </c>
       <c r="N79" t="n">
-        <v>3158.8608143857</v>
+        <v>3158.8608147003</v>
       </c>
       <c r="O79" t="n">
-        <v>10771715.37705524</v>
+        <v>10771715.37812802</v>
       </c>
       <c r="P79" t="n">
         <v>5600</v>
@@ -3949,10 +3949,10 @@
         <v>514</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.8234624043</v>
+        <v>2694.8234565119</v>
       </c>
       <c r="O82" t="n">
-        <v>1385139.25967581</v>
+        <v>1385139.256647117</v>
       </c>
       <c r="P82" t="n">
         <v>4900</v>
@@ -4280,10 +4280,10 @@
         <v>332</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.2541747573</v>
+        <v>3594.25414277</v>
       </c>
       <c r="O89" t="n">
-        <v>1193292.386019424</v>
+        <v>1193292.37539964</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4326,10 +4326,10 @@
         <v>282</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378864577</v>
+        <v>14822.378863905</v>
       </c>
       <c r="O90" t="n">
-        <v>4179910.839810714</v>
+        <v>4179910.83962121</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -4637,10 +4637,10 @@
         <v>317</v>
       </c>
       <c r="N97" t="n">
-        <v>4372.2107869318</v>
+        <v>4372.2107876031</v>
       </c>
       <c r="O97" t="n">
-        <v>1385990.819457381</v>
+        <v>1385990.819670183</v>
       </c>
       <c r="P97" t="n">
         <v>7500</v>
@@ -4770,10 +4770,10 @@
         <v>244</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.5675881262</v>
+        <v>1592.567520267</v>
       </c>
       <c r="O100" t="n">
-        <v>388586.4915027928</v>
+        <v>388586.474945148</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
@@ -5409,10 +5409,10 @@
         <v>636</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9231064431</v>
+        <v>1630.923147125</v>
       </c>
       <c r="O114" t="n">
-        <v>1037267.095697812</v>
+        <v>1037267.1215715</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>23</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.1930735465</v>
+        <v>1550.1931350849</v>
       </c>
       <c r="O115" t="n">
-        <v>35654.4406915695</v>
+        <v>35654.4421069527</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
@@ -5547,10 +5547,10 @@
         <v>171</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5102087442</v>
+        <v>2403.5103430475</v>
       </c>
       <c r="O117" t="n">
-        <v>411000.2456952582</v>
+        <v>411000.2686611225</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5455211726</v>
+        <v>2521.5446987952</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.5491856656</v>
+        <v>141206.5031325312</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -5683,10 +5683,10 @@
         <v>50</v>
       </c>
       <c r="N120" t="n">
-        <v>1830.7563675214</v>
+        <v>1830.7563519313</v>
       </c>
       <c r="O120" t="n">
-        <v>91537.81837607</v>
+        <v>91537.817596565</v>
       </c>
       <c r="P120" t="n">
         <v>3150</v>
@@ -6381,10 +6381,10 @@
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>2029.8736549708</v>
+        <v>2029.8736782737</v>
       </c>
       <c r="O136" t="n">
-        <v>4059.7473099416</v>
+        <v>4059.7473565474</v>
       </c>
       <c r="P136" t="n">
         <v>3600</v>
@@ -6504,10 +6504,10 @@
         <v>402</v>
       </c>
       <c r="N139" t="n">
-        <v>880.32933581916</v>
+        <v>880.32935107376</v>
       </c>
       <c r="O139" t="n">
-        <v>353892.3929993023</v>
+        <v>353892.3991316515</v>
       </c>
       <c r="P139" t="n">
         <v>1200</v>
@@ -6755,10 +6755,10 @@
         <v>4</v>
       </c>
       <c r="N145" t="n">
-        <v>11562.038530184</v>
+        <v>11562.038526316</v>
       </c>
       <c r="O145" t="n">
-        <v>46248.154120736</v>
+        <v>46248.154105264</v>
       </c>
       <c r="P145" t="n">
         <v>18500</v>
@@ -7224,10 +7224,10 @@
         <v>6</v>
       </c>
       <c r="N156" t="n">
-        <v>11662.4</v>
+        <v>12042.695652174</v>
       </c>
       <c r="O156" t="n">
-        <v>69974.39999999999</v>
+        <v>72256.173913044</v>
       </c>
       <c r="P156" t="n">
         <v>19900</v>
@@ -7270,10 +7270,10 @@
         <v>5</v>
       </c>
       <c r="N157" t="n">
-        <v>7969.9501649175</v>
+        <v>7987.9139894816</v>
       </c>
       <c r="O157" t="n">
-        <v>39849.7508245875</v>
+        <v>39939.569947408</v>
       </c>
       <c r="P157" t="n">
         <v>12900</v>
@@ -7994,10 +7994,10 @@
         <v>112</v>
       </c>
       <c r="N173" t="n">
-        <v>5218.1705022831</v>
+        <v>5218.1705134189</v>
       </c>
       <c r="O173" t="n">
-        <v>584435.0962557072</v>
+        <v>584435.0975029168</v>
       </c>
       <c r="P173" t="n">
         <v>8500</v>
@@ -8040,10 +8040,10 @@
         <v>112</v>
       </c>
       <c r="N174" t="n">
-        <v>1595.0094808743</v>
+        <v>1595.0094571429</v>
       </c>
       <c r="O174" t="n">
-        <v>178641.0618579216</v>
+        <v>178641.0592000048</v>
       </c>
       <c r="P174" t="n">
         <v>2600</v>
@@ -8644,22 +8644,22 @@
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
         <v>41112.04</v>
       </c>
       <c r="O187" t="n">
-        <v>82224.08</v>
+        <v>0</v>
       </c>
       <c r="P187" t="n">
         <v>10000</v>
       </c>
       <c r="Q187" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -9340,10 +9340,10 @@
         <v>552</v>
       </c>
       <c r="N202" t="n">
-        <v>1516.0388129219</v>
+        <v>1517.7951815022</v>
       </c>
       <c r="O202" t="n">
-        <v>836853.4247328888</v>
+        <v>837822.9401892144</v>
       </c>
       <c r="P202" t="n">
         <v>2300</v>
@@ -9386,10 +9386,10 @@
         <v>432</v>
       </c>
       <c r="N203" t="n">
-        <v>2458.5134204724</v>
+        <v>2458.5134059343</v>
       </c>
       <c r="O203" t="n">
-        <v>1062077.797644077</v>
+        <v>1062077.791363618</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9432,10 +9432,10 @@
         <v>144</v>
       </c>
       <c r="N204" t="n">
-        <v>1771.0912628399</v>
+        <v>1771.0911342735</v>
       </c>
       <c r="O204" t="n">
-        <v>255037.1418489456</v>
+        <v>255037.123335384</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.384205911</v>
+        <v>2079.3842021449</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.2094186401</v>
+        <v>499052.208514776</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>266</v>
       </c>
       <c r="N206" t="n">
-        <v>1803.0150073855</v>
+        <v>1803.0151441578</v>
       </c>
       <c r="O206" t="n">
-        <v>479601.991964543</v>
+        <v>479602.0283459748</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9570,10 +9570,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>3306.5954372624</v>
+        <v>3306.5953548387</v>
       </c>
       <c r="O207" t="n">
-        <v>158716.5809885952</v>
+        <v>158716.5770322576</v>
       </c>
       <c r="P207" t="n">
         <v>4900</v>
@@ -9616,10 +9616,10 @@
         <v>264</v>
       </c>
       <c r="N208" t="n">
-        <v>2122.1640959855</v>
+        <v>2126.0638621746</v>
       </c>
       <c r="O208" t="n">
-        <v>560251.321340172</v>
+        <v>561280.8596140945</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7899091941</v>
+        <v>2108.7899828473</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.7469239504</v>
+        <v>303665.7575300112</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.083871734</v>
+        <v>2059.7554464286</v>
       </c>
       <c r="O210" t="n">
-        <v>592152.155059392</v>
+        <v>593209.5685714368</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>3224.5680666967</v>
+        <v>3224.5682755432</v>
       </c>
       <c r="O211" t="n">
-        <v>696506.7024064872</v>
+        <v>696506.7475173312</v>
       </c>
       <c r="P211" t="n">
         <v>4500</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.9312964128</v>
+        <v>1657.5320592975</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.2133668864</v>
+        <v>477369.23307768</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9846,10 +9846,10 @@
         <v>97</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.2752659892</v>
+        <v>1592.2754925187</v>
       </c>
       <c r="O213" t="n">
-        <v>154450.7008009524</v>
+        <v>154450.7227743139</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9890,10 +9890,10 @@
         <v>44</v>
       </c>
       <c r="N214" t="n">
-        <v>5347.73</v>
+        <v>5393.6332618026</v>
       </c>
       <c r="O214" t="n">
-        <v>235300.12</v>
+        <v>237319.8635193144</v>
       </c>
       <c r="P214" t="n">
         <v>9500</v>
@@ -9936,10 +9936,10 @@
         <v>36</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9257410562</v>
+        <v>2311.9248916968</v>
       </c>
       <c r="O215" t="n">
-        <v>83229.32667802319</v>
+        <v>83229.29610108479</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -9982,10 +9982,10 @@
         <v>12</v>
       </c>
       <c r="N216" t="n">
-        <v>1906.1864705882</v>
+        <v>1906.1862686567</v>
       </c>
       <c r="O216" t="n">
-        <v>22874.2376470584</v>
+        <v>22874.2352238804</v>
       </c>
       <c r="P216" t="n">
         <v>2900</v>
@@ -10028,10 +10028,10 @@
         <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>2546.9851535836</v>
+        <v>2546.9851286449</v>
       </c>
       <c r="O217" t="n">
-        <v>122255.2873720128</v>
+        <v>122255.2861749552</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
@@ -10074,10 +10074,10 @@
         <v>600</v>
       </c>
       <c r="N218" t="n">
-        <v>1259.2744247206</v>
+        <v>1259.2744276316</v>
       </c>
       <c r="O218" t="n">
-        <v>755564.6548323601</v>
+        <v>755564.65657896</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -10115,10 +10115,10 @@
         <v>120</v>
       </c>
       <c r="N219" t="n">
-        <v>2842.2737735849</v>
+        <v>2851.2399369085</v>
       </c>
       <c r="O219" t="n">
-        <v>341072.852830188</v>
+        <v>342148.79242902</v>
       </c>
       <c r="P219" t="n">
         <v>4900</v>
@@ -10207,10 +10207,10 @@
         <v>8590</v>
       </c>
       <c r="N221" t="n">
-        <v>1801</v>
+        <v>1803.2544202785</v>
       </c>
       <c r="O221" t="n">
-        <v>15470590</v>
+        <v>15489955.47019232</v>
       </c>
       <c r="P221" t="n">
         <v>2900</v>
@@ -10251,10 +10251,10 @@
         <v>192</v>
       </c>
       <c r="N222" t="n">
-        <v>692.15206356312</v>
+        <v>692.15208975521</v>
       </c>
       <c r="O222" t="n">
-        <v>132893.196204119</v>
+        <v>132893.2012330003</v>
       </c>
       <c r="P222" t="n">
         <v>1200</v>
@@ -10539,10 +10539,10 @@
         <v>61</v>
       </c>
       <c r="N228" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O228" t="n">
-        <v>545668.1799999999</v>
+        <v>545827.3829700977</v>
       </c>
       <c r="P228" t="n">
         <v>14900</v>
@@ -10726,10 +10726,10 @@
         <v>324</v>
       </c>
       <c r="N232" t="n">
-        <v>1530.4499204138</v>
+        <v>1530.4499206034</v>
       </c>
       <c r="O232" t="n">
-        <v>495865.7742140712</v>
+        <v>495865.7742755016</v>
       </c>
       <c r="P232" t="n">
         <v>2600</v>
@@ -10956,10 +10956,10 @@
         <v>37</v>
       </c>
       <c r="N237" t="n">
-        <v>6898.4</v>
+        <v>6979.7970501475</v>
       </c>
       <c r="O237" t="n">
-        <v>255240.8</v>
+        <v>258252.4908554575</v>
       </c>
       <c r="P237" t="n">
         <v>12900</v>
@@ -11097,10 +11097,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>1690.8700089286</v>
+        <v>1690.8700089526</v>
       </c>
       <c r="O240" t="n">
-        <v>1690.8700089286</v>
+        <v>1690.8700089526</v>
       </c>
       <c r="P240" t="n">
         <v>3000</v>
@@ -11435,10 +11435,10 @@
         <v>2280</v>
       </c>
       <c r="N247" t="n">
-        <v>517.2878865955601</v>
+        <v>523.15541944326</v>
       </c>
       <c r="O247" t="n">
-        <v>1179416.381437877</v>
+        <v>1192794.356330633</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11674,10 +11674,10 @@
         <v>504</v>
       </c>
       <c r="N252" t="n">
-        <v>3110.8429819337</v>
+        <v>3110.8429525518</v>
       </c>
       <c r="O252" t="n">
-        <v>1567864.862894585</v>
+        <v>1567864.848086107</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
@@ -11902,10 +11902,10 @@
         <v>13152</v>
       </c>
       <c r="N257" t="n">
-        <v>703.79538564105</v>
+        <v>703.79534416571</v>
       </c>
       <c r="O257" t="n">
-        <v>9256316.911951089</v>
+        <v>9256316.366467418</v>
       </c>
       <c r="P257" t="n">
         <v>900</v>
@@ -15312,10 +15312,10 @@
         <v>264</v>
       </c>
       <c r="N328" t="n">
-        <v>3499.72</v>
+        <v>3516.3655172414</v>
       </c>
       <c r="O328" t="n">
-        <v>923926.08</v>
+        <v>928320.4965517296</v>
       </c>
       <c r="P328" t="n">
         <v>6900</v>
@@ -15361,10 +15361,10 @@
         <v>18</v>
       </c>
       <c r="N329" t="n">
-        <v>5347.88</v>
+        <v>5377.3043741403</v>
       </c>
       <c r="O329" t="n">
-        <v>96261.84</v>
+        <v>96791.4787345254</v>
       </c>
       <c r="P329" t="n">
         <v>7900</v>
@@ -15410,10 +15410,10 @@
         <v>82</v>
       </c>
       <c r="N330" t="n">
-        <v>4578.04</v>
+        <v>4597.9229098806</v>
       </c>
       <c r="O330" t="n">
-        <v>375399.28</v>
+        <v>377029.6786102092</v>
       </c>
       <c r="P330" t="n">
         <v>7500</v>
@@ -15941,10 +15941,10 @@
         <v>1</v>
       </c>
       <c r="N341" t="n">
-        <v>10737.526666667</v>
+        <v>11369.145882353</v>
       </c>
       <c r="O341" t="n">
-        <v>10737.526666667</v>
+        <v>11369.145882353</v>
       </c>
       <c r="P341" t="n">
         <v>18900</v>
@@ -16848,10 +16848,10 @@
         <v>3</v>
       </c>
       <c r="N360" t="n">
-        <v>6669.55</v>
+        <v>9170.63125</v>
       </c>
       <c r="O360" t="n">
-        <v>20008.65</v>
+        <v>27511.89375</v>
       </c>
       <c r="P360" t="n">
         <v>25500</v>
@@ -18306,10 +18306,10 @@
         <v>726</v>
       </c>
       <c r="N390" t="n">
-        <v>465.87093087558</v>
+        <v>465.8709360519</v>
       </c>
       <c r="O390" t="n">
-        <v>338222.295815671</v>
+        <v>338222.2995736794</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
@@ -18445,10 +18445,10 @@
         <v>271</v>
       </c>
       <c r="N393" t="n">
-        <v>2000</v>
+        <v>2075.1879699248</v>
       </c>
       <c r="O393" t="n">
-        <v>542000</v>
+        <v>562375.9398496208</v>
       </c>
       <c r="P393" t="n">
         <v>4100</v>
@@ -19565,10 +19565,10 @@
         <v>1827</v>
       </c>
       <c r="N417" t="n">
-        <v>220.00820587826</v>
+        <v>220.00803927108</v>
       </c>
       <c r="O417" t="n">
-        <v>401954.992139581</v>
+        <v>401954.6877482632</v>
       </c>
       <c r="P417" t="n">
         <v>260</v>
@@ -20838,10 +20838,10 @@
         <v>61</v>
       </c>
       <c r="N445" t="n">
-        <v>1129.14</v>
+        <v>1151.172</v>
       </c>
       <c r="O445" t="n">
-        <v>68877.54000000001</v>
+        <v>70221.492</v>
       </c>
       <c r="P445" t="n">
         <v>6900</v>
@@ -21599,10 +21599,10 @@
         <v>42</v>
       </c>
       <c r="N461" t="n">
-        <v>2432.1341071429</v>
+        <v>2432.1345098039</v>
       </c>
       <c r="O461" t="n">
-        <v>102149.6325000018</v>
+        <v>102149.6494117638</v>
       </c>
       <c r="P461" t="n">
         <v>4500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3044829343</v>
+        <v>1811.3047800109</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.613856348</v>
+        <v>652069.720803924</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="O18" t="n">
-        <v>4826.0021231422</v>
+        <v>4826.0021253986</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -1162,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2474.7042043551</v>
+        <v>2474.7041652614</v>
       </c>
       <c r="O19" t="n">
-        <v>9898.8168174204</v>
+        <v>9898.816661045599</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
@@ -1803,10 +1803,10 @@
         <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>28751.742258065</v>
+        <v>28751.742333333</v>
       </c>
       <c r="O34" t="n">
-        <v>115006.96903226</v>
+        <v>115006.969333332</v>
       </c>
       <c r="P34" t="n">
         <v>34800</v>
@@ -3088,10 +3088,10 @@
         <v>92</v>
       </c>
       <c r="N63" t="n">
-        <v>732.63413793103</v>
+        <v>732.63415224913</v>
       </c>
       <c r="O63" t="n">
-        <v>67402.34068965475</v>
+        <v>67402.34200691996</v>
       </c>
       <c r="P63" t="n">
         <v>6200</v>
@@ -3178,10 +3178,10 @@
         <v>33</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O65" t="n">
-        <v>162931.2353186826</v>
+        <v>162931.2353225799</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3350,10 +3350,10 @@
         <v>144</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0555939754</v>
+        <v>1098.055952691</v>
       </c>
       <c r="O69" t="n">
-        <v>158120.0055324576</v>
+        <v>158120.057187504</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3624,10 +3624,10 @@
         <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2560112135</v>
+        <v>2582.2559895309</v>
       </c>
       <c r="O75" t="n">
-        <v>2509952.842899522</v>
+        <v>2509952.821824035</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3670,10 +3670,10 @@
         <v>1438</v>
       </c>
       <c r="N76" t="n">
-        <v>5216.8959654608</v>
+        <v>5216.8959618537</v>
       </c>
       <c r="O76" t="n">
-        <v>7501896.39833263</v>
+        <v>7501896.393145621</v>
       </c>
       <c r="P76" t="n">
         <v>8500</v>
@@ -3716,10 +3716,10 @@
         <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.5670707071</v>
+        <v>2033.5662758621</v>
       </c>
       <c r="O77" t="n">
-        <v>97611.21939394079</v>
+        <v>97611.18124138079</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
@@ -3756,22 +3756,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N78" t="n">
         <v>5503.85</v>
       </c>
       <c r="O78" t="n">
-        <v>99069.3</v>
+        <v>93565.45000000001</v>
       </c>
       <c r="P78" t="n">
         <v>9500</v>
       </c>
       <c r="Q78" t="n">
-        <v>171000</v>
+        <v>161500</v>
       </c>
     </row>
     <row r="79">
@@ -3808,10 +3808,10 @@
         <v>3410</v>
       </c>
       <c r="N79" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O79" t="n">
-        <v>10771715.37839639</v>
+        <v>10771715.38067973</v>
       </c>
       <c r="P79" t="n">
         <v>5600</v>
@@ -3903,10 +3903,10 @@
         <v>60</v>
       </c>
       <c r="N81" t="n">
-        <v>3230.0677414075</v>
+        <v>3230.0677302632</v>
       </c>
       <c r="O81" t="n">
-        <v>193804.06448445</v>
+        <v>193804.063815792</v>
       </c>
       <c r="P81" t="n">
         <v>6200</v>
@@ -3949,10 +3949,10 @@
         <v>514</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.8234565119</v>
+        <v>2694.8234059946</v>
       </c>
       <c r="O82" t="n">
-        <v>1385139.256647117</v>
+        <v>1385139.230681224</v>
       </c>
       <c r="P82" t="n">
         <v>4900</v>
@@ -4280,10 +4280,10 @@
         <v>332</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O89" t="n">
-        <v>1193292.374212441</v>
+        <v>1193292.369449204</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4326,10 +4326,10 @@
         <v>282</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O90" t="n">
-        <v>4179910.839241638</v>
+        <v>4179910.83905157</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -4770,10 +4770,10 @@
         <v>244</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.5674522293</v>
+        <v>1592.5674</v>
       </c>
       <c r="O100" t="n">
-        <v>388586.4583439492</v>
+        <v>388586.4456</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
@@ -5409,10 +5409,10 @@
         <v>636</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O114" t="n">
-        <v>1037267.128971042</v>
+        <v>1037267.138089565</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>23</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O115" t="n">
-        <v>35654.4425852538</v>
+        <v>35654.443226664</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
@@ -5501,10 +5501,10 @@
         <v>168</v>
       </c>
       <c r="N116" t="n">
-        <v>1579.391025</v>
+        <v>1579.3909343434</v>
       </c>
       <c r="O116" t="n">
-        <v>265337.6922</v>
+        <v>265337.6769696912</v>
       </c>
       <c r="P116" t="n">
         <v>2900</v>
@@ -5547,10 +5547,10 @@
         <v>171</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5103724115</v>
+        <v>2403.5104597508</v>
       </c>
       <c r="O117" t="n">
-        <v>411000.2736823665</v>
+        <v>411000.2886173868</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5439240506</v>
+        <v>2521.5426705653</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.4597468336</v>
+        <v>141206.3895516568</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -6294,10 +6294,10 @@
         <v>103</v>
       </c>
       <c r="N134" t="n">
-        <v>5449.53048</v>
+        <v>5449.530483871</v>
       </c>
       <c r="O134" t="n">
-        <v>561301.6394400001</v>
+        <v>561301.639838713</v>
       </c>
       <c r="P134" t="n">
         <v>6200</v>
@@ -6381,10 +6381,10 @@
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>2029.8737073653</v>
+        <v>2029.8737091988</v>
       </c>
       <c r="O136" t="n">
-        <v>4059.7474147306</v>
+        <v>4059.7474183976</v>
       </c>
       <c r="P136" t="n">
         <v>3600</v>
@@ -6504,10 +6504,10 @@
         <v>402</v>
       </c>
       <c r="N139" t="n">
-        <v>880.3293685687599</v>
+        <v>880.32937295274</v>
       </c>
       <c r="O139" t="n">
-        <v>353892.4061646415</v>
+        <v>353892.4079270015</v>
       </c>
       <c r="P139" t="n">
         <v>1200</v>
@@ -7142,10 +7142,10 @@
         <v>21</v>
       </c>
       <c r="N154" t="n">
-        <v>1508.5872340426</v>
+        <v>1508.5871111111</v>
       </c>
       <c r="O154" t="n">
-        <v>31680.3319148946</v>
+        <v>31680.3293333331</v>
       </c>
       <c r="P154" t="n">
         <v>3600</v>
@@ -7183,10 +7183,10 @@
         <v>26</v>
       </c>
       <c r="N155" t="n">
-        <v>2568.8355</v>
+        <v>2568.8354697987</v>
       </c>
       <c r="O155" t="n">
-        <v>66789.723</v>
+        <v>66789.72221476621</v>
       </c>
       <c r="P155" t="n">
         <v>4500</v>
@@ -7758,22 +7758,22 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M168" t="n">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="N168" t="n">
         <v>10911.29</v>
       </c>
       <c r="O168" t="n">
-        <v>2465951.54</v>
+        <v>2302282.19</v>
       </c>
       <c r="P168" t="n">
         <v>17400</v>
       </c>
       <c r="Q168" t="n">
-        <v>3932400</v>
+        <v>3671400</v>
       </c>
     </row>
     <row r="169">
@@ -7994,10 +7994,10 @@
         <v>112</v>
       </c>
       <c r="N173" t="n">
-        <v>5218.1705164319</v>
+        <v>5218.170521327</v>
       </c>
       <c r="O173" t="n">
-        <v>584435.0978403728</v>
+        <v>584435.0983886239</v>
       </c>
       <c r="P173" t="n">
         <v>8500</v>
@@ -8040,10 +8040,10 @@
         <v>92</v>
       </c>
       <c r="N174" t="n">
-        <v>1595.0094492754</v>
+        <v>1595.0094476744</v>
       </c>
       <c r="O174" t="n">
-        <v>146740.8693333368</v>
+        <v>146740.8691860448</v>
       </c>
       <c r="P174" t="n">
         <v>2600</v>
@@ -9340,10 +9340,10 @@
         <v>552</v>
       </c>
       <c r="N202" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O202" t="n">
-        <v>836853.4237203001</v>
+        <v>836853.4232763264</v>
       </c>
       <c r="P202" t="n">
         <v>2300</v>
@@ -9386,10 +9386,10 @@
         <v>432</v>
       </c>
       <c r="N203" t="n">
-        <v>2458.5133829585</v>
+        <v>2458.5133724619</v>
       </c>
       <c r="O203" t="n">
-        <v>1062077.781438072</v>
+        <v>1062077.776903541</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9432,10 +9432,10 @@
         <v>144</v>
       </c>
       <c r="N204" t="n">
-        <v>1771.0911342735</v>
+        <v>1771.0911179361</v>
       </c>
       <c r="O204" t="n">
-        <v>255037.123335384</v>
+        <v>255037.1209827984</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.3841889251</v>
+        <v>2079.3841813438</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.205342024</v>
+        <v>499052.2035225119</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>266</v>
       </c>
       <c r="N206" t="n">
-        <v>1803.0151566778</v>
+        <v>1803.0151724138</v>
       </c>
       <c r="O206" t="n">
-        <v>479602.0316762948</v>
+        <v>479602.0358620708</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9616,10 +9616,10 @@
         <v>264</v>
       </c>
       <c r="N208" t="n">
-        <v>2122.1640073529</v>
+        <v>2122.1640036787</v>
       </c>
       <c r="O208" t="n">
-        <v>560251.2979411656</v>
+        <v>560251.2969711768</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7899885584</v>
+        <v>2108.7900518135</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.7583524096</v>
+        <v>303665.767461144</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.0838222089</v>
+        <v>2056.0837188071</v>
       </c>
       <c r="O210" t="n">
-        <v>592152.1407961632</v>
+        <v>592152.1110164449</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9754,10 +9754,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>3224.568287037</v>
+        <v>3224.5683024119</v>
       </c>
       <c r="O211" t="n">
-        <v>696506.7499999921</v>
+        <v>696506.7533209703</v>
       </c>
       <c r="P211" t="n">
         <v>4500</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.931057226</v>
+        <v>1655.9310223953</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.144481088</v>
+        <v>476908.1344498464</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9846,10 +9846,10 @@
         <v>97</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.2755269762</v>
+        <v>1592.2756948933</v>
       </c>
       <c r="O213" t="n">
-        <v>154450.7261166914</v>
+        <v>154450.7424046501</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9936,10 +9936,10 @@
         <v>36</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9247818182</v>
+        <v>2311.9246983547</v>
       </c>
       <c r="O215" t="n">
-        <v>83229.2921454552</v>
+        <v>83229.28914076919</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -10028,10 +10028,10 @@
         <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>2546.9850949914</v>
+        <v>2546.985</v>
       </c>
       <c r="O217" t="n">
-        <v>122255.2845595872</v>
+        <v>122255.28</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
@@ -10074,10 +10074,10 @@
         <v>600</v>
       </c>
       <c r="N218" t="n">
-        <v>1259.2744422442</v>
+        <v>1259.2744638514</v>
       </c>
       <c r="O218" t="n">
-        <v>755564.6653465199</v>
+        <v>755564.67831084</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -10251,10 +10251,10 @@
         <v>192</v>
       </c>
       <c r="N222" t="n">
-        <v>692.15208975521</v>
+        <v>692.15209736124</v>
       </c>
       <c r="O222" t="n">
-        <v>132893.2012330003</v>
+        <v>132893.2026933581</v>
       </c>
       <c r="P222" t="n">
         <v>1200</v>
@@ -11097,10 +11097,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>1690.8700089526</v>
+        <v>1690.8700089606</v>
       </c>
       <c r="O240" t="n">
-        <v>1690.8700089526</v>
+        <v>1690.8700089606</v>
       </c>
       <c r="P240" t="n">
         <v>3000</v>
@@ -11391,10 +11391,10 @@
         <v>2280</v>
       </c>
       <c r="N246" t="n">
-        <v>517.28815469086</v>
+        <v>517.28824762181</v>
       </c>
       <c r="O246" t="n">
-        <v>1179416.992695161</v>
+        <v>1179417.204577727</v>
       </c>
       <c r="P246" t="n">
         <v>900</v>
@@ -11532,10 +11532,10 @@
         <v>59</v>
       </c>
       <c r="N249" t="n">
-        <v>3259.1342205323</v>
+        <v>3259.1342528736</v>
       </c>
       <c r="O249" t="n">
-        <v>192288.9190114057</v>
+        <v>192288.9209195424</v>
       </c>
       <c r="P249" t="n">
         <v>3600</v>
@@ -11630,10 +11630,10 @@
         <v>504</v>
       </c>
       <c r="N251" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O251" t="n">
-        <v>1567864.756564394</v>
+        <v>1567864.717403897</v>
       </c>
       <c r="P251" t="n">
         <v>4500</v>
@@ -11858,10 +11858,10 @@
         <v>13152</v>
       </c>
       <c r="N256" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O256" t="n">
-        <v>9256316.209115179</v>
+        <v>9256316.050952122</v>
       </c>
       <c r="P256" t="n">
         <v>900</v>
@@ -12137,10 +12137,10 @@
         <v>59</v>
       </c>
       <c r="N262" t="n">
-        <v>2501.3852212389</v>
+        <v>2501.3851351351</v>
       </c>
       <c r="O262" t="n">
-        <v>147581.7280530951</v>
+        <v>147581.7229729709</v>
       </c>
       <c r="P262" t="n">
         <v>4100</v>
@@ -14977,10 +14977,10 @@
         <v>60</v>
       </c>
       <c r="N321" t="n">
-        <v>3067.0905389222</v>
+        <v>3067.0905454545</v>
       </c>
       <c r="O321" t="n">
-        <v>184025.432335332</v>
+        <v>184025.43272727</v>
       </c>
       <c r="P321" t="n">
         <v>7200</v>
@@ -15897,10 +15897,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>10737.526470588</v>
+        <v>10737.5264</v>
       </c>
       <c r="O340" t="n">
-        <v>10737.526470588</v>
+        <v>10737.5264</v>
       </c>
       <c r="P340" t="n">
         <v>18900</v>
@@ -17481,10 +17481,10 @@
         <v>8</v>
       </c>
       <c r="N373" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O373" t="n">
-        <v>56375.518639456</v>
+        <v>56375.5186391664</v>
       </c>
       <c r="P373" t="n">
         <v>9900</v>
@@ -18213,10 +18213,10 @@
         <v>984</v>
       </c>
       <c r="N388" t="n">
-        <v>430.60997670355</v>
+        <v>430.60997668998</v>
       </c>
       <c r="O388" t="n">
-        <v>423720.2170762932</v>
+        <v>423720.2170629403</v>
       </c>
       <c r="P388" t="n">
         <v>2200</v>
@@ -18262,10 +18262,10 @@
         <v>726</v>
       </c>
       <c r="N389" t="n">
-        <v>465.8709360519</v>
+        <v>465.87093953488</v>
       </c>
       <c r="O389" t="n">
-        <v>338222.2995736794</v>
+        <v>338222.3021023229</v>
       </c>
       <c r="P389" t="n">
         <v>2500</v>
@@ -18877,10 +18877,10 @@
         <v>63</v>
       </c>
       <c r="N402" t="n">
-        <v>1757.3205360825</v>
+        <v>1757.3205416667</v>
       </c>
       <c r="O402" t="n">
-        <v>110711.1937731975</v>
+        <v>110711.1941250021</v>
       </c>
       <c r="P402" t="n">
         <v>2000</v>
@@ -19521,10 +19521,10 @@
         <v>1827</v>
       </c>
       <c r="N416" t="n">
-        <v>220.00769152493</v>
+        <v>220.00713026296</v>
       </c>
       <c r="O416" t="n">
-        <v>401954.0524160471</v>
+        <v>401953.0269904279</v>
       </c>
       <c r="P416" t="n">
         <v>260</v>
@@ -20281,28 +20281,28 @@
         </is>
       </c>
       <c r="J433" t="n">
+        <v>144</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="n">
+        <v>144</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" t="n">
         <v>7480</v>
       </c>
-      <c r="K433" t="n">
-        <v>0</v>
-      </c>
-      <c r="L433" t="n">
-        <v>0</v>
-      </c>
-      <c r="M433" t="n">
-        <v>7480</v>
-      </c>
-      <c r="N433" t="n">
-        <v>788.1365841161401</v>
-      </c>
       <c r="O433" t="n">
-        <v>5895261.649188728</v>
+        <v>0</v>
       </c>
       <c r="P433" t="n">
         <v>9500</v>
       </c>
       <c r="Q433" t="n">
-        <v>71060000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -20333,22 +20333,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M434" t="n">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="N434" t="n">
         <v>9240</v>
       </c>
       <c r="O434" t="n">
-        <v>6652800</v>
+        <v>6560400</v>
       </c>
       <c r="P434" t="n">
         <v>11500</v>
       </c>
       <c r="Q434" t="n">
-        <v>8280000</v>
+        <v>8165000</v>
       </c>
     </row>
     <row r="435">
@@ -21647,10 +21647,10 @@
         <v>42</v>
       </c>
       <c r="N462" t="n">
-        <v>2432.1345544554</v>
+        <v>2432.1346</v>
       </c>
       <c r="O462" t="n">
-        <v>102149.6512871268</v>
+        <v>102149.6532</v>
       </c>
       <c r="P462" t="n">
         <v>4500</v>
@@ -22567,10 +22567,10 @@
         <v>28</v>
       </c>
       <c r="N482" t="n">
-        <v>2361.5097222222</v>
+        <v>2361.5097142857</v>
       </c>
       <c r="O482" t="n">
-        <v>66122.2722222216</v>
+        <v>66122.27199999959</v>
       </c>
       <c r="P482" t="n">
         <v>6200</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q551"/>
+  <dimension ref="A1:Q550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>17</v>
@@ -7752,13 +7752,13 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
         <v>211</v>
@@ -20262,12 +20262,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>J-1313</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -20281,39 +20281,39 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>144</v>
+        <v>710</v>
       </c>
       <c r="K433" t="n">
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M433" t="n">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="N433" t="n">
-        <v>7480</v>
+        <v>9240</v>
       </c>
       <c r="O433" t="n">
-        <v>0</v>
+        <v>6560400</v>
       </c>
       <c r="P433" t="n">
-        <v>9500</v>
+        <v>11500</v>
       </c>
       <c r="Q433" t="n">
-        <v>0</v>
+        <v>8165000</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>J-582</t>
+          <t>LP089</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>SET DE BICHOS EN BOLSA 714K-1</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -20327,39 +20327,39 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>720</v>
+        <v>25</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>710</v>
+        <v>25</v>
       </c>
       <c r="N434" t="n">
-        <v>9240</v>
+        <v>10320</v>
       </c>
       <c r="O434" t="n">
-        <v>6560400</v>
+        <v>258000</v>
       </c>
       <c r="P434" t="n">
-        <v>11500</v>
+        <v>12900</v>
       </c>
       <c r="Q434" t="n">
-        <v>8165000</v>
+        <v>322500</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>LP089</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SET DE BICHOS EN BOLSA 714K-1</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K435" t="n">
         <v>0</v>
@@ -20382,35 +20382,35 @@
         <v>0</v>
       </c>
       <c r="M435" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N435" t="n">
-        <v>10320</v>
+        <v>415.07</v>
       </c>
       <c r="O435" t="n">
-        <v>258000</v>
+        <v>9546.610000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>12900</v>
+        <v>2900</v>
       </c>
       <c r="Q435" t="n">
-        <v>322500</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>MFQ01</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>PELUCHE ERIZO 55CM 23FP-029</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -20419,7 +20419,7 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
@@ -20428,44 +20428,34 @@
         <v>0</v>
       </c>
       <c r="M436" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="N436" t="n">
-        <v>415.07</v>
+        <v>17885.0975</v>
       </c>
       <c r="O436" t="n">
-        <v>9546.610000000001</v>
+        <v>71540.39</v>
       </c>
       <c r="P436" t="n">
-        <v>2900</v>
+        <v>46500</v>
       </c>
       <c r="Q436" t="n">
-        <v>66700</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>MFQ01</t>
+          <t>MFQ11</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PELUCHE ERIZO 55CM 23FP-029</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
         </is>
       </c>
       <c r="J437" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -20474,34 +20464,34 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N437" t="n">
-        <v>17885.0975</v>
+        <v>10436.368888889</v>
       </c>
       <c r="O437" t="n">
-        <v>71540.39</v>
+        <v>93927.320000001</v>
       </c>
       <c r="P437" t="n">
-        <v>46500</v>
+        <v>25900</v>
       </c>
       <c r="Q437" t="n">
-        <v>186000</v>
+        <v>233100</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>MFQ11</t>
+          <t>MFQ12</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
+          <t>PELUCHE DINOSAURIO PK FP-166</t>
         </is>
       </c>
       <c r="J438" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K438" t="n">
         <v>0</v>
@@ -20510,34 +20500,49 @@
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N438" t="n">
-        <v>10436.368888889</v>
+        <v>8736.825000000001</v>
       </c>
       <c r="O438" t="n">
-        <v>93927.320000001</v>
+        <v>17473.65</v>
       </c>
       <c r="P438" t="n">
-        <v>25900</v>
+        <v>26500</v>
       </c>
       <c r="Q438" t="n">
-        <v>233100</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>MFQ12</t>
+          <t>MG033</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>MG18880</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK FP-166</t>
+          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J439" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
@@ -20546,40 +20551,40 @@
         <v>0</v>
       </c>
       <c r="M439" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N439" t="n">
-        <v>8736.825000000001</v>
+        <v>1783.57</v>
       </c>
       <c r="O439" t="n">
-        <v>17473.65</v>
+        <v>21402.84</v>
       </c>
       <c r="P439" t="n">
-        <v>26500</v>
+        <v>7800</v>
       </c>
       <c r="Q439" t="n">
-        <v>53000</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>MG033</t>
+          <t>MG045</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MG18880</t>
+          <t>PT20032</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
+          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -20588,7 +20593,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -20597,40 +20602,35 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N440" t="n">
-        <v>1783.57</v>
+        <v>6000</v>
       </c>
       <c r="O440" t="n">
-        <v>21402.84</v>
+        <v>210000</v>
       </c>
       <c r="P440" t="n">
-        <v>7800</v>
+        <v>7500</v>
       </c>
       <c r="Q440" t="n">
-        <v>93600</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>MG045</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>PT20032</t>
+          <t>MG090</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
+          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -20639,7 +20639,7 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
@@ -20648,35 +20648,40 @@
         <v>0</v>
       </c>
       <c r="M441" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="N441" t="n">
-        <v>6000</v>
+        <v>1462.04</v>
       </c>
       <c r="O441" t="n">
-        <v>210000</v>
+        <v>4386.12</v>
       </c>
       <c r="P441" t="n">
-        <v>7500</v>
+        <v>3800</v>
       </c>
       <c r="Q441" t="n">
-        <v>262500</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>MG090</t>
+          <t>MG093</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>mg26016</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
+          <t>CARRO BASURA BOLSA MG26016</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -20685,7 +20690,7 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
@@ -20694,40 +20699,35 @@
         <v>0</v>
       </c>
       <c r="M442" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="N442" t="n">
-        <v>1462.04</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="O442" t="n">
-        <v>4386.12</v>
+        <v>22349.72</v>
       </c>
       <c r="P442" t="n">
-        <v>3800</v>
+        <v>17800</v>
       </c>
       <c r="Q442" t="n">
-        <v>11400</v>
+        <v>516200</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MG093</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>mg26016</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>CARRO BASURA BOLSA MG26016</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="J443" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K443" t="n">
         <v>0</v>
@@ -20745,35 +20745,35 @@
         <v>0</v>
       </c>
       <c r="M443" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N443" t="n">
-        <v>770.6799999999999</v>
+        <v>1482.84</v>
       </c>
       <c r="O443" t="n">
-        <v>22349.72</v>
+        <v>40036.68</v>
       </c>
       <c r="P443" t="n">
-        <v>17800</v>
+        <v>6500</v>
       </c>
       <c r="Q443" t="n">
-        <v>516200</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG21714</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
@@ -20791,35 +20791,35 @@
         <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="N444" t="n">
-        <v>1482.84</v>
+        <v>576.58</v>
       </c>
       <c r="O444" t="n">
-        <v>40036.68</v>
+        <v>33441.64</v>
       </c>
       <c r="P444" t="n">
-        <v>6500</v>
+        <v>5900</v>
       </c>
       <c r="Q444" t="n">
-        <v>175500</v>
+        <v>342200</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MG21714</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -20837,35 +20837,40 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N445" t="n">
-        <v>576.58</v>
+        <v>1129.14</v>
       </c>
       <c r="O445" t="n">
-        <v>33441.64</v>
+        <v>68877.54000000001</v>
       </c>
       <c r="P445" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q445" t="n">
-        <v>342200</v>
+        <v>420900</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>MG22435</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -20874,7 +20879,7 @@
         </is>
       </c>
       <c r="J446" t="n">
-        <v>61</v>
+        <v>250</v>
       </c>
       <c r="K446" t="n">
         <v>0</v>
@@ -20883,40 +20888,35 @@
         <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>61</v>
+        <v>250</v>
       </c>
       <c r="N446" t="n">
-        <v>1129.14</v>
+        <v>1236.3</v>
       </c>
       <c r="O446" t="n">
-        <v>68877.54000000001</v>
+        <v>309075</v>
       </c>
       <c r="P446" t="n">
-        <v>6900</v>
+        <v>2300</v>
       </c>
       <c r="Q446" t="n">
-        <v>420900</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MG22435</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>MG22435</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -20925,7 +20925,7 @@
         </is>
       </c>
       <c r="J447" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="K447" t="n">
         <v>0</v>
@@ -20934,35 +20934,35 @@
         <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="N447" t="n">
-        <v>1236.3</v>
+        <v>8174.05</v>
       </c>
       <c r="O447" t="n">
-        <v>309075</v>
+        <v>16348.1</v>
       </c>
       <c r="P447" t="n">
-        <v>2300</v>
+        <v>8900</v>
       </c>
       <c r="Q447" t="n">
-        <v>575000</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -20971,7 +20971,7 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
@@ -20980,35 +20980,35 @@
         <v>0</v>
       </c>
       <c r="M448" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N448" t="n">
-        <v>8174.05</v>
+        <v>11433.53</v>
       </c>
       <c r="O448" t="n">
-        <v>16348.1</v>
+        <v>45734.12</v>
       </c>
       <c r="P448" t="n">
-        <v>8900</v>
+        <v>15000</v>
       </c>
       <c r="Q448" t="n">
-        <v>17800</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG26011</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>CAMION DE BOMBEROS MG26011</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -21017,7 +21017,7 @@
         </is>
       </c>
       <c r="J449" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K449" t="n">
         <v>0</v>
@@ -21026,30 +21026,30 @@
         <v>0</v>
       </c>
       <c r="M449" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N449" t="n">
-        <v>11433.53</v>
+        <v>5920.69</v>
       </c>
       <c r="O449" t="n">
-        <v>45734.12</v>
+        <v>29603.45</v>
       </c>
       <c r="P449" t="n">
-        <v>15000</v>
+        <v>11900</v>
       </c>
       <c r="Q449" t="n">
-        <v>60000</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MG26011</t>
+          <t>MG26196</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>CAMION DE BOMBEROS MG26011</t>
+          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="J450" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K450" t="n">
         <v>0</v>
@@ -21072,30 +21072,30 @@
         <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N450" t="n">
-        <v>5920.69</v>
+        <v>6272.36</v>
       </c>
       <c r="O450" t="n">
-        <v>29603.45</v>
+        <v>94085.39999999999</v>
       </c>
       <c r="P450" t="n">
-        <v>11900</v>
+        <v>10500</v>
       </c>
       <c r="Q450" t="n">
-        <v>59500</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>MG26196</t>
+          <t>MG27332</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
+          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -21109,7 +21109,7 @@
         </is>
       </c>
       <c r="J451" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K451" t="n">
         <v>0</v>
@@ -21118,30 +21118,30 @@
         <v>0</v>
       </c>
       <c r="M451" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N451" t="n">
-        <v>6272.36</v>
+        <v>6750.7</v>
       </c>
       <c r="O451" t="n">
-        <v>94085.39999999999</v>
+        <v>135014</v>
       </c>
       <c r="P451" t="n">
-        <v>10500</v>
+        <v>22500</v>
       </c>
       <c r="Q451" t="n">
-        <v>157500</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>MG27332</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -21155,7 +21155,7 @@
         </is>
       </c>
       <c r="J452" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K452" t="n">
         <v>0</v>
@@ -21164,35 +21164,35 @@
         <v>0</v>
       </c>
       <c r="M452" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N452" t="n">
-        <v>6750.7</v>
+        <v>9046.99</v>
       </c>
       <c r="O452" t="n">
-        <v>135014</v>
+        <v>63328.93</v>
       </c>
       <c r="P452" t="n">
         <v>22500</v>
       </c>
       <c r="Q452" t="n">
-        <v>450000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -21201,7 +21201,7 @@
         </is>
       </c>
       <c r="J453" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
@@ -21210,35 +21210,40 @@
         <v>0</v>
       </c>
       <c r="M453" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="N453" t="n">
-        <v>9046.99</v>
+        <v>1319.3608823529</v>
       </c>
       <c r="O453" t="n">
-        <v>63328.93</v>
+        <v>50135.7135294102</v>
       </c>
       <c r="P453" t="n">
-        <v>22500</v>
+        <v>3500</v>
       </c>
       <c r="Q453" t="n">
-        <v>157500</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG32342</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>MG32342</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -21247,7 +21252,7 @@
         </is>
       </c>
       <c r="J454" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K454" t="n">
         <v>0</v>
@@ -21256,40 +21261,35 @@
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="N454" t="n">
-        <v>1319.3608823529</v>
+        <v>1161.6</v>
       </c>
       <c r="O454" t="n">
-        <v>50135.7135294102</v>
+        <v>20908.8</v>
       </c>
       <c r="P454" t="n">
-        <v>3500</v>
+        <v>24500</v>
       </c>
       <c r="Q454" t="n">
-        <v>133000</v>
+        <v>441000</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>MG32342</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>MG32342</t>
+          <t>MG32594</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
+          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -21298,7 +21298,7 @@
         </is>
       </c>
       <c r="J455" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="K455" t="n">
         <v>0</v>
@@ -21307,35 +21307,40 @@
         <v>0</v>
       </c>
       <c r="M455" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="N455" t="n">
-        <v>1161.6</v>
+        <v>3088.1420689655</v>
       </c>
       <c r="O455" t="n">
-        <v>20908.8</v>
+        <v>166759.671724137</v>
       </c>
       <c r="P455" t="n">
-        <v>24500</v>
+        <v>8500</v>
       </c>
       <c r="Q455" t="n">
-        <v>441000</v>
+        <v>459000</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>MG32594</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -21344,7 +21349,7 @@
         </is>
       </c>
       <c r="J456" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="K456" t="n">
         <v>0</v>
@@ -21353,40 +21358,35 @@
         <v>0</v>
       </c>
       <c r="M456" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="N456" t="n">
-        <v>3088.1420689655</v>
+        <v>751.45</v>
       </c>
       <c r="O456" t="n">
-        <v>166759.671724137</v>
+        <v>2254.35</v>
       </c>
       <c r="P456" t="n">
-        <v>8500</v>
+        <v>2500</v>
       </c>
       <c r="Q456" t="n">
-        <v>459000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -21395,7 +21395,7 @@
         </is>
       </c>
       <c r="J457" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="K457" t="n">
         <v>0</v>
@@ -21404,35 +21404,35 @@
         <v>0</v>
       </c>
       <c r="M457" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="N457" t="n">
-        <v>751.45</v>
+        <v>571.87</v>
       </c>
       <c r="O457" t="n">
-        <v>2254.35</v>
+        <v>86924.24000000001</v>
       </c>
       <c r="P457" t="n">
         <v>2500</v>
       </c>
       <c r="Q457" t="n">
-        <v>7500</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40226</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>ATARY COCODRILO MG40226</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -21441,7 +21441,7 @@
         </is>
       </c>
       <c r="J458" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="K458" t="n">
         <v>0</v>
@@ -21450,30 +21450,35 @@
         <v>0</v>
       </c>
       <c r="M458" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="N458" t="n">
-        <v>571.87</v>
+        <v>310.41666666667</v>
       </c>
       <c r="O458" t="n">
-        <v>86924.24000000001</v>
+        <v>310.41666666667</v>
       </c>
       <c r="P458" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="Q458" t="n">
-        <v>380000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>MG40226</t>
+          <t>MG40243</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>MG40243</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>ATARY COCODRILO MG40226</t>
+          <t>ATARY DINOSAURIO MG40243</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -21487,7 +21492,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -21496,40 +21501,35 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N459" t="n">
-        <v>310.41666666667</v>
+        <v>520.674</v>
       </c>
       <c r="O459" t="n">
-        <v>310.41666666667</v>
+        <v>4165.392</v>
       </c>
       <c r="P459" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="Q459" t="n">
-        <v>1800</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>MG40243</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>MG40243</t>
+          <t>MG40259</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>ATARY DINOSAURIO MG40243</t>
+          <t>CARRO JET DESTAPADO MG40259</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -21538,7 +21538,7 @@
         </is>
       </c>
       <c r="J460" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K460" t="n">
         <v>0</v>
@@ -21547,35 +21547,40 @@
         <v>0</v>
       </c>
       <c r="M460" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N460" t="n">
-        <v>520.674</v>
+        <v>1153.41</v>
       </c>
       <c r="O460" t="n">
-        <v>4165.392</v>
+        <v>2306.82</v>
       </c>
       <c r="P460" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="Q460" t="n">
-        <v>16000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>MG40259</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>CARRO JET DESTAPADO MG40259</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -21584,7 +21589,7 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -21593,35 +21598,30 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="N461" t="n">
-        <v>1153.41</v>
+        <v>2432.1346</v>
       </c>
       <c r="O461" t="n">
-        <v>2306.82</v>
+        <v>102149.6532</v>
       </c>
       <c r="P461" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="Q461" t="n">
-        <v>8000</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG40327</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>BLISTER PESCA STD  MG40327</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -21635,7 +21635,7 @@
         </is>
       </c>
       <c r="J462" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="K462" t="n">
         <v>0</v>
@@ -21644,35 +21644,35 @@
         <v>0</v>
       </c>
       <c r="M462" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="N462" t="n">
-        <v>2432.1346</v>
+        <v>449.63</v>
       </c>
       <c r="O462" t="n">
-        <v>102149.6532</v>
+        <v>449.63</v>
       </c>
       <c r="P462" t="n">
-        <v>4500</v>
+        <v>5100</v>
       </c>
       <c r="Q462" t="n">
-        <v>189000</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>MG40327</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>BLISTER PESCA STD  MG40327</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -21681,7 +21681,7 @@
         </is>
       </c>
       <c r="J463" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="K463" t="n">
         <v>0</v>
@@ -21690,30 +21690,30 @@
         <v>0</v>
       </c>
       <c r="M463" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="N463" t="n">
-        <v>449.63</v>
+        <v>227.41597222222</v>
       </c>
       <c r="O463" t="n">
-        <v>449.63</v>
+        <v>53442.7534722217</v>
       </c>
       <c r="P463" t="n">
-        <v>5100</v>
+        <v>1200</v>
       </c>
       <c r="Q463" t="n">
-        <v>5100</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40415</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>TELEFONO AVION MG40415</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -21727,7 +21727,7 @@
         </is>
       </c>
       <c r="J464" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="K464" t="n">
         <v>0</v>
@@ -21736,35 +21736,35 @@
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="N464" t="n">
-        <v>227.41597222222</v>
+        <v>13308.19</v>
       </c>
       <c r="O464" t="n">
-        <v>53442.7534722217</v>
+        <v>26616.38</v>
       </c>
       <c r="P464" t="n">
-        <v>1200</v>
+        <v>34600</v>
       </c>
       <c r="Q464" t="n">
-        <v>282000</v>
+        <v>69200</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>MG40415</t>
+          <t>MG40570</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>TELEFONO AVION MG40415</t>
+          <t>REGISTRADORA SENCILLA MG40570</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -21773,7 +21773,7 @@
         </is>
       </c>
       <c r="J465" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K465" t="n">
         <v>0</v>
@@ -21782,35 +21782,35 @@
         <v>0</v>
       </c>
       <c r="M465" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N465" t="n">
-        <v>13308.19</v>
+        <v>8735.540000000001</v>
       </c>
       <c r="O465" t="n">
-        <v>26616.38</v>
+        <v>61148.78000000001</v>
       </c>
       <c r="P465" t="n">
-        <v>34600</v>
+        <v>29900</v>
       </c>
       <c r="Q465" t="n">
-        <v>69200</v>
+        <v>209300</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>MG40570</t>
+          <t>MG40805</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>REGISTRADORA SENCILLA MG40570</t>
+          <t>LANZA DARDOS HERO GDE MG40805</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -21819,7 +21819,7 @@
         </is>
       </c>
       <c r="J466" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K466" t="n">
         <v>0</v>
@@ -21828,35 +21828,35 @@
         <v>0</v>
       </c>
       <c r="M466" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N466" t="n">
-        <v>8735.540000000001</v>
+        <v>22654.34</v>
       </c>
       <c r="O466" t="n">
-        <v>61148.78000000001</v>
+        <v>249197.74</v>
       </c>
       <c r="P466" t="n">
-        <v>29900</v>
+        <v>58900</v>
       </c>
       <c r="Q466" t="n">
-        <v>209300</v>
+        <v>647900</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>MG40805</t>
+          <t>MG41038</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>LANZA DARDOS HERO GDE MG40805</t>
+          <t>VOLQUETA SENCILLA MED MG41038</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="J467" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K467" t="n">
         <v>0</v>
@@ -21874,35 +21874,35 @@
         <v>0</v>
       </c>
       <c r="M467" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N467" t="n">
-        <v>22654.34</v>
+        <v>4962.04</v>
       </c>
       <c r="O467" t="n">
-        <v>249197.74</v>
+        <v>9924.08</v>
       </c>
       <c r="P467" t="n">
-        <v>58900</v>
+        <v>12900</v>
       </c>
       <c r="Q467" t="n">
-        <v>647900</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>MG41038</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>VOLQUETA SENCILLA MED MG41038</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -21911,7 +21911,7 @@
         </is>
       </c>
       <c r="J468" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K468" t="n">
         <v>0</v>
@@ -21920,35 +21920,35 @@
         <v>0</v>
       </c>
       <c r="M468" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N468" t="n">
-        <v>4962.04</v>
+        <v>25110.1</v>
       </c>
       <c r="O468" t="n">
-        <v>9924.08</v>
+        <v>326431.3</v>
       </c>
       <c r="P468" t="n">
-        <v>12900</v>
+        <v>27900</v>
       </c>
       <c r="Q468" t="n">
-        <v>25800</v>
+        <v>362700</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MG41588</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
+          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -21957,7 +21957,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K469" t="n">
         <v>0</v>
@@ -21966,30 +21966,30 @@
         <v>0</v>
       </c>
       <c r="M469" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N469" t="n">
-        <v>25110.1</v>
+        <v>5422.51</v>
       </c>
       <c r="O469" t="n">
-        <v>326431.3</v>
+        <v>32535.06</v>
       </c>
       <c r="P469" t="n">
-        <v>27900</v>
+        <v>19900</v>
       </c>
       <c r="Q469" t="n">
-        <v>362700</v>
+        <v>119400</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>MG41588</t>
+          <t>MG41589</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
+          <t>MUÑECA ODONTOLOGA MG41589</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -22003,7 +22003,7 @@
         </is>
       </c>
       <c r="J470" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K470" t="n">
         <v>0</v>
@@ -22012,35 +22012,35 @@
         <v>0</v>
       </c>
       <c r="M470" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N470" t="n">
-        <v>5422.51</v>
+        <v>5103.23</v>
       </c>
       <c r="O470" t="n">
-        <v>32535.06</v>
+        <v>20412.92</v>
       </c>
       <c r="P470" t="n">
         <v>19900</v>
       </c>
       <c r="Q470" t="n">
-        <v>119400</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>MG41589</t>
+          <t>MJC-558</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>MUÑECA ODONTOLOGA MG41589</t>
+          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="J471" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K471" t="n">
         <v>0</v>
@@ -22058,30 +22058,30 @@
         <v>0</v>
       </c>
       <c r="M471" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N471" t="n">
-        <v>5103.23</v>
+        <v>40500</v>
       </c>
       <c r="O471" t="n">
-        <v>20412.92</v>
+        <v>729000</v>
       </c>
       <c r="P471" t="n">
-        <v>19900</v>
+        <v>48600</v>
       </c>
       <c r="Q471" t="n">
-        <v>79600</v>
+        <v>874800</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>MJC-558</t>
+          <t>MJC-558-1</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="J472" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
@@ -22104,44 +22104,39 @@
         <v>0</v>
       </c>
       <c r="M472" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N472" t="n">
         <v>40500</v>
       </c>
       <c r="O472" t="n">
-        <v>729000</v>
+        <v>324000</v>
       </c>
       <c r="P472" t="n">
         <v>48600</v>
       </c>
       <c r="Q472" t="n">
-        <v>874800</v>
+        <v>388800</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>MJC-558-1</t>
+          <t>MT4004</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J473" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -22150,39 +22145,44 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N473" t="n">
-        <v>40500</v>
+        <v>2058.92</v>
       </c>
       <c r="O473" t="n">
-        <v>324000</v>
+        <v>4117.84</v>
       </c>
       <c r="P473" t="n">
-        <v>48600</v>
+        <v>2500</v>
       </c>
       <c r="Q473" t="n">
-        <v>388800</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>MT4004</t>
+          <t>MT4690</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>BALDE CASTILLO PQÑ MT4690</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -22191,16 +22191,16 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N474" t="n">
-        <v>2058.92</v>
+        <v>3450.4864435564</v>
       </c>
       <c r="O474" t="n">
-        <v>4117.84</v>
+        <v>3450.4864435564</v>
       </c>
       <c r="P474" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="Q474" t="n">
         <v>5000</v>
@@ -22209,17 +22209,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>MT4690</t>
+          <t>PT08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>BALDE CASTILLO PQÑ MT4690</t>
+          <t>ALCANCIA PEQUEÑA PP002</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
@@ -22237,35 +22237,35 @@
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="N475" t="n">
-        <v>3450.4864435564</v>
+        <v>436.24</v>
       </c>
       <c r="O475" t="n">
-        <v>3450.4864435564</v>
+        <v>34899.2</v>
       </c>
       <c r="P475" t="n">
-        <v>5000</v>
+        <v>550</v>
       </c>
       <c r="Q475" t="n">
-        <v>5000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>PT08</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>ALCANCIA PEQUEÑA PP002</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -22283,35 +22283,40 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="N476" t="n">
-        <v>436.24</v>
+        <v>1950.7</v>
       </c>
       <c r="O476" t="n">
-        <v>34899.2</v>
+        <v>206774.2</v>
       </c>
       <c r="P476" t="n">
-        <v>550</v>
+        <v>7500</v>
       </c>
       <c r="Q476" t="n">
-        <v>44000</v>
+        <v>795000</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>PT15838</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>PT15838</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>LANZADORA DE AGUA PT15838</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -22320,7 +22325,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -22329,40 +22334,35 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="N477" t="n">
-        <v>1950.7</v>
+        <v>753.98</v>
       </c>
       <c r="O477" t="n">
-        <v>206774.2</v>
+        <v>37699</v>
       </c>
       <c r="P477" t="n">
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="Q477" t="n">
-        <v>795000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>PT15838</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>PT15838</t>
+          <t>PT25404</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA PT15838</t>
+          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MONTABLES</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -22371,7 +22371,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -22380,30 +22380,30 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="N478" t="n">
-        <v>753.98</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="O478" t="n">
-        <v>37699</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="P478" t="n">
-        <v>4000</v>
+        <v>109900</v>
       </c>
       <c r="Q478" t="n">
-        <v>200000</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>PT25404</t>
+          <t>PT25419</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
+          <t>MONOPATIN CAJA LUCES PT25419</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -22417,7 +22417,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -22426,30 +22426,30 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N479" t="n">
-        <v>84538.46000000001</v>
+        <v>87920</v>
       </c>
       <c r="O479" t="n">
-        <v>84538.46000000001</v>
+        <v>527520</v>
       </c>
       <c r="P479" t="n">
         <v>109900</v>
       </c>
       <c r="Q479" t="n">
-        <v>109900</v>
+        <v>659400</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>PT25419</t>
+          <t>PT25420</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>MONOPATIN CAJA LUCES PT25419</t>
+          <t>MONOPATIN  PATO PT25420</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -22463,7 +22463,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K480" t="n">
         <v>0</v>
@@ -22472,35 +22472,35 @@
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N480" t="n">
-        <v>87920</v>
+        <v>15394.79</v>
       </c>
       <c r="O480" t="n">
-        <v>527520</v>
+        <v>169342.69</v>
       </c>
       <c r="P480" t="n">
-        <v>109900</v>
+        <v>99800</v>
       </c>
       <c r="Q480" t="n">
-        <v>659400</v>
+        <v>1097800</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>PT25420</t>
+          <t>PT26747</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>MONOPATIN  PATO PT25420</t>
+          <t>TABLA LABERINTO PT26747</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>MONTABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -22509,7 +22509,7 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
@@ -22518,30 +22518,30 @@
         <v>0</v>
       </c>
       <c r="M481" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N481" t="n">
-        <v>15394.79</v>
+        <v>2361.5097142857</v>
       </c>
       <c r="O481" t="n">
-        <v>169342.69</v>
+        <v>66122.27199999959</v>
       </c>
       <c r="P481" t="n">
-        <v>99800</v>
+        <v>6200</v>
       </c>
       <c r="Q481" t="n">
-        <v>1097800</v>
+        <v>173600</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>PT26747</t>
+          <t>RL589-28D</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>TABLA LABERINTO PT26747</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -22555,7 +22555,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
@@ -22564,30 +22564,30 @@
         <v>0</v>
       </c>
       <c r="M482" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="N482" t="n">
-        <v>2361.5097142857</v>
+        <v>7046.7433333333</v>
       </c>
       <c r="O482" t="n">
-        <v>66122.27199999959</v>
+        <v>98654.4066666662</v>
       </c>
       <c r="P482" t="n">
-        <v>6200</v>
+        <v>22900</v>
       </c>
       <c r="Q482" t="n">
-        <v>173600</v>
+        <v>320600</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>RL589-28D</t>
+          <t>RL589-33D</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -22601,7 +22601,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -22610,35 +22610,35 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="N483" t="n">
-        <v>7046.7433333333</v>
+        <v>10009.170909091</v>
       </c>
       <c r="O483" t="n">
-        <v>98654.4066666662</v>
+        <v>210192.589090911</v>
       </c>
       <c r="P483" t="n">
         <v>22900</v>
       </c>
       <c r="Q483" t="n">
-        <v>320600</v>
+        <v>480900</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>RL589-33D</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -22647,7 +22647,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -22656,35 +22656,35 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="N484" t="n">
-        <v>10009.170909091</v>
+        <v>4091.4</v>
       </c>
       <c r="O484" t="n">
-        <v>210192.589090911</v>
+        <v>36822.6</v>
       </c>
       <c r="P484" t="n">
-        <v>22900</v>
+        <v>10000</v>
       </c>
       <c r="Q484" t="n">
-        <v>480900</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>SEBQ17</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>CUBO MAGICO COLORES X5 SE-19126</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -22693,7 +22693,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -22702,35 +22702,35 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="N485" t="n">
-        <v>4091.4</v>
+        <v>5148.77</v>
       </c>
       <c r="O485" t="n">
-        <v>36822.6</v>
+        <v>278033.58</v>
       </c>
       <c r="P485" t="n">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="Q485" t="n">
-        <v>90000</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>SEBQ17</t>
+          <t>SEBQ27</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>CUBO MAGICO COLORES X5 SE-19126</t>
+          <t>CELULAR MUÑECO X12 SE1597</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -22739,7 +22739,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>54</v>
+        <v>535</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -22748,30 +22748,30 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>54</v>
+        <v>535</v>
       </c>
       <c r="N486" t="n">
-        <v>5148.77</v>
+        <v>855.85</v>
       </c>
       <c r="O486" t="n">
-        <v>278033.58</v>
+        <v>457879.75</v>
       </c>
       <c r="P486" t="n">
-        <v>10500</v>
+        <v>3500</v>
       </c>
       <c r="Q486" t="n">
-        <v>567000</v>
+        <v>1872500</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>SEBQ27</t>
+          <t>SLT052</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>CELULAR MUÑECO X12 SE1597</t>
+          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -22785,7 +22785,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>535</v>
+        <v>2</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -22794,35 +22794,35 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>535</v>
+        <v>2</v>
       </c>
       <c r="N487" t="n">
-        <v>855.85</v>
+        <v>0</v>
       </c>
       <c r="O487" t="n">
-        <v>457879.75</v>
+        <v>0</v>
       </c>
       <c r="P487" t="n">
-        <v>3500</v>
+        <v>13500</v>
       </c>
       <c r="Q487" t="n">
-        <v>1872500</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>SLT052</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -22831,7 +22831,7 @@
         </is>
       </c>
       <c r="J488" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="K488" t="n">
         <v>0</v>
@@ -22840,30 +22840,30 @@
         <v>0</v>
       </c>
       <c r="M488" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="N488" t="n">
-        <v>0</v>
+        <v>4550</v>
       </c>
       <c r="O488" t="n">
-        <v>0</v>
+        <v>819000</v>
       </c>
       <c r="P488" t="n">
-        <v>13500</v>
+        <v>5500</v>
       </c>
       <c r="Q488" t="n">
-        <v>27000</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>SLT2641</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>BALON BASQUEBOL # 5 SLT2641</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -22877,7 +22877,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -22886,30 +22886,30 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="N489" t="n">
-        <v>4550</v>
+        <v>422.91</v>
       </c>
       <c r="O489" t="n">
-        <v>819000</v>
+        <v>3383.28</v>
       </c>
       <c r="P489" t="n">
-        <v>5500</v>
+        <v>12500</v>
       </c>
       <c r="Q489" t="n">
-        <v>990000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>SLT2641</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 5 SLT2641</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -22923,7 +22923,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
@@ -22932,30 +22932,30 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="N490" t="n">
-        <v>422.91</v>
+        <v>341.02142276423</v>
       </c>
       <c r="O490" t="n">
-        <v>3383.28</v>
+        <v>58314.66329268333</v>
       </c>
       <c r="P490" t="n">
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="Q490" t="n">
-        <v>100000</v>
+        <v>2479500</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>SLT2642</t>
+          <t>SLT2714</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
+          <t>VENTILADOR MINI SLT2714</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -22969,7 +22969,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -22978,35 +22978,35 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="N491" t="n">
-        <v>341.02142276423</v>
+        <v>4158.2962162162</v>
       </c>
       <c r="O491" t="n">
-        <v>58314.66329268333</v>
+        <v>133065.4789189184</v>
       </c>
       <c r="P491" t="n">
-        <v>14500</v>
+        <v>13800</v>
       </c>
       <c r="Q491" t="n">
-        <v>2479500</v>
+        <v>441600</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>SLT2714</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>VENTILADOR MINI SLT2714</t>
+          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -23024,30 +23024,30 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="N492" t="n">
-        <v>4158.2962162162</v>
+        <v>22230.77</v>
       </c>
       <c r="O492" t="n">
-        <v>133065.4789189184</v>
+        <v>111153.85</v>
       </c>
       <c r="P492" t="n">
-        <v>13800</v>
+        <v>28900</v>
       </c>
       <c r="Q492" t="n">
-        <v>441600</v>
+        <v>144500</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T032</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -23061,7 +23061,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -23070,30 +23070,30 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N493" t="n">
-        <v>22230.77</v>
+        <v>33200</v>
       </c>
       <c r="O493" t="n">
-        <v>111153.85</v>
+        <v>33200</v>
       </c>
       <c r="P493" t="n">
-        <v>28900</v>
+        <v>41500</v>
       </c>
       <c r="Q493" t="n">
-        <v>144500</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T038</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
+          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -23119,32 +23119,32 @@
         <v>1</v>
       </c>
       <c r="N494" t="n">
-        <v>33200</v>
+        <v>4962.04</v>
       </c>
       <c r="O494" t="n">
-        <v>33200</v>
+        <v>4962.04</v>
       </c>
       <c r="P494" t="n">
-        <v>41500</v>
+        <v>12900</v>
       </c>
       <c r="Q494" t="n">
-        <v>41500</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>T038</t>
+          <t>T046</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
+          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -23153,7 +23153,7 @@
         </is>
       </c>
       <c r="J495" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K495" t="n">
         <v>0</v>
@@ -23162,35 +23162,35 @@
         <v>0</v>
       </c>
       <c r="M495" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N495" t="n">
-        <v>4962.04</v>
+        <v>22802.484</v>
       </c>
       <c r="O495" t="n">
-        <v>4962.04</v>
+        <v>114012.42</v>
       </c>
       <c r="P495" t="n">
-        <v>12900</v>
+        <v>41500</v>
       </c>
       <c r="Q495" t="n">
-        <v>12900</v>
+        <v>207500</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>T046</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -23208,35 +23208,35 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N496" t="n">
-        <v>22802.484</v>
+        <v>12392.16</v>
       </c>
       <c r="O496" t="n">
-        <v>114012.42</v>
+        <v>557647.2</v>
       </c>
       <c r="P496" t="n">
-        <v>41500</v>
+        <v>15900</v>
       </c>
       <c r="Q496" t="n">
-        <v>207500</v>
+        <v>715500</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="J497" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -23254,35 +23254,35 @@
         <v>0</v>
       </c>
       <c r="M497" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="N497" t="n">
-        <v>12392.16</v>
+        <v>24882.58</v>
       </c>
       <c r="O497" t="n">
-        <v>557647.2</v>
+        <v>174178.06</v>
       </c>
       <c r="P497" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q497" t="n">
-        <v>715500</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T066</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -23291,7 +23291,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -23300,30 +23300,30 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N498" t="n">
-        <v>24882.58</v>
+        <v>16576.2</v>
       </c>
       <c r="O498" t="n">
-        <v>174178.06</v>
+        <v>16576.2</v>
       </c>
       <c r="P498" t="n">
-        <v>31500</v>
+        <v>25900</v>
       </c>
       <c r="Q498" t="n">
-        <v>220500</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>T066</t>
+          <t>T067</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
+          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -23349,27 +23349,27 @@
         <v>1</v>
       </c>
       <c r="N499" t="n">
-        <v>16576.2</v>
+        <v>47600</v>
       </c>
       <c r="O499" t="n">
-        <v>16576.2</v>
+        <v>47600</v>
       </c>
       <c r="P499" t="n">
-        <v>25900</v>
+        <v>59500</v>
       </c>
       <c r="Q499" t="n">
-        <v>25900</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>T067</t>
+          <t>T073</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
+          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -23392,30 +23392,30 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N500" t="n">
-        <v>47600</v>
+        <v>6102.9</v>
       </c>
       <c r="O500" t="n">
-        <v>47600</v>
+        <v>12205.8</v>
       </c>
       <c r="P500" t="n">
-        <v>59500</v>
+        <v>11900</v>
       </c>
       <c r="Q500" t="n">
-        <v>59500</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>T073</t>
+          <t>T079</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
+          <t>PELUCHE 15CM BQ-15</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -23429,7 +23429,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -23438,30 +23438,30 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="N501" t="n">
-        <v>6102.9</v>
+        <v>525.33</v>
       </c>
       <c r="O501" t="n">
-        <v>12205.8</v>
+        <v>12082.59</v>
       </c>
       <c r="P501" t="n">
-        <v>11900</v>
+        <v>5900</v>
       </c>
       <c r="Q501" t="n">
-        <v>23800</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>T079</t>
+          <t>T089</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>PELUCHE 15CM BQ-15</t>
+          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -23475,7 +23475,7 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
@@ -23484,30 +23484,30 @@
         <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N502" t="n">
-        <v>525.33</v>
+        <v>8580.75</v>
       </c>
       <c r="O502" t="n">
-        <v>12082.59</v>
+        <v>17161.5</v>
       </c>
       <c r="P502" t="n">
-        <v>5900</v>
+        <v>42900</v>
       </c>
       <c r="Q502" t="n">
-        <v>135700</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>T089</t>
+          <t>T098</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
+          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -23521,7 +23521,7 @@
         </is>
       </c>
       <c r="J503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
@@ -23530,30 +23530,30 @@
         <v>0</v>
       </c>
       <c r="M503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N503" t="n">
-        <v>8580.75</v>
+        <v>14308.02</v>
       </c>
       <c r="O503" t="n">
-        <v>17161.5</v>
+        <v>14308.02</v>
       </c>
       <c r="P503" t="n">
-        <v>42900</v>
+        <v>27900</v>
       </c>
       <c r="Q503" t="n">
-        <v>85800</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>T098</t>
+          <t>T099</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -23567,7 +23567,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -23576,30 +23576,30 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N504" t="n">
-        <v>14308.02</v>
+        <v>8538.8633333333</v>
       </c>
       <c r="O504" t="n">
-        <v>14308.02</v>
+        <v>17077.7266666666</v>
       </c>
       <c r="P504" t="n">
-        <v>27900</v>
+        <v>18500</v>
       </c>
       <c r="Q504" t="n">
-        <v>27900</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>T099</t>
+          <t>T103</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
+          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -23613,7 +23613,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -23622,30 +23622,30 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N505" t="n">
-        <v>8538.8633333333</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O505" t="n">
-        <v>17077.7266666666</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="P505" t="n">
-        <v>18500</v>
+        <v>25900</v>
       </c>
       <c r="Q505" t="n">
-        <v>37000</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>T103</t>
+          <t>T110</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
+          <t>PELUCHE DINOSAURIO STD 80CM DINO-80</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -23671,27 +23671,27 @@
         <v>1</v>
       </c>
       <c r="N506" t="n">
-        <v>9962.040000000001</v>
+        <v>27734</v>
       </c>
       <c r="O506" t="n">
-        <v>9962.040000000001</v>
+        <v>27734</v>
       </c>
       <c r="P506" t="n">
-        <v>25900</v>
+        <v>104000</v>
       </c>
       <c r="Q506" t="n">
-        <v>25900</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>T110</t>
+          <t>T117</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO STD 80CM DINO-80</t>
+          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -23705,7 +23705,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -23714,30 +23714,30 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N507" t="n">
-        <v>27734</v>
+        <v>14577.42</v>
       </c>
       <c r="O507" t="n">
-        <v>27734</v>
+        <v>29154.84</v>
       </c>
       <c r="P507" t="n">
-        <v>104000</v>
+        <v>37900</v>
       </c>
       <c r="Q507" t="n">
-        <v>104000</v>
+        <v>75800</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>T117</t>
+          <t>T121</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
+          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -23751,7 +23751,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -23760,30 +23760,30 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N508" t="n">
-        <v>14577.42</v>
+        <v>13000.5</v>
       </c>
       <c r="O508" t="n">
-        <v>29154.84</v>
+        <v>13000.5</v>
       </c>
       <c r="P508" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="Q508" t="n">
-        <v>75800</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>T121</t>
+          <t>T135</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
+          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -23797,7 +23797,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -23806,30 +23806,30 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N509" t="n">
-        <v>13000.5</v>
+        <v>7115.88</v>
       </c>
       <c r="O509" t="n">
-        <v>13000.5</v>
+        <v>35579.4</v>
       </c>
       <c r="P509" t="n">
-        <v>32500</v>
+        <v>18500</v>
       </c>
       <c r="Q509" t="n">
-        <v>32500</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>T135</t>
+          <t>T136</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
+          <t>BOLSO PELUCHE ANIMALES P01-30</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23852,30 +23852,30 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N510" t="n">
-        <v>7115.88</v>
+        <v>7886.43</v>
       </c>
       <c r="O510" t="n">
-        <v>35579.4</v>
+        <v>31545.72</v>
       </c>
       <c r="P510" t="n">
-        <v>18500</v>
+        <v>34500</v>
       </c>
       <c r="Q510" t="n">
-        <v>92500</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>T136</t>
+          <t>T143</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>BOLSO PELUCHE ANIMALES P01-30</t>
+          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -23889,7 +23889,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23898,30 +23898,30 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N511" t="n">
-        <v>7886.43</v>
+        <v>23920</v>
       </c>
       <c r="O511" t="n">
-        <v>31545.72</v>
+        <v>23920</v>
       </c>
       <c r="P511" t="n">
-        <v>34500</v>
+        <v>29900</v>
       </c>
       <c r="Q511" t="n">
-        <v>138000</v>
+        <v>29900</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>T143</t>
+          <t>T157</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
+          <t>PELUCHE CONEJO 30CM ANA-28</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="J512" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -23944,30 +23944,30 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N512" t="n">
-        <v>23920</v>
+        <v>11472.4</v>
       </c>
       <c r="O512" t="n">
-        <v>23920</v>
+        <v>34417.2</v>
       </c>
       <c r="P512" t="n">
-        <v>29900</v>
+        <v>23900</v>
       </c>
       <c r="Q512" t="n">
-        <v>29900</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>T157</t>
+          <t>T158</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>PELUCHE CONEJO 30CM ANA-28</t>
+          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -23990,30 +23990,30 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N513" t="n">
-        <v>11472.4</v>
+        <v>10577.42</v>
       </c>
       <c r="O513" t="n">
-        <v>34417.2</v>
+        <v>105774.2</v>
       </c>
       <c r="P513" t="n">
-        <v>23900</v>
+        <v>27500</v>
       </c>
       <c r="Q513" t="n">
-        <v>71700</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>T158</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -24027,7 +24027,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -24036,30 +24036,30 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N514" t="n">
-        <v>10577.42</v>
+        <v>5186.45</v>
       </c>
       <c r="O514" t="n">
-        <v>105774.2</v>
+        <v>103729</v>
       </c>
       <c r="P514" t="n">
-        <v>27500</v>
+        <v>7200</v>
       </c>
       <c r="Q514" t="n">
-        <v>275000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T171</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -24073,7 +24073,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -24082,44 +24082,34 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N515" t="n">
-        <v>5186.45</v>
+        <v>14832.4</v>
       </c>
       <c r="O515" t="n">
-        <v>103729</v>
+        <v>14832.4</v>
       </c>
       <c r="P515" t="n">
-        <v>7200</v>
+        <v>30900</v>
       </c>
       <c r="Q515" t="n">
-        <v>144000</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>T171</t>
+          <t>T172</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
-        </is>
-      </c>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I516" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
         </is>
       </c>
       <c r="J516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -24128,34 +24118,44 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N516" t="n">
-        <v>14832.4</v>
+        <v>4462.14</v>
       </c>
       <c r="O516" t="n">
-        <v>14832.4</v>
+        <v>8924.280000000001</v>
       </c>
       <c r="P516" t="n">
-        <v>30900</v>
+        <v>14500</v>
       </c>
       <c r="Q516" t="n">
-        <v>30900</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>T172</t>
+          <t>T175</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
+          <t>PELUCHE BOWSER 35CM KUP-35</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J517" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -24164,30 +24164,30 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N517" t="n">
-        <v>4462.14</v>
+        <v>4614.22</v>
       </c>
       <c r="O517" t="n">
-        <v>8924.280000000001</v>
+        <v>32299.54</v>
       </c>
       <c r="P517" t="n">
-        <v>14500</v>
+        <v>51900</v>
       </c>
       <c r="Q517" t="n">
-        <v>29000</v>
+        <v>363300</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>T175</t>
+          <t>T181</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>PELUCHE BOWSER 35CM KUP-35</t>
+          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -24201,7 +24201,7 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -24210,30 +24210,30 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N518" t="n">
-        <v>4614.22</v>
+        <v>11692.75</v>
       </c>
       <c r="O518" t="n">
-        <v>32299.54</v>
+        <v>23385.5</v>
       </c>
       <c r="P518" t="n">
-        <v>51900</v>
+        <v>28500</v>
       </c>
       <c r="Q518" t="n">
-        <v>363300</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>T181</t>
+          <t>T182</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
+          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -24247,7 +24247,7 @@
         </is>
       </c>
       <c r="J519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -24256,30 +24256,30 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N519" t="n">
-        <v>11692.75</v>
+        <v>5600.5</v>
       </c>
       <c r="O519" t="n">
-        <v>23385.5</v>
+        <v>5600.5</v>
       </c>
       <c r="P519" t="n">
-        <v>28500</v>
+        <v>14000</v>
       </c>
       <c r="Q519" t="n">
-        <v>57000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>T182</t>
+          <t>T185</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
+          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -24293,7 +24293,7 @@
         </is>
       </c>
       <c r="J520" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -24302,30 +24302,30 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N520" t="n">
-        <v>5600.5</v>
+        <v>9160.5</v>
       </c>
       <c r="O520" t="n">
-        <v>5600.5</v>
+        <v>45802.5</v>
       </c>
       <c r="P520" t="n">
-        <v>14000</v>
+        <v>22900</v>
       </c>
       <c r="Q520" t="n">
-        <v>14000</v>
+        <v>114500</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>T185</t>
+          <t>T195</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
+          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -24339,7 +24339,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -24348,30 +24348,30 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N521" t="n">
-        <v>9160.5</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="O521" t="n">
-        <v>45802.5</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="P521" t="n">
-        <v>22900</v>
+        <v>23900</v>
       </c>
       <c r="Q521" t="n">
-        <v>114500</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>T195</t>
+          <t>T201-LJ</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
+          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -24385,7 +24385,7 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
@@ -24394,35 +24394,35 @@
         <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N522" t="n">
-        <v>9192.809999999999</v>
+        <v>35000</v>
       </c>
       <c r="O522" t="n">
-        <v>9192.809999999999</v>
+        <v>70000</v>
       </c>
       <c r="P522" t="n">
-        <v>23900</v>
+        <v>45500</v>
       </c>
       <c r="Q522" t="n">
-        <v>23900</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>T201-LJ</t>
+          <t>T203</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
+          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -24431,7 +24431,7 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -24440,30 +24440,30 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N523" t="n">
-        <v>35000</v>
+        <v>11885.11</v>
       </c>
       <c r="O523" t="n">
-        <v>70000</v>
+        <v>11885.11</v>
       </c>
       <c r="P523" t="n">
-        <v>45500</v>
+        <v>30900</v>
       </c>
       <c r="Q523" t="n">
-        <v>91000</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>T203</t>
+          <t>T206</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
+          <t>PELUCHE PATO 30CM HJE-30</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -24477,7 +24477,7 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -24486,35 +24486,35 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N524" t="n">
-        <v>11885.11</v>
+        <v>31120</v>
       </c>
       <c r="O524" t="n">
-        <v>11885.11</v>
+        <v>62240</v>
       </c>
       <c r="P524" t="n">
-        <v>30900</v>
+        <v>38900</v>
       </c>
       <c r="Q524" t="n">
-        <v>30900</v>
+        <v>77800</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>T206</t>
+          <t>T207</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM HJE-30</t>
+          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -24535,27 +24535,27 @@
         <v>2</v>
       </c>
       <c r="N525" t="n">
-        <v>31120</v>
+        <v>7520.71</v>
       </c>
       <c r="O525" t="n">
-        <v>62240</v>
+        <v>15041.42</v>
       </c>
       <c r="P525" t="n">
-        <v>38900</v>
+        <v>32900</v>
       </c>
       <c r="Q525" t="n">
-        <v>77800</v>
+        <v>65800</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>T207</t>
+          <t>T211</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
+          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -24581,27 +24581,27 @@
         <v>2</v>
       </c>
       <c r="N526" t="n">
-        <v>7520.71</v>
+        <v>16500.5</v>
       </c>
       <c r="O526" t="n">
-        <v>15041.42</v>
+        <v>33001</v>
       </c>
       <c r="P526" t="n">
-        <v>32900</v>
+        <v>42900</v>
       </c>
       <c r="Q526" t="n">
-        <v>65800</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>T211</t>
+          <t>T213</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
+          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -24615,7 +24615,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24624,30 +24624,30 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N527" t="n">
-        <v>16500.5</v>
+        <v>16220.2125</v>
       </c>
       <c r="O527" t="n">
-        <v>33001</v>
+        <v>64880.85</v>
       </c>
       <c r="P527" t="n">
-        <v>42900</v>
+        <v>36900</v>
       </c>
       <c r="Q527" t="n">
-        <v>85800</v>
+        <v>147600</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>T213</t>
+          <t>T214</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
+          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -24661,7 +24661,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24670,30 +24670,30 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N528" t="n">
-        <v>16220.2125</v>
+        <v>11885.11</v>
       </c>
       <c r="O528" t="n">
-        <v>64880.85</v>
+        <v>11885.11</v>
       </c>
       <c r="P528" t="n">
-        <v>36900</v>
+        <v>30900</v>
       </c>
       <c r="Q528" t="n">
-        <v>147600</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>T214</t>
+          <t>T216</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
+          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -24707,7 +24707,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -24716,30 +24716,30 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N529" t="n">
-        <v>11885.11</v>
+        <v>14760.5</v>
       </c>
       <c r="O529" t="n">
-        <v>11885.11</v>
+        <v>73802.5</v>
       </c>
       <c r="P529" t="n">
-        <v>30900</v>
+        <v>36900</v>
       </c>
       <c r="Q529" t="n">
-        <v>30900</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>T216</t>
+          <t>T217</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
+          <t>PELUCHE GATO TELA 30CM BQM-30</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -24753,7 +24753,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24762,44 +24762,34 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N530" t="n">
-        <v>14760.5</v>
+        <v>8462.040000000001</v>
       </c>
       <c r="O530" t="n">
-        <v>73802.5</v>
+        <v>50772.24000000001</v>
       </c>
       <c r="P530" t="n">
-        <v>36900</v>
+        <v>22000</v>
       </c>
       <c r="Q530" t="n">
-        <v>184500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>T217</t>
+          <t>T222</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>PELUCHE GATO TELA 30CM BQM-30</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
         </is>
       </c>
       <c r="J531" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24808,30 +24798,40 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N531" t="n">
-        <v>8462.040000000001</v>
+        <v>23461.54</v>
       </c>
       <c r="O531" t="n">
-        <v>50772.24000000001</v>
+        <v>23461.54</v>
       </c>
       <c r="P531" t="n">
-        <v>22000</v>
+        <v>30500</v>
       </c>
       <c r="Q531" t="n">
-        <v>132000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>T222</t>
+          <t>T229</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
+          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J532" t="n">
@@ -24847,27 +24847,27 @@
         <v>1</v>
       </c>
       <c r="N532" t="n">
-        <v>23461.54</v>
+        <v>18600.5</v>
       </c>
       <c r="O532" t="n">
-        <v>23461.54</v>
+        <v>18600.5</v>
       </c>
       <c r="P532" t="n">
-        <v>30500</v>
+        <v>46500</v>
       </c>
       <c r="Q532" t="n">
-        <v>30500</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>T229</t>
+          <t>T243</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
+          <t>PELUCHE GATO 40CM DX-60</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -24893,27 +24893,27 @@
         <v>1</v>
       </c>
       <c r="N533" t="n">
-        <v>18600.5</v>
+        <v>26000</v>
       </c>
       <c r="O533" t="n">
-        <v>18600.5</v>
+        <v>26000</v>
       </c>
       <c r="P533" t="n">
-        <v>46500</v>
+        <v>32500</v>
       </c>
       <c r="Q533" t="n">
-        <v>46500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>T243</t>
+          <t>T244</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>PELUCHE GATO 40CM DX-60</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -24927,7 +24927,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24936,30 +24936,30 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N534" t="n">
-        <v>26000</v>
+        <v>7400.5</v>
       </c>
       <c r="O534" t="n">
-        <v>26000</v>
+        <v>22201.5</v>
       </c>
       <c r="P534" t="n">
-        <v>32500</v>
+        <v>18500</v>
       </c>
       <c r="Q534" t="n">
-        <v>32500</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>T244</t>
+          <t>T245</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
+          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24982,30 +24982,30 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N535" t="n">
-        <v>7400.5</v>
+        <v>25200</v>
       </c>
       <c r="O535" t="n">
-        <v>22201.5</v>
+        <v>25200</v>
       </c>
       <c r="P535" t="n">
-        <v>18500</v>
+        <v>31500</v>
       </c>
       <c r="Q535" t="n">
-        <v>55500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>T245</t>
+          <t>T247</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
+          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -25019,7 +25019,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -25028,30 +25028,30 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N536" t="n">
-        <v>25200</v>
+        <v>8667.34</v>
       </c>
       <c r="O536" t="n">
-        <v>25200</v>
+        <v>34669.36</v>
       </c>
       <c r="P536" t="n">
-        <v>31500</v>
+        <v>32500</v>
       </c>
       <c r="Q536" t="n">
-        <v>31500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>T247</t>
+          <t>T248</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
+          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -25065,7 +25065,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -25074,30 +25074,30 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N537" t="n">
-        <v>8667.34</v>
+        <v>40720</v>
       </c>
       <c r="O537" t="n">
-        <v>34669.36</v>
+        <v>81440</v>
       </c>
       <c r="P537" t="n">
-        <v>32500</v>
+        <v>50900</v>
       </c>
       <c r="Q537" t="n">
-        <v>130000</v>
+        <v>101800</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>T248</t>
+          <t>T250</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
+          <t>PELUCHE MAGO 40CM PCO-40</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -25111,7 +25111,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -25120,30 +25120,30 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N538" t="n">
-        <v>40720</v>
+        <v>29520</v>
       </c>
       <c r="O538" t="n">
-        <v>81440</v>
+        <v>88560</v>
       </c>
       <c r="P538" t="n">
-        <v>50900</v>
+        <v>36900</v>
       </c>
       <c r="Q538" t="n">
-        <v>101800</v>
+        <v>110700</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>T250</t>
+          <t>T272</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO 40CM PCO-40</t>
+          <t>PELUCHE BUHO 40CM MTY-40</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -25157,7 +25157,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -25166,30 +25166,30 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N539" t="n">
-        <v>29520</v>
+        <v>12500.5</v>
       </c>
       <c r="O539" t="n">
-        <v>88560</v>
+        <v>12500.5</v>
       </c>
       <c r="P539" t="n">
-        <v>36900</v>
+        <v>32500</v>
       </c>
       <c r="Q539" t="n">
-        <v>110700</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>T272</t>
+          <t>T273</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>PELUCHE BUHO 40CM MTY-40</t>
+          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -25215,37 +25215,27 @@
         <v>1</v>
       </c>
       <c r="N540" t="n">
-        <v>12500.5</v>
+        <v>13808.19</v>
       </c>
       <c r="O540" t="n">
-        <v>12500.5</v>
+        <v>13808.19</v>
       </c>
       <c r="P540" t="n">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="Q540" t="n">
-        <v>32500</v>
+        <v>35900</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>T273</t>
+          <t>T300</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I541" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
         </is>
       </c>
       <c r="J541" t="n">
@@ -25261,27 +25251,37 @@
         <v>1</v>
       </c>
       <c r="N541" t="n">
-        <v>13808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="O541" t="n">
-        <v>13808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="P541" t="n">
-        <v>35900</v>
+        <v>30500</v>
       </c>
       <c r="Q541" t="n">
-        <v>35900</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>T300</t>
+          <t>T308</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
+          <t>PELUCHE ANIMAL ACOSTADO DISFRAZ 25CM DT230918-25</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J542" t="n">
@@ -25297,41 +25297,31 @@
         <v>1</v>
       </c>
       <c r="N542" t="n">
-        <v>13686.31</v>
+        <v>4808.19</v>
       </c>
       <c r="O542" t="n">
-        <v>13686.31</v>
+        <v>4808.19</v>
       </c>
       <c r="P542" t="n">
-        <v>30500</v>
+        <v>12500</v>
       </c>
       <c r="Q542" t="n">
-        <v>30500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>T308</t>
+          <t>T334</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMAL ACOSTADO DISFRAZ 25CM DT230918-25</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE DIGIMON 20CM MD-20</t>
         </is>
       </c>
       <c r="J543" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -25340,34 +25330,34 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N543" t="n">
-        <v>4808.19</v>
+        <v>7571.81</v>
       </c>
       <c r="O543" t="n">
-        <v>4808.19</v>
+        <v>45430.86</v>
       </c>
       <c r="P543" t="n">
-        <v>12500</v>
+        <v>15900</v>
       </c>
       <c r="Q543" t="n">
-        <v>12500</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>T334</t>
+          <t>T336</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>PELUCHE DIGIMON 20CM MD-20</t>
+          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
         </is>
       </c>
       <c r="J544" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -25376,34 +25366,44 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N544" t="n">
-        <v>7571.81</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O544" t="n">
-        <v>45430.86</v>
+        <v>19924.08</v>
       </c>
       <c r="P544" t="n">
-        <v>15900</v>
+        <v>25900</v>
       </c>
       <c r="Q544" t="n">
-        <v>95400</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>T336</t>
+          <t>T345</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
+          <t>PELUCHE ADVNG 20CM ESP-20</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -25412,35 +25412,30 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N545" t="n">
-        <v>9962.040000000001</v>
+        <v>1250.88</v>
       </c>
       <c r="O545" t="n">
-        <v>19924.08</v>
+        <v>3752.64</v>
       </c>
       <c r="P545" t="n">
-        <v>25900</v>
+        <v>12500</v>
       </c>
       <c r="Q545" t="n">
-        <v>51800</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>T345</t>
+          <t>T352</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>PELUCHE ADVNG 20CM ESP-20</t>
-        </is>
-      </c>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>NINJA T352</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -25449,7 +25444,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25458,30 +25453,35 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N546" t="n">
-        <v>1250.88</v>
+        <v>5192.31</v>
       </c>
       <c r="O546" t="n">
-        <v>3752.64</v>
+        <v>5192.31</v>
       </c>
       <c r="P546" t="n">
-        <v>12500</v>
+        <v>13500</v>
       </c>
       <c r="Q546" t="n">
-        <v>37500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>T352</t>
+          <t>TB058</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>NINJA T352</t>
+          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -25490,7 +25490,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25499,35 +25499,35 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N547" t="n">
-        <v>5192.31</v>
+        <v>17159.86</v>
       </c>
       <c r="O547" t="n">
-        <v>5192.31</v>
+        <v>51479.58</v>
       </c>
       <c r="P547" t="n">
-        <v>13500</v>
+        <v>21900</v>
       </c>
       <c r="Q547" t="n">
-        <v>13500</v>
+        <v>65700</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>TB058</t>
+          <t>TO-030</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
+          <t>COJIN ANIMALES 40CM DWKD-40</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -25536,7 +25536,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25545,30 +25545,30 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N548" t="n">
-        <v>17159.86</v>
+        <v>18384.62</v>
       </c>
       <c r="O548" t="n">
-        <v>51479.58</v>
+        <v>18384.62</v>
       </c>
       <c r="P548" t="n">
-        <v>21900</v>
+        <v>23900</v>
       </c>
       <c r="Q548" t="n">
-        <v>65700</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>TO-030</t>
+          <t>TO-038</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>COJIN ANIMALES 40CM DWKD-40</t>
+          <t>COJIN ANIMAL 30CM DXS-25</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -25594,27 +25594,27 @@
         <v>1</v>
       </c>
       <c r="N549" t="n">
-        <v>18384.62</v>
+        <v>14800</v>
       </c>
       <c r="O549" t="n">
-        <v>18384.62</v>
+        <v>14800</v>
       </c>
       <c r="P549" t="n">
-        <v>23900</v>
+        <v>18500</v>
       </c>
       <c r="Q549" t="n">
-        <v>23900</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>TO-038</t>
+          <t>TO-041</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>COJIN ANIMAL 30CM DXS-25</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -25628,7 +25628,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25637,64 +25637,18 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N550" t="n">
-        <v>14800</v>
+        <v>2372.36</v>
       </c>
       <c r="O550" t="n">
-        <v>14800</v>
+        <v>21351.24</v>
       </c>
       <c r="P550" t="n">
-        <v>18500</v>
+        <v>41500</v>
       </c>
       <c r="Q550" t="n">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>TO-041</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I551" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J551" t="n">
-        <v>9</v>
-      </c>
-      <c r="K551" t="n">
-        <v>0</v>
-      </c>
-      <c r="L551" t="n">
-        <v>0</v>
-      </c>
-      <c r="M551" t="n">
-        <v>9</v>
-      </c>
-      <c r="N551" t="n">
-        <v>2372.36</v>
-      </c>
-      <c r="O551" t="n">
-        <v>21351.24</v>
-      </c>
-      <c r="P551" t="n">
-        <v>41500</v>
-      </c>
-      <c r="Q551" t="n">
         <v>373500</v>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3047800109</v>
+        <v>1811.3053012048</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.720803924</v>
+        <v>652069.9084337279</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1084,10 +1084,10 @@
         <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8371237802</v>
+        <v>3926.8371059432</v>
       </c>
       <c r="O17" t="n">
-        <v>90317.2538469446</v>
+        <v>90317.2534366936</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2413.0010626993</v>
+        <v>2413.0010683761</v>
       </c>
       <c r="O18" t="n">
-        <v>4826.0021253986</v>
+        <v>4826.0021367522</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -2898,22 +2898,22 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M59" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N59" t="n">
         <v>11108.253513514</v>
       </c>
       <c r="O59" t="n">
-        <v>288814.591351364</v>
+        <v>255489.830810822</v>
       </c>
       <c r="P59" t="n">
         <v>18900</v>
       </c>
       <c r="Q59" t="n">
-        <v>491400</v>
+        <v>434700</v>
       </c>
     </row>
     <row r="60">
@@ -3350,10 +3350,10 @@
         <v>144</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.055952691</v>
+        <v>1098.0561100153</v>
       </c>
       <c r="O69" t="n">
-        <v>158120.057187504</v>
+        <v>158120.0798422032</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3624,10 +3624,10 @@
         <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2559895309</v>
+        <v>2582.2559749444</v>
       </c>
       <c r="O75" t="n">
-        <v>2509952.821824035</v>
+        <v>2509952.807645957</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3670,10 +3670,10 @@
         <v>1438</v>
       </c>
       <c r="N76" t="n">
-        <v>5216.8959618537</v>
+        <v>5216.8962134973</v>
       </c>
       <c r="O76" t="n">
-        <v>7501896.393145621</v>
+        <v>7501896.755009118</v>
       </c>
       <c r="P76" t="n">
         <v>8500</v>
@@ -3716,10 +3716,10 @@
         <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.5662758621</v>
+        <v>2033.5658041958</v>
       </c>
       <c r="O77" t="n">
-        <v>97611.18124138079</v>
+        <v>97611.15860139841</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
@@ -3808,10 +3808,10 @@
         <v>3410</v>
       </c>
       <c r="N79" t="n">
-        <v>3158.8608154486</v>
+        <v>3158.8608230874</v>
       </c>
       <c r="O79" t="n">
-        <v>10771715.38067973</v>
+        <v>10771715.40672803</v>
       </c>
       <c r="P79" t="n">
         <v>5600</v>
@@ -3903,10 +3903,10 @@
         <v>60</v>
       </c>
       <c r="N81" t="n">
-        <v>3230.0677302632</v>
+        <v>3230.0675874126</v>
       </c>
       <c r="O81" t="n">
-        <v>193804.063815792</v>
+        <v>193804.055244756</v>
       </c>
       <c r="P81" t="n">
         <v>6200</v>
@@ -3949,10 +3949,10 @@
         <v>514</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.8234059946</v>
+        <v>2694.8233333333</v>
       </c>
       <c r="O82" t="n">
-        <v>1385139.230681224</v>
+        <v>1385139.193333316</v>
       </c>
       <c r="P82" t="n">
         <v>4900</v>
@@ -4139,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="N86" t="n">
-        <v>4967.814</v>
+        <v>4967.8238461538</v>
       </c>
       <c r="O86" t="n">
-        <v>14903.442</v>
+        <v>14903.4715384614</v>
       </c>
       <c r="P86" t="n">
         <v>7500</v>
@@ -4280,10 +4280,10 @@
         <v>332</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.254124847</v>
+        <v>3594.2541140405</v>
       </c>
       <c r="O89" t="n">
-        <v>1193292.369449204</v>
+        <v>1193292.365861446</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4637,10 +4637,10 @@
         <v>317</v>
       </c>
       <c r="N97" t="n">
-        <v>4372.2107877711</v>
+        <v>4372.2107879391</v>
       </c>
       <c r="O97" t="n">
-        <v>1385990.819723438</v>
+        <v>1385990.819776695</v>
       </c>
       <c r="P97" t="n">
         <v>7500</v>
@@ -4770,10 +4770,10 @@
         <v>244</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.5674</v>
+        <v>1592.5673455845</v>
       </c>
       <c r="O100" t="n">
-        <v>388586.4456</v>
+        <v>388586.432322618</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
@@ -5172,22 +5172,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M109" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="N109" t="n">
         <v>11921.4</v>
       </c>
       <c r="O109" t="n">
-        <v>631834.2</v>
+        <v>393406.2</v>
       </c>
       <c r="P109" t="n">
         <v>19900</v>
       </c>
       <c r="Q109" t="n">
-        <v>1054700</v>
+        <v>656700</v>
       </c>
     </row>
     <row r="110">
@@ -5409,10 +5409,10 @@
         <v>636</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9231730968</v>
+        <v>1630.9233118002</v>
       </c>
       <c r="O114" t="n">
-        <v>1037267.138089565</v>
+        <v>1037267.226304927</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>23</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.193183768</v>
+        <v>1550.1933219945</v>
       </c>
       <c r="O115" t="n">
-        <v>35654.443226664</v>
+        <v>35654.4464058735</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
@@ -5501,10 +5501,10 @@
         <v>168</v>
       </c>
       <c r="N116" t="n">
-        <v>1579.3909343434</v>
+        <v>1579.3908883249</v>
       </c>
       <c r="O116" t="n">
-        <v>265337.6769696912</v>
+        <v>265337.6692385832</v>
       </c>
       <c r="P116" t="n">
         <v>2900</v>
@@ -5547,10 +5547,10 @@
         <v>171</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5104597508</v>
+        <v>2403.5107961064</v>
       </c>
       <c r="O117" t="n">
-        <v>411000.2886173868</v>
+        <v>411000.3461341944</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5426705653</v>
+        <v>2521.5415942029</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.3895516568</v>
+        <v>141206.3292753624</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -6294,10 +6294,10 @@
         <v>103</v>
       </c>
       <c r="N134" t="n">
-        <v>5449.530483871</v>
+        <v>5449.5305</v>
       </c>
       <c r="O134" t="n">
-        <v>561301.639838713</v>
+        <v>561301.6415</v>
       </c>
       <c r="P134" t="n">
         <v>6200</v>
@@ -7620,22 +7620,22 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M165" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N165" t="n">
         <v>5569.98</v>
       </c>
       <c r="O165" t="n">
-        <v>189379.32</v>
+        <v>133679.52</v>
       </c>
       <c r="P165" t="n">
         <v>8900</v>
       </c>
       <c r="Q165" t="n">
-        <v>302600</v>
+        <v>213600</v>
       </c>
     </row>
     <row r="166">
@@ -7712,22 +7712,22 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M167" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
         <v>5410.72</v>
       </c>
       <c r="O167" t="n">
-        <v>54107.2</v>
+        <v>0</v>
       </c>
       <c r="P167" t="n">
         <v>8700</v>
       </c>
       <c r="Q167" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -7988,22 +7988,22 @@
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M173" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="N173" t="n">
-        <v>5218.170521327</v>
+        <v>5218.1705238095</v>
       </c>
       <c r="O173" t="n">
-        <v>584435.0983886239</v>
+        <v>532253.393428569</v>
       </c>
       <c r="P173" t="n">
         <v>8500</v>
       </c>
       <c r="Q173" t="n">
-        <v>952000</v>
+        <v>867000</v>
       </c>
     </row>
     <row r="174">
@@ -8034,22 +8034,22 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M174" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="N174" t="n">
-        <v>1595.0094476744</v>
+        <v>1595.0094378698</v>
       </c>
       <c r="O174" t="n">
-        <v>146740.8691860448</v>
+        <v>114840.6795266256</v>
       </c>
       <c r="P174" t="n">
         <v>2600</v>
       </c>
       <c r="Q174" t="n">
-        <v>239200</v>
+        <v>187200</v>
       </c>
     </row>
     <row r="175">
@@ -8264,22 +8264,22 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M179" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="N179" t="n">
         <v>1812.57</v>
       </c>
       <c r="O179" t="n">
-        <v>213883.26</v>
+        <v>177631.86</v>
       </c>
       <c r="P179" t="n">
         <v>2900</v>
       </c>
       <c r="Q179" t="n">
-        <v>342200</v>
+        <v>284200</v>
       </c>
     </row>
     <row r="180">
@@ -9340,10 +9340,10 @@
         <v>552</v>
       </c>
       <c r="N202" t="n">
-        <v>1516.0388102832</v>
+        <v>1516.0388052024</v>
       </c>
       <c r="O202" t="n">
-        <v>836853.4232763264</v>
+        <v>836853.4204717248</v>
       </c>
       <c r="P202" t="n">
         <v>2300</v>
@@ -9432,10 +9432,10 @@
         <v>144</v>
       </c>
       <c r="N204" t="n">
-        <v>1771.0911179361</v>
+        <v>1771.0908132147</v>
       </c>
       <c r="O204" t="n">
-        <v>255037.1209827984</v>
+        <v>255037.0771029168</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9478,10 +9478,10 @@
         <v>240</v>
       </c>
       <c r="N205" t="n">
-        <v>2079.3841813438</v>
+        <v>2079.3841354372</v>
       </c>
       <c r="O205" t="n">
-        <v>499052.2035225119</v>
+        <v>499052.192504928</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>266</v>
       </c>
       <c r="N206" t="n">
-        <v>1803.0151724138</v>
+        <v>1803.0152234206</v>
       </c>
       <c r="O206" t="n">
-        <v>479602.0358620708</v>
+        <v>479602.0494298796</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9570,10 +9570,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>3306.5953488372</v>
+        <v>3306.5953246753</v>
       </c>
       <c r="O207" t="n">
-        <v>158716.5767441856</v>
+        <v>158716.5755844144</v>
       </c>
       <c r="P207" t="n">
         <v>4900</v>
@@ -9616,10 +9616,10 @@
         <v>264</v>
       </c>
       <c r="N208" t="n">
-        <v>2122.1640036787</v>
+        <v>2122.164</v>
       </c>
       <c r="O208" t="n">
-        <v>560251.2969711768</v>
+        <v>560251.2960000001</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>2108.7900518135</v>
+        <v>2108.7900692042</v>
       </c>
       <c r="O209" t="n">
-        <v>303665.767461144</v>
+        <v>303665.7699654048</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9708,10 +9708,10 @@
         <v>288</v>
       </c>
       <c r="N210" t="n">
-        <v>2056.0837188071</v>
+        <v>2056.0837111517</v>
       </c>
       <c r="O210" t="n">
-        <v>592152.1110164449</v>
+        <v>592152.1088116895</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9800,10 +9800,10 @@
         <v>288</v>
       </c>
       <c r="N212" t="n">
-        <v>1655.9310223953</v>
+        <v>1655.9309931618</v>
       </c>
       <c r="O212" t="n">
-        <v>476908.1344498464</v>
+        <v>476908.1260305984</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9846,10 +9846,10 @@
         <v>97</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.2756948933</v>
+        <v>1592.27610957</v>
       </c>
       <c r="O213" t="n">
-        <v>154450.7424046501</v>
+        <v>154450.78262829</v>
       </c>
       <c r="P213" t="n">
         <v>2500</v>
@@ -9936,10 +9936,10 @@
         <v>36</v>
       </c>
       <c r="N215" t="n">
-        <v>2311.9246983547</v>
+        <v>2311.9221535181</v>
       </c>
       <c r="O215" t="n">
-        <v>83229.28914076919</v>
+        <v>83229.19752665159</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -9982,10 +9982,10 @@
         <v>12</v>
       </c>
       <c r="N216" t="n">
-        <v>1906.18625</v>
+        <v>1906.1853846154</v>
       </c>
       <c r="O216" t="n">
-        <v>22874.235</v>
+        <v>22874.2246153848</v>
       </c>
       <c r="P216" t="n">
         <v>2900</v>
@@ -10028,10 +10028,10 @@
         <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>2546.985</v>
+        <v>2546.9846915888</v>
       </c>
       <c r="O217" t="n">
-        <v>122255.28</v>
+        <v>122255.2651962624</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
@@ -10251,10 +10251,10 @@
         <v>192</v>
       </c>
       <c r="N222" t="n">
-        <v>692.15209736124</v>
+        <v>692.15211662075</v>
       </c>
       <c r="O222" t="n">
-        <v>132893.2026933581</v>
+        <v>132893.206391184</v>
       </c>
       <c r="P222" t="n">
         <v>1200</v>
@@ -10726,10 +10726,10 @@
         <v>324</v>
       </c>
       <c r="N232" t="n">
-        <v>1530.4499206034</v>
+        <v>1530.4499195171</v>
       </c>
       <c r="O232" t="n">
-        <v>495865.7742755016</v>
+        <v>495865.7739235404</v>
       </c>
       <c r="P232" t="n">
         <v>2600</v>
@@ -11097,10 +11097,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>1690.8700089606</v>
+        <v>1690.8700089847</v>
       </c>
       <c r="O240" t="n">
-        <v>1690.8700089606</v>
+        <v>1690.8700089847</v>
       </c>
       <c r="P240" t="n">
         <v>3000</v>
@@ -11195,10 +11195,10 @@
         <v>-2</v>
       </c>
       <c r="N242" t="n">
-        <v>2270.3211494253</v>
+        <v>2270.3211627907</v>
       </c>
       <c r="O242" t="n">
-        <v>-4540.6422988506</v>
+        <v>-4540.6423255814</v>
       </c>
       <c r="P242" t="n">
         <v>3900</v>
@@ -11391,10 +11391,10 @@
         <v>2280</v>
       </c>
       <c r="N246" t="n">
-        <v>517.28824762181</v>
+        <v>517.28836312001</v>
       </c>
       <c r="O246" t="n">
-        <v>1179417.204577727</v>
+        <v>1179417.467913623</v>
       </c>
       <c r="P246" t="n">
         <v>900</v>
@@ -11630,10 +11630,10 @@
         <v>504</v>
       </c>
       <c r="N251" t="n">
-        <v>3110.8426932617</v>
+        <v>3110.8426185007</v>
       </c>
       <c r="O251" t="n">
-        <v>1567864.717403897</v>
+        <v>1567864.679724353</v>
       </c>
       <c r="P251" t="n">
         <v>4500</v>
@@ -11858,10 +11858,10 @@
         <v>13152</v>
       </c>
       <c r="N256" t="n">
-        <v>703.7953201758</v>
+        <v>703.79529676406</v>
       </c>
       <c r="O256" t="n">
-        <v>9256316.050952122</v>
+        <v>9256315.743040917</v>
       </c>
       <c r="P256" t="n">
         <v>900</v>
@@ -11947,22 +11947,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M258" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="N258" t="n">
         <v>3182.2511009174</v>
       </c>
       <c r="O258" t="n">
-        <v>547347.1893577928</v>
+        <v>512342.4272477014</v>
       </c>
       <c r="P258" t="n">
         <v>6900</v>
       </c>
       <c r="Q258" t="n">
-        <v>1186800</v>
+        <v>1110900</v>
       </c>
     </row>
     <row r="259">
@@ -12765,10 +12765,10 @@
         <v>71</v>
       </c>
       <c r="N275" t="n">
-        <v>2098.4049147727</v>
+        <v>2098.4049570201</v>
       </c>
       <c r="O275" t="n">
-        <v>148986.7489488617</v>
+        <v>148986.7519484271</v>
       </c>
       <c r="P275" t="n">
         <v>9500</v>
@@ -15557,10 +15557,10 @@
         <v>1000</v>
       </c>
       <c r="N333" t="n">
-        <v>1783.7988843537</v>
+        <v>1783.7988833409</v>
       </c>
       <c r="O333" t="n">
-        <v>1783798.8843537</v>
+        <v>1783798.8833409</v>
       </c>
       <c r="P333" t="n">
         <v>1500</v>
@@ -17481,10 +17481,10 @@
         <v>8</v>
       </c>
       <c r="N373" t="n">
-        <v>7046.9398298958</v>
+        <v>7046.9398286204</v>
       </c>
       <c r="O373" t="n">
-        <v>56375.5186391664</v>
+        <v>56375.5186289632</v>
       </c>
       <c r="P373" t="n">
         <v>9900</v>
@@ -18586,10 +18586,10 @@
         <v>30</v>
       </c>
       <c r="N396" t="n">
-        <v>22951.704968711</v>
+        <v>22951.704962406</v>
       </c>
       <c r="O396" t="n">
-        <v>688551.14906133</v>
+        <v>688551.1488721799</v>
       </c>
       <c r="P396" t="n">
         <v>37900</v>
@@ -18775,10 +18775,10 @@
         <v>42</v>
       </c>
       <c r="N400" t="n">
-        <v>1547.8824637681</v>
+        <v>1547.8825373134</v>
       </c>
       <c r="O400" t="n">
-        <v>65011.0634782602</v>
+        <v>65011.0665671628</v>
       </c>
       <c r="P400" t="n">
         <v>5500</v>
@@ -19521,10 +19521,10 @@
         <v>1827</v>
       </c>
       <c r="N416" t="n">
-        <v>220.00713026296</v>
+        <v>220.00693162525</v>
       </c>
       <c r="O416" t="n">
-        <v>401953.0269904279</v>
+        <v>401952.6640793317</v>
       </c>
       <c r="P416" t="n">
         <v>260</v>
@@ -20287,22 +20287,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M433" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="N433" t="n">
         <v>9240</v>
       </c>
       <c r="O433" t="n">
-        <v>6560400</v>
+        <v>6468000</v>
       </c>
       <c r="P433" t="n">
         <v>11500</v>
       </c>
       <c r="Q433" t="n">
-        <v>8165000</v>
+        <v>8050000</v>
       </c>
     </row>
     <row r="434">
@@ -21310,10 +21310,10 @@
         <v>54</v>
       </c>
       <c r="N455" t="n">
-        <v>3088.1420689655</v>
+        <v>3088.1422807018</v>
       </c>
       <c r="O455" t="n">
-        <v>166759.671724137</v>
+        <v>166759.6831578972</v>
       </c>
       <c r="P455" t="n">
         <v>8500</v>
@@ -22567,10 +22567,10 @@
         <v>14</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.7433333333</v>
+        <v>7046.7441176471</v>
       </c>
       <c r="O482" t="n">
-        <v>98654.4066666662</v>
+        <v>98654.4176470594</v>
       </c>
       <c r="P482" t="n">
         <v>22900</v>
@@ -22745,22 +22745,22 @@
         <v>0</v>
       </c>
       <c r="L486" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M486" t="n">
-        <v>535</v>
+        <v>499</v>
       </c>
       <c r="N486" t="n">
         <v>855.85</v>
       </c>
       <c r="O486" t="n">
-        <v>457879.75</v>
+        <v>427069.15</v>
       </c>
       <c r="P486" t="n">
         <v>3500</v>
       </c>
       <c r="Q486" t="n">
-        <v>1872500</v>
+        <v>1746500</v>
       </c>
     </row>
     <row r="487">

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.9084337279</v>
+        <v>652069.9199999881</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N23" t="n">
         <v>27000</v>
       </c>
       <c r="O23" t="n">
-        <v>2025000</v>
+        <v>1809000</v>
       </c>
       <c r="P23" t="n">
         <v>30000</v>
       </c>
       <c r="Q23" t="n">
-        <v>2250000</v>
+        <v>2010000</v>
       </c>
     </row>
     <row r="24">
@@ -1351,22 +1351,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N24" t="n">
         <v>21333.69</v>
       </c>
       <c r="O24" t="n">
-        <v>1194686.64</v>
+        <v>1109351.88</v>
       </c>
       <c r="P24" t="n">
         <v>30000</v>
       </c>
       <c r="Q24" t="n">
-        <v>1680000</v>
+        <v>1560000</v>
       </c>
     </row>
     <row r="25">
@@ -2413,10 +2413,10 @@
         <v>166</v>
       </c>
       <c r="N48" t="n">
-        <v>580.36600536193</v>
+        <v>580.36599462366</v>
       </c>
       <c r="O48" t="n">
-        <v>96340.75689008037</v>
+        <v>96340.75510752756</v>
       </c>
       <c r="P48" t="n">
         <v>6800</v>
@@ -2505,10 +2505,10 @@
         <v>165</v>
       </c>
       <c r="N50" t="n">
-        <v>28.165539906103</v>
+        <v>28.165518867925</v>
       </c>
       <c r="O50" t="n">
-        <v>4647.314084506995</v>
+        <v>4647.310613207625</v>
       </c>
       <c r="P50" t="n">
         <v>6800</v>
@@ -3350,10 +3350,10 @@
         <v>144</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0561100153</v>
+        <v>1098.0566124294</v>
       </c>
       <c r="O69" t="n">
-        <v>158120.0798422032</v>
+        <v>158120.1521898336</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3436,22 +3436,22 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="N71" t="n">
         <v>2600</v>
       </c>
       <c r="O71" t="n">
-        <v>579800</v>
+        <v>540800</v>
       </c>
       <c r="P71" t="n">
         <v>4900</v>
       </c>
       <c r="Q71" t="n">
-        <v>1092700</v>
+        <v>1019200</v>
       </c>
     </row>
     <row r="72">
@@ -3624,10 +3624,10 @@
         <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2559749444</v>
+        <v>2582.255965161</v>
       </c>
       <c r="O75" t="n">
-        <v>2509952.807645957</v>
+        <v>2509952.798136492</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3710,22 +3710,22 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M77" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2033.5658041958</v>
+        <v>2033.56088</v>
       </c>
       <c r="O77" t="n">
-        <v>97611.15860139841</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
         <v>4100</v>
       </c>
       <c r="Q77" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3808,10 +3808,10 @@
         <v>3410</v>
       </c>
       <c r="N79" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O79" t="n">
-        <v>10771715.40672803</v>
+        <v>10771715.4086465</v>
       </c>
       <c r="P79" t="n">
         <v>5600</v>
@@ -3854,10 +3854,10 @@
         <v>320</v>
       </c>
       <c r="N80" t="n">
-        <v>3841.6247414634</v>
+        <v>3841.6247693817</v>
       </c>
       <c r="O80" t="n">
-        <v>1229319.917268288</v>
+        <v>1229319.926202144</v>
       </c>
       <c r="P80" t="n">
         <v>6900</v>
@@ -3903,10 +3903,10 @@
         <v>60</v>
       </c>
       <c r="N81" t="n">
-        <v>3230.0675874126</v>
+        <v>3230.0675313059</v>
       </c>
       <c r="O81" t="n">
-        <v>193804.055244756</v>
+        <v>193804.051878354</v>
       </c>
       <c r="P81" t="n">
         <v>6200</v>
@@ -3949,10 +3949,10 @@
         <v>514</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.8233333333</v>
+        <v>2694.8232839963</v>
       </c>
       <c r="O82" t="n">
-        <v>1385139.193333316</v>
+        <v>1385139.167974098</v>
       </c>
       <c r="P82" t="n">
         <v>4900</v>
@@ -4320,22 +4320,22 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O90" t="n">
-        <v>4179910.83905157</v>
+        <v>4150266.08038056</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
       </c>
       <c r="Q90" t="n">
-        <v>7021800</v>
+        <v>6972000</v>
       </c>
     </row>
     <row r="91">
@@ -4770,10 +4770,10 @@
         <v>244</v>
       </c>
       <c r="N100" t="n">
-        <v>1592.5673455845</v>
+        <v>1592.5672645976</v>
       </c>
       <c r="O100" t="n">
-        <v>388586.432322618</v>
+        <v>388586.4125618144</v>
       </c>
       <c r="P100" t="n">
         <v>3900</v>
@@ -5221,22 +5221,22 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M110" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N110" t="n">
         <v>9903</v>
       </c>
       <c r="O110" t="n">
-        <v>148545</v>
+        <v>108933</v>
       </c>
       <c r="P110" t="n">
         <v>15900</v>
       </c>
       <c r="Q110" t="n">
-        <v>238500</v>
+        <v>174900</v>
       </c>
     </row>
     <row r="111">
@@ -5409,10 +5409,10 @@
         <v>636</v>
       </c>
       <c r="N114" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O114" t="n">
-        <v>1037267.226304927</v>
+        <v>1037267.24276041</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>23</v>
       </c>
       <c r="N115" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O115" t="n">
-        <v>35654.4464058735</v>
+        <v>35654.4471587417</v>
       </c>
       <c r="P115" t="n">
         <v>2500</v>
@@ -5501,10 +5501,10 @@
         <v>168</v>
       </c>
       <c r="N116" t="n">
-        <v>1579.3908883249</v>
+        <v>1579.3908418367</v>
       </c>
       <c r="O116" t="n">
-        <v>265337.6692385832</v>
+        <v>265337.6614285656</v>
       </c>
       <c r="P116" t="n">
         <v>2900</v>
@@ -5547,10 +5547,10 @@
         <v>171</v>
       </c>
       <c r="N117" t="n">
-        <v>2403.5107961064</v>
+        <v>2403.5109560769</v>
       </c>
       <c r="O117" t="n">
-        <v>411000.3461341944</v>
+        <v>411000.3734891499</v>
       </c>
       <c r="P117" t="n">
         <v>3500</v>
@@ -5593,10 +5593,10 @@
         <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>2521.5415942029</v>
+        <v>2521.5405895197</v>
       </c>
       <c r="O118" t="n">
-        <v>141206.3292753624</v>
+        <v>141206.2730131032</v>
       </c>
       <c r="P118" t="n">
         <v>3900</v>
@@ -6381,10 +6381,10 @@
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>2029.8737091988</v>
+        <v>2029.8737110341</v>
       </c>
       <c r="O136" t="n">
-        <v>4059.7474183976</v>
+        <v>4059.7474220682</v>
       </c>
       <c r="P136" t="n">
         <v>3600</v>
@@ -6755,10 +6755,10 @@
         <v>4</v>
       </c>
       <c r="N145" t="n">
-        <v>11562.038526316</v>
+        <v>11562.038522427</v>
       </c>
       <c r="O145" t="n">
-        <v>46248.154105264</v>
+        <v>46248.154089708</v>
       </c>
       <c r="P145" t="n">
         <v>18500</v>
@@ -7948,10 +7948,10 @@
         <v>102</v>
       </c>
       <c r="N172" t="n">
-        <v>5218.1705238095</v>
+        <v>5218.1705269461</v>
       </c>
       <c r="O172" t="n">
-        <v>532253.393428569</v>
+        <v>532253.3937485022</v>
       </c>
       <c r="P172" t="n">
         <v>8500</v>
@@ -7994,10 +7994,10 @@
         <v>72</v>
       </c>
       <c r="N173" t="n">
-        <v>1595.0094378698</v>
+        <v>1595.0094189602</v>
       </c>
       <c r="O173" t="n">
-        <v>114840.6795266256</v>
+        <v>114840.6781651344</v>
       </c>
       <c r="P173" t="n">
         <v>2600</v>
@@ -9432,10 +9432,10 @@
         <v>240</v>
       </c>
       <c r="N204" t="n">
-        <v>2079.3841354372</v>
+        <v>2079.384121911</v>
       </c>
       <c r="O204" t="n">
-        <v>499052.192504928</v>
+        <v>499052.18925864</v>
       </c>
       <c r="P204" t="n">
         <v>2900</v>
@@ -9478,10 +9478,10 @@
         <v>266</v>
       </c>
       <c r="N205" t="n">
-        <v>1803.0152234206</v>
+        <v>1803.0152282542</v>
       </c>
       <c r="O205" t="n">
-        <v>479602.0494298796</v>
+        <v>479602.0507156173</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>
@@ -9524,10 +9524,10 @@
         <v>48</v>
       </c>
       <c r="N206" t="n">
-        <v>3306.5953246753</v>
+        <v>3306.5952380952</v>
       </c>
       <c r="O206" t="n">
-        <v>158716.5755844144</v>
+        <v>158716.5714285696</v>
       </c>
       <c r="P206" t="n">
         <v>4900</v>
@@ -9570,10 +9570,10 @@
         <v>264</v>
       </c>
       <c r="N207" t="n">
-        <v>2122.164</v>
+        <v>2122.1639833897</v>
       </c>
       <c r="O207" t="n">
-        <v>560251.2960000001</v>
+        <v>560251.2916148809</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -9616,10 +9616,10 @@
         <v>144</v>
       </c>
       <c r="N208" t="n">
-        <v>2108.7900692042</v>
+        <v>2108.7902645503</v>
       </c>
       <c r="O208" t="n">
-        <v>303665.7699654048</v>
+        <v>303665.7980952432</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>288</v>
       </c>
       <c r="N209" t="n">
-        <v>2056.0837111517</v>
+        <v>2056.0836725935</v>
       </c>
       <c r="O209" t="n">
-        <v>592152.1088116895</v>
+        <v>592152.097706928</v>
       </c>
       <c r="P209" t="n">
         <v>2900</v>
@@ -9800,10 +9800,10 @@
         <v>97</v>
       </c>
       <c r="N212" t="n">
-        <v>1592.27610957</v>
+        <v>1592.2763108883</v>
       </c>
       <c r="O212" t="n">
-        <v>154450.78262829</v>
+        <v>154450.8021561651</v>
       </c>
       <c r="P212" t="n">
         <v>2500</v>
@@ -9890,10 +9890,10 @@
         <v>36</v>
       </c>
       <c r="N214" t="n">
-        <v>2311.9221535181</v>
+        <v>2311.9216849015</v>
       </c>
       <c r="O214" t="n">
-        <v>83229.19752665159</v>
+        <v>83229.180656454</v>
       </c>
       <c r="P214" t="n">
         <v>3500</v>
@@ -9936,10 +9936,10 @@
         <v>12</v>
       </c>
       <c r="N215" t="n">
-        <v>1906.1853846154</v>
+        <v>1906.1853271028</v>
       </c>
       <c r="O215" t="n">
-        <v>22874.2246153848</v>
+        <v>22874.2239252336</v>
       </c>
       <c r="P215" t="n">
         <v>2900</v>
@@ -9982,10 +9982,10 @@
         <v>48</v>
       </c>
       <c r="N216" t="n">
-        <v>2546.9846915888</v>
+        <v>2546.9846816479</v>
       </c>
       <c r="O216" t="n">
-        <v>122255.2651962624</v>
+        <v>122255.2647190992</v>
       </c>
       <c r="P216" t="n">
         <v>3900</v>
@@ -10028,10 +10028,10 @@
         <v>600</v>
       </c>
       <c r="N217" t="n">
-        <v>1259.2744638514</v>
+        <v>1259.2745016722</v>
       </c>
       <c r="O217" t="n">
-        <v>755564.67831084</v>
+        <v>755564.7010033199</v>
       </c>
       <c r="P217" t="n">
         <v>1900</v>
@@ -10205,10 +10205,10 @@
         <v>192</v>
       </c>
       <c r="N221" t="n">
-        <v>692.15211662075</v>
+        <v>692.1521205151799</v>
       </c>
       <c r="O221" t="n">
-        <v>132893.206391184</v>
+        <v>132893.2071389146</v>
       </c>
       <c r="P221" t="n">
         <v>1200</v>
@@ -11051,10 +11051,10 @@
         <v>1</v>
       </c>
       <c r="N239" t="n">
-        <v>1690.8700089847</v>
+        <v>1690.870009009</v>
       </c>
       <c r="O239" t="n">
-        <v>1690.8700089847</v>
+        <v>1690.870009009</v>
       </c>
       <c r="P239" t="n">
         <v>3000</v>
@@ -11345,10 +11345,10 @@
         <v>2280</v>
       </c>
       <c r="N245" t="n">
-        <v>517.28836312001</v>
+        <v>517.2884408203601</v>
       </c>
       <c r="O245" t="n">
-        <v>1179417.467913623</v>
+        <v>1179417.645070421</v>
       </c>
       <c r="P245" t="n">
         <v>900</v>
@@ -11584,10 +11584,10 @@
         <v>504</v>
       </c>
       <c r="N250" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O250" t="n">
-        <v>1567864.679724353</v>
+        <v>1567864.652334876</v>
       </c>
       <c r="P250" t="n">
         <v>4500</v>
@@ -11812,10 +11812,10 @@
         <v>13152</v>
       </c>
       <c r="N255" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O255" t="n">
-        <v>9256315.743040917</v>
+        <v>9256315.368282832</v>
       </c>
       <c r="P255" t="n">
         <v>900</v>
@@ -12091,10 +12091,10 @@
         <v>59</v>
       </c>
       <c r="N261" t="n">
-        <v>2501.3851351351</v>
+        <v>2501.3850684932</v>
       </c>
       <c r="O261" t="n">
-        <v>147581.7229729709</v>
+        <v>147581.7190410988</v>
       </c>
       <c r="P261" t="n">
         <v>4100</v>
@@ -12811,22 +12811,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M276" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N276" t="n">
         <v>10548.76</v>
       </c>
       <c r="O276" t="n">
-        <v>685669.4</v>
+        <v>664571.88</v>
       </c>
       <c r="P276" t="n">
         <v>35900</v>
       </c>
       <c r="Q276" t="n">
-        <v>2333500</v>
+        <v>2261700</v>
       </c>
     </row>
     <row r="277">
@@ -12903,22 +12903,22 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
         <v>10556.12</v>
       </c>
       <c r="O278" t="n">
-        <v>21112.24</v>
+        <v>0</v>
       </c>
       <c r="P278" t="n">
         <v>32900</v>
       </c>
       <c r="Q278" t="n">
-        <v>65800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -15851,10 +15851,10 @@
         <v>1</v>
       </c>
       <c r="N339" t="n">
-        <v>10737.5264</v>
+        <v>10737.526326531</v>
       </c>
       <c r="O339" t="n">
-        <v>10737.5264</v>
+        <v>10737.526326531</v>
       </c>
       <c r="P339" t="n">
         <v>18900</v>
@@ -15943,22 +15943,22 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M341" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N341" t="n">
         <v>15287.49</v>
       </c>
       <c r="O341" t="n">
-        <v>1207711.71</v>
+        <v>1161849.24</v>
       </c>
       <c r="P341" t="n">
         <v>37500</v>
       </c>
       <c r="Q341" t="n">
-        <v>2962500</v>
+        <v>2850000</v>
       </c>
     </row>
     <row r="342">
@@ -18167,10 +18167,10 @@
         <v>984</v>
       </c>
       <c r="N387" t="n">
-        <v>430.60997668998</v>
+        <v>430.6099765808</v>
       </c>
       <c r="O387" t="n">
-        <v>423720.2170629403</v>
+        <v>423720.2169555072</v>
       </c>
       <c r="P387" t="n">
         <v>2200</v>
@@ -18265,10 +18265,10 @@
         <v>455</v>
       </c>
       <c r="N389" t="n">
-        <v>315.02679218968</v>
+        <v>315.02685915493</v>
       </c>
       <c r="O389" t="n">
-        <v>143337.1904463044</v>
+        <v>143337.2209154931</v>
       </c>
       <c r="P389" t="n">
         <v>2200</v>
@@ -18349,22 +18349,22 @@
         <v>0</v>
       </c>
       <c r="L391" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M391" t="n">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="N391" t="n">
         <v>2000</v>
       </c>
       <c r="O391" t="n">
-        <v>542000</v>
+        <v>496000</v>
       </c>
       <c r="P391" t="n">
         <v>4100</v>
       </c>
       <c r="Q391" t="n">
-        <v>1111100</v>
+        <v>1016800</v>
       </c>
     </row>
     <row r="392">
@@ -18534,22 +18534,22 @@
         <v>0</v>
       </c>
       <c r="L395" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M395" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N395" t="n">
-        <v>22951.704962406</v>
+        <v>22951.704956085</v>
       </c>
       <c r="O395" t="n">
-        <v>688551.1488721799</v>
+        <v>596744.32885821</v>
       </c>
       <c r="P395" t="n">
         <v>37900</v>
       </c>
       <c r="Q395" t="n">
-        <v>1137000</v>
+        <v>985400</v>
       </c>
     </row>
     <row r="396">
@@ -18626,22 +18626,22 @@
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M397" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="N397" t="n">
         <v>1600</v>
       </c>
       <c r="O397" t="n">
-        <v>107200</v>
+        <v>0</v>
       </c>
       <c r="P397" t="n">
         <v>3500</v>
       </c>
       <c r="Q397" t="n">
-        <v>234500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -18825,22 +18825,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M401" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="N401" t="n">
-        <v>1757.3205416667</v>
+        <v>1757.3205462185</v>
       </c>
       <c r="O401" t="n">
-        <v>110711.1941250021</v>
+        <v>75564.7834873955</v>
       </c>
       <c r="P401" t="n">
         <v>2000</v>
       </c>
       <c r="Q401" t="n">
-        <v>126000</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="402">
@@ -19475,10 +19475,10 @@
         <v>1827</v>
       </c>
       <c r="N415" t="n">
-        <v>220.00693162525</v>
+        <v>220.00651536869</v>
       </c>
       <c r="O415" t="n">
-        <v>401952.6640793317</v>
+        <v>401951.9035785967</v>
       </c>
       <c r="P415" t="n">
         <v>260</v>
@@ -20201,10 +20201,10 @@
         <v>3</v>
       </c>
       <c r="N431" t="n">
-        <v>21664.371428571</v>
+        <v>21664.371538462</v>
       </c>
       <c r="O431" t="n">
-        <v>64993.114285713</v>
+        <v>64993.114615386</v>
       </c>
       <c r="P431" t="n">
         <v>30000</v>
@@ -20333,22 +20333,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M434" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="N434" t="n">
         <v>415.07</v>
       </c>
       <c r="O434" t="n">
-        <v>9546.610000000001</v>
+        <v>5395.91</v>
       </c>
       <c r="P434" t="n">
         <v>2900</v>
       </c>
       <c r="Q434" t="n">
-        <v>66700</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="435">
@@ -21264,10 +21264,10 @@
         <v>54</v>
       </c>
       <c r="N454" t="n">
-        <v>3088.1422807018</v>
+        <v>3088.1425</v>
       </c>
       <c r="O454" t="n">
-        <v>166759.6831578972</v>
+        <v>166759.695</v>
       </c>
       <c r="P454" t="n">
         <v>8500</v>
@@ -21555,10 +21555,10 @@
         <v>42</v>
       </c>
       <c r="N460" t="n">
-        <v>2432.1346</v>
+        <v>2432.1346938776</v>
       </c>
       <c r="O460" t="n">
-        <v>102149.6532</v>
+        <v>102149.6571428592</v>
       </c>
       <c r="P460" t="n">
         <v>4500</v>
@@ -22285,22 +22285,22 @@
         <v>0</v>
       </c>
       <c r="L476" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M476" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="N476" t="n">
         <v>753.98</v>
       </c>
       <c r="O476" t="n">
-        <v>37699</v>
+        <v>753.98</v>
       </c>
       <c r="P476" t="n">
         <v>4000</v>
       </c>
       <c r="Q476" t="n">
-        <v>200000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="477">
@@ -22469,22 +22469,22 @@
         <v>0</v>
       </c>
       <c r="L480" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M480" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N480" t="n">
         <v>2361.5097142857</v>
       </c>
       <c r="O480" t="n">
-        <v>66122.27199999959</v>
+        <v>56676.2331428568</v>
       </c>
       <c r="P480" t="n">
         <v>6200</v>
       </c>
       <c r="Q480" t="n">
-        <v>173600</v>
+        <v>148800</v>
       </c>
     </row>
     <row r="481">

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3053333333</v>
+        <v>1811.3054760423</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.9199999881</v>
+        <v>652069.971375228</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -3178,10 +3178,10 @@
         <v>33</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101612903</v>
+        <v>4937.3101616458</v>
       </c>
       <c r="O65" t="n">
-        <v>162931.2353225799</v>
+        <v>162931.2353343114</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3350,10 +3350,10 @@
         <v>144</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0566124294</v>
+        <v>1098.0571872808</v>
       </c>
       <c r="O69" t="n">
-        <v>158120.1521898336</v>
+        <v>158120.2349684352</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3624,10 +3624,10 @@
         <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.255965161</v>
+        <v>2582.2559238797</v>
       </c>
       <c r="O75" t="n">
-        <v>2509952.798136492</v>
+        <v>2509952.758011068</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3664,22 +3664,22 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M76" t="n">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="N76" t="n">
-        <v>5216.8962134973</v>
+        <v>5216.8961954233</v>
       </c>
       <c r="O76" t="n">
-        <v>7501896.755009118</v>
+        <v>7470595.351846166</v>
       </c>
       <c r="P76" t="n">
         <v>8500</v>
       </c>
       <c r="Q76" t="n">
-        <v>12223000</v>
+        <v>12172000</v>
       </c>
     </row>
     <row r="77">
@@ -3762,10 +3762,10 @@
         <v>3410</v>
       </c>
       <c r="N78" t="n">
-        <v>3158.86082365</v>
+        <v>3158.860824576</v>
       </c>
       <c r="O78" t="n">
-        <v>10771715.4086465</v>
+        <v>10771715.41180416</v>
       </c>
       <c r="P78" t="n">
         <v>5600</v>
@@ -3808,10 +3808,10 @@
         <v>320</v>
       </c>
       <c r="N79" t="n">
-        <v>3841.6247693817</v>
+        <v>3841.6247787611</v>
       </c>
       <c r="O79" t="n">
-        <v>1229319.926202144</v>
+        <v>1229319.929203552</v>
       </c>
       <c r="P79" t="n">
         <v>6900</v>
@@ -3857,10 +3857,10 @@
         <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>3230.0675313059</v>
+        <v>3230.0675179856</v>
       </c>
       <c r="O80" t="n">
-        <v>193804.051878354</v>
+        <v>193804.051079136</v>
       </c>
       <c r="P80" t="n">
         <v>6200</v>
@@ -3903,10 +3903,10 @@
         <v>514</v>
       </c>
       <c r="N81" t="n">
-        <v>2694.8232839963</v>
+        <v>2694.8232527881</v>
       </c>
       <c r="O81" t="n">
-        <v>1385139.167974098</v>
+        <v>1385139.151933083</v>
       </c>
       <c r="P81" t="n">
         <v>4900</v>
@@ -4234,10 +4234,10 @@
         <v>332</v>
       </c>
       <c r="N88" t="n">
-        <v>3594.2541140405</v>
+        <v>3594.2540923077</v>
       </c>
       <c r="O88" t="n">
-        <v>1193292.365861446</v>
+        <v>1193292.358646156</v>
       </c>
       <c r="P88" t="n">
         <v>6500</v>
@@ -4274,22 +4274,22 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M89" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="N89" t="n">
-        <v>14822.378858502</v>
+        <v>14822.378857823</v>
       </c>
       <c r="O89" t="n">
-        <v>4150266.08038056</v>
+        <v>4090976.564759148</v>
       </c>
       <c r="P89" t="n">
         <v>24900</v>
       </c>
       <c r="Q89" t="n">
-        <v>6972000</v>
+        <v>6872400</v>
       </c>
     </row>
     <row r="90">
@@ -4463,10 +4463,10 @@
         <v>22</v>
       </c>
       <c r="N93" t="n">
-        <v>19098.75000466</v>
+        <v>19098.750004662</v>
       </c>
       <c r="O93" t="n">
-        <v>420172.50010252</v>
+        <v>420172.500102564</v>
       </c>
       <c r="P93" t="n">
         <v>15000</v>
@@ -4591,10 +4591,10 @@
         <v>317</v>
       </c>
       <c r="N96" t="n">
-        <v>4372.2107879391</v>
+        <v>4372.210788556</v>
       </c>
       <c r="O96" t="n">
-        <v>1385990.819776695</v>
+        <v>1385990.819972252</v>
       </c>
       <c r="P96" t="n">
         <v>7500</v>
@@ -4718,22 +4718,22 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M99" t="n">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="N99" t="n">
-        <v>1592.5672645976</v>
+        <v>1592.5670868347</v>
       </c>
       <c r="O99" t="n">
-        <v>388586.4125618144</v>
+        <v>340809.3565826258</v>
       </c>
       <c r="P99" t="n">
         <v>3900</v>
       </c>
       <c r="Q99" t="n">
-        <v>951600</v>
+        <v>834600</v>
       </c>
     </row>
     <row r="100">
@@ -5363,10 +5363,10 @@
         <v>636</v>
       </c>
       <c r="N113" t="n">
-        <v>1630.9233376736</v>
+        <v>1630.9233676374</v>
       </c>
       <c r="O113" t="n">
-        <v>1037267.24276041</v>
+        <v>1037267.261817386</v>
       </c>
       <c r="P113" t="n">
         <v>2500</v>
@@ -5409,10 +5409,10 @@
         <v>23</v>
       </c>
       <c r="N114" t="n">
-        <v>1550.1933547279</v>
+        <v>1550.1933908991</v>
       </c>
       <c r="O114" t="n">
-        <v>35654.4471587417</v>
+        <v>35654.4479906793</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5495,22 +5495,22 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M116" t="n">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="N116" t="n">
-        <v>2403.5109560769</v>
+        <v>2403.5111708633</v>
       </c>
       <c r="O116" t="n">
-        <v>411000.3734891499</v>
+        <v>295631.8740161859</v>
       </c>
       <c r="P116" t="n">
         <v>3500</v>
       </c>
       <c r="Q116" t="n">
-        <v>598500</v>
+        <v>430500</v>
       </c>
     </row>
     <row r="117">
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M117" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2521.5405895197</v>
+        <v>2521.5386298077</v>
       </c>
       <c r="O117" t="n">
-        <v>141206.2730131032</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
         <v>3900</v>
       </c>
       <c r="Q117" t="n">
-        <v>218400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -6248,10 +6248,10 @@
         <v>103</v>
       </c>
       <c r="N133" t="n">
-        <v>5449.5305</v>
+        <v>5449.5305042017</v>
       </c>
       <c r="O133" t="n">
-        <v>561301.6415</v>
+        <v>561301.641932775</v>
       </c>
       <c r="P133" t="n">
         <v>6200</v>
@@ -6335,10 +6335,10 @@
         <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>2029.8737110341</v>
+        <v>2029.8737332006</v>
       </c>
       <c r="O135" t="n">
-        <v>4059.7474220682</v>
+        <v>4059.7474664012</v>
       </c>
       <c r="P135" t="n">
         <v>3600</v>
@@ -7096,10 +7096,10 @@
         <v>21</v>
       </c>
       <c r="N153" t="n">
-        <v>1508.5871111111</v>
+        <v>1508.5870454545</v>
       </c>
       <c r="O153" t="n">
-        <v>31680.3293333331</v>
+        <v>31680.3279545445</v>
       </c>
       <c r="P153" t="n">
         <v>3600</v>
@@ -7224,10 +7224,10 @@
         <v>5</v>
       </c>
       <c r="N156" t="n">
-        <v>7969.9501652893</v>
+        <v>7969.9501660377</v>
       </c>
       <c r="O156" t="n">
-        <v>39849.7508264465</v>
+        <v>39849.7508301885</v>
       </c>
       <c r="P156" t="n">
         <v>12900</v>
@@ -7896,22 +7896,22 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M171" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="N171" t="n">
-        <v>5218.1705269461</v>
+        <v>5218.1705339806</v>
       </c>
       <c r="O171" t="n">
-        <v>532253.3937485022</v>
+        <v>427889.9837864093</v>
       </c>
       <c r="P171" t="n">
         <v>8500</v>
       </c>
       <c r="Q171" t="n">
-        <v>867000</v>
+        <v>697000</v>
       </c>
     </row>
     <row r="172">
@@ -7948,10 +7948,10 @@
         <v>72</v>
       </c>
       <c r="N172" t="n">
-        <v>1595.0094189602</v>
+        <v>1595.0094144838</v>
       </c>
       <c r="O172" t="n">
-        <v>114840.6781651344</v>
+        <v>114840.6778428336</v>
       </c>
       <c r="P172" t="n">
         <v>2600</v>
@@ -8172,22 +8172,22 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M177" t="n">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="N177" t="n">
         <v>1812.57</v>
       </c>
       <c r="O177" t="n">
-        <v>177631.86</v>
+        <v>43501.68</v>
       </c>
       <c r="P177" t="n">
         <v>2900</v>
       </c>
       <c r="Q177" t="n">
-        <v>284200</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="178">
@@ -9248,10 +9248,10 @@
         <v>552</v>
       </c>
       <c r="N200" t="n">
-        <v>1516.0388052024</v>
+        <v>1516.0388047383</v>
       </c>
       <c r="O200" t="n">
-        <v>836853.4204717248</v>
+        <v>836853.4202155416</v>
       </c>
       <c r="P200" t="n">
         <v>2300</v>
@@ -9294,10 +9294,10 @@
         <v>432</v>
       </c>
       <c r="N201" t="n">
-        <v>2458.5133724619</v>
+        <v>2458.5132807977</v>
       </c>
       <c r="O201" t="n">
-        <v>1062077.776903541</v>
+        <v>1062077.737304606</v>
       </c>
       <c r="P201" t="n">
         <v>3500</v>
@@ -9340,10 +9340,10 @@
         <v>144</v>
       </c>
       <c r="N202" t="n">
-        <v>1771.0908132147</v>
+        <v>1775.6031464968</v>
       </c>
       <c r="O202" t="n">
-        <v>255037.0771029168</v>
+        <v>255686.8530955392</v>
       </c>
       <c r="P202" t="n">
         <v>2500</v>
@@ -9386,10 +9386,10 @@
         <v>240</v>
       </c>
       <c r="N203" t="n">
-        <v>2079.384121911</v>
+        <v>2079.3840612517</v>
       </c>
       <c r="O203" t="n">
-        <v>499052.18925864</v>
+        <v>499052.174700408</v>
       </c>
       <c r="P203" t="n">
         <v>2900</v>
@@ -9432,10 +9432,10 @@
         <v>266</v>
       </c>
       <c r="N204" t="n">
-        <v>1803.0152282542</v>
+        <v>1803.015492547</v>
       </c>
       <c r="O204" t="n">
-        <v>479602.0507156173</v>
+        <v>479602.121017502</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9524,10 +9524,10 @@
         <v>264</v>
       </c>
       <c r="N206" t="n">
-        <v>2122.1639833897</v>
+        <v>2122.163972265</v>
       </c>
       <c r="O206" t="n">
-        <v>560251.2916148809</v>
+        <v>560251.2886779601</v>
       </c>
       <c r="P206" t="n">
         <v>2900</v>
@@ -9570,10 +9570,10 @@
         <v>144</v>
       </c>
       <c r="N207" t="n">
-        <v>2108.7902645503</v>
+        <v>2108.7909398496</v>
       </c>
       <c r="O207" t="n">
-        <v>303665.7980952432</v>
+        <v>303665.8953383424</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -9616,10 +9616,10 @@
         <v>288</v>
       </c>
       <c r="N208" t="n">
-        <v>2056.0836725935</v>
+        <v>2056.0835600624</v>
       </c>
       <c r="O208" t="n">
-        <v>592152.097706928</v>
+        <v>592152.0652979712</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9662,10 +9662,10 @@
         <v>216</v>
       </c>
       <c r="N209" t="n">
-        <v>3224.5683024119</v>
+        <v>3224.5684753788</v>
       </c>
       <c r="O209" t="n">
-        <v>696506.7533209703</v>
+        <v>696506.7906818208</v>
       </c>
       <c r="P209" t="n">
         <v>4500</v>
@@ -9748,22 +9748,22 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M211" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="N211" t="n">
-        <v>1592.2763108883</v>
+        <v>1592.2766843703</v>
       </c>
       <c r="O211" t="n">
-        <v>154450.8021561651</v>
+        <v>1592.2766843703</v>
       </c>
       <c r="P211" t="n">
         <v>2500</v>
       </c>
       <c r="Q211" t="n">
-        <v>242500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="212">
@@ -9844,10 +9844,10 @@
         <v>36</v>
       </c>
       <c r="N213" t="n">
-        <v>2311.9216849015</v>
+        <v>2311.9216447368</v>
       </c>
       <c r="O213" t="n">
-        <v>83229.180656454</v>
+        <v>83229.1792105248</v>
       </c>
       <c r="P213" t="n">
         <v>3500</v>
@@ -9890,10 +9890,10 @@
         <v>12</v>
       </c>
       <c r="N214" t="n">
-        <v>1906.1853271028</v>
+        <v>1906.1850980392</v>
       </c>
       <c r="O214" t="n">
-        <v>22874.2239252336</v>
+        <v>22874.2211764704</v>
       </c>
       <c r="P214" t="n">
         <v>2900</v>
@@ -9982,10 +9982,10 @@
         <v>600</v>
       </c>
       <c r="N216" t="n">
-        <v>1259.2745016722</v>
+        <v>1259.2745137492</v>
       </c>
       <c r="O216" t="n">
-        <v>755564.7010033199</v>
+        <v>755564.7082495199</v>
       </c>
       <c r="P216" t="n">
         <v>1900</v>
@@ -10674,22 +10674,22 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N231" t="n">
         <v>1245.62</v>
       </c>
       <c r="O231" t="n">
-        <v>432230.14</v>
+        <v>430984.52</v>
       </c>
       <c r="P231" t="n">
         <v>4000</v>
       </c>
       <c r="Q231" t="n">
-        <v>1388000</v>
+        <v>1384000</v>
       </c>
     </row>
     <row r="232">
@@ -10864,10 +10864,10 @@
         <v>37</v>
       </c>
       <c r="N235" t="n">
-        <v>6898.4</v>
+        <v>6939.3400593472</v>
       </c>
       <c r="O235" t="n">
-        <v>255240.8</v>
+        <v>256755.5821958464</v>
       </c>
       <c r="P235" t="n">
         <v>12900</v>
@@ -11005,10 +11005,10 @@
         <v>1</v>
       </c>
       <c r="N238" t="n">
-        <v>1690.870009009</v>
+        <v>1690.8700090131</v>
       </c>
       <c r="O238" t="n">
-        <v>1690.870009009</v>
+        <v>1690.8700090131</v>
       </c>
       <c r="P238" t="n">
         <v>3000</v>
@@ -11299,10 +11299,10 @@
         <v>2280</v>
       </c>
       <c r="N244" t="n">
-        <v>517.2884408203601</v>
+        <v>517.28876931766</v>
       </c>
       <c r="O244" t="n">
-        <v>1179417.645070421</v>
+        <v>1179418.394044265</v>
       </c>
       <c r="P244" t="n">
         <v>900</v>
@@ -11440,10 +11440,10 @@
         <v>59</v>
       </c>
       <c r="N247" t="n">
-        <v>3259.1342528736</v>
+        <v>3259.1342692308</v>
       </c>
       <c r="O247" t="n">
-        <v>192288.9209195424</v>
+        <v>192288.9218846172</v>
       </c>
       <c r="P247" t="n">
         <v>3600</v>
@@ -11538,10 +11538,10 @@
         <v>504</v>
       </c>
       <c r="N249" t="n">
-        <v>3110.8425641565</v>
+        <v>3110.8424546425</v>
       </c>
       <c r="O249" t="n">
-        <v>1567864.652334876</v>
+        <v>1567864.59713982</v>
       </c>
       <c r="P249" t="n">
         <v>4500</v>
@@ -11766,10 +11766,10 @@
         <v>13152</v>
       </c>
       <c r="N254" t="n">
-        <v>703.79526826968</v>
+        <v>703.7952483310401</v>
       </c>
       <c r="O254" t="n">
-        <v>9256315.368282832</v>
+        <v>9256315.106049839</v>
       </c>
       <c r="P254" t="n">
         <v>900</v>
@@ -11861,10 +11861,10 @@
         <v>161</v>
       </c>
       <c r="N256" t="n">
-        <v>3182.2511009174</v>
+        <v>3182.2511070111</v>
       </c>
       <c r="O256" t="n">
-        <v>512342.4272477014</v>
+        <v>512342.4282287871</v>
       </c>
       <c r="P256" t="n">
         <v>6900</v>
@@ -12045,10 +12045,10 @@
         <v>59</v>
       </c>
       <c r="N260" t="n">
-        <v>2501.3850684932</v>
+        <v>2501.3850230415</v>
       </c>
       <c r="O260" t="n">
-        <v>147581.7190410988</v>
+        <v>147581.7163594485</v>
       </c>
       <c r="P260" t="n">
         <v>4100</v>
@@ -13010,10 +13010,10 @@
         <v>5</v>
       </c>
       <c r="N280" t="n">
-        <v>2832.1948571429</v>
+        <v>2832.1949275362</v>
       </c>
       <c r="O280" t="n">
-        <v>14160.9742857145</v>
+        <v>14160.974637681</v>
       </c>
       <c r="P280" t="n">
         <v>12900</v>
@@ -14839,10 +14839,10 @@
         <v>60</v>
       </c>
       <c r="N318" t="n">
-        <v>3067.0905454545</v>
+        <v>3067.0905844156</v>
       </c>
       <c r="O318" t="n">
-        <v>184025.43272727</v>
+        <v>184025.435064936</v>
       </c>
       <c r="P318" t="n">
         <v>7200</v>
@@ -15419,10 +15419,10 @@
         <v>1000</v>
       </c>
       <c r="N330" t="n">
-        <v>1783.7988833409</v>
+        <v>1783.798877225</v>
       </c>
       <c r="O330" t="n">
-        <v>1783798.8833409</v>
+        <v>1783798.877225</v>
       </c>
       <c r="P330" t="n">
         <v>1500</v>
@@ -17343,10 +17343,10 @@
         <v>8</v>
       </c>
       <c r="N370" t="n">
-        <v>7046.9398286204</v>
+        <v>7046.9398281418</v>
       </c>
       <c r="O370" t="n">
-        <v>56375.5186289632</v>
+        <v>56375.5186251344</v>
       </c>
       <c r="P370" t="n">
         <v>9900</v>
@@ -17392,10 +17392,10 @@
         <v>2</v>
       </c>
       <c r="N371" t="n">
-        <v>26378.027</v>
+        <v>26378.026666667</v>
       </c>
       <c r="O371" t="n">
-        <v>52756.054</v>
+        <v>52756.053333334</v>
       </c>
       <c r="P371" t="n">
         <v>36500</v>
@@ -17830,10 +17830,10 @@
         <v>35</v>
       </c>
       <c r="N380" t="n">
-        <v>424.99</v>
+        <v>432.57910714286</v>
       </c>
       <c r="O380" t="n">
-        <v>14874.65</v>
+        <v>15140.2687500001</v>
       </c>
       <c r="P380" t="n">
         <v>2300</v>
@@ -18173,10 +18173,10 @@
         <v>455</v>
       </c>
       <c r="N387" t="n">
-        <v>315.02685915493</v>
+        <v>315.02694721826</v>
       </c>
       <c r="O387" t="n">
-        <v>143337.2209154931</v>
+        <v>143337.2609843083</v>
       </c>
       <c r="P387" t="n">
         <v>2200</v>
@@ -18448,10 +18448,10 @@
         <v>26</v>
       </c>
       <c r="N393" t="n">
-        <v>22951.704956085</v>
+        <v>22951.704917826</v>
       </c>
       <c r="O393" t="n">
-        <v>596744.32885821</v>
+        <v>596744.327863476</v>
       </c>
       <c r="P393" t="n">
         <v>37900</v>
@@ -18636,22 +18636,22 @@
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N397" t="n">
         <v>4125</v>
       </c>
       <c r="O397" t="n">
-        <v>177375</v>
+        <v>173250</v>
       </c>
       <c r="P397" t="n">
         <v>5500</v>
       </c>
       <c r="Q397" t="n">
-        <v>236500</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="398">
@@ -18693,10 +18693,10 @@
         <v>43</v>
       </c>
       <c r="N398" t="n">
-        <v>1757.3205462185</v>
+        <v>1775.9757537155</v>
       </c>
       <c r="O398" t="n">
-        <v>75564.7834873955</v>
+        <v>76366.9574097665</v>
       </c>
       <c r="P398" t="n">
         <v>2000</v>
@@ -21509,10 +21509,10 @@
         <v>235</v>
       </c>
       <c r="N459" t="n">
-        <v>227.41597222222</v>
+        <v>229.09061119293</v>
       </c>
       <c r="O459" t="n">
-        <v>53442.7534722217</v>
+        <v>53836.29363033855</v>
       </c>
       <c r="P459" t="n">
         <v>1200</v>
@@ -22010,10 +22010,10 @@
         <v>1</v>
       </c>
       <c r="N470" t="n">
-        <v>3450.4864435564</v>
+        <v>3450.4864371257</v>
       </c>
       <c r="O470" t="n">
-        <v>3450.4864435564</v>
+        <v>3450.4864371257</v>
       </c>
       <c r="P470" t="n">
         <v>5000</v>
@@ -22561,22 +22561,22 @@
         <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M482" t="n">
-        <v>499</v>
+        <v>451</v>
       </c>
       <c r="N482" t="n">
         <v>855.85</v>
       </c>
       <c r="O482" t="n">
-        <v>427069.15</v>
+        <v>385988.35</v>
       </c>
       <c r="P482" t="n">
         <v>3500</v>
       </c>
       <c r="Q482" t="n">
-        <v>1746500</v>
+        <v>1578500</v>
       </c>
     </row>
     <row r="483">
@@ -22751,10 +22751,10 @@
         <v>171</v>
       </c>
       <c r="N486" t="n">
-        <v>341.02142276423</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O486" t="n">
-        <v>58314.66329268333</v>
+        <v>58314.66528688533</v>
       </c>
       <c r="P486" t="n">
         <v>14500</v>
@@ -22797,10 +22797,10 @@
         <v>32</v>
       </c>
       <c r="N487" t="n">
-        <v>4158.2962162162</v>
+        <v>4158.2961111111</v>
       </c>
       <c r="O487" t="n">
-        <v>133065.4789189184</v>
+        <v>133065.4755555552</v>
       </c>
       <c r="P487" t="n">
         <v>13800</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3054760423</v>
+        <v>1811.3058666667</v>
       </c>
       <c r="O6" t="n">
-        <v>652069.971375228</v>
+        <v>652070.112000012</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -3350,10 +3350,10 @@
         <v>144</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0571872808</v>
+        <v>1098.0574483741</v>
       </c>
       <c r="O69" t="n">
-        <v>158120.2349684352</v>
+        <v>158120.2725658704</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
@@ -3624,10 +3624,10 @@
         <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2559238797</v>
+        <v>2582.2558919365</v>
       </c>
       <c r="O75" t="n">
-        <v>2509952.758011068</v>
+        <v>2509952.726962278</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3670,10 +3670,10 @@
         <v>1432</v>
       </c>
       <c r="N76" t="n">
-        <v>5216.8961954233</v>
+        <v>5216.8961798703</v>
       </c>
       <c r="O76" t="n">
-        <v>7470595.351846166</v>
+        <v>7470595.32957427</v>
       </c>
       <c r="P76" t="n">
         <v>8500</v>
@@ -3762,10 +3762,10 @@
         <v>3410</v>
       </c>
       <c r="N78" t="n">
-        <v>3158.860824576</v>
+        <v>3158.8608246566</v>
       </c>
       <c r="O78" t="n">
-        <v>10771715.41180416</v>
+        <v>10771715.41207901</v>
       </c>
       <c r="P78" t="n">
         <v>5600</v>
@@ -3857,10 +3857,10 @@
         <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>3230.0675179856</v>
+        <v>3230.0674725275</v>
       </c>
       <c r="O80" t="n">
-        <v>193804.051079136</v>
+        <v>193804.04835165</v>
       </c>
       <c r="P80" t="n">
         <v>6200</v>
@@ -4234,10 +4234,10 @@
         <v>332</v>
       </c>
       <c r="N88" t="n">
-        <v>3594.2540923077</v>
+        <v>3594.25408867</v>
       </c>
       <c r="O88" t="n">
-        <v>1193292.358646156</v>
+        <v>1193292.35743844</v>
       </c>
       <c r="P88" t="n">
         <v>6500</v>
@@ -4280,10 +4280,10 @@
         <v>276</v>
       </c>
       <c r="N89" t="n">
-        <v>14822.378857823</v>
+        <v>14822.378855098</v>
       </c>
       <c r="O89" t="n">
-        <v>4090976.564759148</v>
+        <v>4090976.564007048</v>
       </c>
       <c r="P89" t="n">
         <v>24900</v>
@@ -4463,10 +4463,10 @@
         <v>22</v>
       </c>
       <c r="N93" t="n">
-        <v>19098.750004662</v>
+        <v>19098.750004663</v>
       </c>
       <c r="O93" t="n">
-        <v>420172.500102564</v>
+        <v>420172.500102586</v>
       </c>
       <c r="P93" t="n">
         <v>15000</v>
@@ -4724,10 +4724,10 @@
         <v>214</v>
       </c>
       <c r="N99" t="n">
-        <v>1592.5670868347</v>
+        <v>1592.5670028818</v>
       </c>
       <c r="O99" t="n">
-        <v>340809.3565826258</v>
+        <v>340809.3386167052</v>
       </c>
       <c r="P99" t="n">
         <v>3900</v>
@@ -5363,10 +5363,10 @@
         <v>636</v>
       </c>
       <c r="N113" t="n">
-        <v>1630.9233676374</v>
+        <v>1630.9234162594</v>
       </c>
       <c r="O113" t="n">
-        <v>1037267.261817386</v>
+        <v>1037267.292740978</v>
       </c>
       <c r="P113" t="n">
         <v>2500</v>
@@ -5409,10 +5409,10 @@
         <v>23</v>
       </c>
       <c r="N114" t="n">
-        <v>1550.1933908991</v>
+        <v>1550.1934418475</v>
       </c>
       <c r="O114" t="n">
-        <v>35654.4479906793</v>
+        <v>35654.4491624925</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5501,10 +5501,10 @@
         <v>123</v>
       </c>
       <c r="N116" t="n">
-        <v>2403.5111708633</v>
+        <v>2403.5113112366</v>
       </c>
       <c r="O116" t="n">
-        <v>295631.8740161859</v>
+        <v>295631.8912821018</v>
       </c>
       <c r="P116" t="n">
         <v>3500</v>
@@ -6161,10 +6161,10 @@
         <v>109</v>
       </c>
       <c r="N131" t="n">
-        <v>4196.8725263158</v>
+        <v>4196.872528417</v>
       </c>
       <c r="O131" t="n">
-        <v>457459.1053684222</v>
+        <v>457459.105597453</v>
       </c>
       <c r="P131" t="n">
         <v>5900</v>
@@ -6412,10 +6412,10 @@
         <v>402</v>
       </c>
       <c r="N137" t="n">
-        <v>880.32937295274</v>
+        <v>880.32945034206</v>
       </c>
       <c r="O137" t="n">
-        <v>353892.4079270015</v>
+        <v>353892.4390375081</v>
       </c>
       <c r="P137" t="n">
         <v>1200</v>
@@ -7856,10 +7856,10 @@
         <v>82</v>
       </c>
       <c r="N170" t="n">
-        <v>5218.1705339806</v>
+        <v>5218.1705346294</v>
       </c>
       <c r="O170" t="n">
-        <v>427889.9837864093</v>
+        <v>427889.9838396108</v>
       </c>
       <c r="P170" t="n">
         <v>8500</v>
@@ -7902,10 +7902,10 @@
         <v>72</v>
       </c>
       <c r="N171" t="n">
-        <v>1595.0094144838</v>
+        <v>1595.0094090202</v>
       </c>
       <c r="O171" t="n">
-        <v>114840.6778428336</v>
+        <v>114840.6774494544</v>
       </c>
       <c r="P171" t="n">
         <v>2600</v>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7991,19 +7991,19 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="N173" t="n">
         <v>3965.02</v>
       </c>
       <c r="O173" t="n">
-        <v>384606.94</v>
+        <v>325131.64</v>
       </c>
       <c r="P173" t="n">
         <v>6500</v>
       </c>
       <c r="Q173" t="n">
-        <v>630500</v>
+        <v>533000</v>
       </c>
     </row>
     <row r="174">
@@ -9202,10 +9202,10 @@
         <v>552</v>
       </c>
       <c r="N199" t="n">
-        <v>1516.0388047383</v>
+        <v>1516.0388031113</v>
       </c>
       <c r="O199" t="n">
-        <v>836853.4202155416</v>
+        <v>836853.4193174376</v>
       </c>
       <c r="P199" t="n">
         <v>2300</v>
@@ -9294,10 +9294,10 @@
         <v>144</v>
       </c>
       <c r="N201" t="n">
-        <v>1771.0907898089</v>
+        <v>1771.0906468305</v>
       </c>
       <c r="O201" t="n">
-        <v>255037.0737324816</v>
+        <v>255037.053143592</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9340,10 +9340,10 @@
         <v>240</v>
       </c>
       <c r="N202" t="n">
-        <v>2079.3840612517</v>
+        <v>2079.3840533333</v>
       </c>
       <c r="O202" t="n">
-        <v>499052.174700408</v>
+        <v>499052.172799992</v>
       </c>
       <c r="P202" t="n">
         <v>2900</v>
@@ -9386,10 +9386,10 @@
         <v>266</v>
       </c>
       <c r="N203" t="n">
-        <v>1803.015492547</v>
+        <v>1803.0155537353</v>
       </c>
       <c r="O203" t="n">
-        <v>479602.121017502</v>
+        <v>479602.1372935898</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9478,10 +9478,10 @@
         <v>264</v>
       </c>
       <c r="N205" t="n">
-        <v>2122.163972265</v>
+        <v>2122.1639235788</v>
       </c>
       <c r="O205" t="n">
-        <v>560251.2886779601</v>
+        <v>560251.2758248033</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>144</v>
       </c>
       <c r="N206" t="n">
-        <v>2108.7909398496</v>
+        <v>2108.7910927573</v>
       </c>
       <c r="O206" t="n">
-        <v>303665.8953383424</v>
+        <v>303665.9173570512</v>
       </c>
       <c r="P206" t="n">
         <v>2900</v>
@@ -9570,10 +9570,10 @@
         <v>288</v>
       </c>
       <c r="N207" t="n">
-        <v>2056.0835600624</v>
+        <v>2056.0834704208</v>
       </c>
       <c r="O207" t="n">
-        <v>592152.0652979712</v>
+        <v>592152.0394811904</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -9616,10 +9616,10 @@
         <v>216</v>
       </c>
       <c r="N208" t="n">
-        <v>3224.5684753788</v>
+        <v>3224.5685035629</v>
       </c>
       <c r="O208" t="n">
-        <v>696506.7906818208</v>
+        <v>696506.7967695864</v>
       </c>
       <c r="P208" t="n">
         <v>4500</v>
@@ -9662,10 +9662,10 @@
         <v>288</v>
       </c>
       <c r="N209" t="n">
-        <v>1655.9309931618</v>
+        <v>1655.9309755302</v>
       </c>
       <c r="O209" t="n">
-        <v>476908.1260305984</v>
+        <v>476908.1209526976</v>
       </c>
       <c r="P209" t="n">
         <v>2500</v>
@@ -9708,10 +9708,10 @@
         <v>1</v>
       </c>
       <c r="N210" t="n">
-        <v>1592.2766843703</v>
+        <v>1592.276898982</v>
       </c>
       <c r="O210" t="n">
-        <v>1592.2766843703</v>
+        <v>1592.276898982</v>
       </c>
       <c r="P210" t="n">
         <v>2500</v>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9749,19 +9749,19 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="N211" t="n">
         <v>5347.73</v>
       </c>
       <c r="O211" t="n">
-        <v>235300.12</v>
+        <v>171127.36</v>
       </c>
       <c r="P211" t="n">
         <v>9500</v>
       </c>
       <c r="Q211" t="n">
-        <v>418000</v>
+        <v>304000</v>
       </c>
     </row>
     <row r="212">
@@ -9798,10 +9798,10 @@
         <v>36</v>
       </c>
       <c r="N212" t="n">
-        <v>2311.9216447368</v>
+        <v>2311.9211486486</v>
       </c>
       <c r="O212" t="n">
-        <v>83229.1792105248</v>
+        <v>83229.16135134961</v>
       </c>
       <c r="P212" t="n">
         <v>3500</v>
@@ -9890,10 +9890,10 @@
         <v>48</v>
       </c>
       <c r="N214" t="n">
-        <v>2546.9846816479</v>
+        <v>2546.9846516008</v>
       </c>
       <c r="O214" t="n">
-        <v>122255.2647190992</v>
+        <v>122255.2632768384</v>
       </c>
       <c r="P214" t="n">
         <v>3900</v>
@@ -10113,10 +10113,10 @@
         <v>192</v>
       </c>
       <c r="N219" t="n">
-        <v>692.1521205151799</v>
+        <v>692.15220363289</v>
       </c>
       <c r="O219" t="n">
-        <v>132893.2071389146</v>
+        <v>132893.2230975149</v>
       </c>
       <c r="P219" t="n">
         <v>1200</v>
@@ -10959,10 +10959,10 @@
         <v>1</v>
       </c>
       <c r="N237" t="n">
-        <v>1690.8700090131</v>
+        <v>1690.870009058</v>
       </c>
       <c r="O237" t="n">
-        <v>1690.8700090131</v>
+        <v>1690.870009058</v>
       </c>
       <c r="P237" t="n">
         <v>3000</v>
@@ -11253,10 +11253,10 @@
         <v>2280</v>
       </c>
       <c r="N243" t="n">
-        <v>517.28876931766</v>
+        <v>517.28896164542</v>
       </c>
       <c r="O243" t="n">
-        <v>1179418.394044265</v>
+        <v>1179418.832551558</v>
       </c>
       <c r="P243" t="n">
         <v>900</v>
@@ -11492,10 +11492,10 @@
         <v>504</v>
       </c>
       <c r="N248" t="n">
-        <v>3110.8424546425</v>
+        <v>3110.8423302235</v>
       </c>
       <c r="O248" t="n">
-        <v>1567864.59713982</v>
+        <v>1567864.534432644</v>
       </c>
       <c r="P248" t="n">
         <v>4500</v>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>13152</v>
+        <v>12794</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11717,19 +11717,19 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>13152</v>
+        <v>12794</v>
       </c>
       <c r="N253" t="n">
-        <v>703.7952483310401</v>
+        <v>703.79522697548</v>
       </c>
       <c r="O253" t="n">
-        <v>9256315.106049839</v>
+        <v>9004356.133924291</v>
       </c>
       <c r="P253" t="n">
         <v>900</v>
       </c>
       <c r="Q253" t="n">
-        <v>11836800</v>
+        <v>11514600</v>
       </c>
     </row>
     <row r="254">
@@ -11999,10 +11999,10 @@
         <v>59</v>
       </c>
       <c r="N259" t="n">
-        <v>2501.3850230415</v>
+        <v>2501.385</v>
       </c>
       <c r="O259" t="n">
-        <v>147581.7163594485</v>
+        <v>147581.715</v>
       </c>
       <c r="P259" t="n">
         <v>4100</v>
@@ -14113,10 +14113,10 @@
         <v>13</v>
       </c>
       <c r="N303" t="n">
-        <v>3093.3711111111</v>
+        <v>3093.3711764706</v>
       </c>
       <c r="O303" t="n">
-        <v>40213.8244444443</v>
+        <v>40213.8252941178</v>
       </c>
       <c r="P303" t="n">
         <v>11500</v>
@@ -15713,10 +15713,10 @@
         <v>1</v>
       </c>
       <c r="N336" t="n">
-        <v>10737.526326531</v>
+        <v>10737.526170213</v>
       </c>
       <c r="O336" t="n">
-        <v>10737.526326531</v>
+        <v>10737.526170213</v>
       </c>
       <c r="P336" t="n">
         <v>18900</v>
@@ -17735,10 +17735,10 @@
         <v>11</v>
       </c>
       <c r="N378" t="n">
-        <v>366.39980582524</v>
+        <v>366.3998019802</v>
       </c>
       <c r="O378" t="n">
-        <v>4030.39786407764</v>
+        <v>4030.3978217822</v>
       </c>
       <c r="P378" t="n">
         <v>2900</v>
@@ -18029,10 +18029,10 @@
         <v>984</v>
       </c>
       <c r="N384" t="n">
-        <v>430.6099765808</v>
+        <v>430.60997630332</v>
       </c>
       <c r="O384" t="n">
-        <v>423720.2169555072</v>
+        <v>423720.2166824669</v>
       </c>
       <c r="P384" t="n">
         <v>2200</v>
@@ -18078,10 +18078,10 @@
         <v>726</v>
       </c>
       <c r="N385" t="n">
-        <v>465.87093953488</v>
+        <v>465.87094835681</v>
       </c>
       <c r="O385" t="n">
-        <v>338222.3021023229</v>
+        <v>338222.308507044</v>
       </c>
       <c r="P385" t="n">
         <v>2500</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -18399,19 +18399,19 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N392" t="n">
-        <v>22951.704917826</v>
+        <v>22951.704911392</v>
       </c>
       <c r="O392" t="n">
-        <v>596744.327863476</v>
+        <v>527889.212962016</v>
       </c>
       <c r="P392" t="n">
         <v>37900</v>
       </c>
       <c r="Q392" t="n">
-        <v>985400</v>
+        <v>871700</v>
       </c>
     </row>
     <row r="393">
@@ -18647,10 +18647,10 @@
         <v>43</v>
       </c>
       <c r="N397" t="n">
-        <v>1757.320552017</v>
+        <v>1757.3205567452</v>
       </c>
       <c r="O397" t="n">
-        <v>75564.783736731</v>
+        <v>75564.78394004361</v>
       </c>
       <c r="P397" t="n">
         <v>2000</v>
@@ -19291,10 +19291,10 @@
         <v>1827</v>
       </c>
       <c r="N411" t="n">
-        <v>220.00651536869</v>
+        <v>220.00629713546</v>
       </c>
       <c r="O411" t="n">
-        <v>401951.9035785967</v>
+        <v>401951.5048664854</v>
       </c>
       <c r="P411" t="n">
         <v>260</v>
@@ -21964,10 +21964,10 @@
         <v>1</v>
       </c>
       <c r="N469" t="n">
-        <v>3450.4864371257</v>
+        <v>3450.4864435564</v>
       </c>
       <c r="O469" t="n">
-        <v>3450.4864371257</v>
+        <v>3450.4864435564</v>
       </c>
       <c r="P469" t="n">
         <v>5000</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3058666667</v>
+        <v>1811.3059701493</v>
       </c>
       <c r="O6" t="n">
-        <v>652070.112000012</v>
+        <v>652070.149253748</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2413.0010683761</v>
+        <v>2413.0010706638</v>
       </c>
       <c r="O18" t="n">
-        <v>4826.0021367522</v>
+        <v>4826.0021413276</v>
       </c>
       <c r="P18" t="n">
         <v>4700</v>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1315,19 +1315,19 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N23" t="n">
         <v>27000</v>
       </c>
       <c r="O23" t="n">
-        <v>1809000</v>
+        <v>1917000</v>
       </c>
       <c r="P23" t="n">
         <v>30000</v>
       </c>
       <c r="Q23" t="n">
-        <v>2010000</v>
+        <v>2130000</v>
       </c>
     </row>
     <row r="24">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1354,19 +1354,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N24" t="n">
         <v>21333.69</v>
       </c>
       <c r="O24" t="n">
-        <v>1109351.88</v>
+        <v>1024017.12</v>
       </c>
       <c r="P24" t="n">
         <v>30000</v>
       </c>
       <c r="Q24" t="n">
-        <v>1560000</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="25">
@@ -3178,10 +3178,10 @@
         <v>33</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="O65" t="n">
-        <v>162931.2353343114</v>
+        <v>162931.2353579328</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3344,22 +3344,22 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M69" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1098.0574483741</v>
+        <v>1098.0580436917</v>
       </c>
       <c r="O69" t="n">
-        <v>158120.2725658704</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
         <v>1500</v>
       </c>
       <c r="Q69" t="n">
-        <v>216000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3624,10 +3624,10 @@
         <v>972</v>
       </c>
       <c r="N75" t="n">
-        <v>2582.2558919365</v>
+        <v>2582.2558569052</v>
       </c>
       <c r="O75" t="n">
-        <v>2509952.726962278</v>
+        <v>2509952.692911854</v>
       </c>
       <c r="P75" t="n">
         <v>4500</v>
@@ -3664,22 +3664,22 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M76" t="n">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="N76" t="n">
-        <v>5216.8961798703</v>
+        <v>5216.8961652752</v>
       </c>
       <c r="O76" t="n">
-        <v>7470595.32957427</v>
+        <v>7288003.942889454</v>
       </c>
       <c r="P76" t="n">
         <v>8500</v>
       </c>
       <c r="Q76" t="n">
-        <v>12172000</v>
+        <v>11874500</v>
       </c>
     </row>
     <row r="77">
@@ -3762,10 +3762,10 @@
         <v>3410</v>
       </c>
       <c r="N78" t="n">
-        <v>3158.8608246566</v>
+        <v>3158.8608249792</v>
       </c>
       <c r="O78" t="n">
-        <v>10771715.41207901</v>
+        <v>10771715.41317907</v>
       </c>
       <c r="P78" t="n">
         <v>5600</v>
@@ -3857,10 +3857,10 @@
         <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>3230.0674725275</v>
+        <v>3230.0674157303</v>
       </c>
       <c r="O80" t="n">
-        <v>193804.04835165</v>
+        <v>193804.044943818</v>
       </c>
       <c r="P80" t="n">
         <v>6200</v>
@@ -3903,10 +3903,10 @@
         <v>514</v>
       </c>
       <c r="N81" t="n">
-        <v>2694.8232527881</v>
+        <v>2694.823243369</v>
       </c>
       <c r="O81" t="n">
-        <v>1385139.151933083</v>
+        <v>1385139.147091666</v>
       </c>
       <c r="P81" t="n">
         <v>4900</v>
@@ -4087,22 +4087,22 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4967.8238461538</v>
+        <v>4967.8308421053</v>
       </c>
       <c r="O85" t="n">
-        <v>14903.4715384614</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
         <v>7500</v>
       </c>
       <c r="Q85" t="n">
-        <v>22500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4234,10 +4234,10 @@
         <v>332</v>
       </c>
       <c r="N88" t="n">
-        <v>3594.25408867</v>
+        <v>3594.2540740741</v>
       </c>
       <c r="O88" t="n">
-        <v>1193292.35743844</v>
+        <v>1193292.352592601</v>
       </c>
       <c r="P88" t="n">
         <v>6500</v>
@@ -4280,10 +4280,10 @@
         <v>276</v>
       </c>
       <c r="N89" t="n">
-        <v>14822.378855098</v>
+        <v>14822.378854415</v>
       </c>
       <c r="O89" t="n">
-        <v>4090976.564007048</v>
+        <v>4090976.56381854</v>
       </c>
       <c r="P89" t="n">
         <v>24900</v>
@@ -4591,10 +4591,10 @@
         <v>317</v>
       </c>
       <c r="N96" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O96" t="n">
-        <v>1385990.819972252</v>
+        <v>1385990.820007819</v>
       </c>
       <c r="P96" t="n">
         <v>7500</v>
@@ -4724,10 +4724,10 @@
         <v>214</v>
       </c>
       <c r="N99" t="n">
-        <v>1592.5670028818</v>
+        <v>1592.5669608416</v>
       </c>
       <c r="O99" t="n">
-        <v>340809.3386167052</v>
+        <v>340809.3296201024</v>
       </c>
       <c r="P99" t="n">
         <v>3900</v>
@@ -5363,10 +5363,10 @@
         <v>636</v>
       </c>
       <c r="N113" t="n">
-        <v>1630.9234162594</v>
+        <v>1630.9234624043</v>
       </c>
       <c r="O113" t="n">
-        <v>1037267.292740978</v>
+        <v>1037267.322089135</v>
       </c>
       <c r="P113" t="n">
         <v>2500</v>
@@ -5409,10 +5409,10 @@
         <v>23</v>
       </c>
       <c r="N114" t="n">
-        <v>1550.1934418475</v>
+        <v>1550.1935205388</v>
       </c>
       <c r="O114" t="n">
-        <v>35654.4491624925</v>
+        <v>35654.4509723924</v>
       </c>
       <c r="P114" t="n">
         <v>2500</v>
@@ -5455,10 +5455,10 @@
         <v>168</v>
       </c>
       <c r="N115" t="n">
-        <v>1579.3908418367</v>
+        <v>1579.3907948718</v>
       </c>
       <c r="O115" t="n">
-        <v>265337.6614285656</v>
+        <v>265337.6535384624</v>
       </c>
       <c r="P115" t="n">
         <v>2900</v>
@@ -5501,10 +5501,10 @@
         <v>123</v>
       </c>
       <c r="N116" t="n">
-        <v>2403.5113112366</v>
+        <v>2403.5114869613</v>
       </c>
       <c r="O116" t="n">
-        <v>295631.8912821018</v>
+        <v>295631.9128962399</v>
       </c>
       <c r="P116" t="n">
         <v>3500</v>
@@ -6202,10 +6202,10 @@
         <v>103</v>
       </c>
       <c r="N132" t="n">
-        <v>5449.5305042017</v>
+        <v>5449.5305084746</v>
       </c>
       <c r="O132" t="n">
-        <v>561301.641932775</v>
+        <v>561301.6423728837</v>
       </c>
       <c r="P132" t="n">
         <v>6200</v>
@@ -6289,10 +6289,10 @@
         <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>2029.8737332006</v>
+        <v>2029.8737350598</v>
       </c>
       <c r="O134" t="n">
-        <v>4059.7474664012</v>
+        <v>4059.7474701196</v>
       </c>
       <c r="P134" t="n">
         <v>3600</v>
@@ -6371,10 +6371,10 @@
         <v>141</v>
       </c>
       <c r="N136" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O136" t="n">
-        <v>377984.2976913708</v>
+        <v>377984.2976394828</v>
       </c>
       <c r="P136" t="n">
         <v>4900</v>
@@ -6412,10 +6412,10 @@
         <v>402</v>
       </c>
       <c r="N137" t="n">
-        <v>880.32945034206</v>
+        <v>880.3295131797699</v>
       </c>
       <c r="O137" t="n">
-        <v>353892.4390375081</v>
+        <v>353892.4642982675</v>
       </c>
       <c r="P137" t="n">
         <v>1200</v>
@@ -6663,10 +6663,10 @@
         <v>4</v>
       </c>
       <c r="N143" t="n">
-        <v>11562.038522427</v>
+        <v>11562.038518519</v>
       </c>
       <c r="O143" t="n">
-        <v>46248.154089708</v>
+        <v>46248.154074076</v>
       </c>
       <c r="P143" t="n">
         <v>18500</v>
@@ -7178,10 +7178,10 @@
         <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>7969.9501660377</v>
+        <v>7969.9501665405</v>
       </c>
       <c r="O155" t="n">
-        <v>39849.7508301885</v>
+        <v>39849.7508327025</v>
       </c>
       <c r="P155" t="n">
         <v>12900</v>
@@ -7574,22 +7574,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
         <v>4690.64</v>
       </c>
       <c r="O164" t="n">
-        <v>4690.64</v>
+        <v>0</v>
       </c>
       <c r="P164" t="n">
         <v>7500</v>
       </c>
       <c r="Q164" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -7856,10 +7856,10 @@
         <v>82</v>
       </c>
       <c r="N170" t="n">
-        <v>5218.1705346294</v>
+        <v>5218.1705412054</v>
       </c>
       <c r="O170" t="n">
-        <v>427889.9838396108</v>
+        <v>427889.9843788428</v>
       </c>
       <c r="P170" t="n">
         <v>8500</v>
@@ -7902,10 +7902,10 @@
         <v>72</v>
       </c>
       <c r="N171" t="n">
-        <v>1595.0094090202</v>
+        <v>1595.0093958665</v>
       </c>
       <c r="O171" t="n">
-        <v>114840.6774494544</v>
+        <v>114840.676502388</v>
       </c>
       <c r="P171" t="n">
         <v>2600</v>
@@ -8972,10 +8972,10 @@
         <v>344</v>
       </c>
       <c r="N194" t="n">
-        <v>17075.98952381</v>
+        <v>17075.989523481</v>
       </c>
       <c r="O194" t="n">
-        <v>5874140.39619064</v>
+        <v>5874140.396077463</v>
       </c>
       <c r="P194" t="n">
         <v>27500</v>
@@ -9202,10 +9202,10 @@
         <v>552</v>
       </c>
       <c r="N199" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O199" t="n">
-        <v>836853.4193174376</v>
+        <v>836853.4186101048</v>
       </c>
       <c r="P199" t="n">
         <v>2300</v>
@@ -9248,10 +9248,10 @@
         <v>432</v>
       </c>
       <c r="N200" t="n">
-        <v>2458.5132807977</v>
+        <v>2458.5132504039</v>
       </c>
       <c r="O200" t="n">
-        <v>1062077.737304606</v>
+        <v>1062077.724174485</v>
       </c>
       <c r="P200" t="n">
         <v>3500</v>
@@ -9294,10 +9294,10 @@
         <v>144</v>
       </c>
       <c r="N201" t="n">
-        <v>1771.0906468305</v>
+        <v>1771.0905981795</v>
       </c>
       <c r="O201" t="n">
-        <v>255037.053143592</v>
+        <v>255037.046137848</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9340,10 +9340,10 @@
         <v>240</v>
       </c>
       <c r="N202" t="n">
-        <v>2079.3840533333</v>
+        <v>2079.3840473807</v>
       </c>
       <c r="O202" t="n">
-        <v>499052.172799992</v>
+        <v>499052.171371368</v>
       </c>
       <c r="P202" t="n">
         <v>2900</v>
@@ -9386,10 +9386,10 @@
         <v>266</v>
       </c>
       <c r="N203" t="n">
-        <v>1803.0155537353</v>
+        <v>1803.0155591997</v>
       </c>
       <c r="O203" t="n">
-        <v>479602.1372935898</v>
+        <v>479602.1387471202</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9432,10 +9432,10 @@
         <v>48</v>
       </c>
       <c r="N204" t="n">
-        <v>3306.5952380952</v>
+        <v>3306.5951935915</v>
       </c>
       <c r="O204" t="n">
-        <v>158716.5714285696</v>
+        <v>158716.569292392</v>
       </c>
       <c r="P204" t="n">
         <v>4900</v>
@@ -9478,10 +9478,10 @@
         <v>264</v>
       </c>
       <c r="N205" t="n">
-        <v>2122.1639235788</v>
+        <v>2122.1639198011</v>
       </c>
       <c r="O205" t="n">
-        <v>560251.2758248033</v>
+        <v>560251.2748274903</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9524,10 +9524,10 @@
         <v>144</v>
       </c>
       <c r="N206" t="n">
-        <v>2108.7910927573</v>
+        <v>2108.7914267016</v>
       </c>
       <c r="O206" t="n">
-        <v>303665.9173570512</v>
+        <v>303665.9654450304</v>
       </c>
       <c r="P206" t="n">
         <v>2900</v>
@@ -9570,10 +9570,10 @@
         <v>288</v>
       </c>
       <c r="N207" t="n">
-        <v>2056.0834704208</v>
+        <v>2056.0834183673</v>
       </c>
       <c r="O207" t="n">
-        <v>592152.0394811904</v>
+        <v>592152.0244897824</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -9616,10 +9616,10 @@
         <v>216</v>
       </c>
       <c r="N208" t="n">
-        <v>3224.5685035629</v>
+        <v>3224.5685238095</v>
       </c>
       <c r="O208" t="n">
-        <v>696506.7967695864</v>
+        <v>696506.8011428521</v>
       </c>
       <c r="P208" t="n">
         <v>4500</v>
@@ -9662,10 +9662,10 @@
         <v>288</v>
       </c>
       <c r="N209" t="n">
-        <v>1655.9309755302</v>
+        <v>1655.9309666884</v>
       </c>
       <c r="O209" t="n">
-        <v>476908.1209526976</v>
+        <v>476908.1184062592</v>
       </c>
       <c r="P209" t="n">
         <v>2500</v>
@@ -9708,10 +9708,10 @@
         <v>1</v>
       </c>
       <c r="N210" t="n">
-        <v>1592.276898982</v>
+        <v>1592.2773416667</v>
       </c>
       <c r="O210" t="n">
-        <v>1592.276898982</v>
+        <v>1592.2773416667</v>
       </c>
       <c r="P210" t="n">
         <v>2500</v>
@@ -9798,10 +9798,10 @@
         <v>36</v>
       </c>
       <c r="N212" t="n">
-        <v>2311.9211486486</v>
+        <v>2311.9204895105</v>
       </c>
       <c r="O212" t="n">
-        <v>83229.16135134961</v>
+        <v>83229.137622378</v>
       </c>
       <c r="P212" t="n">
         <v>3500</v>
@@ -9844,10 +9844,10 @@
         <v>12</v>
       </c>
       <c r="N213" t="n">
-        <v>1906.1850980392</v>
+        <v>1906.1849324324</v>
       </c>
       <c r="O213" t="n">
-        <v>22874.2211764704</v>
+        <v>22874.2191891888</v>
       </c>
       <c r="P213" t="n">
         <v>2900</v>
@@ -9890,10 +9890,10 @@
         <v>48</v>
       </c>
       <c r="N214" t="n">
-        <v>2546.9846516008</v>
+        <v>2546.9843873518</v>
       </c>
       <c r="O214" t="n">
-        <v>122255.2632768384</v>
+        <v>122255.2505928864</v>
       </c>
       <c r="P214" t="n">
         <v>3900</v>
@@ -9936,10 +9936,10 @@
         <v>600</v>
       </c>
       <c r="N215" t="n">
-        <v>1259.2745137492</v>
+        <v>1259.2745258911</v>
       </c>
       <c r="O215" t="n">
-        <v>755564.7082495199</v>
+        <v>755564.71553466</v>
       </c>
       <c r="P215" t="n">
         <v>1900</v>
@@ -9977,10 +9977,10 @@
         <v>120</v>
       </c>
       <c r="N216" t="n">
-        <v>2842.2737539432</v>
+        <v>2842.2737341772</v>
       </c>
       <c r="O216" t="n">
-        <v>341072.850473184</v>
+        <v>341072.848101264</v>
       </c>
       <c r="P216" t="n">
         <v>4900</v>
@@ -10113,10 +10113,10 @@
         <v>192</v>
       </c>
       <c r="N219" t="n">
-        <v>692.15220363289</v>
+        <v>692.15222061657</v>
       </c>
       <c r="O219" t="n">
-        <v>132893.2230975149</v>
+        <v>132893.2263583814</v>
       </c>
       <c r="P219" t="n">
         <v>1200</v>
@@ -10959,10 +10959,10 @@
         <v>1</v>
       </c>
       <c r="N237" t="n">
-        <v>1690.870009058</v>
+        <v>1690.8700090909</v>
       </c>
       <c r="O237" t="n">
-        <v>1690.870009058</v>
+        <v>1690.8700090909</v>
       </c>
       <c r="P237" t="n">
         <v>3000</v>
@@ -11247,22 +11247,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="M243" t="n">
-        <v>2280</v>
+        <v>1704</v>
       </c>
       <c r="N243" t="n">
-        <v>517.28896164542</v>
+        <v>517.28908220781</v>
       </c>
       <c r="O243" t="n">
-        <v>1179418.832551558</v>
+        <v>881460.5960821082</v>
       </c>
       <c r="P243" t="n">
         <v>900</v>
       </c>
       <c r="Q243" t="n">
-        <v>2052000</v>
+        <v>1533600</v>
       </c>
     </row>
     <row r="244">
@@ -11492,10 +11492,10 @@
         <v>504</v>
       </c>
       <c r="N248" t="n">
-        <v>3110.8423302235</v>
+        <v>3110.842321894</v>
       </c>
       <c r="O248" t="n">
-        <v>1567864.534432644</v>
+        <v>1567864.530234576</v>
       </c>
       <c r="P248" t="n">
         <v>4500</v>
@@ -11720,10 +11720,10 @@
         <v>12794</v>
       </c>
       <c r="N253" t="n">
-        <v>703.79522697548</v>
+        <v>703.79521051815</v>
       </c>
       <c r="O253" t="n">
-        <v>9004356.133924291</v>
+        <v>9004355.923369212</v>
       </c>
       <c r="P253" t="n">
         <v>900</v>
@@ -11815,10 +11815,10 @@
         <v>161</v>
       </c>
       <c r="N255" t="n">
-        <v>3182.2511070111</v>
+        <v>3182.2511214953</v>
       </c>
       <c r="O255" t="n">
-        <v>512342.4282287871</v>
+        <v>512342.4305607433</v>
       </c>
       <c r="P255" t="n">
         <v>6900</v>
@@ -17735,10 +17735,10 @@
         <v>11</v>
       </c>
       <c r="N378" t="n">
-        <v>366.3998019802</v>
+        <v>366.39979381443</v>
       </c>
       <c r="O378" t="n">
-        <v>4030.3978217822</v>
+        <v>4030.39773195873</v>
       </c>
       <c r="P378" t="n">
         <v>2900</v>
@@ -18029,10 +18029,10 @@
         <v>984</v>
       </c>
       <c r="N384" t="n">
-        <v>430.60997630332</v>
+        <v>430.60997624703</v>
       </c>
       <c r="O384" t="n">
-        <v>423720.2166824669</v>
+        <v>423720.2166270775</v>
       </c>
       <c r="P384" t="n">
         <v>2200</v>
@@ -18127,10 +18127,10 @@
         <v>455</v>
       </c>
       <c r="N386" t="n">
-        <v>315.02694721826</v>
+        <v>315.02697707736</v>
       </c>
       <c r="O386" t="n">
-        <v>143337.2609843083</v>
+        <v>143337.2745701988</v>
       </c>
       <c r="P386" t="n">
         <v>2200</v>
@@ -18402,10 +18402,10 @@
         <v>23</v>
       </c>
       <c r="N392" t="n">
-        <v>22951.704911392</v>
+        <v>22951.704904943</v>
       </c>
       <c r="O392" t="n">
-        <v>527889.212962016</v>
+        <v>527889.212813689</v>
       </c>
       <c r="P392" t="n">
         <v>37900</v>
@@ -18494,10 +18494,10 @@
         <v>159</v>
       </c>
       <c r="N394" t="n">
-        <v>705.52801204819</v>
+        <v>705.52800453515</v>
       </c>
       <c r="O394" t="n">
-        <v>112178.9539156622</v>
+        <v>112178.9527210888</v>
       </c>
       <c r="P394" t="n">
         <v>1500</v>
@@ -18647,10 +18647,10 @@
         <v>43</v>
       </c>
       <c r="N397" t="n">
-        <v>1757.3205567452</v>
+        <v>1757.3205591398</v>
       </c>
       <c r="O397" t="n">
-        <v>75564.78394004361</v>
+        <v>75564.7840430114</v>
       </c>
       <c r="P397" t="n">
         <v>2000</v>
@@ -19291,10 +19291,10 @@
         <v>1827</v>
       </c>
       <c r="N411" t="n">
-        <v>220.00629713546</v>
+        <v>220.00534867624</v>
       </c>
       <c r="O411" t="n">
-        <v>401951.5048664854</v>
+        <v>401949.7720314905</v>
       </c>
       <c r="P411" t="n">
         <v>260</v>
@@ -20057,22 +20057,22 @@
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M428" t="n">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="N428" t="n">
         <v>9240</v>
       </c>
       <c r="O428" t="n">
-        <v>6468000</v>
+        <v>6283200</v>
       </c>
       <c r="P428" t="n">
         <v>11500</v>
       </c>
       <c r="Q428" t="n">
-        <v>8050000</v>
+        <v>7820000</v>
       </c>
     </row>
     <row r="429">
@@ -22337,10 +22337,10 @@
         <v>14</v>
       </c>
       <c r="N477" t="n">
-        <v>7046.7441176471</v>
+        <v>7046.745</v>
       </c>
       <c r="O477" t="n">
-        <v>98654.4176470594</v>
+        <v>98654.42999999999</v>
       </c>
       <c r="P477" t="n">
         <v>22900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3062015504</v>
+        <v>1811.3067953668</v>
       </c>
       <c r="O6" t="n">
-        <v>652070.232558144</v>
+        <v>652070.446332048</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -3580,10 +3580,10 @@
         <v>972</v>
       </c>
       <c r="N74" t="n">
-        <v>2582.2558256496</v>
+        <v>2582.2557662062</v>
       </c>
       <c r="O74" t="n">
-        <v>2509952.662531411</v>
+        <v>2509952.604752427</v>
       </c>
       <c r="P74" t="n">
         <v>4500</v>
@@ -3626,10 +3626,10 @@
         <v>1372</v>
       </c>
       <c r="N75" t="n">
-        <v>5216.8961603854</v>
+        <v>5216.8961467368</v>
       </c>
       <c r="O75" t="n">
-        <v>7157581.532048769</v>
+        <v>7157581.51332289</v>
       </c>
       <c r="P75" t="n">
         <v>8500</v>
@@ -3813,10 +3813,10 @@
         <v>60</v>
       </c>
       <c r="N79" t="n">
-        <v>3230.0673863636</v>
+        <v>3230.0673814042</v>
       </c>
       <c r="O79" t="n">
-        <v>193804.043181816</v>
+        <v>193804.042884252</v>
       </c>
       <c r="P79" t="n">
         <v>6200</v>
@@ -4144,10 +4144,10 @@
         <v>332</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.2540520446</v>
+        <v>3594.2540372671</v>
       </c>
       <c r="O86" t="n">
-        <v>1193292.345278807</v>
+        <v>1193292.340372677</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -4190,10 +4190,10 @@
         <v>276</v>
       </c>
       <c r="N87" t="n">
-        <v>14822.378854415</v>
+        <v>14822.378852361</v>
       </c>
       <c r="O87" t="n">
-        <v>4090976.56381854</v>
+        <v>4090976.563251636</v>
       </c>
       <c r="P87" t="n">
         <v>24900</v>
@@ -4501,10 +4501,10 @@
         <v>317</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107892862</v>
+        <v>4372.2107896237</v>
       </c>
       <c r="O94" t="n">
-        <v>1385990.820203725</v>
+        <v>1385990.820310713</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -4634,10 +4634,10 @@
         <v>214</v>
       </c>
       <c r="N97" t="n">
-        <v>1592.5669555035</v>
+        <v>1592.5668955224</v>
       </c>
       <c r="O97" t="n">
-        <v>340809.328477749</v>
+        <v>340809.3156417936</v>
       </c>
       <c r="P97" t="n">
         <v>3900</v>
@@ -4977,22 +4977,22 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M105" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N105" t="n">
-        <v>9635.7622222222</v>
+        <v>9635.762500000001</v>
       </c>
       <c r="O105" t="n">
-        <v>86721.8599999998</v>
+        <v>57814.575</v>
       </c>
       <c r="P105" t="n">
         <v>12500</v>
       </c>
       <c r="Q105" t="n">
-        <v>112500</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="106">
@@ -5314,10 +5314,10 @@
         <v>636</v>
       </c>
       <c r="N112" t="n">
-        <v>1630.9234875283</v>
+        <v>1630.9235527836</v>
       </c>
       <c r="O112" t="n">
-        <v>1037267.338067999</v>
+        <v>1037267.379570369</v>
       </c>
       <c r="P112" t="n">
         <v>2500</v>
@@ -5360,10 +5360,10 @@
         <v>23</v>
       </c>
       <c r="N113" t="n">
-        <v>1550.1935332762</v>
+        <v>1550.1935823921</v>
       </c>
       <c r="O113" t="n">
-        <v>35654.4512653526</v>
+        <v>35654.4523950183</v>
       </c>
       <c r="P113" t="n">
         <v>2500</v>
@@ -5406,10 +5406,10 @@
         <v>168</v>
       </c>
       <c r="N114" t="n">
-        <v>1579.3907235142</v>
+        <v>1579.3906753247</v>
       </c>
       <c r="O114" t="n">
-        <v>265337.6415503856</v>
+        <v>265337.6334545496</v>
       </c>
       <c r="P114" t="n">
         <v>2900</v>
@@ -5452,10 +5452,10 @@
         <v>123</v>
       </c>
       <c r="N115" t="n">
-        <v>2403.5115510508</v>
+        <v>2403.5116616598</v>
       </c>
       <c r="O115" t="n">
-        <v>295631.9207792484</v>
+        <v>295631.9343841554</v>
       </c>
       <c r="P115" t="n">
         <v>3500</v>
@@ -5539,10 +5539,10 @@
         <v>50</v>
       </c>
       <c r="N117" t="n">
-        <v>2069.4656884058</v>
+        <v>2069.4655925926</v>
       </c>
       <c r="O117" t="n">
-        <v>103473.28442029</v>
+        <v>103473.27962963</v>
       </c>
       <c r="P117" t="n">
         <v>6500</v>
@@ -6611,10 +6611,10 @@
         <v>4</v>
       </c>
       <c r="N142" t="n">
-        <v>11562.038518519</v>
+        <v>11562.038494624</v>
       </c>
       <c r="O142" t="n">
-        <v>46248.154074076</v>
+        <v>46248.153978496</v>
       </c>
       <c r="P142" t="n">
         <v>18500</v>
@@ -7758,10 +7758,10 @@
         <v>82</v>
       </c>
       <c r="N168" t="n">
-        <v>5218.1705479452</v>
+        <v>5218.1705520703</v>
       </c>
       <c r="O168" t="n">
-        <v>427889.9849315064</v>
+        <v>427889.9852697646</v>
       </c>
       <c r="P168" t="n">
         <v>8500</v>
@@ -7804,10 +7804,10 @@
         <v>52</v>
       </c>
       <c r="N169" t="n">
-        <v>1595.0093800979</v>
+        <v>1595.0093780687</v>
       </c>
       <c r="O169" t="n">
-        <v>82940.4877650908</v>
+        <v>82940.48765957241</v>
       </c>
       <c r="P169" t="n">
         <v>2600</v>
@@ -9058,10 +9058,10 @@
         <v>552</v>
       </c>
       <c r="N196" t="n">
-        <v>1516.0388018299</v>
+        <v>1516.038799961</v>
       </c>
       <c r="O196" t="n">
-        <v>836853.4186101048</v>
+        <v>836853.4175784719</v>
       </c>
       <c r="P196" t="n">
         <v>2300</v>
@@ -9104,10 +9104,10 @@
         <v>432</v>
       </c>
       <c r="N197" t="n">
-        <v>2458.5131932225</v>
+        <v>2458.5131821149</v>
       </c>
       <c r="O197" t="n">
-        <v>1062077.69947212</v>
+        <v>1062077.694673637</v>
       </c>
       <c r="P197" t="n">
         <v>3500</v>
@@ -9242,10 +9242,10 @@
         <v>266</v>
       </c>
       <c r="N200" t="n">
-        <v>1803.0156033058</v>
+        <v>1803.0156051587</v>
       </c>
       <c r="O200" t="n">
-        <v>479602.1504793428</v>
+        <v>479602.1509722142</v>
       </c>
       <c r="P200" t="n">
         <v>2500</v>
@@ -9288,10 +9288,10 @@
         <v>48</v>
       </c>
       <c r="N201" t="n">
-        <v>3306.5951807229</v>
+        <v>3306.5951742627</v>
       </c>
       <c r="O201" t="n">
-        <v>158716.5686746992</v>
+        <v>158716.5683646096</v>
       </c>
       <c r="P201" t="n">
         <v>4900</v>
@@ -9380,10 +9380,10 @@
         <v>144</v>
       </c>
       <c r="N203" t="n">
-        <v>2108.791733871</v>
+        <v>2108.7917654987</v>
       </c>
       <c r="O203" t="n">
-        <v>303666.009677424</v>
+        <v>303666.0142318128</v>
       </c>
       <c r="P203" t="n">
         <v>2900</v>
@@ -9426,10 +9426,10 @@
         <v>288</v>
       </c>
       <c r="N204" t="n">
-        <v>2056.0833654773</v>
+        <v>2056.0833612094</v>
       </c>
       <c r="O204" t="n">
-        <v>592152.0092574625</v>
+        <v>592152.0080283072</v>
       </c>
       <c r="P204" t="n">
         <v>2900</v>
@@ -9472,10 +9472,10 @@
         <v>216</v>
       </c>
       <c r="N205" t="n">
-        <v>3224.5685400763</v>
+        <v>3224.5685727969</v>
       </c>
       <c r="O205" t="n">
-        <v>696506.8046564808</v>
+        <v>696506.8117241304</v>
       </c>
       <c r="P205" t="n">
         <v>4500</v>
@@ -9518,10 +9518,10 @@
         <v>288</v>
       </c>
       <c r="N206" t="n">
-        <v>1655.9308953259</v>
+        <v>1655.9308833223</v>
       </c>
       <c r="O206" t="n">
-        <v>476908.0978538592</v>
+        <v>476908.0943968224</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9564,10 +9564,10 @@
         <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>1592.2776475694</v>
+        <v>1592.2780825688</v>
       </c>
       <c r="O207" t="n">
-        <v>1592.2776475694</v>
+        <v>1592.2780825688</v>
       </c>
       <c r="P207" t="n">
         <v>2500</v>
@@ -9654,10 +9654,10 @@
         <v>36</v>
       </c>
       <c r="N209" t="n">
-        <v>2311.9203981265</v>
+        <v>2311.920212766</v>
       </c>
       <c r="O209" t="n">
-        <v>83229.13433255401</v>
+        <v>83229.127659576</v>
       </c>
       <c r="P209" t="n">
         <v>3500</v>
@@ -9700,10 +9700,10 @@
         <v>12</v>
       </c>
       <c r="N210" t="n">
-        <v>1906.1837238494</v>
+        <v>1906.183697479</v>
       </c>
       <c r="O210" t="n">
-        <v>22874.2046861928</v>
+        <v>22874.204369748</v>
       </c>
       <c r="P210" t="n">
         <v>2900</v>
@@ -9746,10 +9746,10 @@
         <v>48</v>
       </c>
       <c r="N211" t="n">
-        <v>2546.9842276423</v>
+        <v>2546.9839957717</v>
       </c>
       <c r="O211" t="n">
-        <v>122255.2429268304</v>
+        <v>122255.2317970416</v>
       </c>
       <c r="P211" t="n">
         <v>3900</v>
@@ -10064,10 +10064,10 @@
         <v>2829</v>
       </c>
       <c r="N218" t="n">
-        <v>1955.2371159315</v>
+        <v>1955.2371140003</v>
       </c>
       <c r="O218" t="n">
-        <v>5531365.800970213</v>
+        <v>5531365.795506849</v>
       </c>
       <c r="P218" t="n">
         <v>3000</v>
@@ -11109,10 +11109,10 @@
         <v>1704</v>
       </c>
       <c r="N240" t="n">
-        <v>517.28922545101</v>
+        <v>517.2892916984</v>
       </c>
       <c r="O240" t="n">
-        <v>881460.840168521</v>
+        <v>881460.9530540736</v>
       </c>
       <c r="P240" t="n">
         <v>900</v>
@@ -11348,10 +11348,10 @@
         <v>504</v>
       </c>
       <c r="N245" t="n">
-        <v>3110.8421999117</v>
+        <v>3110.8418772978</v>
       </c>
       <c r="O245" t="n">
-        <v>1567864.468755497</v>
+        <v>1567864.306158091</v>
       </c>
       <c r="P245" t="n">
         <v>4500</v>
@@ -11576,10 +11576,10 @@
         <v>12794</v>
       </c>
       <c r="N250" t="n">
-        <v>703.79520622865</v>
+        <v>703.79518726322</v>
       </c>
       <c r="O250" t="n">
-        <v>9004355.868489349</v>
+        <v>9004355.625845637</v>
       </c>
       <c r="P250" t="n">
         <v>900</v>
@@ -13249,10 +13249,10 @@
         <v>1</v>
       </c>
       <c r="N285" t="n">
-        <v>3505.3804</v>
+        <v>3505.3804081633</v>
       </c>
       <c r="O285" t="n">
-        <v>3505.3804</v>
+        <v>3505.3804081633</v>
       </c>
       <c r="P285" t="n">
         <v>12900</v>
@@ -18258,10 +18258,10 @@
         <v>23</v>
       </c>
       <c r="N389" t="n">
-        <v>22951.7048659</v>
+        <v>22951.704852753</v>
       </c>
       <c r="O389" t="n">
-        <v>527889.2119157</v>
+        <v>527889.211613319</v>
       </c>
       <c r="P389" t="n">
         <v>37900</v>
@@ -18503,10 +18503,10 @@
         <v>43</v>
       </c>
       <c r="N394" t="n">
-        <v>1757.3205591398</v>
+        <v>1757.3205603448</v>
       </c>
       <c r="O394" t="n">
-        <v>75564.7840430114</v>
+        <v>75564.78409482641</v>
       </c>
       <c r="P394" t="n">
         <v>2000</v>
@@ -19913,22 +19913,22 @@
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M425" t="n">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="N425" t="n">
         <v>9240</v>
       </c>
       <c r="O425" t="n">
-        <v>6283200</v>
+        <v>6246240</v>
       </c>
       <c r="P425" t="n">
         <v>11500</v>
       </c>
       <c r="Q425" t="n">
-        <v>7820000</v>
+        <v>7774000</v>
       </c>
     </row>
     <row r="426">
@@ -21227,10 +21227,10 @@
         <v>42</v>
       </c>
       <c r="N453" t="n">
-        <v>2432.1346938776</v>
+        <v>2432.1347916667</v>
       </c>
       <c r="O453" t="n">
-        <v>102149.6571428592</v>
+        <v>102149.6612500014</v>
       </c>
       <c r="P453" t="n">
         <v>4500</v>
@@ -21751,9 +21751,17 @@
           <t>MT4004</t>
         </is>
       </c>
+      <c r="B465" t="n">
+        <v>7700154271143</v>
+      </c>
       <c r="C465" t="inlineStr">
         <is>
           <t>MT4004 BLADE PLAYA JUEGO</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -21774,16 +21782,16 @@
         <v>2</v>
       </c>
       <c r="N465" t="n">
-        <v>2058.92</v>
+        <v>2297.5912635379</v>
       </c>
       <c r="O465" t="n">
-        <v>4117.84</v>
+        <v>4595.1825270758</v>
       </c>
       <c r="P465" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="Q465" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="466">
@@ -21820,16 +21828,16 @@
         <v>1</v>
       </c>
       <c r="N466" t="n">
-        <v>3456.93</v>
+        <v>4686.9499667221</v>
       </c>
       <c r="O466" t="n">
-        <v>3456.93</v>
+        <v>4686.9499667221</v>
       </c>
       <c r="P466" t="n">
-        <v>5000</v>
+        <v>5900</v>
       </c>
       <c r="Q466" t="n">
-        <v>5000</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="467">

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4971,13 +4971,13 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>6</v>
@@ -19907,13 +19907,13 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M425" t="n">
         <v>676</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -636,10 +636,10 @@
         <v>360</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="O6" t="n">
-        <v>652070.512291824</v>
+        <v>652070.59885152</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -3580,10 +3580,10 @@
         <v>972</v>
       </c>
       <c r="N74" t="n">
-        <v>2582.2557508532</v>
+        <v>2582.2557353886</v>
       </c>
       <c r="O74" t="n">
-        <v>2509952.58982931</v>
+        <v>2509952.574797719</v>
       </c>
       <c r="P74" t="n">
         <v>4500</v>
@@ -3626,10 +3626,10 @@
         <v>1372</v>
       </c>
       <c r="N75" t="n">
-        <v>5216.8961296772</v>
+        <v>5216.8961258041</v>
       </c>
       <c r="O75" t="n">
-        <v>7157581.489917119</v>
+        <v>7157581.484603225</v>
       </c>
       <c r="P75" t="n">
         <v>8500</v>
@@ -3813,10 +3813,10 @@
         <v>60</v>
       </c>
       <c r="N79" t="n">
-        <v>3230.0672564612</v>
+        <v>3230.067250996</v>
       </c>
       <c r="O79" t="n">
-        <v>193804.035387672</v>
+        <v>193804.03505976</v>
       </c>
       <c r="P79" t="n">
         <v>6200</v>
@@ -4190,10 +4190,10 @@
         <v>276</v>
       </c>
       <c r="N87" t="n">
-        <v>14822.378850987</v>
+        <v>14822.378849611</v>
       </c>
       <c r="O87" t="n">
-        <v>4090976.562872412</v>
+        <v>4090976.562492636</v>
       </c>
       <c r="P87" t="n">
         <v>24900</v>
@@ -4501,10 +4501,10 @@
         <v>317</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O94" t="n">
-        <v>1385990.820310713</v>
+        <v>1385990.820471368</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -4634,10 +4634,10 @@
         <v>214</v>
       </c>
       <c r="N97" t="n">
-        <v>1592.5668693558</v>
+        <v>1592.5667761934</v>
       </c>
       <c r="O97" t="n">
-        <v>340809.3100421412</v>
+        <v>340809.2901053876</v>
       </c>
       <c r="P97" t="n">
         <v>3900</v>
@@ -5273,10 +5273,10 @@
         <v>636</v>
       </c>
       <c r="N111" t="n">
-        <v>1630.9235742505</v>
+        <v>1630.9236077879</v>
       </c>
       <c r="O111" t="n">
-        <v>1037267.393223318</v>
+        <v>1037267.414553104</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5319,10 +5319,10 @@
         <v>23</v>
       </c>
       <c r="N112" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O112" t="n">
-        <v>35654.4536056417</v>
+        <v>35654.4545162876</v>
       </c>
       <c r="P112" t="n">
         <v>2500</v>
@@ -5365,10 +5365,10 @@
         <v>168</v>
       </c>
       <c r="N113" t="n">
-        <v>1579.3906753247</v>
+        <v>1579.3905526316</v>
       </c>
       <c r="O113" t="n">
-        <v>265337.6334545496</v>
+        <v>265337.6128421088</v>
       </c>
       <c r="P113" t="n">
         <v>2900</v>
@@ -5411,10 +5411,10 @@
         <v>123</v>
       </c>
       <c r="N114" t="n">
-        <v>2403.5118666412</v>
+        <v>2403.5119649393</v>
       </c>
       <c r="O114" t="n">
-        <v>295631.9595968676</v>
+        <v>295631.9716875339</v>
       </c>
       <c r="P114" t="n">
         <v>3500</v>
@@ -6196,10 +6196,10 @@
         <v>2</v>
       </c>
       <c r="N132" t="n">
-        <v>2029.8737669513</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O132" t="n">
-        <v>4059.7475339026</v>
+        <v>4059.7477200206</v>
       </c>
       <c r="P132" t="n">
         <v>3600</v>
@@ -6278,10 +6278,10 @@
         <v>141</v>
       </c>
       <c r="N134" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O134" t="n">
-        <v>377984.2976394828</v>
+        <v>377984.297587482</v>
       </c>
       <c r="P134" t="n">
         <v>4900</v>
@@ -6570,10 +6570,10 @@
         <v>4</v>
       </c>
       <c r="N141" t="n">
-        <v>11562.038478261</v>
+        <v>11562.038474114</v>
       </c>
       <c r="O141" t="n">
-        <v>46248.153913044</v>
+        <v>46248.153896456</v>
       </c>
       <c r="P141" t="n">
         <v>18500</v>
@@ -7085,10 +7085,10 @@
         <v>5</v>
       </c>
       <c r="N153" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O153" t="n">
-        <v>39849.750834598</v>
+        <v>39849.7508358665</v>
       </c>
       <c r="P153" t="n">
         <v>12900</v>
@@ -7717,10 +7717,10 @@
         <v>82</v>
       </c>
       <c r="N167" t="n">
-        <v>5218.1705520703</v>
+        <v>5218.1705541562</v>
       </c>
       <c r="O167" t="n">
-        <v>427889.9852697646</v>
+        <v>427889.9854408083</v>
       </c>
       <c r="P167" t="n">
         <v>8500</v>
@@ -7763,10 +7763,10 @@
         <v>52</v>
       </c>
       <c r="N168" t="n">
-        <v>1595.009375</v>
+        <v>1595.0093687708</v>
       </c>
       <c r="O168" t="n">
-        <v>82940.4875</v>
+        <v>82940.4871760816</v>
       </c>
       <c r="P168" t="n">
         <v>2600</v>
@@ -8787,10 +8787,10 @@
         <v>344</v>
       </c>
       <c r="N190" t="n">
-        <v>17075.989523481</v>
+        <v>17075.989523151</v>
       </c>
       <c r="O190" t="n">
-        <v>5874140.396077463</v>
+        <v>5874140.395963944</v>
       </c>
       <c r="P190" t="n">
         <v>27500</v>
@@ -9017,10 +9017,10 @@
         <v>552</v>
       </c>
       <c r="N195" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O195" t="n">
-        <v>836853.4168673856</v>
+        <v>836853.4150504224</v>
       </c>
       <c r="P195" t="n">
         <v>2300</v>
@@ -9063,10 +9063,10 @@
         <v>432</v>
       </c>
       <c r="N196" t="n">
-        <v>2458.5131821149</v>
+        <v>2458.5130781975</v>
       </c>
       <c r="O196" t="n">
-        <v>1062077.694673637</v>
+        <v>1062077.64978132</v>
       </c>
       <c r="P196" t="n">
         <v>3500</v>
@@ -9109,10 +9109,10 @@
         <v>144</v>
       </c>
       <c r="N197" t="n">
-        <v>1771.0904491413</v>
+        <v>1771.0904111406</v>
       </c>
       <c r="O197" t="n">
-        <v>255037.0246763472</v>
+        <v>255037.0192042464</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
@@ -9155,10 +9155,10 @@
         <v>240</v>
       </c>
       <c r="N198" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839770425</v>
       </c>
       <c r="O198" t="n">
-        <v>499052.1661085041</v>
+        <v>499052.1544902</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9247,10 +9247,10 @@
         <v>48</v>
       </c>
       <c r="N200" t="n">
-        <v>3306.5951351351</v>
+        <v>3306.5946902655</v>
       </c>
       <c r="O200" t="n">
-        <v>158716.5664864848</v>
+        <v>158716.545132744</v>
       </c>
       <c r="P200" t="n">
         <v>4900</v>
@@ -9339,10 +9339,10 @@
         <v>144</v>
       </c>
       <c r="N202" t="n">
-        <v>2108.7918292683</v>
+        <v>2108.7920330806</v>
       </c>
       <c r="O202" t="n">
-        <v>303666.0234146352</v>
+        <v>303666.0527636064</v>
       </c>
       <c r="P202" t="n">
         <v>2900</v>
@@ -9385,10 +9385,10 @@
         <v>288</v>
       </c>
       <c r="N203" t="n">
-        <v>2056.0833612094</v>
+        <v>2056.0831903662</v>
       </c>
       <c r="O203" t="n">
-        <v>592152.0080283072</v>
+        <v>592151.9588254656</v>
       </c>
       <c r="P203" t="n">
         <v>2900</v>
@@ -9477,10 +9477,10 @@
         <v>288</v>
       </c>
       <c r="N205" t="n">
-        <v>1655.9308652576</v>
+        <v>1655.9308592201</v>
       </c>
       <c r="O205" t="n">
-        <v>476908.0891941888</v>
+        <v>476908.0874553888</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>
@@ -9523,10 +9523,10 @@
         <v>1</v>
       </c>
       <c r="N206" t="n">
-        <v>1592.278225957</v>
+        <v>1592.2785867446</v>
       </c>
       <c r="O206" t="n">
-        <v>1592.278225957</v>
+        <v>1592.2785867446</v>
       </c>
       <c r="P206" t="n">
         <v>2500</v>
@@ -9751,10 +9751,10 @@
         <v>600</v>
       </c>
       <c r="N211" t="n">
-        <v>1259.2745452499</v>
+        <v>1259.2745472973</v>
       </c>
       <c r="O211" t="n">
-        <v>755564.72714994</v>
+        <v>755564.72837838</v>
       </c>
       <c r="P211" t="n">
         <v>1900</v>
@@ -9928,10 +9928,10 @@
         <v>192</v>
       </c>
       <c r="N215" t="n">
-        <v>692.15222061657</v>
+        <v>692.15222920696</v>
       </c>
       <c r="O215" t="n">
-        <v>132893.2263583814</v>
+        <v>132893.2280077363</v>
       </c>
       <c r="P215" t="n">
         <v>1200</v>
@@ -11068,10 +11068,10 @@
         <v>1704</v>
       </c>
       <c r="N239" t="n">
-        <v>517.28943177426</v>
+        <v>517.28978235968</v>
       </c>
       <c r="O239" t="n">
-        <v>881461.1917433391</v>
+        <v>881461.7891408947</v>
       </c>
       <c r="P239" t="n">
         <v>900</v>
@@ -11307,10 +11307,10 @@
         <v>504</v>
       </c>
       <c r="N244" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O244" t="n">
-        <v>1567864.21479917</v>
+        <v>1567864.142795714</v>
       </c>
       <c r="P244" t="n">
         <v>4500</v>
@@ -11535,10 +11535,10 @@
         <v>12794</v>
       </c>
       <c r="N249" t="n">
-        <v>703.79518287415</v>
+        <v>703.79517569581</v>
       </c>
       <c r="O249" t="n">
-        <v>9004355.569691874</v>
+        <v>9004355.477852194</v>
       </c>
       <c r="P249" t="n">
         <v>900</v>
@@ -12442,10 +12442,10 @@
         <v>71</v>
       </c>
       <c r="N268" t="n">
-        <v>2098.4049712644</v>
+        <v>2098.405</v>
       </c>
       <c r="O268" t="n">
-        <v>148986.7529597724</v>
+        <v>148986.755</v>
       </c>
       <c r="P268" t="n">
         <v>9500</v>
@@ -12779,10 +12779,10 @@
         <v>5</v>
       </c>
       <c r="N275" t="n">
-        <v>2832.1949275362</v>
+        <v>2832.195</v>
       </c>
       <c r="O275" t="n">
-        <v>14160.974637681</v>
+        <v>14160.975</v>
       </c>
       <c r="P275" t="n">
         <v>12900</v>
@@ -17844,10 +17844,10 @@
         <v>984</v>
       </c>
       <c r="N380" t="n">
-        <v>430.60997624703</v>
+        <v>430.6099761621</v>
       </c>
       <c r="O380" t="n">
-        <v>423720.2166270775</v>
+        <v>423720.2165435064</v>
       </c>
       <c r="P380" t="n">
         <v>2200</v>
@@ -18217,10 +18217,10 @@
         <v>23</v>
       </c>
       <c r="N388" t="n">
-        <v>22951.704839538</v>
+        <v>22951.704819588</v>
       </c>
       <c r="O388" t="n">
-        <v>527889.211309374</v>
+        <v>527889.210850524</v>
       </c>
       <c r="P388" t="n">
         <v>37900</v>
@@ -18360,10 +18360,10 @@
         <v>42</v>
       </c>
       <c r="N391" t="n">
-        <v>1547.8825373134</v>
+        <v>1547.8826153846</v>
       </c>
       <c r="O391" t="n">
-        <v>65011.0665671628</v>
+        <v>65011.0698461532</v>
       </c>
       <c r="P391" t="n">
         <v>5500</v>
@@ -19106,10 +19106,10 @@
         <v>1827</v>
       </c>
       <c r="N407" t="n">
-        <v>220.00534867624</v>
+        <v>220.00509068498</v>
       </c>
       <c r="O407" t="n">
-        <v>401949.7720314905</v>
+        <v>401949.3006814584</v>
       </c>
       <c r="P407" t="n">
         <v>260</v>
@@ -20798,10 +20798,10 @@
         <v>38</v>
       </c>
       <c r="N444" t="n">
-        <v>1319.3608823529</v>
+        <v>1319.360887574</v>
       </c>
       <c r="O444" t="n">
-        <v>50135.7135294102</v>
+        <v>50135.713727812</v>
       </c>
       <c r="P444" t="n">
         <v>3500</v>
@@ -21186,10 +21186,10 @@
         <v>42</v>
       </c>
       <c r="N452" t="n">
-        <v>2432.1347916667</v>
+        <v>2432.1351111111</v>
       </c>
       <c r="O452" t="n">
-        <v>102149.6612500014</v>
+        <v>102149.6746666662</v>
       </c>
       <c r="P452" t="n">
         <v>4500</v>
@@ -21787,10 +21787,10 @@
         <v>581</v>
       </c>
       <c r="N465" t="n">
-        <v>4687.974185654</v>
+        <v>4687.974206955</v>
       </c>
       <c r="O465" t="n">
-        <v>2723713.001864974</v>
+        <v>2723713.014240855</v>
       </c>
       <c r="P465" t="n">
         <v>5900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3137,10 +3137,10 @@
         <v>33</v>
       </c>
       <c r="N64" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O64" t="n">
-        <v>162931.2353977704</v>
+        <v>162931.2354017865</v>
       </c>
       <c r="P64" t="n">
         <v>7500</v>
@@ -3539,10 +3539,10 @@
         <v>972</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2557353886</v>
+        <v>2582.2557142857</v>
       </c>
       <c r="O73" t="n">
-        <v>2509952.574797719</v>
+        <v>2509952.5542857</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3585,10 +3585,10 @@
         <v>1372</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8961202577</v>
+        <v>5216.8961124659</v>
       </c>
       <c r="O74" t="n">
-        <v>7157581.476993565</v>
+        <v>7157581.466303214</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
@@ -3677,10 +3677,10 @@
         <v>3410</v>
       </c>
       <c r="N76" t="n">
-        <v>3158.8608260699</v>
+        <v>3158.8608262318</v>
       </c>
       <c r="O76" t="n">
-        <v>10771715.41689836</v>
+        <v>10771715.41745044</v>
       </c>
       <c r="P76" t="n">
         <v>5600</v>
@@ -3723,10 +3723,10 @@
         <v>320</v>
       </c>
       <c r="N77" t="n">
-        <v>3841.6247928994</v>
+        <v>3841.6248214286</v>
       </c>
       <c r="O77" t="n">
-        <v>1229319.933727808</v>
+        <v>1229319.942857152</v>
       </c>
       <c r="P77" t="n">
         <v>6900</v>
@@ -3766,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M78" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N78" t="n">
         <v>3230.0672177419</v>
       </c>
       <c r="O78" t="n">
-        <v>193804.033064514</v>
+        <v>96902.016532257</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
       </c>
       <c r="Q78" t="n">
-        <v>372000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="79">
@@ -4103,10 +4103,10 @@
         <v>332</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="O85" t="n">
-        <v>1193292.334205611</v>
+        <v>1193292.328</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4587,22 +4587,22 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M96" t="n">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="N96" t="n">
-        <v>1592.566762142</v>
+        <v>1592.5667254408</v>
       </c>
       <c r="O96" t="n">
-        <v>340809.287098388</v>
+        <v>293032.2774811072</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
       </c>
       <c r="Q96" t="n">
-        <v>834600</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="97">
@@ -5232,10 +5232,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9235901027</v>
+        <v>1630.9236367936</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.403305317</v>
+        <v>1037267.43300073</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5278,10 +5278,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4545330293</v>
+        <v>35654.4550383577</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5324,10 +5324,10 @@
         <v>168</v>
       </c>
       <c r="N112" t="n">
-        <v>1579.3905526316</v>
+        <v>1579.3904266667</v>
       </c>
       <c r="O112" t="n">
-        <v>265337.6128421088</v>
+        <v>265337.5916800056</v>
       </c>
       <c r="P112" t="n">
         <v>2900</v>
@@ -5370,10 +5370,10 @@
         <v>123</v>
       </c>
       <c r="N113" t="n">
-        <v>2403.5119996136</v>
+        <v>2403.5120742613</v>
       </c>
       <c r="O113" t="n">
-        <v>295631.9759524728</v>
+        <v>295631.9851341399</v>
       </c>
       <c r="P113" t="n">
         <v>3500</v>
@@ -6027,10 +6027,10 @@
         <v>109</v>
       </c>
       <c r="N128" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O128" t="n">
-        <v>457459.1056738729</v>
+        <v>457459.1057503473</v>
       </c>
       <c r="P128" t="n">
         <v>5900</v>
@@ -6068,10 +6068,10 @@
         <v>103</v>
       </c>
       <c r="N129" t="n">
-        <v>5449.5305128205</v>
+        <v>5449.5305217391</v>
       </c>
       <c r="O129" t="n">
-        <v>561301.6428205115</v>
+        <v>561301.6437391273</v>
       </c>
       <c r="P129" t="n">
         <v>6200</v>
@@ -6155,10 +6155,10 @@
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>2029.8738129131</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O131" t="n">
-        <v>4059.7476258262</v>
+        <v>4059.7477200206</v>
       </c>
       <c r="P131" t="n">
         <v>3600</v>
@@ -8700,10 +8700,10 @@
         <v>344</v>
       </c>
       <c r="N188" t="n">
-        <v>17075.989523151</v>
+        <v>17075.989522822</v>
       </c>
       <c r="O188" t="n">
-        <v>5874140.395963944</v>
+        <v>5874140.395850768</v>
       </c>
       <c r="P188" t="n">
         <v>27500</v>
@@ -8930,10 +8930,10 @@
         <v>552</v>
       </c>
       <c r="N193" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O193" t="n">
-        <v>836853.4166084424</v>
+        <v>836853.4149202056</v>
       </c>
       <c r="P193" t="n">
         <v>2300</v>
@@ -8970,22 +8970,22 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M194" t="n">
-        <v>432</v>
+        <v>384</v>
       </c>
       <c r="N194" t="n">
-        <v>2458.5131328074</v>
+        <v>2458.5130759032</v>
       </c>
       <c r="O194" t="n">
-        <v>1062077.673372797</v>
+        <v>944069.0211468288</v>
       </c>
       <c r="P194" t="n">
         <v>3500</v>
       </c>
       <c r="Q194" t="n">
-        <v>1512000</v>
+        <v>1344000</v>
       </c>
     </row>
     <row r="195">
@@ -9068,10 +9068,10 @@
         <v>240</v>
       </c>
       <c r="N196" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839709361</v>
       </c>
       <c r="O196" t="n">
-        <v>499052.1661085041</v>
+        <v>499052.153024664</v>
       </c>
       <c r="P196" t="n">
         <v>2900</v>
@@ -9114,10 +9114,10 @@
         <v>266</v>
       </c>
       <c r="N197" t="n">
-        <v>1803.0156051587</v>
+        <v>1803.0156237558</v>
       </c>
       <c r="O197" t="n">
-        <v>479602.1509722142</v>
+        <v>479602.1559190428</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
@@ -9154,22 +9154,22 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M198" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="N198" t="n">
-        <v>3306.5951153324</v>
+        <v>3306.5946745562</v>
       </c>
       <c r="O198" t="n">
-        <v>158716.5655359552</v>
+        <v>119037.4082840232</v>
       </c>
       <c r="P198" t="n">
         <v>4900</v>
       </c>
       <c r="Q198" t="n">
-        <v>235200</v>
+        <v>176400</v>
       </c>
     </row>
     <row r="199">
@@ -9206,10 +9206,10 @@
         <v>264</v>
       </c>
       <c r="N199" t="n">
-        <v>2122.1638529227</v>
+        <v>2122.1638509903</v>
       </c>
       <c r="O199" t="n">
-        <v>560251.2571715928</v>
+        <v>560251.2566614392</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
@@ -9246,22 +9246,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M200" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="N200" t="n">
-        <v>2108.7920330806</v>
+        <v>2108.792083045</v>
       </c>
       <c r="O200" t="n">
-        <v>303666.0527636064</v>
+        <v>202444.03997232</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
       </c>
       <c r="Q200" t="n">
-        <v>417600</v>
+        <v>278400</v>
       </c>
     </row>
     <row r="201">
@@ -9292,22 +9292,22 @@
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M201" t="n">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="N201" t="n">
-        <v>2056.0831723454</v>
+        <v>2056.0829891304</v>
       </c>
       <c r="O201" t="n">
-        <v>592151.9536354751</v>
+        <v>394767.9339130368</v>
       </c>
       <c r="P201" t="n">
         <v>2900</v>
       </c>
       <c r="Q201" t="n">
-        <v>835200</v>
+        <v>556800</v>
       </c>
     </row>
     <row r="202">
@@ -9338,22 +9338,22 @@
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M202" t="n">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="N202" t="n">
-        <v>3224.5688003933</v>
+        <v>3224.5688090551</v>
       </c>
       <c r="O202" t="n">
-        <v>696506.8608849528</v>
+        <v>580422.385629918</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
       </c>
       <c r="Q202" t="n">
-        <v>972000</v>
+        <v>810000</v>
       </c>
     </row>
     <row r="203">
@@ -9384,22 +9384,22 @@
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M203" t="n">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="N203" t="n">
-        <v>1655.9308592201</v>
+        <v>1655.9308045213</v>
       </c>
       <c r="O203" t="n">
-        <v>476908.0874553888</v>
+        <v>397423.393085112</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
       </c>
       <c r="Q203" t="n">
-        <v>720000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="204">
@@ -9436,10 +9436,10 @@
         <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>1592.2786119257</v>
+        <v>1592.2787749004</v>
       </c>
       <c r="O204" t="n">
-        <v>1592.2786119257</v>
+        <v>1592.2787749004</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9572,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="N207" t="n">
-        <v>1906.1836708861</v>
+        <v>1906.1834782609</v>
       </c>
       <c r="O207" t="n">
-        <v>22874.2040506332</v>
+        <v>22874.2017391308</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -9618,10 +9618,10 @@
         <v>48</v>
       </c>
       <c r="N208" t="n">
-        <v>2546.9839186296</v>
+        <v>2546.9838660907</v>
       </c>
       <c r="O208" t="n">
-        <v>122255.2280942208</v>
+        <v>122255.2255723536</v>
       </c>
       <c r="P208" t="n">
         <v>3900</v>
@@ -9664,10 +9664,10 @@
         <v>600</v>
       </c>
       <c r="N209" t="n">
-        <v>1259.2745472973</v>
+        <v>1259.274561681</v>
       </c>
       <c r="O209" t="n">
-        <v>755564.72837838</v>
+        <v>755564.7370086</v>
       </c>
       <c r="P209" t="n">
         <v>1900</v>
@@ -10981,10 +10981,10 @@
         <v>1704</v>
       </c>
       <c r="N237" t="n">
-        <v>517.2898138359</v>
+        <v>517.28990087531</v>
       </c>
       <c r="O237" t="n">
-        <v>881461.8427763735</v>
+        <v>881461.9910915282</v>
       </c>
       <c r="P237" t="n">
         <v>900</v>
@@ -11220,10 +11220,10 @@
         <v>504</v>
       </c>
       <c r="N242" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O242" t="n">
-        <v>1567864.127482027</v>
+        <v>1567864.06721789</v>
       </c>
       <c r="P242" t="n">
         <v>4500</v>
@@ -11448,10 +11448,10 @@
         <v>12794</v>
       </c>
       <c r="N247" t="n">
-        <v>703.795175</v>
+        <v>703.79516919374</v>
       </c>
       <c r="O247" t="n">
-        <v>9004355.46895</v>
+        <v>9004355.394664709</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -17025,10 +17025,10 @@
         <v>8</v>
       </c>
       <c r="N363" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O363" t="n">
-        <v>56375.5186251344</v>
+        <v>56375.51862336</v>
       </c>
       <c r="P363" t="n">
         <v>9900</v>
@@ -17757,10 +17757,10 @@
         <v>984</v>
       </c>
       <c r="N378" t="n">
-        <v>430.6099761621</v>
+        <v>430.60997607656</v>
       </c>
       <c r="O378" t="n">
-        <v>423720.2165435064</v>
+        <v>423720.216459335</v>
       </c>
       <c r="P378" t="n">
         <v>2200</v>
@@ -17806,10 +17806,10 @@
         <v>726</v>
       </c>
       <c r="N379" t="n">
-        <v>465.87094835681</v>
+        <v>465.87095553453</v>
       </c>
       <c r="O379" t="n">
-        <v>338222.308507044</v>
+        <v>338222.3137180688</v>
       </c>
       <c r="P379" t="n">
         <v>2500</v>
@@ -18124,22 +18124,22 @@
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M386" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="N386" t="n">
-        <v>22951.704812903</v>
+        <v>22951.704799483</v>
       </c>
       <c r="O386" t="n">
-        <v>527889.2106967691</v>
+        <v>298372.162393279</v>
       </c>
       <c r="P386" t="n">
         <v>37900</v>
       </c>
       <c r="Q386" t="n">
-        <v>871700</v>
+        <v>492700</v>
       </c>
     </row>
     <row r="387">
@@ -21700,10 +21700,10 @@
         <v>561</v>
       </c>
       <c r="N463" t="n">
-        <v>4687.9742393162</v>
+        <v>4687.9742611684</v>
       </c>
       <c r="O463" t="n">
-        <v>2629953.548256388</v>
+        <v>2629953.560515472</v>
       </c>
       <c r="P463" t="n">
         <v>5900</v>
@@ -21746,10 +21746,10 @@
         <v>80</v>
       </c>
       <c r="N464" t="n">
-        <v>4171.6687</v>
+        <v>4171.6686912752</v>
       </c>
       <c r="O464" t="n">
-        <v>333733.496</v>
+        <v>333733.495302016</v>
       </c>
       <c r="P464" t="n">
         <v>5500</v>
@@ -22533,10 +22533,10 @@
         <v>32</v>
       </c>
       <c r="N481" t="n">
-        <v>4158.2961111111</v>
+        <v>4158.296</v>
       </c>
       <c r="O481" t="n">
-        <v>133065.4755555552</v>
+        <v>133065.472</v>
       </c>
       <c r="P481" t="n">
         <v>13800</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>972</v>
+        <v>948</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3536,19 +3536,19 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>972</v>
+        <v>948</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2557142857</v>
+        <v>2582.2556563454</v>
       </c>
       <c r="O73" t="n">
-        <v>2509952.5542857</v>
+        <v>2447978.362215439</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
       </c>
       <c r="Q73" t="n">
-        <v>4374000</v>
+        <v>4266000</v>
       </c>
     </row>
     <row r="74">
@@ -3585,10 +3585,10 @@
         <v>1372</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8961124659</v>
+        <v>5216.8961063218</v>
       </c>
       <c r="O74" t="n">
-        <v>7157581.466303214</v>
+        <v>7157581.45787351</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>30</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -4100,19 +4100,19 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="N85" t="n">
         <v>3594.254</v>
       </c>
       <c r="O85" t="n">
-        <v>1193292.328</v>
+        <v>1157349.788</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
       </c>
       <c r="Q85" t="n">
-        <v>2158000</v>
+        <v>2093000</v>
       </c>
     </row>
     <row r="86">
@@ -4460,10 +4460,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107902432</v>
+        <v>4372.2107903559</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.820507094</v>
+        <v>1385990.82054282</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>184</v>
@@ -5232,10 +5232,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9236367936</v>
+        <v>1630.9236471425</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.43300073</v>
+        <v>1037267.43958263</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5278,10 +5278,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1936973199</v>
+        <v>1550.1936995315</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4550383577</v>
+        <v>35654.4550892245</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5370,10 +5370,10 @@
         <v>123</v>
       </c>
       <c r="N113" t="n">
-        <v>2403.5120742613</v>
+        <v>2403.5121001364</v>
       </c>
       <c r="O113" t="n">
-        <v>295631.9851341399</v>
+        <v>295631.9883167772</v>
       </c>
       <c r="P113" t="n">
         <v>3500</v>
@@ -6237,10 +6237,10 @@
         <v>141</v>
       </c>
       <c r="N133" t="n">
-        <v>2680.7396988322</v>
+        <v>2680.739695084</v>
       </c>
       <c r="O133" t="n">
-        <v>377984.2975353402</v>
+        <v>377984.297006844</v>
       </c>
       <c r="P133" t="n">
         <v>4900</v>
@@ -6529,10 +6529,10 @@
         <v>4</v>
       </c>
       <c r="N140" t="n">
-        <v>11562.038474114</v>
+        <v>11562.038465753</v>
       </c>
       <c r="O140" t="n">
-        <v>46248.153896456</v>
+        <v>46248.153863012</v>
       </c>
       <c r="P140" t="n">
         <v>18500</v>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7673,19 +7673,19 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="N166" t="n">
-        <v>5218.170554855</v>
+        <v>5218.1705597964</v>
       </c>
       <c r="O166" t="n">
-        <v>427889.98549811</v>
+        <v>401799.1331043228</v>
       </c>
       <c r="P166" t="n">
         <v>8500</v>
       </c>
       <c r="Q166" t="n">
-        <v>697000</v>
+        <v>654500</v>
       </c>
     </row>
     <row r="167">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -7857,19 +7857,19 @@
         <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N170" t="n">
         <v>10977.27</v>
       </c>
       <c r="O170" t="n">
-        <v>867204.3300000001</v>
+        <v>801340.7100000001</v>
       </c>
       <c r="P170" t="n">
         <v>17900</v>
       </c>
       <c r="Q170" t="n">
-        <v>1414100</v>
+        <v>1306700</v>
       </c>
     </row>
     <row r="171">
@@ -8964,22 +8964,22 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>432</v>
+        <v>384</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
         <v>384</v>
       </c>
       <c r="N194" t="n">
-        <v>2458.5130759032</v>
+        <v>2458.5130690113</v>
       </c>
       <c r="O194" t="n">
-        <v>944069.0211468288</v>
+        <v>944069.0185003392</v>
       </c>
       <c r="P194" t="n">
         <v>3500</v>
@@ -9148,13 +9148,13 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
         <v>36</v>
@@ -9240,22 +9240,22 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
         <v>96</v>
       </c>
       <c r="N200" t="n">
-        <v>2108.792083045</v>
+        <v>2108.7921081831</v>
       </c>
       <c r="O200" t="n">
-        <v>202444.03997232</v>
+        <v>202444.0423855776</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
@@ -9286,22 +9286,22 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
         <v>192</v>
       </c>
       <c r="N201" t="n">
-        <v>2056.0829891304</v>
+        <v>2056.0829843644</v>
       </c>
       <c r="O201" t="n">
-        <v>394767.9339130368</v>
+        <v>394767.9329979648</v>
       </c>
       <c r="P201" t="n">
         <v>2900</v>
@@ -9332,13 +9332,13 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
         <v>180</v>
@@ -9378,13 +9378,13 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
         <v>240</v>
@@ -9436,10 +9436,10 @@
         <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>1592.2787749004</v>
+        <v>1592.27881</v>
       </c>
       <c r="O204" t="n">
-        <v>1592.2787749004</v>
+        <v>1592.27881</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9572,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="N207" t="n">
-        <v>1906.1834782609</v>
+        <v>1906.1829245283</v>
       </c>
       <c r="O207" t="n">
-        <v>22874.2017391308</v>
+        <v>22874.1950943396</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -9618,10 +9618,10 @@
         <v>48</v>
       </c>
       <c r="N208" t="n">
-        <v>2546.9838660907</v>
+        <v>2546.9837028825</v>
       </c>
       <c r="O208" t="n">
-        <v>122255.2255723536</v>
+        <v>122255.21773836</v>
       </c>
       <c r="P208" t="n">
         <v>3900</v>
@@ -10969,7 +10969,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>1704</v>
+        <v>553</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10978,19 +10978,19 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>1704</v>
+        <v>553</v>
       </c>
       <c r="N237" t="n">
-        <v>517.28990087531</v>
+        <v>517.2899423715</v>
       </c>
       <c r="O237" t="n">
-        <v>881461.9910915282</v>
+        <v>286061.3381314395</v>
       </c>
       <c r="P237" t="n">
         <v>900</v>
       </c>
       <c r="Q237" t="n">
-        <v>1533600</v>
+        <v>497700</v>
       </c>
     </row>
     <row r="238">
@@ -11220,10 +11220,10 @@
         <v>504</v>
       </c>
       <c r="N242" t="n">
-        <v>3110.8414032101</v>
+        <v>3110.8413822526</v>
       </c>
       <c r="O242" t="n">
-        <v>1567864.06721789</v>
+        <v>1567864.05665531</v>
       </c>
       <c r="P242" t="n">
         <v>4500</v>
@@ -11448,10 +11448,10 @@
         <v>12794</v>
       </c>
       <c r="N247" t="n">
-        <v>703.79516919374</v>
+        <v>703.79516599434</v>
       </c>
       <c r="O247" t="n">
-        <v>9004355.394664709</v>
+        <v>9004355.353731586</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -18118,13 +18118,13 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M386" t="n">
         <v>13</v>
@@ -18261,7 +18261,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -18270,19 +18270,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N389" t="n">
         <v>1547.8826153846</v>
       </c>
       <c r="O389" t="n">
-        <v>65011.0698461532</v>
+        <v>55723.7741538456</v>
       </c>
       <c r="P389" t="n">
         <v>5500</v>
       </c>
       <c r="Q389" t="n">
-        <v>231000</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="390">
@@ -18312,7 +18312,7 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
@@ -18321,19 +18321,19 @@
         <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N390" t="n">
         <v>4125</v>
       </c>
       <c r="O390" t="n">
-        <v>173250</v>
+        <v>148500</v>
       </c>
       <c r="P390" t="n">
         <v>5500</v>
       </c>
       <c r="Q390" t="n">
-        <v>231000</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="391">
@@ -19007,7 +19007,7 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>1827</v>
+        <v>1527</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
@@ -19016,19 +19016,19 @@
         <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>1827</v>
+        <v>1527</v>
       </c>
       <c r="N405" t="n">
         <v>220.00509068498</v>
       </c>
       <c r="O405" t="n">
-        <v>401949.3006814584</v>
+        <v>335947.7734759644</v>
       </c>
       <c r="P405" t="n">
         <v>260</v>
       </c>
       <c r="Q405" t="n">
-        <v>475020</v>
+        <v>397020</v>
       </c>
     </row>
     <row r="406">

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -1043,10 +1043,10 @@
         <v>23</v>
       </c>
       <c r="N16" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O16" t="n">
-        <v>90317.2532296522</v>
+        <v>90317.2531950211</v>
       </c>
       <c r="P16" t="n">
         <v>4800</v>
@@ -3677,10 +3677,10 @@
         <v>3410</v>
       </c>
       <c r="N76" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O76" t="n">
-        <v>10771715.41745044</v>
+        <v>10776465.54919397</v>
       </c>
       <c r="P76" t="n">
         <v>5600</v>
@@ -3723,10 +3723,10 @@
         <v>320</v>
       </c>
       <c r="N77" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O77" t="n">
-        <v>1229319.942857152</v>
+        <v>1234217.631872512</v>
       </c>
       <c r="P77" t="n">
         <v>6900</v>
@@ -4103,10 +4103,10 @@
         <v>322</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O85" t="n">
-        <v>1157349.788</v>
+        <v>1157349.786791759</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4193,10 +4193,10 @@
         <v>192</v>
       </c>
       <c r="N87" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O87" t="n">
-        <v>401443.2</v>
+        <v>401497.1211820032</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4460,10 +4460,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.82054282</v>
+        <v>1385990.820560699</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4593,10 +4593,10 @@
         <v>184</v>
       </c>
       <c r="N96" t="n">
-        <v>1592.5667254408</v>
+        <v>1600.6713740458</v>
       </c>
       <c r="O96" t="n">
-        <v>293032.2774811072</v>
+        <v>294523.5328244272</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -4950,10 +4950,10 @@
         <v>99</v>
       </c>
       <c r="N104" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O104" t="n">
-        <v>372398.4</v>
+        <v>373762.4967033012</v>
       </c>
       <c r="P104" t="n">
         <v>6900</v>
@@ -5232,10 +5232,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.43958263</v>
+        <v>1037267.445649052</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5278,10 +5278,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4550892245</v>
+        <v>35654.4552166537</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5324,10 +5324,10 @@
         <v>168</v>
       </c>
       <c r="N112" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="O112" t="n">
-        <v>265337.5916800056</v>
+        <v>265337.5830562968</v>
       </c>
       <c r="P112" t="n">
         <v>2900</v>
@@ -5370,10 +5370,10 @@
         <v>123</v>
       </c>
       <c r="N113" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O113" t="n">
-        <v>295631.9883167772</v>
+        <v>295631.9903492046</v>
       </c>
       <c r="P113" t="n">
         <v>3500</v>
@@ -6237,10 +6237,10 @@
         <v>141</v>
       </c>
       <c r="N133" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O133" t="n">
-        <v>377984.297006844</v>
+        <v>377984.2969800681</v>
       </c>
       <c r="P133" t="n">
         <v>4900</v>
@@ -9114,10 +9114,10 @@
         <v>266</v>
       </c>
       <c r="N197" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O197" t="n">
-        <v>479602.1559190428</v>
+        <v>479602.1594014084</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
@@ -9160,10 +9160,10 @@
         <v>36</v>
       </c>
       <c r="N198" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O198" t="n">
-        <v>119037.4082840232</v>
+        <v>119037.4080000012</v>
       </c>
       <c r="P198" t="n">
         <v>4900</v>
@@ -9298,10 +9298,10 @@
         <v>192</v>
       </c>
       <c r="N201" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O201" t="n">
-        <v>394767.9329979648</v>
+        <v>394767.9325399488</v>
       </c>
       <c r="P201" t="n">
         <v>2900</v>
@@ -9390,10 +9390,10 @@
         <v>240</v>
       </c>
       <c r="N203" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O203" t="n">
-        <v>397423.393085112</v>
+        <v>397423.388674224</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9436,10 +9436,10 @@
         <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>1592.27881</v>
+        <v>1592.2788188188</v>
       </c>
       <c r="O204" t="n">
-        <v>1592.27881</v>
+        <v>1592.2788188188</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9572,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="N207" t="n">
-        <v>1906.1829245283</v>
+        <v>1906.1827536232</v>
       </c>
       <c r="O207" t="n">
-        <v>22874.1950943396</v>
+        <v>22874.1930434784</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -10454,10 +10454,10 @@
         <v>63</v>
       </c>
       <c r="N226" t="n">
-        <v>3629.36</v>
+        <v>3642.7032352941</v>
       </c>
       <c r="O226" t="n">
-        <v>228649.68</v>
+        <v>229490.3038235283</v>
       </c>
       <c r="P226" t="n">
         <v>3900</v>
@@ -10981,10 +10981,10 @@
         <v>553</v>
       </c>
       <c r="N237" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O237" t="n">
-        <v>286061.3381314395</v>
+        <v>286061.3538587263</v>
       </c>
       <c r="P237" t="n">
         <v>900</v>
@@ -11220,10 +11220,10 @@
         <v>504</v>
       </c>
       <c r="N242" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O242" t="n">
-        <v>1567864.05665531</v>
+        <v>1567864.051354642</v>
       </c>
       <c r="P242" t="n">
         <v>4500</v>
@@ -11448,10 +11448,10 @@
         <v>12794</v>
       </c>
       <c r="N247" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O247" t="n">
-        <v>9004355.353731586</v>
+        <v>9004355.328400362</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11727,10 +11727,10 @@
         <v>59</v>
       </c>
       <c r="N253" t="n">
-        <v>2501.3849767442</v>
+        <v>2501.384953271</v>
       </c>
       <c r="O253" t="n">
-        <v>147581.7136279078</v>
+        <v>147581.712242989</v>
       </c>
       <c r="P253" t="n">
         <v>4100</v>
@@ -12355,10 +12355,10 @@
         <v>71</v>
       </c>
       <c r="N266" t="n">
-        <v>2098.4050144928</v>
+        <v>2110.6406122449</v>
       </c>
       <c r="O266" t="n">
-        <v>148986.7560289888</v>
+        <v>149855.4834693879</v>
       </c>
       <c r="P266" t="n">
         <v>9500</v>
@@ -20711,10 +20711,10 @@
         <v>38</v>
       </c>
       <c r="N442" t="n">
-        <v>1319.360887574</v>
+        <v>1327.2142261905</v>
       </c>
       <c r="O442" t="n">
-        <v>50135.713727812</v>
+        <v>50434.14059523901</v>
       </c>
       <c r="P442" t="n">
         <v>3500</v>
@@ -21654,10 +21654,10 @@
         <v>582</v>
       </c>
       <c r="N462" t="n">
-        <v>2539.5715559441</v>
+        <v>2539.5715696649</v>
       </c>
       <c r="O462" t="n">
-        <v>1478030.645559466</v>
+        <v>1478030.653544972</v>
       </c>
       <c r="P462" t="n">
         <v>3500</v>
@@ -21700,10 +21700,10 @@
         <v>561</v>
       </c>
       <c r="N463" t="n">
-        <v>4687.9742611684</v>
+        <v>4687.9742758621</v>
       </c>
       <c r="O463" t="n">
-        <v>2629953.560515472</v>
+        <v>2629953.568758638</v>
       </c>
       <c r="P463" t="n">
         <v>5900</v>
@@ -21746,10 +21746,10 @@
         <v>80</v>
       </c>
       <c r="N464" t="n">
-        <v>4171.6686912752</v>
+        <v>4171.6686824324</v>
       </c>
       <c r="O464" t="n">
-        <v>333733.495302016</v>
+        <v>333733.494594592</v>
       </c>
       <c r="P464" t="n">
         <v>5500</v>
@@ -22533,10 +22533,10 @@
         <v>32</v>
       </c>
       <c r="N481" t="n">
-        <v>4158.296</v>
+        <v>4158.2958823529</v>
       </c>
       <c r="O481" t="n">
-        <v>133065.472</v>
+        <v>133065.4682352928</v>
       </c>
       <c r="P481" t="n">
         <v>13800</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -882,10 +882,10 @@
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>31658.725454545</v>
+        <v>31658.725660377</v>
       </c>
       <c r="O12" t="n">
-        <v>94976.17636363501</v>
+        <v>94976.17698113099</v>
       </c>
       <c r="P12" t="n">
         <v>62900</v>
@@ -1082,10 +1082,10 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>2413.0010741139</v>
+        <v>2413.0010834236</v>
       </c>
       <c r="O17" t="n">
-        <v>4826.0021482278</v>
+        <v>4826.0021668472</v>
       </c>
       <c r="P17" t="n">
         <v>4700</v>
@@ -2326,10 +2326,10 @@
         <v>122</v>
       </c>
       <c r="N46" t="n">
-        <v>427.91888111888</v>
+        <v>427.91887323944</v>
       </c>
       <c r="O46" t="n">
-        <v>52206.10349650336</v>
+        <v>52206.10253521168</v>
       </c>
       <c r="P46" t="n">
         <v>6800</v>
@@ -2372,10 +2372,10 @@
         <v>166</v>
       </c>
       <c r="N47" t="n">
-        <v>580.36599462366</v>
+        <v>580.36598382749</v>
       </c>
       <c r="O47" t="n">
-        <v>96340.75510752756</v>
+        <v>96340.75331536334</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
@@ -3539,10 +3539,10 @@
         <v>948</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2556563454</v>
+        <v>2582.2556363636</v>
       </c>
       <c r="O73" t="n">
-        <v>2447978.362215439</v>
+        <v>2447978.343272693</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3585,10 +3585,10 @@
         <v>1372</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8961063218</v>
+        <v>5216.8960979122</v>
       </c>
       <c r="O74" t="n">
-        <v>7157581.45787351</v>
+        <v>7157581.446335539</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
@@ -3677,10 +3677,10 @@
         <v>3410</v>
       </c>
       <c r="N76" t="n">
-        <v>3160.2538267431</v>
+        <v>3158.8608271635</v>
       </c>
       <c r="O76" t="n">
-        <v>10776465.54919397</v>
+        <v>10771715.42062753</v>
       </c>
       <c r="P76" t="n">
         <v>5600</v>
@@ -3723,10 +3723,10 @@
         <v>320</v>
       </c>
       <c r="N77" t="n">
-        <v>3856.9300996016</v>
+        <v>3841.6248454636</v>
       </c>
       <c r="O77" t="n">
-        <v>1234217.631872512</v>
+        <v>1229319.950548352</v>
       </c>
       <c r="P77" t="n">
         <v>6900</v>
@@ -3818,10 +3818,10 @@
         <v>514</v>
       </c>
       <c r="N79" t="n">
-        <v>2694.8231862975</v>
+        <v>2694.8231670588</v>
       </c>
       <c r="O79" t="n">
-        <v>1385139.117756915</v>
+        <v>1385139.107868223</v>
       </c>
       <c r="P79" t="n">
         <v>4900</v>
@@ -4103,10 +4103,10 @@
         <v>322</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2539962477</v>
+        <v>3594.2539736347</v>
       </c>
       <c r="O85" t="n">
-        <v>1157349.786791759</v>
+        <v>1157349.779510373</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4149,10 +4149,10 @@
         <v>276</v>
       </c>
       <c r="N86" t="n">
-        <v>14822.378849611</v>
+        <v>14822.37884823</v>
       </c>
       <c r="O86" t="n">
-        <v>4090976.562492636</v>
+        <v>4090976.56211148</v>
       </c>
       <c r="P86" t="n">
         <v>24900</v>
@@ -4193,10 +4193,10 @@
         <v>192</v>
       </c>
       <c r="N87" t="n">
-        <v>2091.1308394896</v>
+        <v>2090.85</v>
       </c>
       <c r="O87" t="n">
-        <v>401497.1211820032</v>
+        <v>401443.2</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4460,10 +4460,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107904123</v>
+        <v>4372.2107907508</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.820560699</v>
+        <v>1385990.820668004</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4593,10 +4593,10 @@
         <v>184</v>
       </c>
       <c r="N96" t="n">
-        <v>1600.6713740458</v>
+        <v>1592.5665147453</v>
       </c>
       <c r="O96" t="n">
-        <v>294523.5328244272</v>
+        <v>293032.2387131352</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -4950,10 +4950,10 @@
         <v>99</v>
       </c>
       <c r="N104" t="n">
-        <v>3775.3787545788</v>
+        <v>3761.6</v>
       </c>
       <c r="O104" t="n">
-        <v>373762.4967033012</v>
+        <v>372398.4</v>
       </c>
       <c r="P104" t="n">
         <v>6900</v>
@@ -5232,10 +5232,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9236566809</v>
+        <v>1630.923733916</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.445649052</v>
+        <v>1037267.494770576</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5278,10 +5278,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1937050719</v>
+        <v>1550.1937906027</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4552166537</v>
+        <v>35654.4571838621</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5324,10 +5324,10 @@
         <v>168</v>
       </c>
       <c r="N112" t="n">
-        <v>1579.3903753351</v>
+        <v>1579.3897428571</v>
       </c>
       <c r="O112" t="n">
-        <v>265337.5830562968</v>
+        <v>265337.4767999928</v>
       </c>
       <c r="P112" t="n">
         <v>2900</v>
@@ -5370,10 +5370,10 @@
         <v>123</v>
       </c>
       <c r="N113" t="n">
-        <v>2403.5121166602</v>
+        <v>2403.5124244849</v>
       </c>
       <c r="O113" t="n">
-        <v>295631.9903492046</v>
+        <v>295632.0282116427</v>
       </c>
       <c r="P113" t="n">
         <v>3500</v>
@@ -5457,10 +5457,10 @@
         <v>50</v>
       </c>
       <c r="N115" t="n">
-        <v>2069.4655925926</v>
+        <v>2069.4655762082</v>
       </c>
       <c r="O115" t="n">
-        <v>103473.27962963</v>
+        <v>103473.27881041</v>
       </c>
       <c r="P115" t="n">
         <v>6500</v>
@@ -6068,10 +6068,10 @@
         <v>103</v>
       </c>
       <c r="N129" t="n">
-        <v>5449.5305217391</v>
+        <v>5449.5305263158</v>
       </c>
       <c r="O129" t="n">
-        <v>561301.6437391273</v>
+        <v>561301.6442105274</v>
       </c>
       <c r="P129" t="n">
         <v>6200</v>
@@ -6155,10 +6155,10 @@
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>2029.8738600103</v>
+        <v>2029.8738739669</v>
       </c>
       <c r="O131" t="n">
-        <v>4059.7477200206</v>
+        <v>4059.7477479338</v>
       </c>
       <c r="P131" t="n">
         <v>3600</v>
@@ -6278,10 +6278,10 @@
         <v>402</v>
       </c>
       <c r="N134" t="n">
-        <v>880.32952448883</v>
+        <v>880.32953355545</v>
       </c>
       <c r="O134" t="n">
-        <v>353892.4688445096</v>
+        <v>353892.4724892909</v>
       </c>
       <c r="P134" t="n">
         <v>1200</v>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7673,19 +7673,19 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>5218.1705597964</v>
+        <v>5218.1705662806</v>
       </c>
       <c r="O166" t="n">
-        <v>401799.1331043228</v>
+        <v>260908.52831403</v>
       </c>
       <c r="P166" t="n">
         <v>8500</v>
       </c>
       <c r="Q166" t="n">
-        <v>654500</v>
+        <v>425000</v>
       </c>
     </row>
     <row r="167">
@@ -7894,7 +7894,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7903,19 +7903,19 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="N171" t="n">
         <v>6058.52</v>
       </c>
       <c r="O171" t="n">
-        <v>1272289.2</v>
+        <v>1151118.8</v>
       </c>
       <c r="P171" t="n">
         <v>9700</v>
       </c>
       <c r="Q171" t="n">
-        <v>2037000</v>
+        <v>1843000</v>
       </c>
     </row>
     <row r="172">
@@ -8700,10 +8700,10 @@
         <v>344</v>
       </c>
       <c r="N188" t="n">
-        <v>17075.989522822</v>
+        <v>17075.989522491</v>
       </c>
       <c r="O188" t="n">
-        <v>5874140.395850768</v>
+        <v>5874140.395736904</v>
       </c>
       <c r="P188" t="n">
         <v>27500</v>
@@ -8930,10 +8930,10 @@
         <v>552</v>
       </c>
       <c r="N193" t="n">
-        <v>1516.0387951453</v>
+        <v>1516.0387934921</v>
       </c>
       <c r="O193" t="n">
-        <v>836853.4149202056</v>
+        <v>836853.4140076392</v>
       </c>
       <c r="P193" t="n">
         <v>2300</v>
@@ -8976,10 +8976,10 @@
         <v>384</v>
       </c>
       <c r="N194" t="n">
-        <v>2458.5130690113</v>
+        <v>2458.5130528766</v>
       </c>
       <c r="O194" t="n">
-        <v>944069.0185003392</v>
+        <v>944069.0123046143</v>
       </c>
       <c r="P194" t="n">
         <v>3500</v>
@@ -9068,10 +9068,10 @@
         <v>240</v>
       </c>
       <c r="N196" t="n">
-        <v>2079.3839709361</v>
+        <v>2079.3839648173</v>
       </c>
       <c r="O196" t="n">
-        <v>499052.153024664</v>
+        <v>499052.1515561519</v>
       </c>
       <c r="P196" t="n">
         <v>2900</v>
@@ -9114,10 +9114,10 @@
         <v>266</v>
       </c>
       <c r="N197" t="n">
-        <v>1803.0156368474</v>
+        <v>1803.0156556557</v>
       </c>
       <c r="O197" t="n">
-        <v>479602.1594014084</v>
+        <v>479602.1644044162</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
@@ -9160,10 +9160,10 @@
         <v>36</v>
       </c>
       <c r="N198" t="n">
-        <v>3306.5946666667</v>
+        <v>3306.5946508172</v>
       </c>
       <c r="O198" t="n">
-        <v>119037.4080000012</v>
+        <v>119037.4074294192</v>
       </c>
       <c r="P198" t="n">
         <v>4900</v>
@@ -9206,10 +9206,10 @@
         <v>264</v>
       </c>
       <c r="N199" t="n">
-        <v>2122.1638509903</v>
+        <v>2122.163800317</v>
       </c>
       <c r="O199" t="n">
-        <v>560251.2566614392</v>
+        <v>560251.243283688</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
@@ -9252,10 +9252,10 @@
         <v>96</v>
       </c>
       <c r="N200" t="n">
-        <v>2108.7921081831</v>
+        <v>2108.7923742027</v>
       </c>
       <c r="O200" t="n">
-        <v>202444.0423855776</v>
+        <v>202444.0679234592</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
@@ -9298,10 +9298,10 @@
         <v>192</v>
       </c>
       <c r="N201" t="n">
-        <v>2056.0829819789</v>
+        <v>2056.0829556314</v>
       </c>
       <c r="O201" t="n">
-        <v>394767.9325399488</v>
+        <v>394767.9274812288</v>
       </c>
       <c r="P201" t="n">
         <v>2900</v>
@@ -9344,10 +9344,10 @@
         <v>180</v>
       </c>
       <c r="N202" t="n">
-        <v>3224.5688090551</v>
+        <v>3224.5688526212</v>
       </c>
       <c r="O202" t="n">
-        <v>580422.385629918</v>
+        <v>580422.3934718161</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9390,10 +9390,10 @@
         <v>240</v>
       </c>
       <c r="N203" t="n">
-        <v>1655.9307861426</v>
+        <v>1655.9307707708</v>
       </c>
       <c r="O203" t="n">
-        <v>397423.388674224</v>
+        <v>397423.384984992</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9436,10 +9436,10 @@
         <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>1592.2788188188</v>
+        <v>1592.279767184</v>
       </c>
       <c r="O204" t="n">
-        <v>1592.2788188188</v>
+        <v>1592.279767184</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9526,10 +9526,10 @@
         <v>36</v>
       </c>
       <c r="N206" t="n">
-        <v>2311.9201658768</v>
+        <v>2311.9177393617</v>
       </c>
       <c r="O206" t="n">
-        <v>83229.1259715648</v>
+        <v>83229.0386170212</v>
       </c>
       <c r="P206" t="n">
         <v>3500</v>
@@ -9572,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="N207" t="n">
-        <v>1906.1827536232</v>
+        <v>1906.1819786096</v>
       </c>
       <c r="O207" t="n">
-        <v>22874.1930434784</v>
+        <v>22874.1837433152</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -9618,10 +9618,10 @@
         <v>48</v>
       </c>
       <c r="N208" t="n">
-        <v>2546.9837028825</v>
+        <v>2546.9835746606</v>
       </c>
       <c r="O208" t="n">
-        <v>122255.21773836</v>
+        <v>122255.2115837088</v>
       </c>
       <c r="P208" t="n">
         <v>3900</v>
@@ -9664,10 +9664,10 @@
         <v>600</v>
       </c>
       <c r="N209" t="n">
-        <v>1259.274561681</v>
+        <v>1259.2746169678</v>
       </c>
       <c r="O209" t="n">
-        <v>755564.7370086</v>
+        <v>755564.7701806801</v>
       </c>
       <c r="P209" t="n">
         <v>1900</v>
@@ -9841,10 +9841,10 @@
         <v>192</v>
       </c>
       <c r="N213" t="n">
-        <v>692.15222920696</v>
+        <v>692.1522422179</v>
       </c>
       <c r="O213" t="n">
-        <v>132893.2280077363</v>
+        <v>132893.2305058368</v>
       </c>
       <c r="P213" t="n">
         <v>1200</v>
@@ -9982,10 +9982,10 @@
         <v>2761</v>
       </c>
       <c r="N216" t="n">
-        <v>1185.3195716639</v>
+        <v>1185.31957078</v>
       </c>
       <c r="O216" t="n">
-        <v>3272667.337364028</v>
+        <v>3272667.33492358</v>
       </c>
       <c r="P216" t="n">
         <v>1900</v>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -10126,19 +10126,19 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="N219" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O219" t="n">
-        <v>545668.1799999999</v>
+        <v>277306.78</v>
       </c>
       <c r="P219" t="n">
         <v>14900</v>
       </c>
       <c r="Q219" t="n">
-        <v>908900</v>
+        <v>461900</v>
       </c>
     </row>
     <row r="220">
@@ -10687,10 +10687,10 @@
         <v>1</v>
       </c>
       <c r="N231" t="n">
-        <v>1690.870009095</v>
+        <v>1690.8700091449</v>
       </c>
       <c r="O231" t="n">
-        <v>1690.870009095</v>
+        <v>1690.8700091449</v>
       </c>
       <c r="P231" t="n">
         <v>3000</v>
@@ -10785,10 +10785,10 @@
         <v>-2</v>
       </c>
       <c r="N233" t="n">
-        <v>2270.3211764706</v>
+        <v>2270.3212345679</v>
       </c>
       <c r="O233" t="n">
-        <v>-4540.6423529412</v>
+        <v>-4540.6424691358</v>
       </c>
       <c r="P233" t="n">
         <v>3900</v>
@@ -10981,10 +10981,10 @@
         <v>553</v>
       </c>
       <c r="N237" t="n">
-        <v>517.28997081144</v>
+        <v>517.29010591089</v>
       </c>
       <c r="O237" t="n">
-        <v>286061.3538587263</v>
+        <v>286061.4285687222</v>
       </c>
       <c r="P237" t="n">
         <v>900</v>
@@ -11220,10 +11220,10 @@
         <v>504</v>
       </c>
       <c r="N242" t="n">
-        <v>3110.8413717354</v>
+        <v>3110.8411757364</v>
       </c>
       <c r="O242" t="n">
-        <v>1567864.051354642</v>
+        <v>1567863.952571146</v>
       </c>
       <c r="P242" t="n">
         <v>4500</v>
@@ -11448,10 +11448,10 @@
         <v>12794</v>
       </c>
       <c r="N247" t="n">
-        <v>703.79516401441</v>
+        <v>703.79514130448</v>
       </c>
       <c r="O247" t="n">
-        <v>9004355.328400362</v>
+        <v>9004355.037849518</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
@@ -11543,10 +11543,10 @@
         <v>161</v>
       </c>
       <c r="N249" t="n">
-        <v>3182.2511235955</v>
+        <v>3182.2511173184</v>
       </c>
       <c r="O249" t="n">
-        <v>512342.4308988755</v>
+        <v>512342.4298882624</v>
       </c>
       <c r="P249" t="n">
         <v>6900</v>
@@ -11727,10 +11727,10 @@
         <v>59</v>
       </c>
       <c r="N253" t="n">
-        <v>2501.384953271</v>
+        <v>2501.3849295775</v>
       </c>
       <c r="O253" t="n">
-        <v>147581.712242989</v>
+        <v>147581.7108450725</v>
       </c>
       <c r="P253" t="n">
         <v>4100</v>
@@ -12355,10 +12355,10 @@
         <v>71</v>
       </c>
       <c r="N266" t="n">
-        <v>2110.6406122449</v>
+        <v>2098.4050733138</v>
       </c>
       <c r="O266" t="n">
-        <v>149855.4834693879</v>
+        <v>148986.7602052798</v>
       </c>
       <c r="P266" t="n">
         <v>9500</v>
@@ -13841,10 +13841,10 @@
         <v>13</v>
       </c>
       <c r="N297" t="n">
-        <v>3093.3711764706</v>
+        <v>3093.37125</v>
       </c>
       <c r="O297" t="n">
-        <v>40213.8252941178</v>
+        <v>40213.82625</v>
       </c>
       <c r="P297" t="n">
         <v>11500</v>
@@ -17025,10 +17025,10 @@
         <v>8</v>
       </c>
       <c r="N363" t="n">
-        <v>7046.93982792</v>
+        <v>7046.939827883</v>
       </c>
       <c r="O363" t="n">
-        <v>56375.51862336</v>
+        <v>56375.518623064</v>
       </c>
       <c r="P363" t="n">
         <v>9900</v>
@@ -17757,10 +17757,10 @@
         <v>984</v>
       </c>
       <c r="N378" t="n">
-        <v>430.60997607656</v>
+        <v>430.6099760479</v>
       </c>
       <c r="O378" t="n">
-        <v>423720.216459335</v>
+        <v>423720.2164311336</v>
       </c>
       <c r="P378" t="n">
         <v>2200</v>
@@ -17806,10 +17806,10 @@
         <v>726</v>
       </c>
       <c r="N379" t="n">
-        <v>465.87095553453</v>
+        <v>465.87095916429</v>
       </c>
       <c r="O379" t="n">
-        <v>338222.3137180688</v>
+        <v>338222.3163532746</v>
       </c>
       <c r="P379" t="n">
         <v>2500</v>
@@ -17855,10 +17855,10 @@
         <v>455</v>
       </c>
       <c r="N380" t="n">
-        <v>315.02697707736</v>
+        <v>315.02699712644</v>
       </c>
       <c r="O380" t="n">
-        <v>143337.2745701988</v>
+        <v>143337.2836925302</v>
       </c>
       <c r="P380" t="n">
         <v>2200</v>
@@ -21191,10 +21191,10 @@
         <v>235</v>
       </c>
       <c r="N452" t="n">
-        <v>227.41601620029</v>
+        <v>227.41613363363</v>
       </c>
       <c r="O452" t="n">
-        <v>53442.76380706815</v>
+        <v>53442.79140390305</v>
       </c>
       <c r="P452" t="n">
         <v>1200</v>
@@ -21700,10 +21700,10 @@
         <v>561</v>
       </c>
       <c r="N463" t="n">
-        <v>4687.9742758621</v>
+        <v>4687.9743167972</v>
       </c>
       <c r="O463" t="n">
-        <v>2629953.568758638</v>
+        <v>2629953.591723229</v>
       </c>
       <c r="P463" t="n">
         <v>5900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -10454,10 +10454,10 @@
         <v>63</v>
       </c>
       <c r="N226" t="n">
-        <v>3642.7032352941</v>
+        <v>3629.36</v>
       </c>
       <c r="O226" t="n">
-        <v>229490.3038235283</v>
+        <v>228649.68</v>
       </c>
       <c r="P226" t="n">
         <v>3900</v>
@@ -20711,10 +20711,10 @@
         <v>38</v>
       </c>
       <c r="N442" t="n">
-        <v>1327.2142261905</v>
+        <v>1319.3608928571</v>
       </c>
       <c r="O442" t="n">
-        <v>50434.14059523901</v>
+        <v>50135.7139285698</v>
       </c>
       <c r="P442" t="n">
         <v>3500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -1121,10 +1121,10 @@
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2474.7041355932</v>
+        <v>2474.7040753425</v>
       </c>
       <c r="O18" t="n">
-        <v>9898.816542372801</v>
+        <v>9898.81630137</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -3539,10 +3539,10 @@
         <v>948</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2556363636</v>
+        <v>2582.2556074972</v>
       </c>
       <c r="O73" t="n">
-        <v>2447978.343272693</v>
+        <v>2447978.315907346</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3585,10 +3585,10 @@
         <v>1372</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8960979122</v>
+        <v>5216.8960939752</v>
       </c>
       <c r="O74" t="n">
-        <v>7157581.446335539</v>
+        <v>7157581.440933974</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
@@ -4103,10 +4103,10 @@
         <v>322</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2539736347</v>
+        <v>3594.2539698492</v>
       </c>
       <c r="O85" t="n">
-        <v>1157349.779510373</v>
+        <v>1157349.778291442</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4460,10 +4460,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107907508</v>
+        <v>4372.2107910895</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.820668004</v>
+        <v>1385990.820775372</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4593,10 +4593,10 @@
         <v>184</v>
       </c>
       <c r="N96" t="n">
-        <v>1592.5665147453</v>
+        <v>1592.566460177</v>
       </c>
       <c r="O96" t="n">
-        <v>293032.2387131352</v>
+        <v>293032.228672568</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -5232,10 +5232,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.923733916</v>
+        <v>1630.9237493905</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.494770576</v>
+        <v>1037267.504612358</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5278,10 +5278,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1937906027</v>
+        <v>1550.1937917646</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4571838621</v>
+        <v>35654.4572105858</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5370,10 +5370,10 @@
         <v>123</v>
       </c>
       <c r="N113" t="n">
-        <v>2403.5124244849</v>
+        <v>2403.5125045299</v>
       </c>
       <c r="O113" t="n">
-        <v>295632.0282116427</v>
+        <v>295632.0380571777</v>
       </c>
       <c r="P113" t="n">
         <v>3500</v>
@@ -6155,10 +6155,10 @@
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>2029.8738739669</v>
+        <v>2029.8739473684</v>
       </c>
       <c r="O131" t="n">
-        <v>4059.7477479338</v>
+        <v>4059.7478947368</v>
       </c>
       <c r="P131" t="n">
         <v>3600</v>
@@ -8976,10 +8976,10 @@
         <v>384</v>
       </c>
       <c r="N194" t="n">
-        <v>2458.5130528766</v>
+        <v>2458.5130063609</v>
       </c>
       <c r="O194" t="n">
-        <v>944069.0123046143</v>
+        <v>944068.9944425856</v>
       </c>
       <c r="P194" t="n">
         <v>3500</v>
@@ -9022,10 +9022,10 @@
         <v>144</v>
       </c>
       <c r="N195" t="n">
-        <v>1771.0904111406</v>
+        <v>1771.0903664224</v>
       </c>
       <c r="O195" t="n">
-        <v>255037.0192042464</v>
+        <v>255037.0127648256</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9114,10 +9114,10 @@
         <v>266</v>
       </c>
       <c r="N197" t="n">
-        <v>1803.0156556557</v>
+        <v>1803.0157013118</v>
       </c>
       <c r="O197" t="n">
-        <v>479602.1644044162</v>
+        <v>479602.1765489388</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
@@ -9298,10 +9298,10 @@
         <v>192</v>
       </c>
       <c r="N201" t="n">
-        <v>2056.0829556314</v>
+        <v>2056.0829120879</v>
       </c>
       <c r="O201" t="n">
-        <v>394767.9274812288</v>
+        <v>394767.9191208768</v>
       </c>
       <c r="P201" t="n">
         <v>2900</v>
@@ -9436,10 +9436,10 @@
         <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>1592.279767184</v>
+        <v>1592.2798435754</v>
       </c>
       <c r="O204" t="n">
-        <v>1592.279767184</v>
+        <v>1592.2798435754</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9526,10 +9526,10 @@
         <v>36</v>
       </c>
       <c r="N206" t="n">
-        <v>2311.9177393617</v>
+        <v>2311.9170054945</v>
       </c>
       <c r="O206" t="n">
-        <v>83229.0386170212</v>
+        <v>83229.01219780199</v>
       </c>
       <c r="P206" t="n">
         <v>3500</v>
@@ -9572,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="N207" t="n">
-        <v>1906.1819786096</v>
+        <v>1906.1816666667</v>
       </c>
       <c r="O207" t="n">
-        <v>22874.1837433152</v>
+        <v>22874.1800000004</v>
       </c>
       <c r="P207" t="n">
         <v>2900</v>
@@ -10687,10 +10687,10 @@
         <v>1</v>
       </c>
       <c r="N231" t="n">
-        <v>1690.8700091449</v>
+        <v>1690.8700091701</v>
       </c>
       <c r="O231" t="n">
-        <v>1690.8700091449</v>
+        <v>1690.8700091701</v>
       </c>
       <c r="P231" t="n">
         <v>3000</v>
@@ -10981,10 +10981,10 @@
         <v>553</v>
       </c>
       <c r="N237" t="n">
-        <v>517.29010591089</v>
+        <v>517.2904197169401</v>
       </c>
       <c r="O237" t="n">
-        <v>286061.4285687222</v>
+        <v>286061.6021034679</v>
       </c>
       <c r="P237" t="n">
         <v>900</v>
@@ -11122,10 +11122,10 @@
         <v>59</v>
       </c>
       <c r="N240" t="n">
-        <v>3259.1342692308</v>
+        <v>3259.1343023256</v>
       </c>
       <c r="O240" t="n">
-        <v>192288.9218846172</v>
+        <v>192288.9238372104</v>
       </c>
       <c r="P240" t="n">
         <v>3600</v>
@@ -11220,10 +11220,10 @@
         <v>504</v>
       </c>
       <c r="N242" t="n">
-        <v>3110.8411757364</v>
+        <v>3110.8406506215</v>
       </c>
       <c r="O242" t="n">
-        <v>1567863.952571146</v>
+        <v>1567863.687913236</v>
       </c>
       <c r="P242" t="n">
         <v>4500</v>
@@ -11448,10 +11448,10 @@
         <v>12794</v>
       </c>
       <c r="N247" t="n">
-        <v>703.79514130448</v>
+        <v>703.79512253205</v>
       </c>
       <c r="O247" t="n">
-        <v>9004355.037849518</v>
+        <v>9004354.797675047</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3718,10 +3718,10 @@
         <v>3410</v>
       </c>
       <c r="N77" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O77" t="n">
-        <v>10771715.42062753</v>
+        <v>10771715.42076598</v>
       </c>
       <c r="P77" t="n">
         <v>5600</v>
@@ -4144,10 +4144,10 @@
         <v>322</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O86" t="n">
-        <v>1157349.775849072</v>
+        <v>1157349.773400488</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -9155,10 +9155,10 @@
         <v>266</v>
       </c>
       <c r="N198" t="n">
-        <v>1803.0157013118</v>
+        <v>1803.0157128413</v>
       </c>
       <c r="O198" t="n">
-        <v>479602.1765489388</v>
+        <v>479602.1796157858</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
@@ -9293,10 +9293,10 @@
         <v>96</v>
       </c>
       <c r="N201" t="n">
-        <v>2108.7924270463</v>
+        <v>2108.7924803431</v>
       </c>
       <c r="O201" t="n">
-        <v>202444.0729964448</v>
+        <v>202444.0781129376</v>
       </c>
       <c r="P201" t="n">
         <v>2900</v>
@@ -9339,10 +9339,10 @@
         <v>192</v>
       </c>
       <c r="N202" t="n">
-        <v>2056.0829120879</v>
+        <v>2056.0828974535</v>
       </c>
       <c r="O202" t="n">
-        <v>394767.9191208768</v>
+        <v>394767.9163110721</v>
       </c>
       <c r="P202" t="n">
         <v>2900</v>
@@ -9477,10 +9477,10 @@
         <v>1</v>
       </c>
       <c r="N205" t="n">
-        <v>1592.2799548023</v>
+        <v>1592.2799660633</v>
       </c>
       <c r="O205" t="n">
-        <v>1592.2799548023</v>
+        <v>1592.2799660633</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>
@@ -11489,10 +11489,10 @@
         <v>12794</v>
       </c>
       <c r="N248" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O248" t="n">
-        <v>9004354.734682254</v>
+        <v>9004354.725564225</v>
       </c>
       <c r="P248" t="n">
         <v>900</v>
@@ -18171,10 +18171,10 @@
         <v>13</v>
       </c>
       <c r="N387" t="n">
-        <v>22951.704792746</v>
+        <v>22951.704785992</v>
       </c>
       <c r="O387" t="n">
-        <v>298372.162305698</v>
+        <v>298372.162217896</v>
       </c>
       <c r="P387" t="n">
         <v>37900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3580,10 +3580,10 @@
         <v>948</v>
       </c>
       <c r="N74" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O74" t="n">
-        <v>2447978.266666709</v>
+        <v>2447978.264785687</v>
       </c>
       <c r="P74" t="n">
         <v>4500</v>
@@ -9431,10 +9431,10 @@
         <v>240</v>
       </c>
       <c r="N204" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O204" t="n">
-        <v>397423.370852928</v>
+        <v>397423.367854752</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9477,10 +9477,10 @@
         <v>1</v>
       </c>
       <c r="N205" t="n">
-        <v>1592.2805889423</v>
+        <v>1592.2806787879</v>
       </c>
       <c r="O205" t="n">
-        <v>1592.2805889423</v>
+        <v>1592.2806787879</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>
@@ -9567,10 +9567,10 @@
         <v>36</v>
       </c>
       <c r="N207" t="n">
-        <v>2311.9153823529</v>
+        <v>2311.9150892857</v>
       </c>
       <c r="O207" t="n">
-        <v>83228.95376470441</v>
+        <v>83228.9432142852</v>
       </c>
       <c r="P207" t="n">
         <v>3500</v>
@@ -9613,10 +9613,10 @@
         <v>2</v>
       </c>
       <c r="N208" t="n">
-        <v>1906.1813793103</v>
+        <v>1906.1812280702</v>
       </c>
       <c r="O208" t="n">
-        <v>3812.3627586206</v>
+        <v>3812.3624561404</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9705,10 +9705,10 @@
         <v>600</v>
       </c>
       <c r="N210" t="n">
-        <v>1259.2746360505</v>
+        <v>1259.2746413793</v>
       </c>
       <c r="O210" t="n">
-        <v>755564.7816303</v>
+        <v>755564.78482758</v>
       </c>
       <c r="P210" t="n">
         <v>1900</v>
@@ -11212,10 +11212,10 @@
         <v>504</v>
       </c>
       <c r="N242" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O242" t="n">
-        <v>1567863.574322875</v>
+        <v>1567863.569088936</v>
       </c>
       <c r="P242" t="n">
         <v>4500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -1121,10 +1121,10 @@
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2474.7040344828</v>
+        <v>2474.7040138408</v>
       </c>
       <c r="O18" t="n">
-        <v>9898.816137931201</v>
+        <v>9898.816055363201</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -2372,10 +2372,10 @@
         <v>166</v>
       </c>
       <c r="N47" t="n">
-        <v>580.36598382749</v>
+        <v>580.36597297297</v>
       </c>
       <c r="O47" t="n">
-        <v>96340.75331536334</v>
+        <v>96340.75151351302</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>2189</v>
       </c>
       <c r="O69" t="n">
-        <v>6567</v>
+        <v>4378</v>
       </c>
       <c r="P69" t="n">
         <v>4500</v>
       </c>
       <c r="Q69" t="n">
-        <v>13500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="70">
@@ -3580,10 +3580,10 @@
         <v>948</v>
       </c>
       <c r="N74" t="n">
-        <v>2582.2555535714</v>
+        <v>2582.255546613</v>
       </c>
       <c r="O74" t="n">
-        <v>2447978.264785687</v>
+        <v>2447978.258189124</v>
       </c>
       <c r="P74" t="n">
         <v>4500</v>
@@ -3626,10 +3626,10 @@
         <v>1372</v>
       </c>
       <c r="N75" t="n">
-        <v>5216.89608155</v>
+        <v>5216.8960627633</v>
       </c>
       <c r="O75" t="n">
-        <v>7157581.423886601</v>
+        <v>7157581.398111247</v>
       </c>
       <c r="P75" t="n">
         <v>8500</v>
@@ -3718,10 +3718,10 @@
         <v>3410</v>
       </c>
       <c r="N77" t="n">
-        <v>3158.8608285041</v>
+        <v>3158.8608303391</v>
       </c>
       <c r="O77" t="n">
-        <v>10771715.42519898</v>
+        <v>10771715.43145633</v>
       </c>
       <c r="P77" t="n">
         <v>5600</v>
@@ -3764,10 +3764,10 @@
         <v>320</v>
       </c>
       <c r="N78" t="n">
-        <v>3841.6248454636</v>
+        <v>3841.62486</v>
       </c>
       <c r="O78" t="n">
-        <v>1229319.950548352</v>
+        <v>1229319.9552</v>
       </c>
       <c r="P78" t="n">
         <v>6900</v>
@@ -3813,10 +3813,10 @@
         <v>30</v>
       </c>
       <c r="N79" t="n">
-        <v>3230.0671836735</v>
+        <v>3230.0670700637</v>
       </c>
       <c r="O79" t="n">
-        <v>96902.015510205</v>
+        <v>96902.01210191101</v>
       </c>
       <c r="P79" t="n">
         <v>6200</v>
@@ -4144,10 +4144,10 @@
         <v>322</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.2538892425</v>
+        <v>3594.2538618926</v>
       </c>
       <c r="O86" t="n">
-        <v>1157349.752336085</v>
+        <v>1157349.743529417</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -4501,10 +4501,10 @@
         <v>317</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107914851</v>
+        <v>4372.2107916548</v>
       </c>
       <c r="O94" t="n">
-        <v>1385990.820900777</v>
+        <v>1385990.820954572</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4631,19 +4631,19 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="N97" t="n">
-        <v>1592.5663938974</v>
+        <v>1592.5662962963</v>
       </c>
       <c r="O97" t="n">
-        <v>293032.2164771216</v>
+        <v>264366.0051851858</v>
       </c>
       <c r="P97" t="n">
         <v>3900</v>
       </c>
       <c r="Q97" t="n">
-        <v>717600</v>
+        <v>647400</v>
       </c>
     </row>
     <row r="98">
@@ -5273,10 +5273,10 @@
         <v>636</v>
       </c>
       <c r="N111" t="n">
-        <v>1630.9238354115</v>
+        <v>1630.9238750315</v>
       </c>
       <c r="O111" t="n">
-        <v>1037267.559321714</v>
+        <v>1037267.584520034</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5319,10 +5319,10 @@
         <v>23</v>
       </c>
       <c r="N112" t="n">
-        <v>1550.1938475894</v>
+        <v>1550.1938919769</v>
       </c>
       <c r="O112" t="n">
-        <v>35654.4584945562</v>
+        <v>35654.4595154687</v>
       </c>
       <c r="P112" t="n">
         <v>2500</v>
@@ -5365,10 +5365,10 @@
         <v>72</v>
       </c>
       <c r="N113" t="n">
-        <v>1579.3893154762</v>
+        <v>1579.3891212121</v>
       </c>
       <c r="O113" t="n">
-        <v>113716.0307142864</v>
+        <v>113716.0167272712</v>
       </c>
       <c r="P113" t="n">
         <v>2900</v>
@@ -5411,10 +5411,10 @@
         <v>123</v>
       </c>
       <c r="N114" t="n">
-        <v>2403.5129584811</v>
+        <v>2403.5131199831</v>
       </c>
       <c r="O114" t="n">
-        <v>295632.0938931753</v>
+        <v>295632.1137579213</v>
       </c>
       <c r="P114" t="n">
         <v>3500</v>
@@ -6068,10 +6068,10 @@
         <v>109</v>
       </c>
       <c r="N129" t="n">
-        <v>4196.8725305216</v>
+        <v>4196.872531224</v>
       </c>
       <c r="O129" t="n">
-        <v>457459.1058268544</v>
+        <v>457459.1059034161</v>
       </c>
       <c r="P129" t="n">
         <v>5900</v>
@@ -6319,10 +6319,10 @@
         <v>402</v>
       </c>
       <c r="N135" t="n">
-        <v>880.32953355545</v>
+        <v>880.32956085919</v>
       </c>
       <c r="O135" t="n">
-        <v>353892.4724892909</v>
+        <v>353892.4834653944</v>
       </c>
       <c r="P135" t="n">
         <v>1200</v>
@@ -7717,10 +7717,10 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>5218.1705677419</v>
+        <v>5218.1705692109</v>
       </c>
       <c r="O167" t="n">
-        <v>260908.528387095</v>
+        <v>260908.528460545</v>
       </c>
       <c r="P167" t="n">
         <v>8500</v>
@@ -8971,10 +8971,10 @@
         <v>552</v>
       </c>
       <c r="N194" t="n">
-        <v>1516.0387919529</v>
+        <v>1516.0387905286</v>
       </c>
       <c r="O194" t="n">
-        <v>836853.4131580008</v>
+        <v>836853.4123717872</v>
       </c>
       <c r="P194" t="n">
         <v>2300</v>
@@ -9017,10 +9017,10 @@
         <v>384</v>
       </c>
       <c r="N195" t="n">
-        <v>2458.5129828687</v>
+        <v>2458.5129162428</v>
       </c>
       <c r="O195" t="n">
-        <v>944068.9854215807</v>
+        <v>944068.9598372353</v>
       </c>
       <c r="P195" t="n">
         <v>3500</v>
@@ -9063,10 +9063,10 @@
         <v>144</v>
       </c>
       <c r="N196" t="n">
-        <v>1771.0903406814</v>
+        <v>1771.0902822581</v>
       </c>
       <c r="O196" t="n">
-        <v>255037.0090581216</v>
+        <v>255037.0006451664</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9155,10 +9155,10 @@
         <v>266</v>
       </c>
       <c r="N198" t="n">
-        <v>1803.0157988368</v>
+        <v>1803.015867082</v>
       </c>
       <c r="O198" t="n">
-        <v>479602.2024905888</v>
+        <v>479602.220643812</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
@@ -9247,10 +9247,10 @@
         <v>264</v>
       </c>
       <c r="N200" t="n">
-        <v>2122.1637428023</v>
+        <v>2122.163732778</v>
       </c>
       <c r="O200" t="n">
-        <v>560251.2280998072</v>
+        <v>560251.225453392</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
@@ -9339,10 +9339,10 @@
         <v>192</v>
       </c>
       <c r="N202" t="n">
-        <v>2056.0828901137</v>
+        <v>2056.0828704663</v>
       </c>
       <c r="O202" t="n">
-        <v>394767.9149018304</v>
+        <v>394767.9111295296</v>
       </c>
       <c r="P202" t="n">
         <v>2900</v>
@@ -9385,10 +9385,10 @@
         <v>180</v>
       </c>
       <c r="N203" t="n">
-        <v>3224.5688657751</v>
+        <v>3224.5689232303</v>
       </c>
       <c r="O203" t="n">
-        <v>580422.3958395181</v>
+        <v>580422.406181454</v>
       </c>
       <c r="P203" t="n">
         <v>4500</v>
@@ -9431,10 +9431,10 @@
         <v>240</v>
       </c>
       <c r="N204" t="n">
-        <v>1655.9306993948</v>
+        <v>1655.9305693829</v>
       </c>
       <c r="O204" t="n">
-        <v>397423.367854752</v>
+        <v>397423.336651896</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9477,10 +9477,10 @@
         <v>1</v>
       </c>
       <c r="N205" t="n">
-        <v>1592.2806787879</v>
+        <v>1592.2810401003</v>
       </c>
       <c r="O205" t="n">
-        <v>1592.2806787879</v>
+        <v>1592.2810401003</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>
@@ -9567,10 +9567,10 @@
         <v>36</v>
       </c>
       <c r="N207" t="n">
-        <v>2311.9150892857</v>
+        <v>2311.9150149254</v>
       </c>
       <c r="O207" t="n">
-        <v>83228.9432142852</v>
+        <v>83228.9405373144</v>
       </c>
       <c r="P207" t="n">
         <v>3500</v>
@@ -9613,10 +9613,10 @@
         <v>2</v>
       </c>
       <c r="N208" t="n">
-        <v>1906.1812280702</v>
+        <v>1906.1809638554</v>
       </c>
       <c r="O208" t="n">
-        <v>3812.3624561404</v>
+        <v>3812.3619277108</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9659,10 +9659,10 @@
         <v>48</v>
       </c>
       <c r="N209" t="n">
-        <v>2546.9831400966</v>
+        <v>2546.9829528536</v>
       </c>
       <c r="O209" t="n">
-        <v>122255.1907246368</v>
+        <v>122255.1817369728</v>
       </c>
       <c r="P209" t="n">
         <v>3900</v>
@@ -9705,10 +9705,10 @@
         <v>600</v>
       </c>
       <c r="N210" t="n">
-        <v>1259.2746413793</v>
+        <v>1259.2746531459</v>
       </c>
       <c r="O210" t="n">
-        <v>755564.78482758</v>
+        <v>755564.79188754</v>
       </c>
       <c r="P210" t="n">
         <v>1900</v>
@@ -9882,10 +9882,10 @@
         <v>192</v>
       </c>
       <c r="N214" t="n">
-        <v>692.15225097656</v>
+        <v>692.1522598039199</v>
       </c>
       <c r="O214" t="n">
-        <v>132893.2321874995</v>
+        <v>132893.2338823526</v>
       </c>
       <c r="P214" t="n">
         <v>1200</v>
@@ -10728,10 +10728,10 @@
         <v>1</v>
       </c>
       <c r="N232" t="n">
-        <v>1690.8700091743</v>
+        <v>1690.8700092251</v>
       </c>
       <c r="O232" t="n">
-        <v>1690.8700091743</v>
+        <v>1690.8700092251</v>
       </c>
       <c r="P232" t="n">
         <v>3000</v>
@@ -10826,10 +10826,10 @@
         <v>-2</v>
       </c>
       <c r="N234" t="n">
-        <v>2270.3212345679</v>
+        <v>2270.3212658228</v>
       </c>
       <c r="O234" t="n">
-        <v>-4540.6424691358</v>
+        <v>-4540.6425316456</v>
       </c>
       <c r="P234" t="n">
         <v>3900</v>
@@ -11114,10 +11114,10 @@
         <v>59</v>
       </c>
       <c r="N240" t="n">
-        <v>3259.1343529412</v>
+        <v>3259.1343700787</v>
       </c>
       <c r="O240" t="n">
-        <v>192288.9268235308</v>
+        <v>192288.9278346433</v>
       </c>
       <c r="P240" t="n">
         <v>3600</v>
@@ -11212,10 +11212,10 @@
         <v>504</v>
       </c>
       <c r="N242" t="n">
-        <v>3110.840414859</v>
+        <v>3110.8403177212</v>
       </c>
       <c r="O242" t="n">
-        <v>1567863.569088936</v>
+        <v>1567863.520131485</v>
       </c>
       <c r="P242" t="n">
         <v>4500</v>
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>12794</v>
+        <v>12506</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11437,19 +11437,19 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>12794</v>
+        <v>12506</v>
       </c>
       <c r="N247" t="n">
-        <v>703.79510612101</v>
+        <v>703.79509062003</v>
       </c>
       <c r="O247" t="n">
-        <v>9004354.587712202</v>
+        <v>8801661.403294096</v>
       </c>
       <c r="P247" t="n">
         <v>900</v>
       </c>
       <c r="Q247" t="n">
-        <v>11514600</v>
+        <v>11255400</v>
       </c>
     </row>
     <row r="248">
@@ -13113,10 +13113,10 @@
         <v>1</v>
       </c>
       <c r="N282" t="n">
-        <v>3505.3804081633</v>
+        <v>3505.3804255319</v>
       </c>
       <c r="O282" t="n">
-        <v>3505.3804081633</v>
+        <v>3505.3804255319</v>
       </c>
       <c r="P282" t="n">
         <v>12900</v>
@@ -19011,10 +19011,10 @@
         <v>1527</v>
       </c>
       <c r="N405" t="n">
-        <v>220.00509068498</v>
+        <v>220.00482072427</v>
       </c>
       <c r="O405" t="n">
-        <v>335947.7734759644</v>
+        <v>335947.3612459603</v>
       </c>
       <c r="P405" t="n">
         <v>260</v>
@@ -21091,10 +21091,10 @@
         <v>42</v>
       </c>
       <c r="N450" t="n">
-        <v>2432.1354117647</v>
+        <v>2432.1354761905</v>
       </c>
       <c r="O450" t="n">
-        <v>102149.6872941174</v>
+        <v>102149.690000001</v>
       </c>
       <c r="P450" t="n">
         <v>4500</v>
@@ -21692,10 +21692,10 @@
         <v>561</v>
       </c>
       <c r="N463" t="n">
-        <v>4687.9743738977</v>
+        <v>4687.9743932684</v>
       </c>
       <c r="O463" t="n">
-        <v>2629953.62375661</v>
+        <v>2629953.634623572</v>
       </c>
       <c r="P463" t="n">
         <v>5900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3580,10 +3580,10 @@
         <v>948</v>
       </c>
       <c r="N74" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O74" t="n">
-        <v>2447978.258189124</v>
+        <v>2447978.255355742</v>
       </c>
       <c r="P74" t="n">
         <v>4500</v>
@@ -5319,10 +5319,10 @@
         <v>23</v>
       </c>
       <c r="N112" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O112" t="n">
-        <v>35654.4595154687</v>
+        <v>35654.4595530369</v>
       </c>
       <c r="P112" t="n">
         <v>2500</v>
@@ -8741,10 +8741,10 @@
         <v>344</v>
       </c>
       <c r="N189" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O189" t="n">
-        <v>5874140.395736904</v>
+        <v>5874140.395623383</v>
       </c>
       <c r="P189" t="n">
         <v>27500</v>
@@ -9477,10 +9477,10 @@
         <v>1</v>
       </c>
       <c r="N205" t="n">
-        <v>1592.2810401003</v>
+        <v>1592.2811378003</v>
       </c>
       <c r="O205" t="n">
-        <v>1592.2810401003</v>
+        <v>1592.2811378003</v>
       </c>
       <c r="P205" t="n">
         <v>2500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3774,10 +3774,10 @@
         <v>30</v>
       </c>
       <c r="N78" t="n">
-        <v>3230.0670575693</v>
+        <v>3230.0670386266</v>
       </c>
       <c r="O78" t="n">
-        <v>96902.01172707899</v>
+        <v>96902.01115879801</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -4195,10 +4195,10 @@
         <v>192</v>
       </c>
       <c r="N87" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O87" t="n">
-        <v>401443.2</v>
+        <v>401787.638610048</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4462,10 +4462,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.820990424</v>
+        <v>1385990.821026309</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4595,10 +4595,10 @@
         <v>166</v>
       </c>
       <c r="N96" t="n">
-        <v>1592.5662209302</v>
+        <v>1617.3578206079</v>
       </c>
       <c r="O96" t="n">
-        <v>264365.9926744132</v>
+        <v>268481.3982209114</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -5234,10 +5234,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.585141152</v>
+        <v>1037267.591993924</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4598452634</v>
+        <v>35654.4600063278</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -7632,10 +7632,10 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>5218.1705692109</v>
+        <v>5218.1705706874</v>
       </c>
       <c r="O165" t="n">
-        <v>260908.528460545</v>
+        <v>260908.52853437</v>
       </c>
       <c r="P165" t="n">
         <v>8500</v>
@@ -8886,10 +8886,10 @@
         <v>552</v>
       </c>
       <c r="N192" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O192" t="n">
-        <v>836853.4115836968</v>
+        <v>837842.4051762648</v>
       </c>
       <c r="P192" t="n">
         <v>2300</v>
@@ -9070,10 +9070,10 @@
         <v>266</v>
       </c>
       <c r="N196" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O196" t="n">
-        <v>479602.2260645994</v>
+        <v>479602.2276981852</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -11355,10 +11355,10 @@
         <v>12506</v>
       </c>
       <c r="N245" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O245" t="n">
-        <v>8801660.543720448</v>
+        <v>8801660.501230437</v>
       </c>
       <c r="P245" t="n">
         <v>900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2284,19 +2284,19 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="N45" t="n">
         <v>427.91886524823</v>
       </c>
       <c r="O45" t="n">
-        <v>52206.10156028406</v>
+        <v>49638.58836879468</v>
       </c>
       <c r="P45" t="n">
         <v>6800</v>
       </c>
       <c r="Q45" t="n">
-        <v>829600</v>
+        <v>788800</v>
       </c>
     </row>
     <row r="46">
@@ -2333,10 +2333,10 @@
         <v>166</v>
       </c>
       <c r="N46" t="n">
-        <v>580.36597297297</v>
+        <v>580.36596205962</v>
       </c>
       <c r="O46" t="n">
-        <v>96340.75151351302</v>
+        <v>96340.74970189692</v>
       </c>
       <c r="P46" t="n">
         <v>6800</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2376,19 +2376,19 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N47" t="n">
-        <v>538.40041666667</v>
+        <v>538.40045627376</v>
       </c>
       <c r="O47" t="n">
-        <v>62992.84875000039</v>
+        <v>59762.45064638736</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
       </c>
       <c r="Q47" t="n">
-        <v>795600</v>
+        <v>754800</v>
       </c>
     </row>
     <row r="48">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3356,19 +3356,19 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="N69" t="n">
         <v>2600</v>
       </c>
       <c r="O69" t="n">
-        <v>540800</v>
+        <v>488800</v>
       </c>
       <c r="P69" t="n">
         <v>4900</v>
       </c>
       <c r="Q69" t="n">
-        <v>1019200</v>
+        <v>921200</v>
       </c>
     </row>
     <row r="70">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3538,19 +3538,19 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2555195682</v>
+        <v>2582.2555145238</v>
       </c>
       <c r="O73" t="n">
-        <v>2447978.232550654</v>
+        <v>2386004.095419991</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
       </c>
       <c r="Q73" t="n">
-        <v>4266000</v>
+        <v>4158000</v>
       </c>
     </row>
     <row r="74">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>1372</v>
+        <v>1352</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3584,19 +3584,19 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1372</v>
+        <v>1352</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8960541642</v>
+        <v>5216.8960524399</v>
       </c>
       <c r="O74" t="n">
-        <v>7157581.386313282</v>
+        <v>7053243.462898744</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
       </c>
       <c r="Q74" t="n">
-        <v>11662000</v>
+        <v>11492000</v>
       </c>
     </row>
     <row r="75">
@@ -3679,10 +3679,10 @@
         <v>3410</v>
       </c>
       <c r="N76" t="n">
-        <v>3158.8608303391</v>
+        <v>3158.8608305026</v>
       </c>
       <c r="O76" t="n">
-        <v>10771715.43145633</v>
+        <v>10771715.43201387</v>
       </c>
       <c r="P76" t="n">
         <v>5600</v>
@@ -4105,10 +4105,10 @@
         <v>301</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2537131631</v>
+        <v>3594.2536883629</v>
       </c>
       <c r="O85" t="n">
-        <v>1081870.367662093</v>
+        <v>1081870.360197233</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -4148,19 +4148,19 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N86" t="n">
         <v>14822.378847539</v>
       </c>
       <c r="O86" t="n">
-        <v>4090976.561920764</v>
+        <v>4076154.183073225</v>
       </c>
       <c r="P86" t="n">
         <v>24900</v>
       </c>
       <c r="Q86" t="n">
-        <v>6872400</v>
+        <v>6847500</v>
       </c>
     </row>
     <row r="87">
@@ -4195,10 +4195,10 @@
         <v>192</v>
       </c>
       <c r="N87" t="n">
-        <v>2092.643951094</v>
+        <v>2090.85</v>
       </c>
       <c r="O87" t="n">
-        <v>401787.638610048</v>
+        <v>401443.2</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4462,10 +4462,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107918811</v>
+        <v>4372.2107921642</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.821026309</v>
+        <v>1385990.821116051</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4595,10 +4595,10 @@
         <v>166</v>
       </c>
       <c r="N96" t="n">
-        <v>1617.3578206079</v>
+        <v>1592.5661309524</v>
       </c>
       <c r="O96" t="n">
-        <v>268481.3982209114</v>
+        <v>264365.9777380984</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -5000,19 +5000,19 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N105" t="n">
         <v>11921.4</v>
       </c>
       <c r="O105" t="n">
-        <v>393406.2</v>
+        <v>309956.4</v>
       </c>
       <c r="P105" t="n">
         <v>19900</v>
       </c>
       <c r="Q105" t="n">
-        <v>656700</v>
+        <v>517400</v>
       </c>
     </row>
     <row r="106">
@@ -5234,10 +5234,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9238867829</v>
+        <v>1630.9239095069</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.591993924</v>
+        <v>1037267.606446388</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1939133186</v>
+        <v>1550.1939407455</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4600063278</v>
+        <v>35654.4606371465</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5326,10 +5326,10 @@
         <v>72</v>
       </c>
       <c r="N112" t="n">
-        <v>1579.3888161994</v>
+        <v>1579.388566879</v>
       </c>
       <c r="O112" t="n">
-        <v>113715.9947663568</v>
+        <v>113715.976815288</v>
       </c>
       <c r="P112" t="n">
         <v>2900</v>
@@ -5983,10 +5983,10 @@
         <v>109</v>
       </c>
       <c r="N127" t="n">
-        <v>4196.8725319267</v>
+        <v>4196.8725326298</v>
       </c>
       <c r="O127" t="n">
-        <v>457459.1059800102</v>
+        <v>457459.1060566482</v>
       </c>
       <c r="P127" t="n">
         <v>5900</v>
@@ -6111,10 +6111,10 @@
         <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>2029.8739515279</v>
+        <v>2029.873953611</v>
       </c>
       <c r="O130" t="n">
-        <v>4059.7479030558</v>
+        <v>4059.747907222</v>
       </c>
       <c r="P130" t="n">
         <v>3600</v>
@@ -6234,10 +6234,10 @@
         <v>402</v>
       </c>
       <c r="N133" t="n">
-        <v>880.32956314156</v>
+        <v>880.32958602536</v>
       </c>
       <c r="O133" t="n">
-        <v>353892.4843829071</v>
+        <v>353892.4935821947</v>
       </c>
       <c r="P133" t="n">
         <v>1200</v>
@@ -6485,10 +6485,10 @@
         <v>4</v>
       </c>
       <c r="N139" t="n">
-        <v>11562.038444444</v>
+        <v>11562.038426966</v>
       </c>
       <c r="O139" t="n">
-        <v>46248.153777776</v>
+        <v>46248.153707864</v>
       </c>
       <c r="P139" t="n">
         <v>18500</v>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6659,19 +6659,19 @@
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="N143" t="n">
         <v>4793.53</v>
       </c>
       <c r="O143" t="n">
-        <v>354721.22</v>
+        <v>282818.27</v>
       </c>
       <c r="P143" t="n">
         <v>7900</v>
       </c>
       <c r="Q143" t="n">
-        <v>584600</v>
+        <v>466100</v>
       </c>
     </row>
     <row r="144">
@@ -7632,10 +7632,10 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>5218.1705706874</v>
+        <v>5218.1705736636</v>
       </c>
       <c r="O165" t="n">
-        <v>260908.52853437</v>
+        <v>260908.52868318</v>
       </c>
       <c r="P165" t="n">
         <v>8500</v>
@@ -8886,10 +8886,10 @@
         <v>552</v>
       </c>
       <c r="N192" t="n">
-        <v>1517.8304441599</v>
+        <v>1516.0387847976</v>
       </c>
       <c r="O192" t="n">
-        <v>837842.4051762648</v>
+        <v>836853.4092082753</v>
       </c>
       <c r="P192" t="n">
         <v>2300</v>
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>384</v>
+        <v>312</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -8929,19 +8929,19 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>384</v>
+        <v>312</v>
       </c>
       <c r="N193" t="n">
         <v>2458.5128483396</v>
       </c>
       <c r="O193" t="n">
-        <v>944068.9337624065</v>
+        <v>767056.0086819553</v>
       </c>
       <c r="P193" t="n">
         <v>3500</v>
       </c>
       <c r="Q193" t="n">
-        <v>1344000</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="194">
@@ -8978,10 +8978,10 @@
         <v>144</v>
       </c>
       <c r="N194" t="n">
-        <v>1771.0902626263</v>
+        <v>1771.090242915</v>
       </c>
       <c r="O194" t="n">
-        <v>255036.9978181872</v>
+        <v>255036.99497976</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -9021,19 +9021,19 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="N195" t="n">
-        <v>2079.3839381583</v>
+        <v>2079.3838525155</v>
       </c>
       <c r="O195" t="n">
-        <v>499052.145157992</v>
+        <v>449146.912143348</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
       </c>
       <c r="Q195" t="n">
-        <v>696000</v>
+        <v>626400</v>
       </c>
     </row>
     <row r="196">
@@ -9070,10 +9070,10 @@
         <v>266</v>
       </c>
       <c r="N196" t="n">
-        <v>1803.0158936022</v>
+        <v>1803.0158997564</v>
       </c>
       <c r="O196" t="n">
-        <v>479602.2276981852</v>
+        <v>479602.2293352024</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -9205,19 +9205,19 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="N199" t="n">
-        <v>2108.7933180778</v>
+        <v>2108.7936087295</v>
       </c>
       <c r="O199" t="n">
-        <v>202444.1585354688</v>
+        <v>151833.139828524</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
       </c>
       <c r="Q199" t="n">
-        <v>278400</v>
+        <v>208800</v>
       </c>
     </row>
     <row r="200">
@@ -9254,10 +9254,10 @@
         <v>192</v>
       </c>
       <c r="N200" t="n">
-        <v>2056.0827781666</v>
+        <v>2056.0827629734</v>
       </c>
       <c r="O200" t="n">
-        <v>394767.8934079872</v>
+        <v>394767.8904908928</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9297,19 +9297,19 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="N201" t="n">
-        <v>3224.5689410589</v>
+        <v>3224.56895</v>
       </c>
       <c r="O201" t="n">
-        <v>580422.4093906019</v>
+        <v>522380.1699</v>
       </c>
       <c r="P201" t="n">
         <v>4500</v>
       </c>
       <c r="Q201" t="n">
-        <v>810000</v>
+        <v>729000</v>
       </c>
     </row>
     <row r="202">
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -9343,19 +9343,19 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="N202" t="n">
-        <v>1655.9305111492</v>
+        <v>1655.9303958333</v>
       </c>
       <c r="O202" t="n">
-        <v>397423.322675808</v>
+        <v>385831.7822291589</v>
       </c>
       <c r="P202" t="n">
         <v>2500</v>
       </c>
       <c r="Q202" t="n">
-        <v>600000</v>
+        <v>582500</v>
       </c>
     </row>
     <row r="203">
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.2816534392</v>
+        <v>1592.2817466667</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.2816534392</v>
+        <v>1592.2817466667</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9482,10 +9482,10 @@
         <v>36</v>
       </c>
       <c r="N205" t="n">
-        <v>2311.9148648649</v>
+        <v>2311.9128246753</v>
       </c>
       <c r="O205" t="n">
-        <v>83228.9351351364</v>
+        <v>83228.86168831079</v>
       </c>
       <c r="P205" t="n">
         <v>3500</v>
@@ -9574,10 +9574,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>2546.9828463476</v>
+        <v>2546.9826614987</v>
       </c>
       <c r="O207" t="n">
-        <v>122255.1766246848</v>
+        <v>122255.1677519376</v>
       </c>
       <c r="P207" t="n">
         <v>3900</v>
@@ -9797,10 +9797,10 @@
         <v>192</v>
       </c>
       <c r="N212" t="n">
-        <v>692.1522598039199</v>
+        <v>692.15226424361</v>
       </c>
       <c r="O212" t="n">
-        <v>132893.2338823526</v>
+        <v>132893.2347347731</v>
       </c>
       <c r="P212" t="n">
         <v>1200</v>
@@ -9938,10 +9938,10 @@
         <v>2761</v>
       </c>
       <c r="N215" t="n">
-        <v>1185.31957078</v>
+        <v>1185.3195703545</v>
       </c>
       <c r="O215" t="n">
-        <v>3272667.33492358</v>
+        <v>3272667.333748775</v>
       </c>
       <c r="P215" t="n">
         <v>1900</v>
@@ -10272,10 +10272,10 @@
         <v>324</v>
       </c>
       <c r="N222" t="n">
-        <v>1530.4499191266</v>
+        <v>1530.4499189299</v>
       </c>
       <c r="O222" t="n">
-        <v>495865.7737970184</v>
+        <v>495865.7737332876</v>
       </c>
       <c r="P222" t="n">
         <v>2600</v>
@@ -10643,10 +10643,10 @@
         <v>1</v>
       </c>
       <c r="N230" t="n">
-        <v>1690.8700092336</v>
+        <v>1690.8700092421</v>
       </c>
       <c r="O230" t="n">
-        <v>1690.8700092336</v>
+        <v>1690.8700092421</v>
       </c>
       <c r="P230" t="n">
         <v>3000</v>
@@ -11029,10 +11029,10 @@
         <v>59</v>
       </c>
       <c r="N238" t="n">
-        <v>3259.1343700787</v>
+        <v>3259.1344047619</v>
       </c>
       <c r="O238" t="n">
-        <v>192288.9278346433</v>
+        <v>192288.9298809521</v>
       </c>
       <c r="P238" t="n">
         <v>3600</v>
@@ -11127,10 +11127,10 @@
         <v>504</v>
       </c>
       <c r="N240" t="n">
-        <v>3110.8402590245</v>
+        <v>3110.8401559454</v>
       </c>
       <c r="O240" t="n">
-        <v>1567863.490548348</v>
+        <v>1567863.438596482</v>
       </c>
       <c r="P240" t="n">
         <v>4500</v>
@@ -11355,10 +11355,10 @@
         <v>12506</v>
       </c>
       <c r="N245" t="n">
-        <v>703.79501848956</v>
+        <v>703.79500857932</v>
       </c>
       <c r="O245" t="n">
-        <v>8801660.501230437</v>
+        <v>8801660.377292976</v>
       </c>
       <c r="P245" t="n">
         <v>900</v>
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12308,19 +12308,19 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N265" t="n">
         <v>2948.43</v>
       </c>
       <c r="O265" t="n">
-        <v>53071.74</v>
+        <v>41278.02</v>
       </c>
       <c r="P265" t="n">
         <v>34900</v>
       </c>
       <c r="Q265" t="n">
-        <v>628200</v>
+        <v>488600</v>
       </c>
     </row>
     <row r="266">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15541,19 +15541,19 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N332" t="n">
         <v>14590.52</v>
       </c>
       <c r="O332" t="n">
-        <v>131314.68</v>
+        <v>14590.52</v>
       </c>
       <c r="P332" t="n">
         <v>26500</v>
       </c>
       <c r="Q332" t="n">
-        <v>238500</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="333">
@@ -16932,10 +16932,10 @@
         <v>8</v>
       </c>
       <c r="N361" t="n">
-        <v>7046.9398275862</v>
+        <v>7046.9398275119</v>
       </c>
       <c r="O361" t="n">
-        <v>56375.5186206896</v>
+        <v>56375.5186200952</v>
       </c>
       <c r="P361" t="n">
         <v>9900</v>
@@ -17370,10 +17370,10 @@
         <v>11</v>
       </c>
       <c r="N370" t="n">
-        <v>366.39979381443</v>
+        <v>366.39977777778</v>
       </c>
       <c r="O370" t="n">
-        <v>4030.39773195873</v>
+        <v>4030.39755555558</v>
       </c>
       <c r="P370" t="n">
         <v>2900</v>
@@ -17517,10 +17517,10 @@
         <v>89</v>
       </c>
       <c r="N373" t="n">
-        <v>540.40112612613</v>
+        <v>540.40115740741</v>
       </c>
       <c r="O373" t="n">
-        <v>48095.70022522556</v>
+        <v>48095.70300925949</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -17713,10 +17713,10 @@
         <v>726</v>
       </c>
       <c r="N377" t="n">
-        <v>465.87095916429</v>
+        <v>465.87096374046</v>
       </c>
       <c r="O377" t="n">
-        <v>338222.3163532746</v>
+        <v>338222.319675574</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
@@ -18037,10 +18037,10 @@
         <v>13</v>
       </c>
       <c r="N384" t="n">
-        <v>22951.704785992</v>
+        <v>22951.704779221</v>
       </c>
       <c r="O384" t="n">
-        <v>298372.162217896</v>
+        <v>298372.162129873</v>
       </c>
       <c r="P384" t="n">
         <v>37900</v>
@@ -18180,10 +18180,10 @@
         <v>36</v>
       </c>
       <c r="N387" t="n">
-        <v>1547.8827419355</v>
+        <v>1547.8827868852</v>
       </c>
       <c r="O387" t="n">
-        <v>55723.778709678</v>
+        <v>55723.7803278672</v>
       </c>
       <c r="P387" t="n">
         <v>5500</v>
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
@@ -19107,19 +19107,19 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N407" t="n">
         <v>5120.05</v>
       </c>
       <c r="O407" t="n">
-        <v>281602.75</v>
+        <v>240642.35</v>
       </c>
       <c r="P407" t="n">
         <v>5700</v>
       </c>
       <c r="Q407" t="n">
-        <v>313500</v>
+        <v>267900</v>
       </c>
     </row>
     <row r="408">
@@ -19180,7 +19180,7 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="K409" t="n">
         <v>0</v>
@@ -19189,19 +19189,19 @@
         <v>0</v>
       </c>
       <c r="M409" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="N409" t="n">
         <v>1952.66</v>
       </c>
       <c r="O409" t="n">
-        <v>138638.86</v>
+        <v>123017.58</v>
       </c>
       <c r="P409" t="n">
         <v>3500</v>
       </c>
       <c r="Q409" t="n">
-        <v>248500</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="410">
@@ -19514,10 +19514,10 @@
         <v>3</v>
       </c>
       <c r="N416" t="n">
-        <v>9855.0381481481</v>
+        <v>9855.0380769231</v>
       </c>
       <c r="O416" t="n">
-        <v>29565.1144444443</v>
+        <v>29565.1142307693</v>
       </c>
       <c r="P416" t="n">
         <v>15500</v>
@@ -19652,10 +19652,10 @@
         <v>3</v>
       </c>
       <c r="N419" t="n">
-        <v>21664.371538462</v>
+        <v>21664.371666667</v>
       </c>
       <c r="O419" t="n">
-        <v>64993.114615386</v>
+        <v>64993.115000001</v>
       </c>
       <c r="P419" t="n">
         <v>30000</v>
@@ -20618,10 +20618,10 @@
         <v>38</v>
       </c>
       <c r="N440" t="n">
-        <v>1319.3608928571</v>
+        <v>1319.3609009009</v>
       </c>
       <c r="O440" t="n">
-        <v>50135.7139285698</v>
+        <v>50135.7142342342</v>
       </c>
       <c r="P440" t="n">
         <v>3500</v>
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
@@ -20712,19 +20712,19 @@
         <v>0</v>
       </c>
       <c r="M442" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N442" t="n">
         <v>3088.144</v>
       </c>
       <c r="O442" t="n">
-        <v>142054.624</v>
+        <v>111173.184</v>
       </c>
       <c r="P442" t="n">
         <v>8500</v>
       </c>
       <c r="Q442" t="n">
-        <v>391000</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="443">
@@ -21006,10 +21006,10 @@
         <v>42</v>
       </c>
       <c r="N448" t="n">
-        <v>2432.1354761905</v>
+        <v>2432.1356790123</v>
       </c>
       <c r="O448" t="n">
-        <v>102149.690000001</v>
+        <v>102149.6985185166</v>
       </c>
       <c r="P448" t="n">
         <v>4500</v>
@@ -21561,10 +21561,10 @@
         <v>582</v>
       </c>
       <c r="N460" t="n">
-        <v>2539.5715935542</v>
+        <v>2539.5715978456</v>
       </c>
       <c r="O460" t="n">
-        <v>1478030.667448544</v>
+        <v>1478030.669946139</v>
       </c>
       <c r="P460" t="n">
         <v>3500</v>
@@ -21980,10 +21980,10 @@
         <v>24</v>
       </c>
       <c r="N469" t="n">
-        <v>2361.5097142857</v>
+        <v>2361.5097058824</v>
       </c>
       <c r="O469" t="n">
-        <v>56676.2331428568</v>
+        <v>56676.2329411776</v>
       </c>
       <c r="P469" t="n">
         <v>6200</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3541,10 +3541,10 @@
         <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O73" t="n">
-        <v>2386004.095419991</v>
+        <v>2386004.089812882</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3725,10 +3725,10 @@
         <v>320</v>
       </c>
       <c r="N77" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O77" t="n">
-        <v>1229319.9552</v>
+        <v>1229319.959879648</v>
       </c>
       <c r="P77" t="n">
         <v>6900</v>
@@ -5234,10 +5234,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.606446388</v>
+        <v>1037267.61024439</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -11355,10 +11355,10 @@
         <v>12506</v>
       </c>
       <c r="N245" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O245" t="n">
-        <v>8801660.377292976</v>
+        <v>8801660.36875413</v>
       </c>
       <c r="P245" t="n">
         <v>900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1447,10 +1447,10 @@
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>29000</v>
+        <v>30074.074074074</v>
       </c>
       <c r="O26" t="n">
-        <v>116000</v>
+        <v>120296.296296296</v>
       </c>
       <c r="P26" t="n">
         <v>34800</v>
@@ -2333,10 +2333,10 @@
         <v>166</v>
       </c>
       <c r="N46" t="n">
-        <v>580.36596205962</v>
+        <v>580.3659400545</v>
       </c>
       <c r="O46" t="n">
-        <v>96340.74970189692</v>
+        <v>96340.746049047</v>
       </c>
       <c r="P46" t="n">
         <v>6800</v>
@@ -2379,10 +2379,10 @@
         <v>111</v>
       </c>
       <c r="N47" t="n">
-        <v>538.40045627376</v>
+        <v>538.40049618321</v>
       </c>
       <c r="O47" t="n">
-        <v>59762.45064638736</v>
+        <v>59762.45507633631</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
@@ -3008,10 +3008,10 @@
         <v>92</v>
       </c>
       <c r="N61" t="n">
-        <v>732.63425531915</v>
+        <v>732.63427046263</v>
       </c>
       <c r="O61" t="n">
-        <v>67402.3514893618</v>
+        <v>67402.35288256196</v>
       </c>
       <c r="P61" t="n">
         <v>6200</v>
@@ -3098,10 +3098,10 @@
         <v>33</v>
       </c>
       <c r="N63" t="n">
-        <v>4937.3101649175</v>
+        <v>4937.3101654135</v>
       </c>
       <c r="O63" t="n">
-        <v>162931.2354422775</v>
+        <v>162931.2354586455</v>
       </c>
       <c r="P63" t="n">
         <v>7500</v>
@@ -3446,10 +3446,10 @@
         <v>11</v>
       </c>
       <c r="N71" t="n">
-        <v>17207.41</v>
+        <v>17234.854035088</v>
       </c>
       <c r="O71" t="n">
-        <v>189281.51</v>
+        <v>189583.394385968</v>
       </c>
       <c r="P71" t="n">
         <v>20000</v>
@@ -3541,10 +3541,10 @@
         <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2555084555</v>
+        <v>2582.2554768392</v>
       </c>
       <c r="O73" t="n">
-        <v>2386004.089812882</v>
+        <v>2386004.060599421</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3587,10 +3587,10 @@
         <v>1352</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8960524399</v>
+        <v>5216.8960380117</v>
       </c>
       <c r="O74" t="n">
-        <v>7053243.462898744</v>
+        <v>7053243.443391818</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
@@ -3679,10 +3679,10 @@
         <v>3410</v>
       </c>
       <c r="N76" t="n">
-        <v>3158.8608305026</v>
+        <v>3158.860831485</v>
       </c>
       <c r="O76" t="n">
-        <v>10771715.43201387</v>
+        <v>10771715.43536385</v>
       </c>
       <c r="P76" t="n">
         <v>5600</v>
@@ -3820,10 +3820,10 @@
         <v>514</v>
       </c>
       <c r="N79" t="n">
-        <v>2694.8231638418</v>
+        <v>2694.8231444759</v>
       </c>
       <c r="O79" t="n">
-        <v>1385139.106214685</v>
+        <v>1385139.096260613</v>
       </c>
       <c r="P79" t="n">
         <v>4900</v>
@@ -3964,10 +3964,10 @@
         <v>20</v>
       </c>
       <c r="N82" t="n">
-        <v>8796</v>
+        <v>8807.6968085106</v>
       </c>
       <c r="O82" t="n">
-        <v>175920</v>
+        <v>176153.936170212</v>
       </c>
       <c r="P82" t="n">
         <v>14900</v>
@@ -4105,10 +4105,10 @@
         <v>301</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2536883629</v>
+        <v>3594.253608522</v>
       </c>
       <c r="O85" t="n">
-        <v>1081870.360197233</v>
+        <v>1081870.336165122</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4151,10 +4151,10 @@
         <v>275</v>
       </c>
       <c r="N86" t="n">
-        <v>14822.378847539</v>
+        <v>14822.378837068</v>
       </c>
       <c r="O86" t="n">
-        <v>4076154.183073225</v>
+        <v>4076154.1801937</v>
       </c>
       <c r="P86" t="n">
         <v>24900</v>
@@ -4462,10 +4462,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107921642</v>
+        <v>4372.5234503719</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.821116051</v>
+        <v>1386089.933767892</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4595,10 +4595,10 @@
         <v>166</v>
       </c>
       <c r="N96" t="n">
-        <v>1592.5661309524</v>
+        <v>1592.5660665658</v>
       </c>
       <c r="O96" t="n">
-        <v>264365.9777380984</v>
+        <v>264365.9670499228</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -4726,10 +4726,10 @@
         <v>66</v>
       </c>
       <c r="N99" t="n">
-        <v>1530.63</v>
+        <v>1530.7162764218</v>
       </c>
       <c r="O99" t="n">
-        <v>101021.58</v>
+        <v>101027.2742438388</v>
       </c>
       <c r="P99" t="n">
         <v>2900</v>
@@ -5234,10 +5234,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9239154786</v>
+        <v>1630.9239476386</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.61024439</v>
+        <v>1037267.63069815</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1939407455</v>
+        <v>1550.1940319426</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4606371465</v>
+        <v>35654.4627346798</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5326,10 +5326,10 @@
         <v>72</v>
       </c>
       <c r="N112" t="n">
-        <v>1579.388566879</v>
+        <v>1579.3884193548</v>
       </c>
       <c r="O112" t="n">
-        <v>113715.976815288</v>
+        <v>113715.9661935456</v>
       </c>
       <c r="P112" t="n">
         <v>2900</v>
@@ -5983,10 +5983,10 @@
         <v>109</v>
       </c>
       <c r="N127" t="n">
-        <v>4196.8725326298</v>
+        <v>4196.8725382689</v>
       </c>
       <c r="O127" t="n">
-        <v>457459.1060566482</v>
+        <v>457459.1066713101</v>
       </c>
       <c r="P127" t="n">
         <v>5900</v>
@@ -6070,10 +6070,10 @@
         <v>576</v>
       </c>
       <c r="N129" t="n">
-        <v>2567</v>
+        <v>2569.7269830028</v>
       </c>
       <c r="O129" t="n">
-        <v>1478592</v>
+        <v>1480162.742209613</v>
       </c>
       <c r="P129" t="n">
         <v>4500</v>
@@ -6111,10 +6111,10 @@
         <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>2029.873953611</v>
+        <v>2029.8739872408</v>
       </c>
       <c r="O130" t="n">
-        <v>4059.747907222</v>
+        <v>4059.7479744816</v>
       </c>
       <c r="P130" t="n">
         <v>3600</v>
@@ -6234,10 +6234,10 @@
         <v>402</v>
       </c>
       <c r="N133" t="n">
-        <v>880.32958602536</v>
+        <v>880.32962749339</v>
       </c>
       <c r="O133" t="n">
-        <v>353892.4935821947</v>
+        <v>353892.5102523428</v>
       </c>
       <c r="P133" t="n">
         <v>1200</v>
@@ -6913,10 +6913,10 @@
         <v>26</v>
       </c>
       <c r="N149" t="n">
-        <v>2568.8354237288</v>
+        <v>2568.8354081633</v>
       </c>
       <c r="O149" t="n">
-        <v>66789.7210169488</v>
+        <v>66789.7206122458</v>
       </c>
       <c r="P149" t="n">
         <v>4500</v>
@@ -7000,10 +7000,10 @@
         <v>5</v>
       </c>
       <c r="N151" t="n">
-        <v>7969.9501675552</v>
+        <v>7982.1180305344</v>
       </c>
       <c r="O151" t="n">
-        <v>39849.750837776</v>
+        <v>39910.590152672</v>
       </c>
       <c r="P151" t="n">
         <v>12900</v>
@@ -7298,7 +7298,7 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -7307,19 +7307,19 @@
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N158" t="n">
         <v>2634.61</v>
       </c>
       <c r="O158" t="n">
-        <v>200230.36</v>
+        <v>197595.75</v>
       </c>
       <c r="P158" t="n">
         <v>4200</v>
       </c>
       <c r="Q158" t="n">
-        <v>319200</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="159">
@@ -7632,10 +7632,10 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>5218.1705736636</v>
+        <v>5218.1705744125</v>
       </c>
       <c r="O165" t="n">
-        <v>260908.52868318</v>
+        <v>260908.528720625</v>
       </c>
       <c r="P165" t="n">
         <v>8500</v>
@@ -8656,10 +8656,10 @@
         <v>344</v>
       </c>
       <c r="N187" t="n">
-        <v>17075.989522161</v>
+        <v>17075.98952183</v>
       </c>
       <c r="O187" t="n">
-        <v>5874140.395623383</v>
+        <v>5874140.395509521</v>
       </c>
       <c r="P187" t="n">
         <v>27500</v>
@@ -8886,10 +8886,10 @@
         <v>552</v>
       </c>
       <c r="N192" t="n">
-        <v>1516.0387847976</v>
+        <v>1516.0387762203</v>
       </c>
       <c r="O192" t="n">
-        <v>836853.4092082753</v>
+        <v>836853.4044736056</v>
       </c>
       <c r="P192" t="n">
         <v>2300</v>
@@ -8932,10 +8932,10 @@
         <v>312</v>
       </c>
       <c r="N193" t="n">
-        <v>2458.5128483396</v>
+        <v>2458.5128385327</v>
       </c>
       <c r="O193" t="n">
-        <v>767056.0086819553</v>
+        <v>767056.0056222023</v>
       </c>
       <c r="P193" t="n">
         <v>3500</v>
@@ -8978,10 +8978,10 @@
         <v>144</v>
       </c>
       <c r="N194" t="n">
-        <v>1771.090242915</v>
+        <v>1771.0901699524</v>
       </c>
       <c r="O194" t="n">
-        <v>255036.99497976</v>
+        <v>255036.9844731456</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9024,10 +9024,10 @@
         <v>216</v>
       </c>
       <c r="N195" t="n">
-        <v>2079.3838525155</v>
+        <v>2079.3837839721</v>
       </c>
       <c r="O195" t="n">
-        <v>449146.912143348</v>
+        <v>449146.8973379736</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9070,10 +9070,10 @@
         <v>266</v>
       </c>
       <c r="N196" t="n">
-        <v>1803.0158997564</v>
+        <v>1803.0159162304</v>
       </c>
       <c r="O196" t="n">
-        <v>479602.2293352024</v>
+        <v>479602.2337172864</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9116,10 +9116,10 @@
         <v>36</v>
       </c>
       <c r="N197" t="n">
-        <v>3306.5945945946</v>
+        <v>3306.5945783133</v>
       </c>
       <c r="O197" t="n">
-        <v>119037.4054054056</v>
+        <v>119037.4048192788</v>
       </c>
       <c r="P197" t="n">
         <v>4900</v>
@@ -9208,10 +9208,10 @@
         <v>72</v>
       </c>
       <c r="N199" t="n">
-        <v>2108.7936087295</v>
+        <v>2108.7939012739</v>
       </c>
       <c r="O199" t="n">
-        <v>151833.139828524</v>
+        <v>151833.1608917208</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
@@ -9254,10 +9254,10 @@
         <v>192</v>
       </c>
       <c r="N200" t="n">
-        <v>2056.0827629734</v>
+        <v>2056.082714437</v>
       </c>
       <c r="O200" t="n">
-        <v>394767.8904908928</v>
+        <v>394767.881171904</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
@@ -9300,10 +9300,10 @@
         <v>162</v>
       </c>
       <c r="N201" t="n">
-        <v>3224.56895</v>
+        <v>3224.5689724311</v>
       </c>
       <c r="O201" t="n">
-        <v>522380.1699</v>
+        <v>522380.1735338382</v>
       </c>
       <c r="P201" t="n">
         <v>4500</v>
@@ -9346,10 +9346,10 @@
         <v>233</v>
       </c>
       <c r="N202" t="n">
-        <v>1655.9303958333</v>
+        <v>1655.9303421788</v>
       </c>
       <c r="O202" t="n">
-        <v>385831.7822291589</v>
+        <v>385831.7697276604</v>
       </c>
       <c r="P202" t="n">
         <v>2500</v>
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.281793842</v>
+        <v>1592.2820519836</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.281793842</v>
+        <v>1592.2820519836</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9436,10 +9436,10 @@
         <v>34</v>
       </c>
       <c r="N204" t="n">
-        <v>5347.73</v>
+        <v>5372.836713615</v>
       </c>
       <c r="O204" t="n">
-        <v>181822.82</v>
+        <v>182676.44826291</v>
       </c>
       <c r="P204" t="n">
         <v>9500</v>
@@ -9482,10 +9482,10 @@
         <v>36</v>
       </c>
       <c r="N205" t="n">
-        <v>2311.9128246753</v>
+        <v>2311.912006689</v>
       </c>
       <c r="O205" t="n">
-        <v>83228.86168831079</v>
+        <v>83228.832240804</v>
       </c>
       <c r="P205" t="n">
         <v>3500</v>
@@ -9528,10 +9528,10 @@
         <v>2</v>
       </c>
       <c r="N206" t="n">
-        <v>1906.1809090909</v>
+        <v>1906.180625</v>
       </c>
       <c r="O206" t="n">
-        <v>3812.3618181818</v>
+        <v>3812.36125</v>
       </c>
       <c r="P206" t="n">
         <v>2900</v>
@@ -9574,10 +9574,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>2546.9826614987</v>
+        <v>2546.9826041667</v>
       </c>
       <c r="O207" t="n">
-        <v>122255.1677519376</v>
+        <v>122255.1650000016</v>
       </c>
       <c r="P207" t="n">
         <v>3900</v>
@@ -9620,10 +9620,10 @@
         <v>600</v>
       </c>
       <c r="N208" t="n">
-        <v>1259.2746638947</v>
+        <v>1259.2746779425</v>
       </c>
       <c r="O208" t="n">
-        <v>755564.7983368201</v>
+        <v>755564.8067655</v>
       </c>
       <c r="P208" t="n">
         <v>1900</v>
@@ -9661,10 +9661,10 @@
         <v>201</v>
       </c>
       <c r="N209" t="n">
-        <v>2842.2744460028</v>
+        <v>2842.2744382022</v>
       </c>
       <c r="O209" t="n">
-        <v>571297.1636465627</v>
+        <v>571297.1620786423</v>
       </c>
       <c r="P209" t="n">
         <v>4900</v>
@@ -9797,10 +9797,10 @@
         <v>192</v>
       </c>
       <c r="N212" t="n">
-        <v>692.15226424361</v>
+        <v>692.15226870079</v>
       </c>
       <c r="O212" t="n">
-        <v>132893.2347347731</v>
+        <v>132893.2355905517</v>
       </c>
       <c r="P212" t="n">
         <v>1200</v>
@@ -9846,10 +9846,10 @@
         <v>3</v>
       </c>
       <c r="N213" t="n">
-        <v>18491</v>
+        <v>18654.637168142</v>
       </c>
       <c r="O213" t="n">
-        <v>55473</v>
+        <v>55963.911504426</v>
       </c>
       <c r="P213" t="n">
         <v>13500</v>
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -10033,19 +10033,19 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="N217" t="n">
         <v>2438.7</v>
       </c>
       <c r="O217" t="n">
-        <v>414578.9999999999</v>
+        <v>358488.9</v>
       </c>
       <c r="P217" t="n">
         <v>11500</v>
       </c>
       <c r="Q217" t="n">
-        <v>1955000</v>
+        <v>1690500</v>
       </c>
     </row>
     <row r="218">
@@ -11127,10 +11127,10 @@
         <v>504</v>
       </c>
       <c r="N240" t="n">
-        <v>3110.8401559454</v>
+        <v>3110.8400113026</v>
       </c>
       <c r="O240" t="n">
-        <v>1567863.438596482</v>
+        <v>1567863.36569651</v>
       </c>
       <c r="P240" t="n">
         <v>4500</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>12506</v>
+        <v>12218</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11352,19 +11352,19 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>12506</v>
+        <v>12218</v>
       </c>
       <c r="N245" t="n">
-        <v>703.79500789654</v>
+        <v>703.7949766627</v>
       </c>
       <c r="O245" t="n">
-        <v>8801660.36875413</v>
+        <v>8598967.024864869</v>
       </c>
       <c r="P245" t="n">
         <v>900</v>
       </c>
       <c r="Q245" t="n">
-        <v>11255400</v>
+        <v>10996200</v>
       </c>
     </row>
     <row r="246">
@@ -11634,10 +11634,10 @@
         <v>59</v>
       </c>
       <c r="N251" t="n">
-        <v>2501.3848325359</v>
+        <v>2501.3847317073</v>
       </c>
       <c r="O251" t="n">
-        <v>147581.7051196181</v>
+        <v>147581.6991707307</v>
       </c>
       <c r="P251" t="n">
         <v>4100</v>
@@ -12970,7 +12970,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12979,19 +12979,19 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N279" t="n">
         <v>52454.27</v>
       </c>
       <c r="O279" t="n">
-        <v>839268.3199999999</v>
+        <v>734359.7799999999</v>
       </c>
       <c r="P279" t="n">
         <v>88500</v>
       </c>
       <c r="Q279" t="n">
-        <v>1416000</v>
+        <v>1239000</v>
       </c>
     </row>
     <row r="280">
@@ -13028,10 +13028,10 @@
         <v>1</v>
       </c>
       <c r="N280" t="n">
-        <v>3505.3804255319</v>
+        <v>3505.3804651163</v>
       </c>
       <c r="O280" t="n">
-        <v>3505.3804255319</v>
+        <v>3505.3804651163</v>
       </c>
       <c r="P280" t="n">
         <v>12900</v>
@@ -14379,10 +14379,10 @@
         <v>7</v>
       </c>
       <c r="N308" t="n">
-        <v>14276.106086957</v>
+        <v>14276.105909091</v>
       </c>
       <c r="O308" t="n">
-        <v>99932.74260869899</v>
+        <v>99932.741363637</v>
       </c>
       <c r="P308" t="n">
         <v>44500</v>
@@ -14428,10 +14428,10 @@
         <v>60</v>
       </c>
       <c r="N309" t="n">
-        <v>3067.0905844156</v>
+        <v>3067.0906</v>
       </c>
       <c r="O309" t="n">
-        <v>184025.435064936</v>
+        <v>184025.436</v>
       </c>
       <c r="P309" t="n">
         <v>7200</v>
@@ -15348,10 +15348,10 @@
         <v>1</v>
       </c>
       <c r="N328" t="n">
-        <v>10737.526170213</v>
+        <v>10737.525909091</v>
       </c>
       <c r="O328" t="n">
-        <v>10737.526170213</v>
+        <v>10737.525909091</v>
       </c>
       <c r="P328" t="n">
         <v>18900</v>
@@ -16301,10 +16301,10 @@
         <v>159</v>
       </c>
       <c r="N348" t="n">
-        <v>5216.9</v>
+        <v>5235.0773519164</v>
       </c>
       <c r="O348" t="n">
-        <v>829487.1</v>
+        <v>832377.2989547077</v>
       </c>
       <c r="P348" t="n">
         <v>20500</v>
@@ -16932,10 +16932,10 @@
         <v>8</v>
       </c>
       <c r="N361" t="n">
-        <v>7046.9398275119</v>
+        <v>7049.9805782093</v>
       </c>
       <c r="O361" t="n">
-        <v>56375.5186200952</v>
+        <v>56399.8446256744</v>
       </c>
       <c r="P361" t="n">
         <v>9900</v>
@@ -16981,10 +16981,10 @@
         <v>2</v>
       </c>
       <c r="N362" t="n">
-        <v>26378.026666667</v>
+        <v>26378.02625</v>
       </c>
       <c r="O362" t="n">
-        <v>52756.053333334</v>
+        <v>52756.0525</v>
       </c>
       <c r="P362" t="n">
         <v>36500</v>
@@ -17370,10 +17370,10 @@
         <v>11</v>
       </c>
       <c r="N370" t="n">
-        <v>366.39977777778</v>
+        <v>366.39975903614</v>
       </c>
       <c r="O370" t="n">
-        <v>4030.39755555558</v>
+        <v>4030.39734939754</v>
       </c>
       <c r="P370" t="n">
         <v>2900</v>
@@ -17664,10 +17664,10 @@
         <v>984</v>
       </c>
       <c r="N376" t="n">
-        <v>430.6099760479</v>
+        <v>430.60997577226</v>
       </c>
       <c r="O376" t="n">
-        <v>423720.2164311336</v>
+        <v>423720.2161599039</v>
       </c>
       <c r="P376" t="n">
         <v>2200</v>
@@ -17713,10 +17713,10 @@
         <v>726</v>
       </c>
       <c r="N377" t="n">
-        <v>465.87096374046</v>
+        <v>465.87096743295</v>
       </c>
       <c r="O377" t="n">
-        <v>338222.319675574</v>
+        <v>338222.3223563217</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
@@ -17762,10 +17762,10 @@
         <v>455</v>
       </c>
       <c r="N378" t="n">
-        <v>315.02705797101</v>
+        <v>315.02716176471</v>
       </c>
       <c r="O378" t="n">
-        <v>143337.3113768095</v>
+        <v>143337.358602943</v>
       </c>
       <c r="P378" t="n">
         <v>2200</v>
@@ -18037,10 +18037,10 @@
         <v>13</v>
       </c>
       <c r="N384" t="n">
-        <v>22951.704779221</v>
+        <v>22951.704751958</v>
       </c>
       <c r="O384" t="n">
-        <v>298372.162129873</v>
+        <v>298372.161775454</v>
       </c>
       <c r="P384" t="n">
         <v>37900</v>
@@ -18282,10 +18282,10 @@
         <v>43</v>
       </c>
       <c r="N389" t="n">
-        <v>1757.3205652174</v>
+        <v>1757.3205676856</v>
       </c>
       <c r="O389" t="n">
-        <v>75564.7843043482</v>
+        <v>75564.7844104808</v>
       </c>
       <c r="P389" t="n">
         <v>2000</v>
@@ -18926,10 +18926,10 @@
         <v>1527</v>
       </c>
       <c r="N403" t="n">
-        <v>220.00454362906</v>
+        <v>220.00364812669</v>
       </c>
       <c r="O403" t="n">
-        <v>335946.9381215746</v>
+        <v>335945.5706894556</v>
       </c>
       <c r="P403" t="n">
         <v>260</v>
@@ -19640,7 +19640,7 @@
         </is>
       </c>
       <c r="J419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K419" t="n">
         <v>0</v>
@@ -19649,19 +19649,19 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N419" t="n">
-        <v>21664.371666667</v>
+        <v>21664.371818182</v>
       </c>
       <c r="O419" t="n">
-        <v>64993.115000001</v>
+        <v>43328.743636364</v>
       </c>
       <c r="P419" t="n">
         <v>30000</v>
       </c>
       <c r="Q419" t="n">
-        <v>90000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="420">
@@ -20618,10 +20618,10 @@
         <v>38</v>
       </c>
       <c r="N440" t="n">
-        <v>1319.3609009009</v>
+        <v>1319.3609036145</v>
       </c>
       <c r="O440" t="n">
-        <v>50135.7142342342</v>
+        <v>50135.714337351</v>
       </c>
       <c r="P440" t="n">
         <v>3500</v>
@@ -20715,10 +20715,10 @@
         <v>36</v>
       </c>
       <c r="N442" t="n">
-        <v>3088.144</v>
+        <v>3088.1445833333</v>
       </c>
       <c r="O442" t="n">
-        <v>111173.184</v>
+        <v>111173.2049999988</v>
       </c>
       <c r="P442" t="n">
         <v>8500</v>
@@ -21561,10 +21561,10 @@
         <v>582</v>
       </c>
       <c r="N460" t="n">
-        <v>2539.5715978456</v>
+        <v>2539.5716527391</v>
       </c>
       <c r="O460" t="n">
-        <v>1478030.669946139</v>
+        <v>1478030.701894156</v>
       </c>
       <c r="P460" t="n">
         <v>3500</v>
@@ -21607,10 +21607,10 @@
         <v>561</v>
       </c>
       <c r="N461" t="n">
-        <v>4687.9744010648</v>
+        <v>4687.9744444444</v>
       </c>
       <c r="O461" t="n">
-        <v>2629953.638997353</v>
+        <v>2629953.663333308</v>
       </c>
       <c r="P461" t="n">
         <v>5900</v>
@@ -21653,10 +21653,10 @@
         <v>80</v>
       </c>
       <c r="N462" t="n">
-        <v>4171.6686597938</v>
+        <v>4171.6686473988</v>
       </c>
       <c r="O462" t="n">
-        <v>333733.492783504</v>
+        <v>333733.491791904</v>
       </c>
       <c r="P462" t="n">
         <v>5500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -1447,10 +1447,10 @@
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>30074.074074074</v>
+        <v>29000</v>
       </c>
       <c r="O26" t="n">
-        <v>120296.296296296</v>
+        <v>116000</v>
       </c>
       <c r="P26" t="n">
         <v>34800</v>
@@ -3446,10 +3446,10 @@
         <v>11</v>
       </c>
       <c r="N71" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O71" t="n">
-        <v>189583.394385968</v>
+        <v>189281.51</v>
       </c>
       <c r="P71" t="n">
         <v>20000</v>
@@ -3964,10 +3964,10 @@
         <v>20</v>
       </c>
       <c r="N82" t="n">
-        <v>8807.6968085106</v>
+        <v>8796</v>
       </c>
       <c r="O82" t="n">
-        <v>176153.936170212</v>
+        <v>175920</v>
       </c>
       <c r="P82" t="n">
         <v>14900</v>
@@ -4462,10 +4462,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O93" t="n">
-        <v>1386089.933767892</v>
+        <v>1385990.82116991</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4726,10 +4726,10 @@
         <v>66</v>
       </c>
       <c r="N99" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O99" t="n">
-        <v>101027.2742438388</v>
+        <v>101021.58</v>
       </c>
       <c r="P99" t="n">
         <v>2900</v>
@@ -6070,10 +6070,10 @@
         <v>576</v>
       </c>
       <c r="N129" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O129" t="n">
-        <v>1480162.742209613</v>
+        <v>1478592</v>
       </c>
       <c r="P129" t="n">
         <v>4500</v>
@@ -7000,10 +7000,10 @@
         <v>5</v>
       </c>
       <c r="N151" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O151" t="n">
-        <v>39910.590152672</v>
+        <v>39849.7508396945</v>
       </c>
       <c r="P151" t="n">
         <v>12900</v>
@@ -9436,10 +9436,10 @@
         <v>34</v>
       </c>
       <c r="N204" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O204" t="n">
-        <v>182676.44826291</v>
+        <v>181822.82</v>
       </c>
       <c r="P204" t="n">
         <v>9500</v>
@@ -9846,10 +9846,10 @@
         <v>3</v>
       </c>
       <c r="N213" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="O213" t="n">
-        <v>55963.911504426</v>
+        <v>55473</v>
       </c>
       <c r="P213" t="n">
         <v>13500</v>
@@ -16301,10 +16301,10 @@
         <v>159</v>
       </c>
       <c r="N348" t="n">
-        <v>5235.0773519164</v>
+        <v>5216.9</v>
       </c>
       <c r="O348" t="n">
-        <v>832377.2989547077</v>
+        <v>829487.1</v>
       </c>
       <c r="P348" t="n">
         <v>20500</v>
@@ -16932,10 +16932,10 @@
         <v>8</v>
       </c>
       <c r="N361" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O361" t="n">
-        <v>56399.8446256744</v>
+        <v>56375.5186192016</v>
       </c>
       <c r="P361" t="n">
         <v>9900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3541,10 +3541,10 @@
         <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O73" t="n">
-        <v>2386004.060599421</v>
+        <v>2386004.056800025</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -4105,10 +4105,10 @@
         <v>301</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O85" t="n">
-        <v>1081870.336165122</v>
+        <v>1081870.3336</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4151,10 +4151,10 @@
         <v>275</v>
       </c>
       <c r="N86" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O86" t="n">
-        <v>4076154.1801937</v>
+        <v>4076154.1800001</v>
       </c>
       <c r="P86" t="n">
         <v>24900</v>
@@ -4595,10 +4595,10 @@
         <v>166</v>
       </c>
       <c r="N96" t="n">
-        <v>1592.5660665658</v>
+        <v>1592.5660516325</v>
       </c>
       <c r="O96" t="n">
-        <v>264365.9670499228</v>
+        <v>264365.964570995</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1940319426</v>
+        <v>1550.1940372063</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4627346798</v>
+        <v>35654.4628557449</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -6111,10 +6111,10 @@
         <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>2029.8739872408</v>
+        <v>2029.8739957379</v>
       </c>
       <c r="O130" t="n">
-        <v>4059.7479744816</v>
+        <v>4059.7479914758</v>
       </c>
       <c r="P130" t="n">
         <v>3600</v>
@@ -8656,10 +8656,10 @@
         <v>344</v>
       </c>
       <c r="N187" t="n">
-        <v>17075.98952183</v>
+        <v>17075.989521166</v>
       </c>
       <c r="O187" t="n">
-        <v>5874140.395509521</v>
+        <v>5874140.395281104</v>
       </c>
       <c r="P187" t="n">
         <v>27500</v>
@@ -9254,10 +9254,10 @@
         <v>192</v>
       </c>
       <c r="N200" t="n">
-        <v>2056.082714437</v>
+        <v>2056.08270929</v>
       </c>
       <c r="O200" t="n">
-        <v>394767.881171904</v>
+        <v>394767.88018368</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
@@ -9300,10 +9300,10 @@
         <v>162</v>
       </c>
       <c r="N201" t="n">
-        <v>3224.5689724311</v>
+        <v>3224.568981435</v>
       </c>
       <c r="O201" t="n">
-        <v>522380.1735338382</v>
+        <v>522380.17499247</v>
       </c>
       <c r="P201" t="n">
         <v>4500</v>
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.2820519836</v>
+        <v>1592.2820684932</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.2820519836</v>
+        <v>1592.2820684932</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9482,10 +9482,10 @@
         <v>36</v>
       </c>
       <c r="N205" t="n">
-        <v>2311.912006689</v>
+        <v>2311.9102135231</v>
       </c>
       <c r="O205" t="n">
-        <v>83228.832240804</v>
+        <v>83228.7676868316</v>
       </c>
       <c r="P205" t="n">
         <v>3500</v>
@@ -11127,10 +11127,10 @@
         <v>504</v>
       </c>
       <c r="N240" t="n">
-        <v>3110.8400113026</v>
+        <v>3110.8399744753</v>
       </c>
       <c r="O240" t="n">
-        <v>1567863.36569651</v>
+        <v>1567863.347135551</v>
       </c>
       <c r="P240" t="n">
         <v>4500</v>
@@ -17370,10 +17370,10 @@
         <v>11</v>
       </c>
       <c r="N370" t="n">
-        <v>366.39975903614</v>
+        <v>366.39975609756</v>
       </c>
       <c r="O370" t="n">
-        <v>4030.39734939754</v>
+        <v>4030.39731707316</v>
       </c>
       <c r="P370" t="n">
         <v>2900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q537"/>
+  <dimension ref="A1:Q538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -3541,10 +3541,10 @@
         <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2554727273</v>
+        <v>2582.2554675768</v>
       </c>
       <c r="O73" t="n">
-        <v>2386004.056800025</v>
+        <v>2386004.052040963</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3587,10 +3587,10 @@
         <v>1352</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8960380117</v>
+        <v>5216.8960345332</v>
       </c>
       <c r="O74" t="n">
-        <v>7053243.443391818</v>
+        <v>7053243.438688886</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
@@ -3679,10 +3679,10 @@
         <v>3410</v>
       </c>
       <c r="N76" t="n">
-        <v>3158.860831485</v>
+        <v>3158.860831608</v>
       </c>
       <c r="O76" t="n">
-        <v>10771715.43536385</v>
+        <v>10771715.43578328</v>
       </c>
       <c r="P76" t="n">
         <v>5600</v>
@@ -3725,10 +3725,10 @@
         <v>320</v>
       </c>
       <c r="N77" t="n">
-        <v>3841.6248746239</v>
+        <v>3841.6248795181</v>
       </c>
       <c r="O77" t="n">
-        <v>1229319.959879648</v>
+        <v>1229319.961445792</v>
       </c>
       <c r="P77" t="n">
         <v>6900</v>
@@ -3774,10 +3774,10 @@
         <v>30</v>
       </c>
       <c r="N78" t="n">
-        <v>3230.0670386266</v>
+        <v>3230.0670258621</v>
       </c>
       <c r="O78" t="n">
-        <v>96902.01115879801</v>
+        <v>96902.01077586299</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -4105,10 +4105,10 @@
         <v>301</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2536</v>
+        <v>3594.2535871743</v>
       </c>
       <c r="O85" t="n">
-        <v>1081870.3336</v>
+        <v>1081870.329739464</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4462,10 +4462,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107923341</v>
+        <v>4372.2107923908</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.82116991</v>
+        <v>1385990.821187884</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4595,10 +4595,10 @@
         <v>166</v>
       </c>
       <c r="N96" t="n">
-        <v>1592.5660516325</v>
+        <v>1592.5658958169</v>
       </c>
       <c r="O96" t="n">
-        <v>264365.964570995</v>
+        <v>264365.9387056054</v>
       </c>
       <c r="P96" t="n">
         <v>3900</v>
@@ -5234,10 +5234,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9239476386</v>
+        <v>1630.9239618753</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.63069815</v>
+        <v>1037267.639752691</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1940372063</v>
+        <v>1550.1940686328</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4628557449</v>
+        <v>35654.4635785544</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -5326,10 +5326,10 @@
         <v>72</v>
       </c>
       <c r="N112" t="n">
-        <v>1579.3884193548</v>
+        <v>1579.388381877</v>
       </c>
       <c r="O112" t="n">
-        <v>113715.9661935456</v>
+        <v>113715.963495144</v>
       </c>
       <c r="P112" t="n">
         <v>2900</v>
@@ -5413,10 +5413,10 @@
         <v>50</v>
       </c>
       <c r="N114" t="n">
-        <v>2069.4655762082</v>
+        <v>2069.4655430712</v>
       </c>
       <c r="O114" t="n">
-        <v>103473.27881041</v>
+        <v>103473.27715356</v>
       </c>
       <c r="P114" t="n">
         <v>6500</v>
@@ -6111,10 +6111,10 @@
         <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>2029.8739957379</v>
+        <v>2029.8740214477</v>
       </c>
       <c r="O130" t="n">
-        <v>4059.7479914758</v>
+        <v>4059.7480428954</v>
       </c>
       <c r="P130" t="n">
         <v>3600</v>
@@ -6234,10 +6234,10 @@
         <v>402</v>
       </c>
       <c r="N133" t="n">
-        <v>880.32962749339</v>
+        <v>880.32965533864</v>
       </c>
       <c r="O133" t="n">
-        <v>353892.5102523428</v>
+        <v>353892.5214461333</v>
       </c>
       <c r="P133" t="n">
         <v>1200</v>
@@ -6872,10 +6872,10 @@
         <v>21</v>
       </c>
       <c r="N148" t="n">
-        <v>1508.5870454545</v>
+        <v>1508.5869767442</v>
       </c>
       <c r="O148" t="n">
-        <v>31680.3279545445</v>
+        <v>31680.3265116282</v>
       </c>
       <c r="P148" t="n">
         <v>3600</v>
@@ -7000,10 +7000,10 @@
         <v>5</v>
       </c>
       <c r="N151" t="n">
-        <v>7969.9501679389</v>
+        <v>7969.9501684533</v>
       </c>
       <c r="O151" t="n">
-        <v>39849.7508396945</v>
+        <v>39849.7508422665</v>
       </c>
       <c r="P151" t="n">
         <v>12900</v>
@@ -8886,10 +8886,10 @@
         <v>552</v>
       </c>
       <c r="N192" t="n">
-        <v>1516.0387762203</v>
+        <v>1516.0387732935</v>
       </c>
       <c r="O192" t="n">
-        <v>836853.4044736056</v>
+        <v>836853.402858012</v>
       </c>
       <c r="P192" t="n">
         <v>2300</v>
@@ -8978,10 +8978,10 @@
         <v>144</v>
       </c>
       <c r="N194" t="n">
-        <v>1771.0901699524</v>
+        <v>1771.0901431493</v>
       </c>
       <c r="O194" t="n">
-        <v>255036.9844731456</v>
+        <v>255036.9806134992</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9024,10 +9024,10 @@
         <v>216</v>
       </c>
       <c r="N195" t="n">
-        <v>2079.3837839721</v>
+        <v>2079.3837796374</v>
       </c>
       <c r="O195" t="n">
-        <v>449146.8973379736</v>
+        <v>449146.8964016784</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9070,10 +9070,10 @@
         <v>266</v>
       </c>
       <c r="N196" t="n">
-        <v>1803.0159162304</v>
+        <v>1803.0159286464</v>
       </c>
       <c r="O196" t="n">
-        <v>479602.2337172864</v>
+        <v>479602.2370199424</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9116,10 +9116,10 @@
         <v>36</v>
       </c>
       <c r="N197" t="n">
-        <v>3306.5945783133</v>
+        <v>3306.5945619335</v>
       </c>
       <c r="O197" t="n">
-        <v>119037.4048192788</v>
+        <v>119037.404229606</v>
       </c>
       <c r="P197" t="n">
         <v>4900</v>
@@ -9208,10 +9208,10 @@
         <v>72</v>
       </c>
       <c r="N199" t="n">
-        <v>2108.7939012739</v>
+        <v>2108.793968</v>
       </c>
       <c r="O199" t="n">
-        <v>151833.1608917208</v>
+        <v>151833.165696</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
@@ -9254,10 +9254,10 @@
         <v>192</v>
       </c>
       <c r="N200" t="n">
-        <v>2056.08270929</v>
+        <v>2056.0827015559</v>
       </c>
       <c r="O200" t="n">
-        <v>394767.88018368</v>
+        <v>394767.8786987328</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
@@ -9346,10 +9346,10 @@
         <v>233</v>
       </c>
       <c r="N202" t="n">
-        <v>1655.9303421788</v>
+        <v>1655.9303117338</v>
       </c>
       <c r="O202" t="n">
-        <v>385831.7697276604</v>
+        <v>385831.7626339754</v>
       </c>
       <c r="P202" t="n">
         <v>2500</v>
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.2820684932</v>
+        <v>1592.2821517241</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.2820684932</v>
+        <v>1592.2821517241</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9482,10 +9482,10 @@
         <v>36</v>
       </c>
       <c r="N205" t="n">
-        <v>2311.9102135231</v>
+        <v>2311.9088847584</v>
       </c>
       <c r="O205" t="n">
-        <v>83228.7676868316</v>
+        <v>83228.71985130239</v>
       </c>
       <c r="P205" t="n">
         <v>3500</v>
@@ -9574,10 +9574,10 @@
         <v>48</v>
       </c>
       <c r="N207" t="n">
-        <v>2546.9826041667</v>
+        <v>2546.9824867725</v>
       </c>
       <c r="O207" t="n">
-        <v>122255.1650000016</v>
+        <v>122255.15936508</v>
       </c>
       <c r="P207" t="n">
         <v>3900</v>
@@ -9620,10 +9620,10 @@
         <v>600</v>
       </c>
       <c r="N208" t="n">
-        <v>1259.2746779425</v>
+        <v>1259.2746877177</v>
       </c>
       <c r="O208" t="n">
-        <v>755564.8067655</v>
+        <v>755564.8126306201</v>
       </c>
       <c r="P208" t="n">
         <v>1900</v>
@@ -9661,10 +9661,10 @@
         <v>201</v>
       </c>
       <c r="N209" t="n">
-        <v>2842.2744382022</v>
+        <v>2842.2744146685</v>
       </c>
       <c r="O209" t="n">
-        <v>571297.1620786423</v>
+        <v>571297.1573483685</v>
       </c>
       <c r="P209" t="n">
         <v>4900</v>
@@ -9797,10 +9797,10 @@
         <v>192</v>
       </c>
       <c r="N212" t="n">
-        <v>692.15226870079</v>
+        <v>692.15227579398</v>
       </c>
       <c r="O212" t="n">
-        <v>132893.2355905517</v>
+        <v>132893.2369524442</v>
       </c>
       <c r="P212" t="n">
         <v>1200</v>
@@ -10643,10 +10643,10 @@
         <v>1</v>
       </c>
       <c r="N230" t="n">
-        <v>1690.8700092421</v>
+        <v>1690.8700092764</v>
       </c>
       <c r="O230" t="n">
-        <v>1690.8700092421</v>
+        <v>1690.8700092764</v>
       </c>
       <c r="P230" t="n">
         <v>3000</v>
@@ -11127,10 +11127,10 @@
         <v>504</v>
       </c>
       <c r="N240" t="n">
-        <v>3110.8399744753</v>
+        <v>3110.8399287749</v>
       </c>
       <c r="O240" t="n">
-        <v>1567863.347135551</v>
+        <v>1567863.32410255</v>
       </c>
       <c r="P240" t="n">
         <v>4500</v>
@@ -11355,10 +11355,10 @@
         <v>12218</v>
       </c>
       <c r="N245" t="n">
-        <v>703.7949766627</v>
+        <v>703.79497049501</v>
       </c>
       <c r="O245" t="n">
-        <v>8598967.024864869</v>
+        <v>8598966.949508032</v>
       </c>
       <c r="P245" t="n">
         <v>900</v>
@@ -11634,10 +11634,10 @@
         <v>59</v>
       </c>
       <c r="N251" t="n">
-        <v>2501.3847317073</v>
+        <v>2501.3847058824</v>
       </c>
       <c r="O251" t="n">
-        <v>147581.6991707307</v>
+        <v>147581.6976470616</v>
       </c>
       <c r="P251" t="n">
         <v>4100</v>
@@ -12262,10 +12262,10 @@
         <v>71</v>
       </c>
       <c r="N264" t="n">
-        <v>2098.4050882353</v>
+        <v>2098.4051032448</v>
       </c>
       <c r="O264" t="n">
-        <v>148986.7612647063</v>
+        <v>148986.7623303808</v>
       </c>
       <c r="P264" t="n">
         <v>9500</v>
@@ -15348,10 +15348,10 @@
         <v>1</v>
       </c>
       <c r="N328" t="n">
-        <v>10737.525909091</v>
+        <v>10737.525813953</v>
       </c>
       <c r="O328" t="n">
-        <v>10737.525909091</v>
+        <v>10737.525813953</v>
       </c>
       <c r="P328" t="n">
         <v>18900</v>
@@ -18037,10 +18037,10 @@
         <v>13</v>
       </c>
       <c r="N384" t="n">
-        <v>22951.704751958</v>
+        <v>22951.704745098</v>
       </c>
       <c r="O384" t="n">
-        <v>298372.161775454</v>
+        <v>298372.161686274</v>
       </c>
       <c r="P384" t="n">
         <v>37900</v>
@@ -18180,10 +18180,10 @@
         <v>36</v>
       </c>
       <c r="N387" t="n">
-        <v>1547.8827868852</v>
+        <v>1547.8828813559</v>
       </c>
       <c r="O387" t="n">
-        <v>55723.7803278672</v>
+        <v>55723.7837288124</v>
       </c>
       <c r="P387" t="n">
         <v>5500</v>
@@ -18282,10 +18282,10 @@
         <v>43</v>
       </c>
       <c r="N389" t="n">
-        <v>1757.3205676856</v>
+        <v>1757.3205689278</v>
       </c>
       <c r="O389" t="n">
-        <v>75564.7844104808</v>
+        <v>75564.7844638954</v>
       </c>
       <c r="P389" t="n">
         <v>2000</v>
@@ -19667,12 +19667,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>J-582</t>
+          <t>J-138</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>PERRO CAMINA J-138</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -19686,7 +19686,7 @@
         </is>
       </c>
       <c r="J420" t="n">
-        <v>646</v>
+        <v>288</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
@@ -19695,30 +19695,30 @@
         <v>0</v>
       </c>
       <c r="M420" t="n">
-        <v>646</v>
+        <v>288</v>
       </c>
       <c r="N420" t="n">
-        <v>9240</v>
+        <v>6160</v>
       </c>
       <c r="O420" t="n">
-        <v>5969040</v>
+        <v>1774080</v>
       </c>
       <c r="P420" t="n">
-        <v>11500</v>
+        <v>7500</v>
       </c>
       <c r="Q420" t="n">
-        <v>7429000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>LP089</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SET DE BICHOS EN BOLSA 714K-1</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -19732,7 +19732,7 @@
         </is>
       </c>
       <c r="J421" t="n">
-        <v>25</v>
+        <v>646</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
@@ -19741,30 +19741,30 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
-        <v>25</v>
+        <v>646</v>
       </c>
       <c r="N421" t="n">
-        <v>10320</v>
+        <v>9240</v>
       </c>
       <c r="O421" t="n">
-        <v>258000</v>
+        <v>5969040</v>
       </c>
       <c r="P421" t="n">
-        <v>12900</v>
+        <v>11500</v>
       </c>
       <c r="Q421" t="n">
-        <v>322500</v>
+        <v>7429000</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>LP089</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>SET DE BICHOS EN BOLSA 714K-1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
@@ -19787,35 +19787,35 @@
         <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="N422" t="n">
-        <v>415.07</v>
+        <v>10320</v>
       </c>
       <c r="O422" t="n">
-        <v>5395.91</v>
+        <v>258000</v>
       </c>
       <c r="P422" t="n">
-        <v>2900</v>
+        <v>12900</v>
       </c>
       <c r="Q422" t="n">
-        <v>37700</v>
+        <v>322500</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MFQ01</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PELUCHE ERIZO 55CM 23FP-029</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="J423" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K423" t="n">
         <v>0</v>
@@ -19833,34 +19833,44 @@
         <v>0</v>
       </c>
       <c r="M423" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N423" t="n">
-        <v>17885.0975</v>
+        <v>415.07</v>
       </c>
       <c r="O423" t="n">
-        <v>71540.39</v>
+        <v>5395.91</v>
       </c>
       <c r="P423" t="n">
-        <v>46500</v>
+        <v>2900</v>
       </c>
       <c r="Q423" t="n">
-        <v>186000</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MFQ11</t>
+          <t>MFQ01</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
+          <t>PELUCHE ERIZO 55CM 23FP-029</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J424" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
@@ -19869,34 +19879,34 @@
         <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N424" t="n">
-        <v>10436.368888889</v>
+        <v>17885.0975</v>
       </c>
       <c r="O424" t="n">
-        <v>93927.320000001</v>
+        <v>71540.39</v>
       </c>
       <c r="P424" t="n">
-        <v>25900</v>
+        <v>46500</v>
       </c>
       <c r="Q424" t="n">
-        <v>233100</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>MFQ12</t>
+          <t>MFQ11</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK FP-166</t>
+          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
         </is>
       </c>
       <c r="J425" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
@@ -19905,49 +19915,34 @@
         <v>0</v>
       </c>
       <c r="M425" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N425" t="n">
-        <v>8736.825000000001</v>
+        <v>10436.368888889</v>
       </c>
       <c r="O425" t="n">
-        <v>17473.65</v>
+        <v>93927.320000001</v>
       </c>
       <c r="P425" t="n">
-        <v>26500</v>
+        <v>25900</v>
       </c>
       <c r="Q425" t="n">
-        <v>53000</v>
+        <v>233100</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MG033</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>MG18880</t>
+          <t>MFQ12</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I426" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE DINOSAURIO PK FP-166</t>
         </is>
       </c>
       <c r="J426" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -19956,40 +19951,40 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N426" t="n">
-        <v>1783.57</v>
+        <v>8736.825000000001</v>
       </c>
       <c r="O426" t="n">
-        <v>21402.84</v>
+        <v>17473.65</v>
       </c>
       <c r="P426" t="n">
-        <v>7800</v>
+        <v>26500</v>
       </c>
       <c r="Q426" t="n">
-        <v>93600</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MG045</t>
+          <t>MG033</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>PT20032</t>
+          <t>MG18880</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
+          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -19998,7 +19993,7 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
@@ -20007,35 +20002,40 @@
         <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="N427" t="n">
-        <v>6000</v>
+        <v>1783.57</v>
       </c>
       <c r="O427" t="n">
-        <v>210000</v>
+        <v>21402.84</v>
       </c>
       <c r="P427" t="n">
-        <v>7500</v>
+        <v>7800</v>
       </c>
       <c r="Q427" t="n">
-        <v>262500</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MG090</t>
+          <t>MG045</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>PT20032</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
+          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -20044,7 +20044,7 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
@@ -20053,40 +20053,35 @@
         <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N428" t="n">
-        <v>1462.04</v>
+        <v>6000</v>
       </c>
       <c r="O428" t="n">
-        <v>4386.12</v>
+        <v>210000</v>
       </c>
       <c r="P428" t="n">
-        <v>3800</v>
+        <v>7500</v>
       </c>
       <c r="Q428" t="n">
-        <v>11400</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MG093</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>mg26016</t>
+          <t>MG090</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>CARRO BASURA BOLSA MG26016</t>
+          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -20095,7 +20090,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -20104,35 +20099,40 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="N429" t="n">
-        <v>770.6799999999999</v>
+        <v>1462.04</v>
       </c>
       <c r="O429" t="n">
-        <v>22349.72</v>
+        <v>4386.12</v>
       </c>
       <c r="P429" t="n">
-        <v>17800</v>
+        <v>3800</v>
       </c>
       <c r="Q429" t="n">
-        <v>516200</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG093</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>mg26016</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>CARRO BASURA BOLSA MG26016</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -20141,7 +20141,7 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K430" t="n">
         <v>0</v>
@@ -20150,35 +20150,35 @@
         <v>0</v>
       </c>
       <c r="M430" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N430" t="n">
-        <v>1482.84</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="O430" t="n">
-        <v>40036.68</v>
+        <v>22349.72</v>
       </c>
       <c r="P430" t="n">
-        <v>6500</v>
+        <v>17800</v>
       </c>
       <c r="Q430" t="n">
-        <v>175500</v>
+        <v>516200</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MG21714</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -20187,7 +20187,7 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
@@ -20196,35 +20196,35 @@
         <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N431" t="n">
-        <v>576.58</v>
+        <v>1482.84</v>
       </c>
       <c r="O431" t="n">
-        <v>33441.64</v>
+        <v>40036.68</v>
       </c>
       <c r="P431" t="n">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="Q431" t="n">
-        <v>342200</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG21714</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -20233,7 +20233,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -20242,40 +20242,35 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N432" t="n">
-        <v>1129.14</v>
+        <v>576.58</v>
       </c>
       <c r="O432" t="n">
-        <v>68877.54000000001</v>
+        <v>33441.64</v>
       </c>
       <c r="P432" t="n">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="Q432" t="n">
-        <v>420900</v>
+        <v>342200</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>MG22435</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>MG22435</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -20284,7 +20279,7 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>226</v>
+        <v>61</v>
       </c>
       <c r="K433" t="n">
         <v>0</v>
@@ -20293,35 +20288,40 @@
         <v>0</v>
       </c>
       <c r="M433" t="n">
-        <v>226</v>
+        <v>61</v>
       </c>
       <c r="N433" t="n">
-        <v>1236.3</v>
+        <v>1129.14</v>
       </c>
       <c r="O433" t="n">
-        <v>279403.8</v>
+        <v>68877.54000000001</v>
       </c>
       <c r="P433" t="n">
-        <v>2300</v>
+        <v>6900</v>
       </c>
       <c r="Q433" t="n">
-        <v>519800</v>
+        <v>420900</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>MG22435</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -20330,7 +20330,7 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>2</v>
+        <v>226</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
@@ -20339,35 +20339,35 @@
         <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>2</v>
+        <v>226</v>
       </c>
       <c r="N434" t="n">
-        <v>8174.05</v>
+        <v>1236.3</v>
       </c>
       <c r="O434" t="n">
-        <v>16348.1</v>
+        <v>279403.8</v>
       </c>
       <c r="P434" t="n">
-        <v>8900</v>
+        <v>2300</v>
       </c>
       <c r="Q434" t="n">
-        <v>17800</v>
+        <v>519800</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -20376,7 +20376,7 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K435" t="n">
         <v>0</v>
@@ -20385,35 +20385,35 @@
         <v>0</v>
       </c>
       <c r="M435" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N435" t="n">
-        <v>11433.53</v>
+        <v>8174.05</v>
       </c>
       <c r="O435" t="n">
-        <v>45734.12</v>
+        <v>16348.1</v>
       </c>
       <c r="P435" t="n">
-        <v>15000</v>
+        <v>8900</v>
       </c>
       <c r="Q435" t="n">
-        <v>60000</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>MG26011</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CAMION DE BOMBEROS MG26011</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
@@ -20431,30 +20431,30 @@
         <v>0</v>
       </c>
       <c r="M436" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N436" t="n">
-        <v>5920.69</v>
+        <v>11433.53</v>
       </c>
       <c r="O436" t="n">
-        <v>29603.45</v>
+        <v>45734.12</v>
       </c>
       <c r="P436" t="n">
-        <v>11900</v>
+        <v>15000</v>
       </c>
       <c r="Q436" t="n">
-        <v>59500</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>MG26196</t>
+          <t>MG26011</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
+          <t>CAMION DE BOMBEROS MG26011</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -20468,7 +20468,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -20477,30 +20477,30 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N437" t="n">
-        <v>6272.36</v>
+        <v>5920.69</v>
       </c>
       <c r="O437" t="n">
-        <v>94085.39999999999</v>
+        <v>29603.45</v>
       </c>
       <c r="P437" t="n">
-        <v>10500</v>
+        <v>11900</v>
       </c>
       <c r="Q437" t="n">
-        <v>157500</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>MG27332</t>
+          <t>MG26196</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
+          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -20514,7 +20514,7 @@
         </is>
       </c>
       <c r="J438" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K438" t="n">
         <v>0</v>
@@ -20523,30 +20523,30 @@
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N438" t="n">
-        <v>6750.7</v>
+        <v>6272.36</v>
       </c>
       <c r="O438" t="n">
-        <v>135014</v>
+        <v>94085.39999999999</v>
       </c>
       <c r="P438" t="n">
-        <v>22500</v>
+        <v>10500</v>
       </c>
       <c r="Q438" t="n">
-        <v>450000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG27332</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -20560,7 +20560,7 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
@@ -20569,35 +20569,35 @@
         <v>0</v>
       </c>
       <c r="M439" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N439" t="n">
-        <v>9046.99</v>
+        <v>6750.7</v>
       </c>
       <c r="O439" t="n">
-        <v>63328.93</v>
+        <v>135014</v>
       </c>
       <c r="P439" t="n">
         <v>22500</v>
       </c>
       <c r="Q439" t="n">
-        <v>157500</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -20606,7 +20606,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -20615,40 +20615,35 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="N440" t="n">
-        <v>1319.3609036145</v>
+        <v>9046.99</v>
       </c>
       <c r="O440" t="n">
-        <v>50135.714337351</v>
+        <v>63328.93</v>
       </c>
       <c r="P440" t="n">
-        <v>3500</v>
+        <v>22500</v>
       </c>
       <c r="Q440" t="n">
-        <v>133000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>MG32342</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>MG32342</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -20657,7 +20652,7 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
@@ -20666,35 +20661,40 @@
         <v>0</v>
       </c>
       <c r="M441" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="N441" t="n">
-        <v>1161.6</v>
+        <v>1319.3609090909</v>
       </c>
       <c r="O441" t="n">
-        <v>20908.8</v>
+        <v>50135.7145454542</v>
       </c>
       <c r="P441" t="n">
-        <v>24500</v>
+        <v>3500</v>
       </c>
       <c r="Q441" t="n">
-        <v>441000</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>MG32594</t>
+          <t>MG32342</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>MG32342</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
+          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
@@ -20712,40 +20712,35 @@
         <v>0</v>
       </c>
       <c r="M442" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="N442" t="n">
-        <v>3088.1445833333</v>
+        <v>1161.6</v>
       </c>
       <c r="O442" t="n">
-        <v>111173.2049999988</v>
+        <v>20908.8</v>
       </c>
       <c r="P442" t="n">
-        <v>8500</v>
+        <v>24500</v>
       </c>
       <c r="Q442" t="n">
-        <v>306000</v>
+        <v>441000</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG32594</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -20754,7 +20749,7 @@
         </is>
       </c>
       <c r="J443" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="K443" t="n">
         <v>0</v>
@@ -20763,35 +20758,40 @@
         <v>0</v>
       </c>
       <c r="M443" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="N443" t="n">
-        <v>751.45</v>
+        <v>3088.1445833333</v>
       </c>
       <c r="O443" t="n">
-        <v>2254.35</v>
+        <v>111173.2049999988</v>
       </c>
       <c r="P443" t="n">
-        <v>2500</v>
+        <v>8500</v>
       </c>
       <c r="Q443" t="n">
-        <v>7500</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -20800,7 +20800,7 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
@@ -20809,35 +20809,35 @@
         <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="N444" t="n">
-        <v>571.87</v>
+        <v>751.45</v>
       </c>
       <c r="O444" t="n">
-        <v>86924.24000000001</v>
+        <v>2254.35</v>
       </c>
       <c r="P444" t="n">
         <v>2500</v>
       </c>
       <c r="Q444" t="n">
-        <v>380000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MG40226</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>ATARY COCODRILO MG40226</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -20846,7 +20846,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -20855,35 +20855,30 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="N445" t="n">
-        <v>310.41666666667</v>
+        <v>571.87</v>
       </c>
       <c r="O445" t="n">
-        <v>310.41666666667</v>
+        <v>86924.24000000001</v>
       </c>
       <c r="P445" t="n">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="Q445" t="n">
-        <v>1800</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MG40243</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>MG40243</t>
+          <t>MG40226</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>ATARY DINOSAURIO MG40243</t>
+          <t>ATARY COCODRILO MG40226</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -20897,7 +20892,7 @@
         </is>
       </c>
       <c r="J446" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K446" t="n">
         <v>0</v>
@@ -20906,35 +20901,40 @@
         <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N446" t="n">
-        <v>520.674</v>
+        <v>310.41666666667</v>
       </c>
       <c r="O446" t="n">
-        <v>4165.392</v>
+        <v>310.41666666667</v>
       </c>
       <c r="P446" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="Q446" t="n">
-        <v>16000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MG40259</t>
+          <t>MG40243</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>MG40243</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>CARRO JET DESTAPADO MG40259</t>
+          <t>ATARY DINOSAURIO MG40243</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="J447" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K447" t="n">
         <v>0</v>
@@ -20952,40 +20952,35 @@
         <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N447" t="n">
-        <v>1153.41</v>
+        <v>520.674</v>
       </c>
       <c r="O447" t="n">
-        <v>2306.82</v>
+        <v>4165.392</v>
       </c>
       <c r="P447" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="Q447" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG40259</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>CARRO JET DESTAPADO MG40259</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -20994,7 +20989,7 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
@@ -21003,30 +20998,35 @@
         <v>0</v>
       </c>
       <c r="M448" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="N448" t="n">
-        <v>2432.1356790123</v>
+        <v>1153.41</v>
       </c>
       <c r="O448" t="n">
-        <v>102149.6985185166</v>
+        <v>2306.82</v>
       </c>
       <c r="P448" t="n">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="Q448" t="n">
-        <v>189000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MG40327</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>BLISTER PESCA STD  MG40327</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -21040,7 +21040,7 @@
         </is>
       </c>
       <c r="J449" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="K449" t="n">
         <v>0</v>
@@ -21049,35 +21049,35 @@
         <v>0</v>
       </c>
       <c r="M449" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="N449" t="n">
-        <v>449.63</v>
+        <v>2432.1356790123</v>
       </c>
       <c r="O449" t="n">
-        <v>449.63</v>
+        <v>102149.6985185166</v>
       </c>
       <c r="P449" t="n">
-        <v>5100</v>
+        <v>4500</v>
       </c>
       <c r="Q449" t="n">
-        <v>5100</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40327</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>BLISTER PESCA STD  MG40327</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="J450" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="K450" t="n">
         <v>0</v>
@@ -21095,30 +21095,30 @@
         <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="N450" t="n">
-        <v>227.41613824192</v>
+        <v>449.63</v>
       </c>
       <c r="O450" t="n">
-        <v>53442.79248685121</v>
+        <v>449.63</v>
       </c>
       <c r="P450" t="n">
-        <v>1200</v>
+        <v>5100</v>
       </c>
       <c r="Q450" t="n">
-        <v>282000</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>MG40415</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>TELEFONO AVION MG40415</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -21132,7 +21132,7 @@
         </is>
       </c>
       <c r="J451" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="K451" t="n">
         <v>0</v>
@@ -21141,35 +21141,35 @@
         <v>0</v>
       </c>
       <c r="M451" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="N451" t="n">
-        <v>13308.19</v>
+        <v>227.41613824192</v>
       </c>
       <c r="O451" t="n">
-        <v>26616.38</v>
+        <v>53442.79248685121</v>
       </c>
       <c r="P451" t="n">
-        <v>34600</v>
+        <v>1200</v>
       </c>
       <c r="Q451" t="n">
-        <v>69200</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>MG40570</t>
+          <t>MG40415</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>REGISTRADORA SENCILLA MG40570</t>
+          <t>TELEFONO AVION MG40415</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -21178,7 +21178,7 @@
         </is>
       </c>
       <c r="J452" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K452" t="n">
         <v>0</v>
@@ -21187,35 +21187,35 @@
         <v>0</v>
       </c>
       <c r="M452" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N452" t="n">
-        <v>8735.540000000001</v>
+        <v>13308.19</v>
       </c>
       <c r="O452" t="n">
-        <v>61148.78000000001</v>
+        <v>26616.38</v>
       </c>
       <c r="P452" t="n">
-        <v>29900</v>
+        <v>34600</v>
       </c>
       <c r="Q452" t="n">
-        <v>209300</v>
+        <v>69200</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>MG40805</t>
+          <t>MG40570</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>LANZA DARDOS HERO GDE MG40805</t>
+          <t>REGISTRADORA SENCILLA MG40570</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -21224,7 +21224,7 @@
         </is>
       </c>
       <c r="J453" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
@@ -21233,35 +21233,35 @@
         <v>0</v>
       </c>
       <c r="M453" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N453" t="n">
-        <v>22654.34</v>
+        <v>8735.540000000001</v>
       </c>
       <c r="O453" t="n">
-        <v>249197.74</v>
+        <v>61148.78000000001</v>
       </c>
       <c r="P453" t="n">
-        <v>58900</v>
+        <v>29900</v>
       </c>
       <c r="Q453" t="n">
-        <v>647900</v>
+        <v>209300</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>MG41038</t>
+          <t>MG40805</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>VOLQUETA SENCILLA MED MG41038</t>
+          <t>LANZA DARDOS HERO GDE MG40805</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -21270,7 +21270,7 @@
         </is>
       </c>
       <c r="J454" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K454" t="n">
         <v>0</v>
@@ -21279,35 +21279,35 @@
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N454" t="n">
-        <v>4962.04</v>
+        <v>22654.34</v>
       </c>
       <c r="O454" t="n">
-        <v>9924.08</v>
+        <v>249197.74</v>
       </c>
       <c r="P454" t="n">
-        <v>12900</v>
+        <v>58900</v>
       </c>
       <c r="Q454" t="n">
-        <v>25800</v>
+        <v>647900</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MG41038</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
+          <t>VOLQUETA SENCILLA MED MG41038</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="J455" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K455" t="n">
         <v>0</v>
@@ -21325,35 +21325,35 @@
         <v>0</v>
       </c>
       <c r="M455" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N455" t="n">
-        <v>25110.1</v>
+        <v>4962.04</v>
       </c>
       <c r="O455" t="n">
-        <v>326431.3</v>
+        <v>9924.08</v>
       </c>
       <c r="P455" t="n">
-        <v>27900</v>
+        <v>12900</v>
       </c>
       <c r="Q455" t="n">
-        <v>362700</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>MG41588</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -21362,7 +21362,7 @@
         </is>
       </c>
       <c r="J456" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K456" t="n">
         <v>0</v>
@@ -21371,30 +21371,30 @@
         <v>0</v>
       </c>
       <c r="M456" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N456" t="n">
-        <v>5422.51</v>
+        <v>25110.1</v>
       </c>
       <c r="O456" t="n">
-        <v>32535.06</v>
+        <v>326431.3</v>
       </c>
       <c r="P456" t="n">
-        <v>19900</v>
+        <v>27900</v>
       </c>
       <c r="Q456" t="n">
-        <v>119400</v>
+        <v>362700</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>MG41589</t>
+          <t>MG41588</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>MUÑECA ODONTOLOGA MG41589</t>
+          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="J457" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K457" t="n">
         <v>0</v>
@@ -21417,35 +21417,35 @@
         <v>0</v>
       </c>
       <c r="M457" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N457" t="n">
-        <v>5103.23</v>
+        <v>5422.51</v>
       </c>
       <c r="O457" t="n">
-        <v>20412.92</v>
+        <v>32535.06</v>
       </c>
       <c r="P457" t="n">
         <v>19900</v>
       </c>
       <c r="Q457" t="n">
-        <v>79600</v>
+        <v>119400</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>MJC-558</t>
+          <t>MG41589</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+          <t>MUÑECA ODONTOLOGA MG41589</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -21454,7 +21454,7 @@
         </is>
       </c>
       <c r="J458" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K458" t="n">
         <v>0</v>
@@ -21463,30 +21463,30 @@
         <v>0</v>
       </c>
       <c r="M458" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N458" t="n">
-        <v>40500</v>
+        <v>5103.23</v>
       </c>
       <c r="O458" t="n">
-        <v>729000</v>
+        <v>20412.92</v>
       </c>
       <c r="P458" t="n">
-        <v>48600</v>
+        <v>19900</v>
       </c>
       <c r="Q458" t="n">
-        <v>874800</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>MJC-558-1</t>
+          <t>MJC-558</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
+          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -21509,33 +21509,30 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N459" t="n">
         <v>40500</v>
       </c>
       <c r="O459" t="n">
-        <v>324000</v>
+        <v>729000</v>
       </c>
       <c r="P459" t="n">
         <v>48600</v>
       </c>
       <c r="Q459" t="n">
-        <v>388800</v>
+        <v>874800</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B460" t="n">
-        <v>7700154271143</v>
+          <t>MJC-558-1</t>
+        </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -21545,11 +21542,11 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J460" t="n">
-        <v>582</v>
+        <v>8</v>
       </c>
       <c r="K460" t="n">
         <v>0</v>
@@ -21558,30 +21555,33 @@
         <v>0</v>
       </c>
       <c r="M460" t="n">
-        <v>582</v>
+        <v>8</v>
       </c>
       <c r="N460" t="n">
-        <v>2539.5716527391</v>
+        <v>40500</v>
       </c>
       <c r="O460" t="n">
-        <v>1478030.701894156</v>
+        <v>324000</v>
       </c>
       <c r="P460" t="n">
-        <v>3500</v>
+        <v>48600</v>
       </c>
       <c r="Q460" t="n">
-        <v>2037000</v>
+        <v>388800</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>MT4690</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>BALDE CASTILLO PQÑ MT4690</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -21591,11 +21591,11 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J461" t="n">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -21604,30 +21604,30 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="N461" t="n">
-        <v>4687.9744444444</v>
+        <v>2539.5716527391</v>
       </c>
       <c r="O461" t="n">
-        <v>2629953.663333308</v>
+        <v>1478030.701894156</v>
       </c>
       <c r="P461" t="n">
-        <v>5900</v>
+        <v>3500</v>
       </c>
       <c r="Q461" t="n">
-        <v>3309900</v>
+        <v>2037000</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>MT4690</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>BALDE CASTILLO PQÑ MT4690</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -21641,7 +21641,7 @@
         </is>
       </c>
       <c r="J462" t="n">
-        <v>80</v>
+        <v>561</v>
       </c>
       <c r="K462" t="n">
         <v>0</v>
@@ -21650,35 +21650,35 @@
         <v>0</v>
       </c>
       <c r="M462" t="n">
-        <v>80</v>
+        <v>561</v>
       </c>
       <c r="N462" t="n">
-        <v>4171.6686473988</v>
+        <v>4687.9744604317</v>
       </c>
       <c r="O462" t="n">
-        <v>333733.491791904</v>
+        <v>2629953.672302184</v>
       </c>
       <c r="P462" t="n">
-        <v>5500</v>
+        <v>5900</v>
       </c>
       <c r="Q462" t="n">
-        <v>440000</v>
+        <v>3309900</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>PT08</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>ALCANCIA PEQUEÑA PP002</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -21699,32 +21699,32 @@
         <v>80</v>
       </c>
       <c r="N463" t="n">
-        <v>436.24</v>
+        <v>4171.6686379511</v>
       </c>
       <c r="O463" t="n">
-        <v>34899.2</v>
+        <v>333733.491036088</v>
       </c>
       <c r="P463" t="n">
-        <v>550</v>
+        <v>5500</v>
       </c>
       <c r="Q463" t="n">
-        <v>44000</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>PT08</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>ALCANCIA PEQUEÑA PP002</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -21733,7 +21733,7 @@
         </is>
       </c>
       <c r="J464" t="n">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="K464" t="n">
         <v>0</v>
@@ -21742,40 +21742,35 @@
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="N464" t="n">
-        <v>1950.7</v>
+        <v>436.24</v>
       </c>
       <c r="O464" t="n">
-        <v>206774.2</v>
+        <v>34899.2</v>
       </c>
       <c r="P464" t="n">
-        <v>7500</v>
+        <v>550</v>
       </c>
       <c r="Q464" t="n">
-        <v>795000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>PT15838</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>PT15838</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA PT15838</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -21784,7 +21779,7 @@
         </is>
       </c>
       <c r="J465" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="K465" t="n">
         <v>0</v>
@@ -21793,35 +21788,40 @@
         <v>0</v>
       </c>
       <c r="M465" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="N465" t="n">
-        <v>753.98</v>
+        <v>1950.7</v>
       </c>
       <c r="O465" t="n">
-        <v>753.98</v>
+        <v>206774.2</v>
       </c>
       <c r="P465" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="Q465" t="n">
-        <v>4000</v>
+        <v>795000</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>PT25404</t>
+          <t>PT15838</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>PT15838</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
+          <t>LANZADORA DE AGUA PT15838</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>MONTABLES</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -21842,27 +21842,27 @@
         <v>1</v>
       </c>
       <c r="N466" t="n">
-        <v>84538.46000000001</v>
+        <v>753.98</v>
       </c>
       <c r="O466" t="n">
-        <v>84538.46000000001</v>
+        <v>753.98</v>
       </c>
       <c r="P466" t="n">
-        <v>109900</v>
+        <v>4000</v>
       </c>
       <c r="Q466" t="n">
-        <v>109900</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>PT25419</t>
+          <t>PT25404</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>MONOPATIN CAJA LUCES PT25419</t>
+          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="J467" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K467" t="n">
         <v>0</v>
@@ -21885,30 +21885,30 @@
         <v>0</v>
       </c>
       <c r="M467" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N467" t="n">
-        <v>87920</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="O467" t="n">
-        <v>527520</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="P467" t="n">
         <v>109900</v>
       </c>
       <c r="Q467" t="n">
-        <v>659400</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>PT25420</t>
+          <t>PT25419</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>MONOPATIN  PATO PT25420</t>
+          <t>MONOPATIN CAJA LUCES PT25419</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="J468" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K468" t="n">
         <v>0</v>
@@ -21931,35 +21931,35 @@
         <v>0</v>
       </c>
       <c r="M468" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N468" t="n">
-        <v>15394.79</v>
+        <v>87920</v>
       </c>
       <c r="O468" t="n">
-        <v>169342.69</v>
+        <v>527520</v>
       </c>
       <c r="P468" t="n">
-        <v>99800</v>
+        <v>109900</v>
       </c>
       <c r="Q468" t="n">
-        <v>1097800</v>
+        <v>659400</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>PT26747</t>
+          <t>PT25420</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>TABLA LABERINTO PT26747</t>
+          <t>MONOPATIN  PATO PT25420</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MONTABLES</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -21968,7 +21968,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K469" t="n">
         <v>0</v>
@@ -21977,30 +21977,30 @@
         <v>0</v>
       </c>
       <c r="M469" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="N469" t="n">
-        <v>2361.5097058824</v>
+        <v>15394.79</v>
       </c>
       <c r="O469" t="n">
-        <v>56676.2329411776</v>
+        <v>169342.69</v>
       </c>
       <c r="P469" t="n">
-        <v>6200</v>
+        <v>99800</v>
       </c>
       <c r="Q469" t="n">
-        <v>148800</v>
+        <v>1097800</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>RL589-28D</t>
+          <t>PT26747</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
+          <t>TABLA LABERINTO PT26747</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -22026,27 +22026,27 @@
         <v>24</v>
       </c>
       <c r="N470" t="n">
-        <v>7046.7385714286</v>
+        <v>2361.5097058824</v>
       </c>
       <c r="O470" t="n">
-        <v>169121.7257142864</v>
+        <v>56676.2329411776</v>
       </c>
       <c r="P470" t="n">
-        <v>22900</v>
+        <v>6200</v>
       </c>
       <c r="Q470" t="n">
-        <v>549600</v>
+        <v>148800</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>RL589-33D</t>
+          <t>RL589-28D</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -22060,7 +22060,7 @@
         </is>
       </c>
       <c r="J471" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K471" t="n">
         <v>0</v>
@@ -22069,35 +22069,35 @@
         <v>0</v>
       </c>
       <c r="M471" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N471" t="n">
-        <v>10009.172</v>
+        <v>7046.7388888889</v>
       </c>
       <c r="O471" t="n">
-        <v>30027.516</v>
+        <v>169121.7333333336</v>
       </c>
       <c r="P471" t="n">
         <v>22900</v>
       </c>
       <c r="Q471" t="n">
-        <v>68700</v>
+        <v>549600</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>RL589-33D</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="J472" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
@@ -22115,35 +22115,35 @@
         <v>0</v>
       </c>
       <c r="M472" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N472" t="n">
-        <v>4091.4</v>
+        <v>10009.172</v>
       </c>
       <c r="O472" t="n">
-        <v>36822.6</v>
+        <v>30027.516</v>
       </c>
       <c r="P472" t="n">
-        <v>10000</v>
+        <v>22900</v>
       </c>
       <c r="Q472" t="n">
-        <v>90000</v>
+        <v>68700</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>SEBQ17</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>CUBO MAGICO COLORES X5 SE-19126</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -22152,7 +22152,7 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -22161,35 +22161,35 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="N473" t="n">
-        <v>5148.77</v>
+        <v>4091.4</v>
       </c>
       <c r="O473" t="n">
-        <v>278033.58</v>
+        <v>36822.6</v>
       </c>
       <c r="P473" t="n">
-        <v>10500</v>
+        <v>10000</v>
       </c>
       <c r="Q473" t="n">
-        <v>567000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>SEBQ27</t>
+          <t>SEBQ17</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>CELULAR MUÑECO X12 SE1597</t>
+          <t>CUBO MAGICO COLORES X5 SE-19126</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -22198,7 +22198,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>451</v>
+        <v>54</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -22207,30 +22207,30 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>451</v>
+        <v>54</v>
       </c>
       <c r="N474" t="n">
-        <v>855.85</v>
+        <v>5148.77</v>
       </c>
       <c r="O474" t="n">
-        <v>385988.35</v>
+        <v>278033.58</v>
       </c>
       <c r="P474" t="n">
-        <v>3500</v>
+        <v>10500</v>
       </c>
       <c r="Q474" t="n">
-        <v>1578500</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SLT052</t>
+          <t>SEBQ27</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
+          <t>CELULAR MUÑECO X12 SE1597</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -22244,7 +22244,7 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>2</v>
+        <v>451</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
@@ -22253,35 +22253,35 @@
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>2</v>
+        <v>451</v>
       </c>
       <c r="N475" t="n">
-        <v>0</v>
+        <v>855.85</v>
       </c>
       <c r="O475" t="n">
-        <v>0</v>
+        <v>385988.35</v>
       </c>
       <c r="P475" t="n">
-        <v>13500</v>
+        <v>3500</v>
       </c>
       <c r="Q475" t="n">
-        <v>27000</v>
+        <v>1578500</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>SLT052</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -22299,30 +22299,30 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="N476" t="n">
-        <v>4550</v>
+        <v>0</v>
       </c>
       <c r="O476" t="n">
-        <v>819000</v>
+        <v>0</v>
       </c>
       <c r="P476" t="n">
-        <v>5500</v>
+        <v>13500</v>
       </c>
       <c r="Q476" t="n">
-        <v>990000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>SLT2641</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 5 SLT2641</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -22336,7 +22336,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -22345,30 +22345,30 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="N477" t="n">
-        <v>422.91</v>
+        <v>4550</v>
       </c>
       <c r="O477" t="n">
-        <v>3383.28</v>
+        <v>819000</v>
       </c>
       <c r="P477" t="n">
-        <v>12500</v>
+        <v>5500</v>
       </c>
       <c r="Q477" t="n">
-        <v>100000</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>SLT2642</t>
+          <t>SLT2641</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
+          <t>BALON BASQUEBOL # 5 SLT2641</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -22391,30 +22391,30 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="N478" t="n">
-        <v>341.02143442623</v>
+        <v>422.91</v>
       </c>
       <c r="O478" t="n">
-        <v>58314.66528688533</v>
+        <v>3383.28</v>
       </c>
       <c r="P478" t="n">
-        <v>14500</v>
+        <v>12500</v>
       </c>
       <c r="Q478" t="n">
-        <v>2479500</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>SLT2714</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>VENTILADOR MINI SLT2714</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -22428,7 +22428,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -22437,35 +22437,35 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="N479" t="n">
-        <v>4158.2958823529</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O479" t="n">
-        <v>133065.4682352928</v>
+        <v>58314.66528688533</v>
       </c>
       <c r="P479" t="n">
-        <v>13800</v>
+        <v>14500</v>
       </c>
       <c r="Q479" t="n">
-        <v>441600</v>
+        <v>2479500</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>SLT2714</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
+          <t>VENTILADOR MINI SLT2714</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -22474,7 +22474,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="K480" t="n">
         <v>0</v>
@@ -22483,30 +22483,30 @@
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N480" t="n">
-        <v>22230.77</v>
+        <v>4158.2958823529</v>
       </c>
       <c r="O480" t="n">
-        <v>111153.85</v>
+        <v>133065.4682352928</v>
       </c>
       <c r="P480" t="n">
-        <v>28900</v>
+        <v>13800</v>
       </c>
       <c r="Q480" t="n">
-        <v>144500</v>
+        <v>441600</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
+          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -22520,7 +22520,7 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
@@ -22529,30 +22529,30 @@
         <v>0</v>
       </c>
       <c r="M481" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N481" t="n">
-        <v>33200</v>
+        <v>22230.77</v>
       </c>
       <c r="O481" t="n">
-        <v>33200</v>
+        <v>111153.85</v>
       </c>
       <c r="P481" t="n">
-        <v>41500</v>
+        <v>28900</v>
       </c>
       <c r="Q481" t="n">
-        <v>41500</v>
+        <v>144500</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>T038</t>
+          <t>T032</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -22578,32 +22578,32 @@
         <v>1</v>
       </c>
       <c r="N482" t="n">
-        <v>4962.04</v>
+        <v>33200</v>
       </c>
       <c r="O482" t="n">
-        <v>4962.04</v>
+        <v>33200</v>
       </c>
       <c r="P482" t="n">
-        <v>12900</v>
+        <v>41500</v>
       </c>
       <c r="Q482" t="n">
-        <v>12900</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>T046</t>
+          <t>T038</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
+          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -22621,35 +22621,35 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N483" t="n">
-        <v>22802.484</v>
+        <v>4962.04</v>
       </c>
       <c r="O483" t="n">
-        <v>114012.42</v>
+        <v>4962.04</v>
       </c>
       <c r="P483" t="n">
-        <v>41500</v>
+        <v>12900</v>
       </c>
       <c r="Q483" t="n">
-        <v>207500</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>T046</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -22658,7 +22658,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -22667,35 +22667,35 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="N484" t="n">
-        <v>12392.16</v>
+        <v>22802.484</v>
       </c>
       <c r="O484" t="n">
-        <v>557647.2</v>
+        <v>114012.42</v>
       </c>
       <c r="P484" t="n">
-        <v>15900</v>
+        <v>41500</v>
       </c>
       <c r="Q484" t="n">
-        <v>715500</v>
+        <v>207500</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -22713,35 +22713,35 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="N485" t="n">
-        <v>24882.58</v>
+        <v>12392.16</v>
       </c>
       <c r="O485" t="n">
-        <v>174178.06</v>
+        <v>557647.2</v>
       </c>
       <c r="P485" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q485" t="n">
-        <v>220500</v>
+        <v>715500</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>T066</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -22750,7 +22750,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -22759,30 +22759,30 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N486" t="n">
-        <v>16576.2</v>
+        <v>24882.58</v>
       </c>
       <c r="O486" t="n">
-        <v>16576.2</v>
+        <v>174178.06</v>
       </c>
       <c r="P486" t="n">
-        <v>25900</v>
+        <v>31500</v>
       </c>
       <c r="Q486" t="n">
-        <v>25900</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>T067</t>
+          <t>T066</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
+          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -22808,27 +22808,27 @@
         <v>1</v>
       </c>
       <c r="N487" t="n">
-        <v>47600</v>
+        <v>16576.2</v>
       </c>
       <c r="O487" t="n">
-        <v>47600</v>
+        <v>16576.2</v>
       </c>
       <c r="P487" t="n">
-        <v>59500</v>
+        <v>25900</v>
       </c>
       <c r="Q487" t="n">
-        <v>59500</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>T073</t>
+          <t>T067</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
+          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="J488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K488" t="n">
         <v>0</v>
@@ -22851,30 +22851,30 @@
         <v>0</v>
       </c>
       <c r="M488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N488" t="n">
-        <v>6102.9</v>
+        <v>47600</v>
       </c>
       <c r="O488" t="n">
-        <v>12205.8</v>
+        <v>47600</v>
       </c>
       <c r="P488" t="n">
-        <v>11900</v>
+        <v>59500</v>
       </c>
       <c r="Q488" t="n">
-        <v>23800</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>T079</t>
+          <t>T073</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>PELUCHE 15CM BQ-15</t>
+          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -22888,7 +22888,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -22897,30 +22897,30 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N489" t="n">
-        <v>525.33</v>
+        <v>6102.9</v>
       </c>
       <c r="O489" t="n">
-        <v>12082.59</v>
+        <v>12205.8</v>
       </c>
       <c r="P489" t="n">
-        <v>5900</v>
+        <v>11900</v>
       </c>
       <c r="Q489" t="n">
-        <v>135700</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>T089</t>
+          <t>T079</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
+          <t>PELUCHE 15CM BQ-15</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -22934,7 +22934,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
@@ -22943,30 +22943,30 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="N490" t="n">
-        <v>8580.75</v>
+        <v>525.33</v>
       </c>
       <c r="O490" t="n">
-        <v>17161.5</v>
+        <v>12082.59</v>
       </c>
       <c r="P490" t="n">
-        <v>42900</v>
+        <v>5900</v>
       </c>
       <c r="Q490" t="n">
-        <v>85800</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>T098</t>
+          <t>T089</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
+          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -22980,7 +22980,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -22989,30 +22989,30 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N491" t="n">
-        <v>14308.02</v>
+        <v>8580.75</v>
       </c>
       <c r="O491" t="n">
-        <v>14308.02</v>
+        <v>17161.5</v>
       </c>
       <c r="P491" t="n">
-        <v>27900</v>
+        <v>42900</v>
       </c>
       <c r="Q491" t="n">
-        <v>27900</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>T099</t>
+          <t>T098</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
+          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -23035,30 +23035,30 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N492" t="n">
-        <v>8538.8633333333</v>
+        <v>14308.02</v>
       </c>
       <c r="O492" t="n">
-        <v>17077.7266666666</v>
+        <v>14308.02</v>
       </c>
       <c r="P492" t="n">
-        <v>18500</v>
+        <v>27900</v>
       </c>
       <c r="Q492" t="n">
-        <v>37000</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>T103</t>
+          <t>T099</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -23072,7 +23072,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -23081,30 +23081,30 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N493" t="n">
-        <v>9962.040000000001</v>
+        <v>8538.8633333333</v>
       </c>
       <c r="O493" t="n">
-        <v>9962.040000000001</v>
+        <v>17077.7266666666</v>
       </c>
       <c r="P493" t="n">
-        <v>25900</v>
+        <v>18500</v>
       </c>
       <c r="Q493" t="n">
-        <v>25900</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>T117</t>
+          <t>T103</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
+          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -23118,7 +23118,7 @@
         </is>
       </c>
       <c r="J494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
@@ -23127,30 +23127,30 @@
         <v>0</v>
       </c>
       <c r="M494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N494" t="n">
-        <v>14577.42</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O494" t="n">
-        <v>29154.84</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="P494" t="n">
-        <v>37900</v>
+        <v>25900</v>
       </c>
       <c r="Q494" t="n">
-        <v>75800</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>T121</t>
+          <t>T117</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
+          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -23164,7 +23164,7 @@
         </is>
       </c>
       <c r="J495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K495" t="n">
         <v>0</v>
@@ -23173,30 +23173,30 @@
         <v>0</v>
       </c>
       <c r="M495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N495" t="n">
-        <v>13000.5</v>
+        <v>14577.42</v>
       </c>
       <c r="O495" t="n">
-        <v>13000.5</v>
+        <v>29154.84</v>
       </c>
       <c r="P495" t="n">
-        <v>32500</v>
+        <v>37900</v>
       </c>
       <c r="Q495" t="n">
-        <v>32500</v>
+        <v>75800</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>T135</t>
+          <t>T121</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
+          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -23210,7 +23210,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -23219,30 +23219,30 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N496" t="n">
-        <v>7115.88</v>
+        <v>13000.5</v>
       </c>
       <c r="O496" t="n">
-        <v>35579.4</v>
+        <v>13000.5</v>
       </c>
       <c r="P496" t="n">
-        <v>18500</v>
+        <v>32500</v>
       </c>
       <c r="Q496" t="n">
-        <v>92500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>T136</t>
+          <t>T135</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>BOLSO PELUCHE ANIMALES P01-30</t>
+          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -23256,7 +23256,7 @@
         </is>
       </c>
       <c r="J497" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -23265,30 +23265,30 @@
         <v>0</v>
       </c>
       <c r="M497" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N497" t="n">
-        <v>7886.43</v>
+        <v>7115.88</v>
       </c>
       <c r="O497" t="n">
-        <v>31545.72</v>
+        <v>35579.4</v>
       </c>
       <c r="P497" t="n">
-        <v>34500</v>
+        <v>18500</v>
       </c>
       <c r="Q497" t="n">
-        <v>138000</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>T143</t>
+          <t>T136</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
+          <t>BOLSO PELUCHE ANIMALES P01-30</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -23302,7 +23302,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -23311,30 +23311,30 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N498" t="n">
-        <v>23920</v>
+        <v>7886.43</v>
       </c>
       <c r="O498" t="n">
-        <v>23920</v>
+        <v>31545.72</v>
       </c>
       <c r="P498" t="n">
-        <v>29900</v>
+        <v>34500</v>
       </c>
       <c r="Q498" t="n">
-        <v>29900</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>T157</t>
+          <t>T143</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>PELUCHE CONEJO 30CM ANA-28</t>
+          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -23348,7 +23348,7 @@
         </is>
       </c>
       <c r="J499" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -23357,30 +23357,30 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N499" t="n">
-        <v>11472.4</v>
+        <v>23920</v>
       </c>
       <c r="O499" t="n">
-        <v>34417.2</v>
+        <v>23920</v>
       </c>
       <c r="P499" t="n">
-        <v>23900</v>
+        <v>29900</v>
       </c>
       <c r="Q499" t="n">
-        <v>71700</v>
+        <v>29900</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>T158</t>
+          <t>T157</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
+          <t>PELUCHE CONEJO 30CM ANA-28</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -23394,7 +23394,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -23403,30 +23403,30 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N500" t="n">
-        <v>10577.42</v>
+        <v>11472.4</v>
       </c>
       <c r="O500" t="n">
-        <v>105774.2</v>
+        <v>34417.2</v>
       </c>
       <c r="P500" t="n">
-        <v>27500</v>
+        <v>23900</v>
       </c>
       <c r="Q500" t="n">
-        <v>275000</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T158</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -23440,7 +23440,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -23449,30 +23449,30 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N501" t="n">
-        <v>5186.45</v>
+        <v>10577.42</v>
       </c>
       <c r="O501" t="n">
-        <v>103729</v>
+        <v>105774.2</v>
       </c>
       <c r="P501" t="n">
-        <v>7200</v>
+        <v>27500</v>
       </c>
       <c r="Q501" t="n">
-        <v>144000</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>T171</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -23486,7 +23486,7 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
@@ -23495,34 +23495,44 @@
         <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N502" t="n">
-        <v>14832.4</v>
+        <v>5186.45</v>
       </c>
       <c r="O502" t="n">
-        <v>14832.4</v>
+        <v>103729</v>
       </c>
       <c r="P502" t="n">
-        <v>30900</v>
+        <v>7200</v>
       </c>
       <c r="Q502" t="n">
-        <v>30900</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>T172</t>
+          <t>T171</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
+          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
@@ -23531,44 +23541,34 @@
         <v>0</v>
       </c>
       <c r="M503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N503" t="n">
-        <v>4462.14</v>
+        <v>14832.4</v>
       </c>
       <c r="O503" t="n">
-        <v>8924.280000000001</v>
+        <v>14832.4</v>
       </c>
       <c r="P503" t="n">
-        <v>14500</v>
+        <v>30900</v>
       </c>
       <c r="Q503" t="n">
-        <v>29000</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>T175</t>
+          <t>T172</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>PELUCHE BOWSER 35CM KUP-35</t>
-        </is>
-      </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I504" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
         </is>
       </c>
       <c r="J504" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -23577,30 +23577,30 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N504" t="n">
-        <v>4614.22</v>
+        <v>4462.14</v>
       </c>
       <c r="O504" t="n">
-        <v>32299.54</v>
+        <v>8924.280000000001</v>
       </c>
       <c r="P504" t="n">
-        <v>51900</v>
+        <v>14500</v>
       </c>
       <c r="Q504" t="n">
-        <v>363300</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>T181</t>
+          <t>T175</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
+          <t>PELUCHE BOWSER 35CM KUP-35</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -23614,7 +23614,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -23623,30 +23623,30 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N505" t="n">
-        <v>11692.75</v>
+        <v>4614.22</v>
       </c>
       <c r="O505" t="n">
-        <v>23385.5</v>
+        <v>32299.54</v>
       </c>
       <c r="P505" t="n">
-        <v>28500</v>
+        <v>51900</v>
       </c>
       <c r="Q505" t="n">
-        <v>57000</v>
+        <v>363300</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>T182</t>
+          <t>T181</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
+          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -23660,7 +23660,7 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
@@ -23669,30 +23669,30 @@
         <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N506" t="n">
-        <v>5600.5</v>
+        <v>11692.75</v>
       </c>
       <c r="O506" t="n">
-        <v>5600.5</v>
+        <v>23385.5</v>
       </c>
       <c r="P506" t="n">
-        <v>14000</v>
+        <v>28500</v>
       </c>
       <c r="Q506" t="n">
-        <v>14000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>T185</t>
+          <t>T182</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
+          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -23706,7 +23706,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -23715,30 +23715,30 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N507" t="n">
-        <v>9160.5</v>
+        <v>5600.5</v>
       </c>
       <c r="O507" t="n">
-        <v>45802.5</v>
+        <v>5600.5</v>
       </c>
       <c r="P507" t="n">
-        <v>22900</v>
+        <v>14000</v>
       </c>
       <c r="Q507" t="n">
-        <v>114500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>T195</t>
+          <t>T185</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
+          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -23752,7 +23752,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -23761,30 +23761,30 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N508" t="n">
-        <v>9192.809999999999</v>
+        <v>9160.5</v>
       </c>
       <c r="O508" t="n">
-        <v>9192.809999999999</v>
+        <v>45802.5</v>
       </c>
       <c r="P508" t="n">
-        <v>23900</v>
+        <v>22900</v>
       </c>
       <c r="Q508" t="n">
-        <v>23900</v>
+        <v>114500</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>T201-LJ</t>
+          <t>T195</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
+          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -23798,7 +23798,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -23807,35 +23807,35 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N509" t="n">
-        <v>35000</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="O509" t="n">
-        <v>70000</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="P509" t="n">
-        <v>45500</v>
+        <v>23900</v>
       </c>
       <c r="Q509" t="n">
-        <v>91000</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>T203</t>
+          <t>T201-LJ</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
+          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23853,30 +23853,30 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N510" t="n">
-        <v>11885.11</v>
+        <v>35000</v>
       </c>
       <c r="O510" t="n">
-        <v>11885.11</v>
+        <v>70000</v>
       </c>
       <c r="P510" t="n">
-        <v>30900</v>
+        <v>45500</v>
       </c>
       <c r="Q510" t="n">
-        <v>30900</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>T206</t>
+          <t>T203</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM HJE-30</t>
+          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -23890,7 +23890,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23899,35 +23899,35 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N511" t="n">
-        <v>31120</v>
+        <v>11885.11</v>
       </c>
       <c r="O511" t="n">
-        <v>62240</v>
+        <v>11885.11</v>
       </c>
       <c r="P511" t="n">
-        <v>38900</v>
+        <v>30900</v>
       </c>
       <c r="Q511" t="n">
-        <v>77800</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>T207</t>
+          <t>T206</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
+          <t>PELUCHE PATO 30CM HJE-30</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -23948,27 +23948,27 @@
         <v>2</v>
       </c>
       <c r="N512" t="n">
-        <v>7520.71</v>
+        <v>31120</v>
       </c>
       <c r="O512" t="n">
-        <v>15041.42</v>
+        <v>62240</v>
       </c>
       <c r="P512" t="n">
-        <v>32900</v>
+        <v>38900</v>
       </c>
       <c r="Q512" t="n">
-        <v>65800</v>
+        <v>77800</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>T211</t>
+          <t>T207</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
+          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -23994,27 +23994,27 @@
         <v>2</v>
       </c>
       <c r="N513" t="n">
-        <v>16500.5</v>
+        <v>7520.71</v>
       </c>
       <c r="O513" t="n">
-        <v>33001</v>
+        <v>15041.42</v>
       </c>
       <c r="P513" t="n">
-        <v>42900</v>
+        <v>32900</v>
       </c>
       <c r="Q513" t="n">
-        <v>85800</v>
+        <v>65800</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>T213</t>
+          <t>T211</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
+          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -24028,7 +24028,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -24037,30 +24037,30 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N514" t="n">
-        <v>16220.2125</v>
+        <v>16500.5</v>
       </c>
       <c r="O514" t="n">
-        <v>64880.85</v>
+        <v>33001</v>
       </c>
       <c r="P514" t="n">
-        <v>36900</v>
+        <v>42900</v>
       </c>
       <c r="Q514" t="n">
-        <v>147600</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>T214</t>
+          <t>T213</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
+          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -24074,7 +24074,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -24083,30 +24083,30 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N515" t="n">
-        <v>11885.11</v>
+        <v>16220.2125</v>
       </c>
       <c r="O515" t="n">
-        <v>11885.11</v>
+        <v>64880.85</v>
       </c>
       <c r="P515" t="n">
-        <v>30900</v>
+        <v>36900</v>
       </c>
       <c r="Q515" t="n">
-        <v>30900</v>
+        <v>147600</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>T216</t>
+          <t>T214</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
+          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -24120,7 +24120,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -24129,30 +24129,30 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N516" t="n">
-        <v>14760.5</v>
+        <v>11885.11</v>
       </c>
       <c r="O516" t="n">
-        <v>73802.5</v>
+        <v>11885.11</v>
       </c>
       <c r="P516" t="n">
-        <v>36900</v>
+        <v>30900</v>
       </c>
       <c r="Q516" t="n">
-        <v>184500</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>T217</t>
+          <t>T216</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>PELUCHE GATO TELA 30CM BQM-30</t>
+          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -24166,7 +24166,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -24175,34 +24175,44 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N517" t="n">
-        <v>8462.040000000001</v>
+        <v>14760.5</v>
       </c>
       <c r="O517" t="n">
-        <v>50772.24000000001</v>
+        <v>73802.5</v>
       </c>
       <c r="P517" t="n">
-        <v>22000</v>
+        <v>36900</v>
       </c>
       <c r="Q517" t="n">
-        <v>132000</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>T222</t>
+          <t>T217</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
+          <t>PELUCHE GATO TELA 30CM BQM-30</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J518" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -24211,40 +24221,30 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N518" t="n">
-        <v>23461.54</v>
+        <v>8462.040000000001</v>
       </c>
       <c r="O518" t="n">
-        <v>23461.54</v>
+        <v>50772.24000000001</v>
       </c>
       <c r="P518" t="n">
-        <v>30500</v>
+        <v>22000</v>
       </c>
       <c r="Q518" t="n">
-        <v>30500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>T229</t>
+          <t>T222</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
-        </is>
-      </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I519" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
         </is>
       </c>
       <c r="J519" t="n">
@@ -24260,27 +24260,27 @@
         <v>1</v>
       </c>
       <c r="N519" t="n">
-        <v>18600.5</v>
+        <v>23461.54</v>
       </c>
       <c r="O519" t="n">
-        <v>18600.5</v>
+        <v>23461.54</v>
       </c>
       <c r="P519" t="n">
-        <v>46500</v>
+        <v>30500</v>
       </c>
       <c r="Q519" t="n">
-        <v>46500</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>T243</t>
+          <t>T229</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>PELUCHE GATO 40CM DX-60</t>
+          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -24306,27 +24306,27 @@
         <v>1</v>
       </c>
       <c r="N520" t="n">
-        <v>26000</v>
+        <v>18600.5</v>
       </c>
       <c r="O520" t="n">
-        <v>26000</v>
+        <v>18600.5</v>
       </c>
       <c r="P520" t="n">
-        <v>32500</v>
+        <v>46500</v>
       </c>
       <c r="Q520" t="n">
-        <v>32500</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>T244</t>
+          <t>T243</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
+          <t>PELUCHE GATO 40CM DX-60</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -24349,30 +24349,30 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N521" t="n">
-        <v>7400.5</v>
+        <v>26000</v>
       </c>
       <c r="O521" t="n">
-        <v>22201.5</v>
+        <v>26000</v>
       </c>
       <c r="P521" t="n">
-        <v>18500</v>
+        <v>32500</v>
       </c>
       <c r="Q521" t="n">
-        <v>55500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>T245</t>
+          <t>T244</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -24386,7 +24386,7 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
@@ -24395,30 +24395,30 @@
         <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N522" t="n">
-        <v>25200</v>
+        <v>7400.5</v>
       </c>
       <c r="O522" t="n">
-        <v>25200</v>
+        <v>22201.5</v>
       </c>
       <c r="P522" t="n">
-        <v>31500</v>
+        <v>18500</v>
       </c>
       <c r="Q522" t="n">
-        <v>31500</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>T247</t>
+          <t>T245</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
+          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -24441,30 +24441,30 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N523" t="n">
-        <v>8667.34</v>
+        <v>25200</v>
       </c>
       <c r="O523" t="n">
-        <v>34669.36</v>
+        <v>25200</v>
       </c>
       <c r="P523" t="n">
-        <v>32500</v>
+        <v>31500</v>
       </c>
       <c r="Q523" t="n">
-        <v>130000</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>T248</t>
+          <t>T247</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
+          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -24478,7 +24478,7 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -24487,30 +24487,30 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N524" t="n">
-        <v>40720</v>
+        <v>8667.34</v>
       </c>
       <c r="O524" t="n">
-        <v>81440</v>
+        <v>34669.36</v>
       </c>
       <c r="P524" t="n">
-        <v>50900</v>
+        <v>32500</v>
       </c>
       <c r="Q524" t="n">
-        <v>101800</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>T250</t>
+          <t>T248</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO 40CM PCO-40</t>
+          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="J525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -24533,30 +24533,30 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N525" t="n">
-        <v>29520</v>
+        <v>40720</v>
       </c>
       <c r="O525" t="n">
-        <v>88560</v>
+        <v>81440</v>
       </c>
       <c r="P525" t="n">
-        <v>36900</v>
+        <v>50900</v>
       </c>
       <c r="Q525" t="n">
-        <v>110700</v>
+        <v>101800</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>T272</t>
+          <t>T250</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>PELUCHE BUHO 40CM MTY-40</t>
+          <t>PELUCHE MAGO 40CM PCO-40</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -24570,7 +24570,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24579,30 +24579,30 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N526" t="n">
-        <v>12500.5</v>
+        <v>29520</v>
       </c>
       <c r="O526" t="n">
-        <v>12500.5</v>
+        <v>88560</v>
       </c>
       <c r="P526" t="n">
-        <v>32500</v>
+        <v>36900</v>
       </c>
       <c r="Q526" t="n">
-        <v>32500</v>
+        <v>110700</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>T273</t>
+          <t>T272</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
+          <t>PELUCHE BUHO 40CM MTY-40</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -24628,27 +24628,37 @@
         <v>1</v>
       </c>
       <c r="N527" t="n">
-        <v>13808.19</v>
+        <v>12500.5</v>
       </c>
       <c r="O527" t="n">
-        <v>13808.19</v>
+        <v>12500.5</v>
       </c>
       <c r="P527" t="n">
-        <v>35900</v>
+        <v>32500</v>
       </c>
       <c r="Q527" t="n">
-        <v>35900</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>T300</t>
+          <t>T273</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
+          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J528" t="n">
@@ -24664,37 +24674,27 @@
         <v>1</v>
       </c>
       <c r="N528" t="n">
-        <v>13686.31</v>
+        <v>13808.19</v>
       </c>
       <c r="O528" t="n">
-        <v>13686.31</v>
+        <v>13808.19</v>
       </c>
       <c r="P528" t="n">
-        <v>30500</v>
+        <v>35900</v>
       </c>
       <c r="Q528" t="n">
-        <v>30500</v>
+        <v>35900</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>T308</t>
+          <t>T300</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMAL ACOSTADO DISFRAZ 25CM DT230918-25</t>
-        </is>
-      </c>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I529" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
         </is>
       </c>
       <c r="J529" t="n">
@@ -24710,31 +24710,41 @@
         <v>1</v>
       </c>
       <c r="N529" t="n">
-        <v>4808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="O529" t="n">
-        <v>4808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="P529" t="n">
-        <v>12500</v>
+        <v>30500</v>
       </c>
       <c r="Q529" t="n">
-        <v>12500</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>T334</t>
+          <t>T308</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>PELUCHE DIGIMON 20CM MD-20</t>
+          <t>PELUCHE ANIMAL ACOSTADO DISFRAZ 25CM DT230918-25</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J530" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24743,34 +24753,34 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N530" t="n">
-        <v>7571.81</v>
+        <v>4808.19</v>
       </c>
       <c r="O530" t="n">
-        <v>45430.86</v>
+        <v>4808.19</v>
       </c>
       <c r="P530" t="n">
-        <v>15900</v>
+        <v>12500</v>
       </c>
       <c r="Q530" t="n">
-        <v>95400</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>T336</t>
+          <t>T334</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
+          <t>PELUCHE DIGIMON 20CM MD-20</t>
         </is>
       </c>
       <c r="J531" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24779,44 +24789,34 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N531" t="n">
-        <v>9962.040000000001</v>
+        <v>7571.81</v>
       </c>
       <c r="O531" t="n">
-        <v>19924.08</v>
+        <v>45430.86</v>
       </c>
       <c r="P531" t="n">
-        <v>25900</v>
+        <v>15900</v>
       </c>
       <c r="Q531" t="n">
-        <v>51800</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>T345</t>
+          <t>T336</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>PELUCHE ADVNG 20CM ESP-20</t>
-        </is>
-      </c>
-      <c r="E532" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I532" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
         </is>
       </c>
       <c r="J532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24825,30 +24825,35 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N532" t="n">
-        <v>1250.88</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O532" t="n">
-        <v>3752.64</v>
+        <v>19924.08</v>
       </c>
       <c r="P532" t="n">
-        <v>12500</v>
+        <v>25900</v>
       </c>
       <c r="Q532" t="n">
-        <v>37500</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>T352</t>
+          <t>T345</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>NINJA T352</t>
+          <t>PELUCHE ADVNG 20CM ESP-20</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -24857,7 +24862,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24866,35 +24871,30 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N533" t="n">
-        <v>5192.31</v>
+        <v>1250.88</v>
       </c>
       <c r="O533" t="n">
-        <v>5192.31</v>
+        <v>3752.64</v>
       </c>
       <c r="P533" t="n">
-        <v>13500</v>
+        <v>12500</v>
       </c>
       <c r="Q533" t="n">
-        <v>13500</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>TB058</t>
+          <t>T352</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
-        </is>
-      </c>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>NINJA T352</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -24903,7 +24903,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24912,35 +24912,35 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N534" t="n">
-        <v>17159.86</v>
+        <v>5192.31</v>
       </c>
       <c r="O534" t="n">
-        <v>51479.58</v>
+        <v>5192.31</v>
       </c>
       <c r="P534" t="n">
-        <v>21900</v>
+        <v>13500</v>
       </c>
       <c r="Q534" t="n">
-        <v>65700</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>TO-030</t>
+          <t>TB058</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>COJIN ANIMALES 40CM DWKD-40</t>
+          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -24949,7 +24949,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24958,30 +24958,30 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N535" t="n">
-        <v>18384.62</v>
+        <v>17159.86</v>
       </c>
       <c r="O535" t="n">
-        <v>18384.62</v>
+        <v>51479.58</v>
       </c>
       <c r="P535" t="n">
-        <v>23900</v>
+        <v>21900</v>
       </c>
       <c r="Q535" t="n">
-        <v>23900</v>
+        <v>65700</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>TO-038</t>
+          <t>TO-030</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>COJIN ANIMAL 30CM DXS-25</t>
+          <t>COJIN ANIMALES 40CM DWKD-40</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -25007,61 +25007,107 @@
         <v>1</v>
       </c>
       <c r="N536" t="n">
-        <v>14800</v>
+        <v>18384.62</v>
       </c>
       <c r="O536" t="n">
-        <v>14800</v>
+        <v>18384.62</v>
       </c>
       <c r="P536" t="n">
-        <v>18500</v>
+        <v>23900</v>
       </c>
       <c r="Q536" t="n">
-        <v>18500</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
+          <t>TO-038</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>COJIN ANIMAL 30CM DXS-25</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J537" t="n">
+        <v>1</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0</v>
+      </c>
+      <c r="L537" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" t="n">
+        <v>1</v>
+      </c>
+      <c r="N537" t="n">
+        <v>14800</v>
+      </c>
+      <c r="O537" t="n">
+        <v>14800</v>
+      </c>
+      <c r="P537" t="n">
+        <v>18500</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
           <t>TO-041</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>PELUCHE ELMO COSQUILLAS A-88</t>
         </is>
       </c>
-      <c r="E537" t="inlineStr">
+      <c r="E538" t="inlineStr">
         <is>
           <t>JUGUETERIA</t>
         </is>
       </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J537" t="n">
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J538" t="n">
         <v>9</v>
       </c>
-      <c r="K537" t="n">
-        <v>0</v>
-      </c>
-      <c r="L537" t="n">
-        <v>0</v>
-      </c>
-      <c r="M537" t="n">
+      <c r="K538" t="n">
+        <v>0</v>
+      </c>
+      <c r="L538" t="n">
+        <v>0</v>
+      </c>
+      <c r="M538" t="n">
         <v>9</v>
       </c>
-      <c r="N537" t="n">
+      <c r="N538" t="n">
         <v>2372.36</v>
       </c>
-      <c r="O537" t="n">
+      <c r="O538" t="n">
         <v>21351.24</v>
       </c>
-      <c r="P537" t="n">
+      <c r="P538" t="n">
         <v>41500</v>
       </c>
-      <c r="Q537" t="n">
+      <c r="Q538" t="n">
         <v>373500</v>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3541,10 +3541,10 @@
         <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O73" t="n">
-        <v>2386004.052040963</v>
+        <v>2386004.046315767</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3866,10 +3866,10 @@
         <v>150</v>
       </c>
       <c r="N80" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O80" t="n">
-        <v>1126108.5</v>
+        <v>1127729.966522685</v>
       </c>
       <c r="P80" t="n">
         <v>13500</v>
@@ -3964,10 +3964,10 @@
         <v>20</v>
       </c>
       <c r="N82" t="n">
-        <v>8796</v>
+        <v>8831.230974632799</v>
       </c>
       <c r="O82" t="n">
-        <v>175920</v>
+        <v>176624.619492656</v>
       </c>
       <c r="P82" t="n">
         <v>14900</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4635785544</v>
+        <v>35654.4636196117</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -8794,10 +8794,10 @@
         <v>85</v>
       </c>
       <c r="N190" t="n">
-        <v>10713.21</v>
+        <v>10792.371650246</v>
       </c>
       <c r="O190" t="n">
-        <v>910622.85</v>
+        <v>917351.5902709099</v>
       </c>
       <c r="P190" t="n">
         <v>20900</v>
@@ -9070,10 +9070,10 @@
         <v>266</v>
       </c>
       <c r="N196" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O196" t="n">
-        <v>479602.2370199424</v>
+        <v>479602.2381238956</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9528,10 +9528,10 @@
         <v>2</v>
       </c>
       <c r="N206" t="n">
-        <v>1906.180625</v>
+        <v>1906.1803846154</v>
       </c>
       <c r="O206" t="n">
-        <v>3812.36125</v>
+        <v>3812.3607692308</v>
       </c>
       <c r="P206" t="n">
         <v>2900</v>
@@ -11355,10 +11355,10 @@
         <v>12218</v>
       </c>
       <c r="N245" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O245" t="n">
-        <v>8598966.949508032</v>
+        <v>8598966.942578228</v>
       </c>
       <c r="P245" t="n">
         <v>900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3541,10 +3541,10 @@
         <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O73" t="n">
-        <v>2387653.692555886</v>
+        <v>2386003.99799029</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3587,10 +3587,10 @@
         <v>1352</v>
       </c>
       <c r="N74" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O74" t="n">
-        <v>7053243.407123878</v>
+        <v>7053243.404741519</v>
       </c>
       <c r="P74" t="n">
         <v>8500</v>
@@ -3679,10 +3679,10 @@
         <v>3410</v>
       </c>
       <c r="N76" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O76" t="n">
-        <v>10780218.02320193</v>
+        <v>10771715.4380216</v>
       </c>
       <c r="P76" t="n">
         <v>5600</v>
@@ -3964,10 +3964,10 @@
         <v>20</v>
       </c>
       <c r="N82" t="n">
-        <v>8807.775100401601</v>
+        <v>8796</v>
       </c>
       <c r="O82" t="n">
-        <v>176155.502008032</v>
+        <v>175920</v>
       </c>
       <c r="P82" t="n">
         <v>14900</v>
@@ -4105,10 +4105,10 @@
         <v>301</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O85" t="n">
-        <v>1081870.327157185</v>
+        <v>1081870.325863457</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4151,10 +4151,10 @@
         <v>275</v>
       </c>
       <c r="N86" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O86" t="n">
-        <v>4083578.86885245</v>
+        <v>4076154.1794171</v>
       </c>
       <c r="P86" t="n">
         <v>24900</v>
@@ -4462,10 +4462,10 @@
         <v>317</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O93" t="n">
-        <v>1385990.821277721</v>
+        <v>1386784.51680889</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -5003,10 +5003,10 @@
         <v>26</v>
       </c>
       <c r="N105" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O105" t="n">
-        <v>310432.523502296</v>
+        <v>309956.4</v>
       </c>
       <c r="P105" t="n">
         <v>19900</v>
@@ -5052,10 +5052,10 @@
         <v>9</v>
       </c>
       <c r="N106" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O106" t="n">
-        <v>89334.59394409919</v>
+        <v>89127</v>
       </c>
       <c r="P106" t="n">
         <v>15900</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.464542535</v>
+        <v>35654.4682989755</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -6485,10 +6485,10 @@
         <v>4</v>
       </c>
       <c r="N139" t="n">
-        <v>11594.607549296</v>
+        <v>11562.038422535</v>
       </c>
       <c r="O139" t="n">
-        <v>46378.430197184</v>
+        <v>46248.15369014</v>
       </c>
       <c r="P139" t="n">
         <v>18500</v>
@@ -8288,10 +8288,10 @@
         <v>153</v>
       </c>
       <c r="N179" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O179" t="n">
-        <v>2081801.646248112</v>
+        <v>2075445</v>
       </c>
       <c r="P179" t="n">
         <v>22500</v>
@@ -8334,10 +8334,10 @@
         <v>382</v>
       </c>
       <c r="N180" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O180" t="n">
-        <v>2921458.106145261</v>
+        <v>2916570</v>
       </c>
       <c r="P180" t="n">
         <v>13900</v>
@@ -8380,10 +8380,10 @@
         <v>154</v>
       </c>
       <c r="N181" t="n">
-        <v>5690.8504672897</v>
+        <v>5682</v>
       </c>
       <c r="O181" t="n">
-        <v>876390.9719626138</v>
+        <v>875028</v>
       </c>
       <c r="P181" t="n">
         <v>9900</v>
@@ -8426,10 +8426,10 @@
         <v>22</v>
       </c>
       <c r="N182" t="n">
-        <v>5465.19</v>
+        <v>5438</v>
       </c>
       <c r="O182" t="n">
-        <v>120234.18</v>
+        <v>119636</v>
       </c>
       <c r="P182" t="n">
         <v>8900</v>
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.2821517241</v>
+        <v>1789.7745116279</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.2821517241</v>
+        <v>1789.7745116279</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -11081,10 +11081,10 @@
         <v>504</v>
       </c>
       <c r="N239" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O239" t="n">
-        <v>1567863.280344816</v>
+        <v>1567863.258181819</v>
       </c>
       <c r="P239" t="n">
         <v>4500</v>
@@ -14382,10 +14382,10 @@
         <v>60</v>
       </c>
       <c r="N308" t="n">
-        <v>3098.3874489796</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O308" t="n">
-        <v>185903.246938776</v>
+        <v>184025.436734694</v>
       </c>
       <c r="P308" t="n">
         <v>7200</v>
@@ -15302,10 +15302,10 @@
         <v>1</v>
       </c>
       <c r="N327" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="O327" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="P327" t="n">
         <v>18900</v>
@@ -20715,10 +20715,10 @@
         <v>36</v>
       </c>
       <c r="N442" t="n">
-        <v>3088.1445833333</v>
+        <v>3088.1452173913</v>
       </c>
       <c r="O442" t="n">
-        <v>111173.2049999988</v>
+        <v>111173.2278260868</v>
       </c>
       <c r="P442" t="n">
         <v>8500</v>
@@ -22026,10 +22026,10 @@
         <v>24</v>
       </c>
       <c r="N470" t="n">
-        <v>7046.7388888889</v>
+        <v>7046.7392307692</v>
       </c>
       <c r="O470" t="n">
-        <v>169121.7333333336</v>
+        <v>169121.7415384608</v>
       </c>
       <c r="P470" t="n">
         <v>22900</v>
@@ -22302,10 +22302,10 @@
         <v>180</v>
       </c>
       <c r="N476" t="n">
-        <v>4566.0211267606</v>
+        <v>4550</v>
       </c>
       <c r="O476" t="n">
-        <v>821883.802816908</v>
+        <v>819000</v>
       </c>
       <c r="P476" t="n">
         <v>5500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3541,10 +3541,10 @@
         <v>924</v>
       </c>
       <c r="N73" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O73" t="n">
-        <v>2386003.992116329</v>
+        <v>2386003.989173204</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3774,10 +3774,10 @@
         <v>30</v>
       </c>
       <c r="N78" t="n">
-        <v>3230.0666176471</v>
+        <v>3230.0665925926</v>
       </c>
       <c r="O78" t="n">
-        <v>96901.998529413</v>
+        <v>96901.997777778</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -5003,10 +5003,10 @@
         <v>11</v>
       </c>
       <c r="N105" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O105" t="n">
-        <v>131135.4</v>
+        <v>131442.269110768</v>
       </c>
       <c r="P105" t="n">
         <v>19900</v>
@@ -5234,10 +5234,10 @@
         <v>636</v>
       </c>
       <c r="N110" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O110" t="n">
-        <v>1037267.708430833</v>
+        <v>1037267.709801413</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O111" t="n">
-        <v>35654.4657838634</v>
+        <v>35654.4658376374</v>
       </c>
       <c r="P111" t="n">
         <v>2500</v>
@@ -9392,10 +9392,10 @@
         <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>1592.2821517241</v>
+        <v>1592.2821853389</v>
       </c>
       <c r="O203" t="n">
-        <v>1592.2821517241</v>
+        <v>1592.2821853389</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -11081,10 +11081,10 @@
         <v>378</v>
       </c>
       <c r="N239" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O239" t="n">
-        <v>1175897.407690076</v>
+        <v>1175897.400875417</v>
       </c>
       <c r="P239" t="n">
         <v>4500</v>
@@ -12498,22 +12498,22 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M269" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="N269" t="n">
         <v>3057.26</v>
       </c>
       <c r="O269" t="n">
-        <v>272096.14</v>
+        <v>110061.36</v>
       </c>
       <c r="P269" t="n">
         <v>4900</v>
       </c>
       <c r="Q269" t="n">
-        <v>436100</v>
+        <v>176400</v>
       </c>
     </row>
     <row r="270">

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -11035,10 +11035,10 @@
         <v>378</v>
       </c>
       <c r="N238" t="n">
-        <v>3110.8396334311</v>
+        <v>3110.8396273474</v>
       </c>
       <c r="O238" t="n">
-        <v>1175897.381436956</v>
+        <v>1175897.379137317</v>
       </c>
       <c r="P238" t="n">
         <v>4500</v>
@@ -11263,10 +11263,10 @@
         <v>11930</v>
       </c>
       <c r="N243" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O243" t="n">
-        <v>8396272.97657772</v>
+        <v>8396272.961022669</v>
       </c>
       <c r="P243" t="n">
         <v>900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q534"/>
+  <dimension ref="A1:Q532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>27000</v>
+        <v>27117.391304348</v>
       </c>
       <c r="O6" t="n">
-        <v>324000</v>
+        <v>325408.695652176</v>
       </c>
       <c r="P6" t="n">
         <v>30000</v>
@@ -1082,10 +1082,10 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>2413.0010857763</v>
+        <v>2413.0010952903</v>
       </c>
       <c r="O17" t="n">
-        <v>4826.0021715526</v>
+        <v>4826.0021905806</v>
       </c>
       <c r="P17" t="n">
         <v>4700</v>
@@ -1121,10 +1121,10 @@
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2474.7039826087</v>
+        <v>2474.703951049</v>
       </c>
       <c r="O18" t="n">
-        <v>9898.815930434799</v>
+        <v>9898.815804196</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -3008,10 +3008,10 @@
         <v>92</v>
       </c>
       <c r="N61" t="n">
-        <v>732.6342857142899</v>
+        <v>732.63431654676</v>
       </c>
       <c r="O61" t="n">
-        <v>67402.35428571468</v>
+        <v>67402.35712230192</v>
       </c>
       <c r="P61" t="n">
         <v>6200</v>
@@ -3495,10 +3495,10 @@
         <v>924</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2552</v>
+        <v>2582.2551814224</v>
       </c>
       <c r="O72" t="n">
-        <v>2386003.8048</v>
+        <v>2386003.787634297</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3541,10 +3541,10 @@
         <v>1352</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8959994095</v>
+        <v>5224.6087374335</v>
       </c>
       <c r="O73" t="n">
-        <v>7053243.391201644</v>
+        <v>7063671.013010092</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -3633,10 +3633,10 @@
         <v>3410</v>
       </c>
       <c r="N75" t="n">
-        <v>3158.8608346114</v>
+        <v>3158.8608347353</v>
       </c>
       <c r="O75" t="n">
-        <v>10771715.44602487</v>
+        <v>10771715.44644737</v>
       </c>
       <c r="P75" t="n">
         <v>5600</v>
@@ -3728,10 +3728,10 @@
         <v>30</v>
       </c>
       <c r="N77" t="n">
-        <v>3230.0665756824</v>
+        <v>3230.06655</v>
       </c>
       <c r="O77" t="n">
-        <v>96901.997270472</v>
+        <v>96901.99649999999</v>
       </c>
       <c r="P77" t="n">
         <v>6200</v>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -4056,19 +4056,19 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2535397039</v>
+        <v>3594.2534111187</v>
       </c>
       <c r="O84" t="n">
-        <v>1081870.315450874</v>
+        <v>1009985.208524355</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
       </c>
       <c r="Q84" t="n">
-        <v>1956500</v>
+        <v>1826500</v>
       </c>
     </row>
     <row r="85">
@@ -4105,10 +4105,10 @@
         <v>275</v>
       </c>
       <c r="N85" t="n">
-        <v>14822.378830694</v>
+        <v>14831.411358927</v>
       </c>
       <c r="O85" t="n">
-        <v>4076154.17844085</v>
+        <v>4078638.123704925</v>
       </c>
       <c r="P85" t="n">
         <v>24900</v>
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712607216</v>
+        <v>4371.171261065</v>
       </c>
       <c r="O92" t="n">
-        <v>1385661.289648747</v>
+        <v>1385661.289757605</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -4549,10 +4549,10 @@
         <v>166</v>
       </c>
       <c r="N95" t="n">
-        <v>1592.5656339211</v>
+        <v>1592.5656302521</v>
       </c>
       <c r="O95" t="n">
-        <v>264365.8952309026</v>
+        <v>264365.8946218486</v>
       </c>
       <c r="P95" t="n">
         <v>3900</v>
@@ -4957,10 +4957,10 @@
         <v>11</v>
       </c>
       <c r="N104" t="n">
-        <v>11921.4</v>
+        <v>11959.066350711</v>
       </c>
       <c r="O104" t="n">
-        <v>131135.4</v>
+        <v>131549.729857821</v>
       </c>
       <c r="P104" t="n">
         <v>19900</v>
@@ -5188,10 +5188,10 @@
         <v>636</v>
       </c>
       <c r="N109" t="n">
-        <v>1630.924143319</v>
+        <v>1630.9241816204</v>
       </c>
       <c r="O109" t="n">
-        <v>1037267.755150884</v>
+        <v>1037267.779510574</v>
       </c>
       <c r="P109" t="n">
         <v>2500</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.1943181289</v>
+        <v>1550.1943423824</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.4693169647</v>
+        <v>35654.4698747952</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>72</v>
       </c>
       <c r="N111" t="n">
-        <v>1579.3874912892</v>
+        <v>1579.3866044776</v>
       </c>
       <c r="O111" t="n">
-        <v>113715.8993728224</v>
+        <v>113715.8355223872</v>
       </c>
       <c r="P111" t="n">
         <v>2900</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>2029.8740606389</v>
+        <v>2029.8740628386</v>
       </c>
       <c r="O129" t="n">
-        <v>4059.7481212778</v>
+        <v>4059.7481256772</v>
       </c>
       <c r="P129" t="n">
         <v>3600</v>
@@ -6106,10 +6106,10 @@
         <v>6</v>
       </c>
       <c r="N130" t="n">
-        <v>38630</v>
+        <v>39703.055555556</v>
       </c>
       <c r="O130" t="n">
-        <v>231780</v>
+        <v>238218.333333336</v>
       </c>
       <c r="P130" t="n">
         <v>46500</v>
@@ -6188,10 +6188,10 @@
         <v>402</v>
       </c>
       <c r="N132" t="n">
-        <v>880.3297635876201</v>
+        <v>880.32978266178</v>
       </c>
       <c r="O132" t="n">
-        <v>353892.5649622233</v>
+        <v>353892.5726300356</v>
       </c>
       <c r="P132" t="n">
         <v>1200</v>
@@ -6439,10 +6439,10 @@
         <v>4</v>
       </c>
       <c r="N138" t="n">
-        <v>11562.038422535</v>
+        <v>11594.699548023</v>
       </c>
       <c r="O138" t="n">
-        <v>46248.15369014</v>
+        <v>46378.798192092</v>
       </c>
       <c r="P138" t="n">
         <v>18500</v>
@@ -6785,10 +6785,10 @@
         <v>16</v>
       </c>
       <c r="N146" t="n">
-        <v>26854</v>
+        <v>27011.040935673</v>
       </c>
       <c r="O146" t="n">
-        <v>429664</v>
+        <v>432176.654970768</v>
       </c>
       <c r="P146" t="n">
         <v>43900</v>
@@ -6954,10 +6954,10 @@
         <v>5</v>
       </c>
       <c r="N150" t="n">
-        <v>7969.9501688411</v>
+        <v>7969.9501692308</v>
       </c>
       <c r="O150" t="n">
-        <v>39849.7508442055</v>
+        <v>39849.750846154</v>
       </c>
       <c r="P150" t="n">
         <v>12900</v>
@@ -7123,10 +7123,10 @@
         <v>13</v>
       </c>
       <c r="N154" t="n">
-        <v>12981.59</v>
+        <v>13079.564264151</v>
       </c>
       <c r="O154" t="n">
-        <v>168760.67</v>
+        <v>170034.335433963</v>
       </c>
       <c r="P154" t="n">
         <v>21900</v>
@@ -7586,10 +7586,10 @@
         <v>35</v>
       </c>
       <c r="N164" t="n">
-        <v>5218.1705744125</v>
+        <v>5218.1705789474</v>
       </c>
       <c r="O164" t="n">
-        <v>182635.9701044375</v>
+        <v>182635.970263159</v>
       </c>
       <c r="P164" t="n">
         <v>8500</v>
@@ -8610,10 +8610,10 @@
         <v>344</v>
       </c>
       <c r="N186" t="n">
-        <v>17075.989520833</v>
+        <v>17123.621290098</v>
       </c>
       <c r="O186" t="n">
-        <v>5874140.395166553</v>
+        <v>5890525.723793712</v>
       </c>
       <c r="P186" t="n">
         <v>27500</v>
@@ -8656,10 +8656,10 @@
         <v>4</v>
       </c>
       <c r="N187" t="n">
-        <v>17168</v>
+        <v>17325.987730061</v>
       </c>
       <c r="O187" t="n">
-        <v>68672</v>
+        <v>69303.95092024399</v>
       </c>
       <c r="P187" t="n">
         <v>27900</v>
@@ -8932,10 +8932,10 @@
         <v>144</v>
       </c>
       <c r="N193" t="n">
-        <v>1771.0896492484</v>
+        <v>1771.0894683176</v>
       </c>
       <c r="O193" t="n">
-        <v>255036.9094917696</v>
+        <v>255036.8834377344</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -9024,10 +9024,10 @@
         <v>266</v>
       </c>
       <c r="N195" t="n">
-        <v>1803.0162754535</v>
+        <v>1803.0162940958</v>
       </c>
       <c r="O195" t="n">
-        <v>479602.329270631</v>
+        <v>479602.3342294828</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9116,10 +9116,10 @@
         <v>264</v>
       </c>
       <c r="N197" t="n">
-        <v>2122.1635573123</v>
+        <v>2122.1635509397</v>
       </c>
       <c r="O197" t="n">
-        <v>560251.1791304472</v>
+        <v>560251.1774480809</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9162,10 +9162,10 @@
         <v>72</v>
       </c>
       <c r="N198" t="n">
-        <v>2108.7953562005</v>
+        <v>2108.7954376658</v>
       </c>
       <c r="O198" t="n">
-        <v>151833.265646436</v>
+        <v>151833.2715119376</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9254,10 +9254,10 @@
         <v>162</v>
       </c>
       <c r="N200" t="n">
-        <v>3224.5693083723</v>
+        <v>3224.5693375065</v>
       </c>
       <c r="O200" t="n">
-        <v>522380.2279563126</v>
+        <v>522380.232676053</v>
       </c>
       <c r="P200" t="n">
         <v>4500</v>
@@ -9300,10 +9300,10 @@
         <v>233</v>
       </c>
       <c r="N201" t="n">
-        <v>1655.9297971228</v>
+        <v>1655.9297403561</v>
       </c>
       <c r="O201" t="n">
-        <v>385831.6427296124</v>
+        <v>385831.6295029713</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9346,10 +9346,10 @@
         <v>1</v>
       </c>
       <c r="N202" t="n">
-        <v>1592.2823909986</v>
+        <v>1592.2824611033</v>
       </c>
       <c r="O202" t="n">
-        <v>1592.2823909986</v>
+        <v>1592.2824611033</v>
       </c>
       <c r="P202" t="n">
         <v>2500</v>
@@ -9436,10 +9436,10 @@
         <v>2</v>
       </c>
       <c r="N204" t="n">
-        <v>1906.1797959184</v>
+        <v>1906.1797260274</v>
       </c>
       <c r="O204" t="n">
-        <v>3812.3595918368</v>
+        <v>3812.3594520548</v>
       </c>
       <c r="P204" t="n">
         <v>2900</v>
@@ -9528,10 +9528,10 @@
         <v>600</v>
       </c>
       <c r="N206" t="n">
-        <v>1259.2747084888</v>
+        <v>1259.2747095871</v>
       </c>
       <c r="O206" t="n">
-        <v>755564.8250932799</v>
+        <v>755564.82575226</v>
       </c>
       <c r="P206" t="n">
         <v>1900</v>
@@ -9705,10 +9705,10 @@
         <v>192</v>
       </c>
       <c r="N210" t="n">
-        <v>692.1523548442</v>
+        <v>692.15238407171</v>
       </c>
       <c r="O210" t="n">
-        <v>132893.2521300864</v>
+        <v>132893.2577417683</v>
       </c>
       <c r="P210" t="n">
         <v>1200</v>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9797,19 +9797,19 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="N212" t="n">
         <v>1955.2371140003</v>
       </c>
       <c r="O212" t="n">
-        <v>5531365.795506849</v>
+        <v>5529410.558392848</v>
       </c>
       <c r="P212" t="n">
         <v>3000</v>
       </c>
       <c r="Q212" t="n">
-        <v>8487000</v>
+        <v>8484000</v>
       </c>
     </row>
     <row r="213">
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9843,19 +9843,19 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="N213" t="n">
         <v>1185.3195700703</v>
       </c>
       <c r="O213" t="n">
-        <v>3272667.332964098</v>
+        <v>3271482.013394028</v>
       </c>
       <c r="P213" t="n">
         <v>1900</v>
       </c>
       <c r="Q213" t="n">
-        <v>5245900</v>
+        <v>5244000</v>
       </c>
     </row>
     <row r="214">
@@ -10180,10 +10180,10 @@
         <v>324</v>
       </c>
       <c r="N220" t="n">
-        <v>1530.4499189299</v>
+        <v>1530.449918633</v>
       </c>
       <c r="O220" t="n">
-        <v>495865.7737332876</v>
+        <v>495865.773637092</v>
       </c>
       <c r="P220" t="n">
         <v>2600</v>
@@ -10551,10 +10551,10 @@
         <v>1</v>
       </c>
       <c r="N228" t="n">
-        <v>1690.8700092807</v>
+        <v>1690.8700092894</v>
       </c>
       <c r="O228" t="n">
-        <v>1690.8700092807</v>
+        <v>1690.8700092894</v>
       </c>
       <c r="P228" t="n">
         <v>3000</v>
@@ -11035,10 +11035,10 @@
         <v>378</v>
       </c>
       <c r="N238" t="n">
-        <v>3110.8396273474</v>
+        <v>3110.8392324094</v>
       </c>
       <c r="O238" t="n">
-        <v>1175897.379137317</v>
+        <v>1175897.229850753</v>
       </c>
       <c r="P238" t="n">
         <v>4500</v>
@@ -11263,10 +11263,10 @@
         <v>11930</v>
       </c>
       <c r="N243" t="n">
-        <v>703.79488357273</v>
+        <v>703.79485280542</v>
       </c>
       <c r="O243" t="n">
-        <v>8396272.961022669</v>
+        <v>8396272.59396866</v>
       </c>
       <c r="P243" t="n">
         <v>900</v>
@@ -11542,10 +11542,10 @@
         <v>59</v>
       </c>
       <c r="N249" t="n">
-        <v>2501.3846268657</v>
+        <v>2501.3845728643</v>
       </c>
       <c r="O249" t="n">
-        <v>147581.6929850763</v>
+        <v>147581.6897989937</v>
       </c>
       <c r="P249" t="n">
         <v>4100</v>
@@ -12170,10 +12170,10 @@
         <v>71</v>
       </c>
       <c r="N262" t="n">
-        <v>2098.4051183432</v>
+        <v>2098.4051335312</v>
       </c>
       <c r="O262" t="n">
-        <v>148986.7634023672</v>
+        <v>148986.7644807152</v>
       </c>
       <c r="P262" t="n">
         <v>9500</v>
@@ -12268,10 +12268,10 @@
         <v>63</v>
       </c>
       <c r="N264" t="n">
-        <v>10548.76</v>
+        <v>10639.697586207</v>
       </c>
       <c r="O264" t="n">
-        <v>664571.88</v>
+        <v>670300.947931041</v>
       </c>
       <c r="P264" t="n">
         <v>35900</v>
@@ -12507,10 +12507,10 @@
         <v>5</v>
       </c>
       <c r="N269" t="n">
-        <v>2832.1951515152</v>
+        <v>2832.1952307692</v>
       </c>
       <c r="O269" t="n">
-        <v>14160.975757576</v>
+        <v>14160.976153846</v>
       </c>
       <c r="P269" t="n">
         <v>12900</v>
@@ -15014,10 +15014,10 @@
         <v>214</v>
       </c>
       <c r="N321" t="n">
-        <v>2356.29</v>
+        <v>2830.7108053691</v>
       </c>
       <c r="O321" t="n">
-        <v>504246.06</v>
+        <v>605772.1123489874</v>
       </c>
       <c r="P321" t="n">
         <v>6500</v>
@@ -15342,7 +15342,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15351,19 +15351,19 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N328" t="n">
         <v>11939.92</v>
       </c>
       <c r="O328" t="n">
-        <v>143279.04</v>
+        <v>71639.52</v>
       </c>
       <c r="P328" t="n">
         <v>25900</v>
       </c>
       <c r="Q328" t="n">
-        <v>310800</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="329">
@@ -16368,17 +16368,20 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>C7511</t>
-        </is>
+          <t>C7513</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>6905698382824</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA C7511</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -16387,7 +16390,7 @@
         </is>
       </c>
       <c r="J350" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
@@ -16396,33 +16399,33 @@
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="N350" t="n">
-        <v>6064.2616666667</v>
+        <v>1024.29</v>
       </c>
       <c r="O350" t="n">
-        <v>12128.5233333334</v>
+        <v>91161.81</v>
       </c>
       <c r="P350" t="n">
-        <v>16100</v>
+        <v>2900</v>
       </c>
       <c r="Q350" t="n">
-        <v>32200</v>
+        <v>258100</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C7514</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>6905698382824</v>
+        <v>6905698386815</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
+          <t>SONAJERO LUZ BOLSA C7514</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -16436,7 +16439,7 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>89</v>
+        <v>496</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
@@ -16445,33 +16448,33 @@
         <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>89</v>
+        <v>496</v>
       </c>
       <c r="N351" t="n">
-        <v>1024.29</v>
+        <v>711.48</v>
       </c>
       <c r="O351" t="n">
-        <v>91161.81</v>
+        <v>352894.08</v>
       </c>
       <c r="P351" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q351" t="n">
-        <v>258100</v>
+        <v>1240000</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>C7514</t>
+          <t>C7515</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>6905698386815</v>
+        <v>6920240711013</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ BOLSA C7514</t>
+          <t>ATARY AGUA OSO GOMELO C7515</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -16485,7 +16488,7 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -16494,38 +16497,38 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="N352" t="n">
-        <v>711.48</v>
+        <v>2391.79</v>
       </c>
       <c r="O352" t="n">
-        <v>352894.08</v>
+        <v>2391.79</v>
       </c>
       <c r="P352" t="n">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="Q352" t="n">
-        <v>1240000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>C7515</t>
+          <t>C7523</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>6920240711013</v>
+        <v>6905454130812</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>ATARY AGUA OSO GOMELO C7515</t>
+          <t>CARRO TRUCK BEBE X3 C7523</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -16534,7 +16537,7 @@
         </is>
       </c>
       <c r="J353" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
@@ -16543,33 +16546,33 @@
         <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N353" t="n">
-        <v>2391.79</v>
+        <v>3113.75</v>
       </c>
       <c r="O353" t="n">
-        <v>2391.79</v>
+        <v>52933.75</v>
       </c>
       <c r="P353" t="n">
-        <v>3200</v>
+        <v>10500</v>
       </c>
       <c r="Q353" t="n">
-        <v>3200</v>
+        <v>178500</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>C7523</t>
+          <t>C7524</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>6905454130812</v>
+        <v>6905454130201</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>CARRO TRUCK BEBE X3 C7523</t>
+          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -16583,7 +16586,7 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -16592,38 +16595,38 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="N354" t="n">
-        <v>3113.75</v>
+        <v>1934.77</v>
       </c>
       <c r="O354" t="n">
-        <v>52933.75</v>
+        <v>96738.5</v>
       </c>
       <c r="P354" t="n">
-        <v>10500</v>
+        <v>8900</v>
       </c>
       <c r="Q354" t="n">
-        <v>178500</v>
+        <v>445000</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>C7524</t>
+          <t>C7527</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>6905454130201</v>
+        <v>8823306251417</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
+          <t>ARCO Y FLECHA BLISTER SENCILLO C7527</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -16632,7 +16635,7 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="K355" t="n">
         <v>0</v>
@@ -16641,33 +16644,33 @@
         <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="N355" t="n">
-        <v>1934.77</v>
+        <v>7465.9</v>
       </c>
       <c r="O355" t="n">
-        <v>96738.5</v>
+        <v>119454.4</v>
       </c>
       <c r="P355" t="n">
-        <v>8900</v>
+        <v>11900</v>
       </c>
       <c r="Q355" t="n">
-        <v>445000</v>
+        <v>190400</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>C7527</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>8823306251417</v>
+        <v>6923669699979</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA BLISTER SENCILLO C7527</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -16681,7 +16684,7 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>16</v>
+        <v>5000</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
@@ -16690,33 +16693,33 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>16</v>
+        <v>5000</v>
       </c>
       <c r="N356" t="n">
-        <v>7465.9</v>
+        <v>509.69</v>
       </c>
       <c r="O356" t="n">
-        <v>119454.4</v>
+        <v>2548450</v>
       </c>
       <c r="P356" t="n">
-        <v>11900</v>
+        <v>750</v>
       </c>
       <c r="Q356" t="n">
-        <v>190400</v>
+        <v>3750000</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>C7533</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>6923669699979</v>
+        <v>6951241752002</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -16730,7 +16733,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>5000</v>
+        <v>8</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -16739,38 +16742,38 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>5000</v>
+        <v>8</v>
       </c>
       <c r="N357" t="n">
-        <v>509.69</v>
+        <v>7046.939827363</v>
       </c>
       <c r="O357" t="n">
-        <v>2548450</v>
+        <v>56375.518618904</v>
       </c>
       <c r="P357" t="n">
-        <v>750</v>
+        <v>9900</v>
       </c>
       <c r="Q357" t="n">
-        <v>3750000</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>C7534</t>
+          <t>C7552-A</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>6951241752002</v>
+        <v>6970635795425</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>FICHAS DE ARMAR 3D  PERRITO LOBO 1900PCS/16042</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>FICHA DE ARMAR</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -16779,7 +16782,7 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K358" t="n">
         <v>0</v>
@@ -16788,33 +16791,33 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N358" t="n">
-        <v>7046.939827363</v>
+        <v>26378.02625</v>
       </c>
       <c r="O358" t="n">
-        <v>56375.518618904</v>
+        <v>52756.0525</v>
       </c>
       <c r="P358" t="n">
-        <v>9900</v>
+        <v>36500</v>
       </c>
       <c r="Q358" t="n">
-        <v>79200</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>C7552-A</t>
+          <t>C7553-A</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>6970635795425</v>
+        <v>6970635795647</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR 3D  PERRITO LOBO 1900PCS/16042</t>
+          <t>FICHAS DE ARMAR PEERO TERRY SMALL 1350PCS/16064</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -16828,7 +16831,7 @@
         </is>
       </c>
       <c r="J359" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
@@ -16837,33 +16840,33 @@
         <v>0</v>
       </c>
       <c r="M359" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N359" t="n">
-        <v>26378.02625</v>
+        <v>12400.38</v>
       </c>
       <c r="O359" t="n">
-        <v>52756.0525</v>
+        <v>37201.14</v>
       </c>
       <c r="P359" t="n">
-        <v>36500</v>
+        <v>26900</v>
       </c>
       <c r="Q359" t="n">
-        <v>73000</v>
+        <v>80700</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>C7553-A</t>
+          <t>C7554-E</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>6970635795647</v>
+        <v>6970635793964</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR PEERO TERRY SMALL 1350PCS/16064</t>
+          <t>FICHAS 3D MINI PERRITO WELSH CORGI 997PCS C7554-E/18396</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -16877,7 +16880,7 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -16886,38 +16889,35 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N360" t="n">
-        <v>12400.38</v>
+        <v>14320.330526316</v>
       </c>
       <c r="O360" t="n">
-        <v>37201.14</v>
+        <v>114562.644210528</v>
       </c>
       <c r="P360" t="n">
-        <v>26900</v>
+        <v>19900</v>
       </c>
       <c r="Q360" t="n">
-        <v>80700</v>
+        <v>159200</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>C7554-E</t>
-        </is>
-      </c>
-      <c r="B361" t="n">
-        <v>6970635793964</v>
+          <t>C7560-AC</t>
+        </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FICHAS 3D MINI PERRITO WELSH CORGI 997PCS C7554-E/18396</t>
+          <t>TRICICLO APRENDIZAJE OSITO Y PATICO STD C7560-AC</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>FICHA DE ARMAR</t>
+          <t>SCOTTER</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -16935,35 +16935,38 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N361" t="n">
-        <v>14320.330526316</v>
+        <v>19260.68</v>
       </c>
       <c r="O361" t="n">
-        <v>114562.644210528</v>
+        <v>77042.72</v>
       </c>
       <c r="P361" t="n">
-        <v>19900</v>
+        <v>73900</v>
       </c>
       <c r="Q361" t="n">
-        <v>159200</v>
+        <v>295600</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>C7560-AC</t>
-        </is>
+          <t>C7582</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>8602584075829</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>TRICICLO APRENDIZAJE OSITO Y PATICO STD C7560-AC</t>
+          <t>SLIME DINOSAURIOS 154gr C7582</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>SCOTTER</t>
+          <t>SLIME</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -16972,7 +16975,7 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
@@ -16981,38 +16984,38 @@
         <v>0</v>
       </c>
       <c r="M362" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N362" t="n">
-        <v>19260.68</v>
+        <v>1538.46</v>
       </c>
       <c r="O362" t="n">
-        <v>77042.72</v>
+        <v>13846.14</v>
       </c>
       <c r="P362" t="n">
-        <v>73900</v>
+        <v>2000</v>
       </c>
       <c r="Q362" t="n">
-        <v>295600</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>C7582</t>
+          <t>C7587</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>8602584075829</v>
+        <v>7587228020247</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>SLIME DINOSAURIOS 154gr C7582</t>
+          <t>TROMPO LUCES DEPORTES C7587</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>SLIME</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -17021,7 +17024,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>9</v>
+        <v>816</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -17030,33 +17033,33 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>9</v>
+        <v>816</v>
       </c>
       <c r="N363" t="n">
-        <v>1538.46</v>
+        <v>1080.18</v>
       </c>
       <c r="O363" t="n">
-        <v>13846.14</v>
+        <v>881426.88</v>
       </c>
       <c r="P363" t="n">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="Q363" t="n">
-        <v>18000</v>
+        <v>3998400</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>C7587</t>
+          <t>C7588</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>7587228020247</v>
+        <v>7588228020244</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>TROMPO LUCES DEPORTES C7587</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -17070,7 +17073,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>816</v>
+        <v>526</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -17079,38 +17082,38 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>816</v>
+        <v>526</v>
       </c>
       <c r="N364" t="n">
-        <v>1080.18</v>
+        <v>641.78</v>
       </c>
       <c r="O364" t="n">
-        <v>881426.88</v>
+        <v>337576.28</v>
       </c>
       <c r="P364" t="n">
-        <v>4900</v>
+        <v>2500</v>
       </c>
       <c r="Q364" t="n">
-        <v>3998400</v>
+        <v>1315000</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7591</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>7588228020244</v>
+        <v>7500363551131</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOLITRON GUSANO TORNASOL C7591</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>BOLITRONES</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -17119,7 +17122,7 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>526</v>
+        <v>45</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
@@ -17128,38 +17131,38 @@
         <v>0</v>
       </c>
       <c r="M365" t="n">
-        <v>526</v>
+        <v>45</v>
       </c>
       <c r="N365" t="n">
-        <v>641.78</v>
+        <v>619.01</v>
       </c>
       <c r="O365" t="n">
-        <v>337576.28</v>
+        <v>27855.45</v>
       </c>
       <c r="P365" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="Q365" t="n">
-        <v>1315000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>C7591</t>
+          <t>C7604</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>7500363551131</v>
+        <v>6905534128272</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BOLITRON GUSANO TORNASOL C7591</t>
+          <t>PELOTA BANBAN LUZ CON CUERDA STD C7604</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>BOLITRONES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -17168,7 +17171,7 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="K366" t="n">
         <v>0</v>
@@ -17177,38 +17180,38 @@
         <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="N366" t="n">
-        <v>619.01</v>
+        <v>366.39971428571</v>
       </c>
       <c r="O366" t="n">
-        <v>27855.45</v>
+        <v>4030.39685714281</v>
       </c>
       <c r="P366" t="n">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="Q366" t="n">
-        <v>157500</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>C7604</t>
+          <t>C7605</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>6905534128272</v>
+        <v>5391528076055</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>PELOTA BANBAN LUZ CON CUERDA STD C7604</t>
+          <t>ROMPECABEZAS 3D SURTIDO C7605</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -17217,7 +17220,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -17226,38 +17229,38 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="N367" t="n">
-        <v>366.39971428571</v>
+        <v>424.99</v>
       </c>
       <c r="O367" t="n">
-        <v>4030.39685714281</v>
+        <v>14874.65</v>
       </c>
       <c r="P367" t="n">
-        <v>2900</v>
+        <v>2300</v>
       </c>
       <c r="Q367" t="n">
-        <v>31900</v>
+        <v>80500</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>C7605</t>
+          <t>C7616</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>5391528076055</v>
+        <v>6999989900118</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>ROMPECABEZAS 3D SURTIDO C7605</t>
+          <t>CHALECO PISCINA NIÑO TALLA A 21.5X21.5xcm C7616</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -17266,7 +17269,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -17275,33 +17278,33 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="N368" t="n">
-        <v>424.99</v>
+        <v>1378.96</v>
       </c>
       <c r="O368" t="n">
-        <v>14874.65</v>
+        <v>182022.72</v>
       </c>
       <c r="P368" t="n">
-        <v>2300</v>
+        <v>6600</v>
       </c>
       <c r="Q368" t="n">
-        <v>80500</v>
+        <v>871200</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>C7616</t>
+          <t>C7617</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>6999989900118</v>
+        <v>6999899236192</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>CHALECO PISCINA NIÑO TALLA A 21.5X21.5xcm C7616</t>
+          <t>BRAZITOS PISCINA #A 12PCS</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -17315,7 +17318,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -17324,33 +17327,33 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="N369" t="n">
-        <v>1378.96</v>
+        <v>540.40115740741</v>
       </c>
       <c r="O369" t="n">
-        <v>182022.72</v>
+        <v>48095.70300925949</v>
       </c>
       <c r="P369" t="n">
-        <v>6600</v>
+        <v>2500</v>
       </c>
       <c r="Q369" t="n">
-        <v>871200</v>
+        <v>222500</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>C7617</t>
+          <t>C7618</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>6999899236192</v>
+        <v>6999899236208</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>BRAZITOS PISCINA #A 12PCS</t>
+          <t>BRAZITO PISCINA  27X17 C7618</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -17364,7 +17367,7 @@
         </is>
       </c>
       <c r="J370" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
@@ -17373,33 +17376,33 @@
         <v>0</v>
       </c>
       <c r="M370" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="N370" t="n">
-        <v>540.40115740741</v>
+        <v>616.4</v>
       </c>
       <c r="O370" t="n">
-        <v>48095.70300925949</v>
+        <v>40682.4</v>
       </c>
       <c r="P370" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q370" t="n">
-        <v>222500</v>
+        <v>191400</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>C7618</t>
+          <t>C7628</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>6999899236208</v>
+        <v>6999899236321</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>BRAZITO PISCINA  27X17 C7618</t>
+          <t>PELOTA PISCINA  KIKO  C7628</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -17413,7 +17416,7 @@
         </is>
       </c>
       <c r="J371" t="n">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="K371" t="n">
         <v>0</v>
@@ -17422,33 +17425,33 @@
         <v>0</v>
       </c>
       <c r="M371" t="n">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="N371" t="n">
-        <v>616.4</v>
+        <v>426.1</v>
       </c>
       <c r="O371" t="n">
-        <v>40682.4</v>
+        <v>145300.1</v>
       </c>
       <c r="P371" t="n">
         <v>2900</v>
       </c>
       <c r="Q371" t="n">
-        <v>191400</v>
+        <v>988900</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>C7628</t>
+          <t>C7629</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>6999899236321</v>
+        <v>6999899236338</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA  KIKO  C7628</t>
+          <t>PELOTA PISCINA KIKO C7629</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -17462,7 +17465,7 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>341</v>
+        <v>984</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
@@ -17471,33 +17474,33 @@
         <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>341</v>
+        <v>984</v>
       </c>
       <c r="N372" t="n">
-        <v>426.1</v>
+        <v>430.60997569866</v>
       </c>
       <c r="O372" t="n">
-        <v>145300.1</v>
+        <v>423720.2160874814</v>
       </c>
       <c r="P372" t="n">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="Q372" t="n">
-        <v>988900</v>
+        <v>2164800</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>C7629</t>
+          <t>C7630</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>6999899236338</v>
+        <v>6999899236345</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA KIKO C7629</t>
+          <t>PELOTA PISCINA KIKO C7630</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -17511,7 +17514,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>984</v>
+        <v>726</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
@@ -17520,33 +17523,33 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>984</v>
+        <v>726</v>
       </c>
       <c r="N373" t="n">
-        <v>430.60997577226</v>
+        <v>465.8709683605</v>
       </c>
       <c r="O373" t="n">
-        <v>423720.2161599039</v>
+        <v>338222.323029723</v>
       </c>
       <c r="P373" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="Q373" t="n">
-        <v>2164800</v>
+        <v>1815000</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>C7630</t>
+          <t>C7631</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>6999899236345</v>
+        <v>6999899236352</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA KIKO C7630</t>
+          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -17560,7 +17563,7 @@
         </is>
       </c>
       <c r="J374" t="n">
-        <v>726</v>
+        <v>455</v>
       </c>
       <c r="K374" t="n">
         <v>0</v>
@@ -17569,38 +17572,35 @@
         <v>0</v>
       </c>
       <c r="M374" t="n">
-        <v>726</v>
+        <v>455</v>
       </c>
       <c r="N374" t="n">
-        <v>465.87096743295</v>
+        <v>315.02726865672</v>
       </c>
       <c r="O374" t="n">
-        <v>338222.3223563217</v>
+        <v>143337.4072388076</v>
       </c>
       <c r="P374" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="Q374" t="n">
-        <v>1815000</v>
+        <v>1001000</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>C7631</t>
-        </is>
-      </c>
-      <c r="B375" t="n">
-        <v>6999899236352</v>
+          <t>C8-IO</t>
+        </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
+          <t>BOLITRON ESPINAS</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>BOLITRONES</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>455</v>
+        <v>180</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
@@ -17618,44 +17618,42 @@
         <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>455</v>
+        <v>180</v>
       </c>
       <c r="N375" t="n">
-        <v>315.02716176471</v>
+        <v>1098.06</v>
       </c>
       <c r="O375" t="n">
-        <v>143337.358602943</v>
+        <v>197650.8</v>
       </c>
       <c r="P375" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="Q375" t="n">
-        <v>1001000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>C8-IO</t>
-        </is>
+          <t>C80</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>9352149303728</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>BOLITRON ESPINAS</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>BOLITRONES</t>
+          <t>LAZADOR AGUA</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J376" t="n">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="K376" t="n">
         <v>0</v>
@@ -17664,33 +17662,33 @@
         <v>0</v>
       </c>
       <c r="M376" t="n">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="N376" t="n">
-        <v>1098.06</v>
+        <v>2000</v>
       </c>
       <c r="O376" t="n">
-        <v>197650.8</v>
+        <v>496000</v>
       </c>
       <c r="P376" t="n">
-        <v>800</v>
+        <v>4100</v>
       </c>
       <c r="Q376" t="n">
-        <v>144000</v>
+        <v>1016800</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>C80</t>
+          <t>C808</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>9352149303728</v>
+        <v>8989201808061</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>LAZADOR AGUA</t>
+          <t>ESPADA LUZ SENCILLAS</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -17699,7 +17697,7 @@
         </is>
       </c>
       <c r="J377" t="n">
-        <v>248</v>
+        <v>129</v>
       </c>
       <c r="K377" t="n">
         <v>0</v>
@@ -17708,42 +17706,47 @@
         <v>0</v>
       </c>
       <c r="M377" t="n">
-        <v>248</v>
+        <v>129</v>
       </c>
       <c r="N377" t="n">
-        <v>2000</v>
+        <v>1297.52</v>
       </c>
       <c r="O377" t="n">
-        <v>496000</v>
+        <v>167380.08</v>
       </c>
       <c r="P377" t="n">
-        <v>4100</v>
+        <v>1800</v>
       </c>
       <c r="Q377" t="n">
-        <v>1016800</v>
+        <v>232200</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>C808</t>
+          <t>C842-IO</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>8989201808061</v>
+        <v>6901234567885</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ESPADA LUZ SENCILLAS</t>
+          <t>MINI DRON OVNI PTW</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J378" t="n">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="K378" t="n">
         <v>0</v>
@@ -17752,38 +17755,35 @@
         <v>0</v>
       </c>
       <c r="M378" t="n">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="N378" t="n">
-        <v>1297.52</v>
+        <v>6153.85</v>
       </c>
       <c r="O378" t="n">
-        <v>167380.08</v>
+        <v>166153.95</v>
       </c>
       <c r="P378" t="n">
-        <v>1800</v>
+        <v>8000</v>
       </c>
       <c r="Q378" t="n">
-        <v>232200</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>C842-IO</t>
-        </is>
-      </c>
-      <c r="B379" t="n">
-        <v>6901234567885</v>
+          <t>C9</t>
+        </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>MINI DRON OVNI PTW</t>
+          <t>PELUCHE 30CM 774-1</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -17792,7 +17792,7 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
@@ -17801,44 +17801,44 @@
         <v>0</v>
       </c>
       <c r="M379" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N379" t="n">
-        <v>6153.85</v>
+        <v>497.63</v>
       </c>
       <c r="O379" t="n">
-        <v>166153.95</v>
+        <v>9454.969999999999</v>
       </c>
       <c r="P379" t="n">
-        <v>8000</v>
+        <v>14900</v>
       </c>
       <c r="Q379" t="n">
-        <v>216000</v>
+        <v>283100</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C943</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>PELUCHE 30CM 774-1</t>
+          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J380" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K380" t="n">
         <v>0</v>
@@ -17847,44 +17847,44 @@
         <v>0</v>
       </c>
       <c r="M380" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N380" t="n">
-        <v>497.63</v>
+        <v>22951.70473822</v>
       </c>
       <c r="O380" t="n">
-        <v>9454.969999999999</v>
+        <v>298372.16159686</v>
       </c>
       <c r="P380" t="n">
-        <v>14900</v>
+        <v>37900</v>
       </c>
       <c r="Q380" t="n">
-        <v>283100</v>
+        <v>492700</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>C943</t>
+          <t>C956-IO</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
+          <t>PALO GLOBO COLORES 40CM</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J381" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
@@ -17893,44 +17893,44 @@
         <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="N381" t="n">
-        <v>22951.70473822</v>
+        <v>280</v>
       </c>
       <c r="O381" t="n">
-        <v>298372.16159686</v>
+        <v>15400</v>
       </c>
       <c r="P381" t="n">
-        <v>37900</v>
+        <v>350</v>
       </c>
       <c r="Q381" t="n">
-        <v>492700</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>C956-IO</t>
+          <t>C984</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>CG2016531</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>PALO GLOBO COLORES 40CM</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>TANGRAM</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J382" t="n">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -17939,44 +17939,49 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="N382" t="n">
-        <v>280</v>
+        <v>705.52797546012</v>
       </c>
       <c r="O382" t="n">
-        <v>15400</v>
+        <v>112178.9480981591</v>
       </c>
       <c r="P382" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="Q382" t="n">
-        <v>19250</v>
+        <v>238500</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>C984</t>
+          <t>CA1673</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>CG2016531</t>
+          <t>CA11673</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>TANGRAM</t>
+          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J383" t="n">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -17985,35 +17990,35 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="N383" t="n">
-        <v>705.52797546012</v>
+        <v>1547.8828813559</v>
       </c>
       <c r="O383" t="n">
-        <v>112178.9480981591</v>
+        <v>55723.7837288124</v>
       </c>
       <c r="P383" t="n">
-        <v>1500</v>
+        <v>5500</v>
       </c>
       <c r="Q383" t="n">
-        <v>238500</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CA1673</t>
+          <t>CA1674</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>CA11673</t>
+          <t>CA1674</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+          <t>JUGUETE GUITARRA MUSICAL OVEJA CA1674</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -18039,10 +18044,10 @@
         <v>36</v>
       </c>
       <c r="N384" t="n">
-        <v>1547.8828813559</v>
+        <v>4125</v>
       </c>
       <c r="O384" t="n">
-        <v>55723.7837288124</v>
+        <v>148500</v>
       </c>
       <c r="P384" t="n">
         <v>5500</v>
@@ -18054,22 +18059,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CA1674</t>
+          <t>CA886</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>CA1674</t>
+          <t>CA886</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>JUGUETE GUITARRA MUSICAL OVEJA CA1674</t>
+          <t>ANIMAL TAMBOR  CERDITO CA886</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -18078,7 +18083,7 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -18087,40 +18092,35 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="N385" t="n">
-        <v>4125</v>
+        <v>1757.3206175772</v>
       </c>
       <c r="O385" t="n">
-        <v>148500</v>
+        <v>75564.78655581961</v>
       </c>
       <c r="P385" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="Q385" t="n">
-        <v>198000</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CA886</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>CA886</t>
+          <t>CM-MORRAL01</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ANIMAL TAMBOR  CERDITO CA886</t>
+          <t>MORRAL GRANDE PARA NIÑAS PRINCESS</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -18129,7 +18129,7 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
@@ -18138,30 +18138,30 @@
         <v>0</v>
       </c>
       <c r="M386" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="N386" t="n">
-        <v>1757.3206175772</v>
+        <v>31846.46</v>
       </c>
       <c r="O386" t="n">
-        <v>75564.78655581961</v>
+        <v>414003.98</v>
       </c>
       <c r="P386" t="n">
-        <v>2000</v>
+        <v>55900</v>
       </c>
       <c r="Q386" t="n">
-        <v>86000</v>
+        <v>726700</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CM-MORRAL01</t>
+          <t>CO-9</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>MORRAL GRANDE PARA NIÑAS PRINCESS</t>
+          <t>PELUCHE OSO 1489-30-1</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K387" t="n">
         <v>0</v>
@@ -18184,35 +18184,35 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N387" t="n">
-        <v>31846.46</v>
+        <v>18320</v>
       </c>
       <c r="O387" t="n">
-        <v>414003.98</v>
+        <v>36640</v>
       </c>
       <c r="P387" t="n">
-        <v>55900</v>
+        <v>22900</v>
       </c>
       <c r="Q387" t="n">
-        <v>726700</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CO-9</t>
+          <t>DPB052</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>PELUCHE OSO 1489-30-1</t>
+          <t>PELUCHE ZOOLOGICO PQÑ DP05-5</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -18233,27 +18233,27 @@
         <v>2</v>
       </c>
       <c r="N388" t="n">
-        <v>18320</v>
+        <v>5000</v>
       </c>
       <c r="O388" t="n">
-        <v>36640</v>
+        <v>10000</v>
       </c>
       <c r="P388" t="n">
-        <v>22900</v>
+        <v>6500</v>
       </c>
       <c r="Q388" t="n">
-        <v>45800</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>DPB052</t>
+          <t>DPB07</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO PQÑ DP05-5</t>
+          <t>PELUCHE ZOOLOGICO BORDADO 20CM DP05-1</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -18276,30 +18276,30 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N389" t="n">
-        <v>5000</v>
+        <v>2847.525</v>
       </c>
       <c r="O389" t="n">
-        <v>10000</v>
+        <v>11390.1</v>
       </c>
       <c r="P389" t="n">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="Q389" t="n">
-        <v>13000</v>
+        <v>27600</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>DPB07</t>
+          <t>DPB086</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO BORDADO 20CM DP05-1</t>
+          <t>OSO NAVIDEÑO CM30 DP20-5</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -18313,7 +18313,7 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
@@ -18322,30 +18322,30 @@
         <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N390" t="n">
-        <v>2847.525</v>
+        <v>4538.13</v>
       </c>
       <c r="O390" t="n">
-        <v>11390.1</v>
+        <v>4538.13</v>
       </c>
       <c r="P390" t="n">
-        <v>6900</v>
+        <v>22500</v>
       </c>
       <c r="Q390" t="n">
-        <v>27600</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>DPB086</t>
+          <t>DPB13</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>OSO NAVIDEÑO CM30 DP20-5</t>
+          <t>PELUCHE OSO CORAZON BORDADO 25CM</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -18359,7 +18359,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -18368,30 +18368,30 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N391" t="n">
-        <v>4538.13</v>
+        <v>7776.29</v>
       </c>
       <c r="O391" t="n">
-        <v>4538.13</v>
+        <v>69986.61</v>
       </c>
       <c r="P391" t="n">
-        <v>22500</v>
+        <v>10000</v>
       </c>
       <c r="Q391" t="n">
-        <v>22500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>DPB13</t>
+          <t>DPBQ05</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORAZON BORDADO 25CM</t>
+          <t>PELUCHE ABRASADO WZ44</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -18414,30 +18414,30 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="N392" t="n">
-        <v>7776.29</v>
+        <v>4518.3764150943</v>
       </c>
       <c r="O392" t="n">
-        <v>69986.61</v>
+        <v>230437.1971698093</v>
       </c>
       <c r="P392" t="n">
-        <v>10000</v>
+        <v>11500</v>
       </c>
       <c r="Q392" t="n">
-        <v>90000</v>
+        <v>586500</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>DPBQ05</t>
+          <t>DPBQ09</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>PELUCHE ABRASADO WZ44</t>
+          <t>PELUCHE PATRULLA PQÑ 20CM PATROL</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -18451,7 +18451,7 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
@@ -18460,30 +18460,30 @@
         <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="N393" t="n">
-        <v>4518.3764150943</v>
+        <v>5384.62</v>
       </c>
       <c r="O393" t="n">
-        <v>230437.1971698093</v>
+        <v>5384.62</v>
       </c>
       <c r="P393" t="n">
-        <v>11500</v>
+        <v>7000</v>
       </c>
       <c r="Q393" t="n">
-        <v>586500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>DPBQ09</t>
+          <t>DPBQ11</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>PELUCHE PATRULLA PQÑ 20CM PATROL</t>
+          <t>PELUCHE PERRO STD 25CM  PERROX3</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -18509,27 +18509,27 @@
         <v>1</v>
       </c>
       <c r="N394" t="n">
-        <v>5384.62</v>
+        <v>9153.85</v>
       </c>
       <c r="O394" t="n">
-        <v>5384.62</v>
+        <v>9153.85</v>
       </c>
       <c r="P394" t="n">
-        <v>7000</v>
+        <v>11900</v>
       </c>
       <c r="Q394" t="n">
-        <v>7000</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>DPBQ11</t>
+          <t>DPBQ15</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO STD 25CM  PERROX3</t>
+          <t>PELUCHE TIGRES 25CM</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -18555,27 +18555,27 @@
         <v>1</v>
       </c>
       <c r="N395" t="n">
-        <v>9153.85</v>
+        <v>7280.46</v>
       </c>
       <c r="O395" t="n">
-        <v>9153.85</v>
+        <v>7280.46</v>
       </c>
       <c r="P395" t="n">
-        <v>11900</v>
+        <v>16900</v>
       </c>
       <c r="Q395" t="n">
-        <v>11900</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>DPBQ15</t>
+          <t>DPBQ16</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRES 25CM</t>
+          <t>PELUCHE PERRO SENTADO 28CM</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
@@ -18598,30 +18598,30 @@
         <v>0</v>
       </c>
       <c r="M396" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N396" t="n">
-        <v>7280.46</v>
+        <v>5782.36</v>
       </c>
       <c r="O396" t="n">
-        <v>7280.46</v>
+        <v>17347.08</v>
       </c>
       <c r="P396" t="n">
-        <v>16900</v>
+        <v>15900</v>
       </c>
       <c r="Q396" t="n">
-        <v>16900</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>DPBQ16</t>
+          <t>DPBQ18</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO SENTADO 28CM</t>
+          <t>PELUCHE VIEJITOS 25CM</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
@@ -18644,30 +18644,30 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N397" t="n">
-        <v>5782.36</v>
+        <v>2868.67</v>
       </c>
       <c r="O397" t="n">
-        <v>17347.08</v>
+        <v>31555.37</v>
       </c>
       <c r="P397" t="n">
-        <v>15900</v>
+        <v>16900</v>
       </c>
       <c r="Q397" t="n">
-        <v>47700</v>
+        <v>185900</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>DPBQ18</t>
+          <t>DPBQ26</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>PELUCHE VIEJITOS 25CM</t>
+          <t>PELUCHE OSO CUMPLEAÑOS 30CM</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -18681,7 +18681,7 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
@@ -18690,35 +18690,35 @@
         <v>0</v>
       </c>
       <c r="M398" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N398" t="n">
-        <v>2868.67</v>
+        <v>2223.11</v>
       </c>
       <c r="O398" t="n">
-        <v>31555.37</v>
+        <v>11115.55</v>
       </c>
       <c r="P398" t="n">
-        <v>16900</v>
+        <v>25000</v>
       </c>
       <c r="Q398" t="n">
-        <v>185900</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>DPBQ26</t>
+          <t>DV052</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CUMPLEAÑOS 30CM</t>
+          <t>PELOTA PISCINA DV052</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -18727,7 +18727,7 @@
         </is>
       </c>
       <c r="J399" t="n">
-        <v>5</v>
+        <v>1527</v>
       </c>
       <c r="K399" t="n">
         <v>0</v>
@@ -18736,30 +18736,30 @@
         <v>0</v>
       </c>
       <c r="M399" t="n">
-        <v>5</v>
+        <v>1527</v>
       </c>
       <c r="N399" t="n">
-        <v>2223.11</v>
+        <v>220.00299116111</v>
       </c>
       <c r="O399" t="n">
-        <v>11115.55</v>
+        <v>335944.567503015</v>
       </c>
       <c r="P399" t="n">
-        <v>25000</v>
+        <v>260</v>
       </c>
       <c r="Q399" t="n">
-        <v>125000</v>
+        <v>397020</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>DV052</t>
+          <t>DV077</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DV052</t>
+          <t>RELLENO DE PIÑATA GDE DV077</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -18773,7 +18773,7 @@
         </is>
       </c>
       <c r="J400" t="n">
-        <v>1527</v>
+        <v>20</v>
       </c>
       <c r="K400" t="n">
         <v>0</v>
@@ -18782,30 +18782,30 @@
         <v>0</v>
       </c>
       <c r="M400" t="n">
-        <v>1527</v>
+        <v>20</v>
       </c>
       <c r="N400" t="n">
-        <v>220.00299116111</v>
+        <v>705.11</v>
       </c>
       <c r="O400" t="n">
-        <v>335944.567503015</v>
+        <v>14102.2</v>
       </c>
       <c r="P400" t="n">
-        <v>260</v>
+        <v>11000</v>
       </c>
       <c r="Q400" t="n">
-        <v>397020</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>DV077</t>
+          <t>DV083</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>RELLENO DE PIÑATA GDE DV077</t>
+          <t>RELLENO PIÑATA PQÑ DV083</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -18819,7 +18819,7 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K401" t="n">
         <v>0</v>
@@ -18828,30 +18828,30 @@
         <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N401" t="n">
-        <v>705.11</v>
+        <v>504.3</v>
       </c>
       <c r="O401" t="n">
-        <v>14102.2</v>
+        <v>3530.1</v>
       </c>
       <c r="P401" t="n">
-        <v>11000</v>
+        <v>5900</v>
       </c>
       <c r="Q401" t="n">
-        <v>220000</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>DV083</t>
+          <t>EMI066</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>RELLENO PIÑATA PQÑ DV083</t>
+          <t>PELUCHE ENCANTO E22-11</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
@@ -18874,35 +18874,35 @@
         <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N402" t="n">
-        <v>504.3</v>
+        <v>11475</v>
       </c>
       <c r="O402" t="n">
-        <v>3530.1</v>
+        <v>34425</v>
       </c>
       <c r="P402" t="n">
-        <v>5900</v>
+        <v>14900</v>
       </c>
       <c r="Q402" t="n">
-        <v>41300</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>EMI066</t>
+          <t>FG045</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>PELUCHE ENCANTO E22-11</t>
+          <t>HELICPTERO DIDACTICO BOLSA BP1235513</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
@@ -18920,44 +18920,34 @@
         <v>0</v>
       </c>
       <c r="M403" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="N403" t="n">
-        <v>11475</v>
+        <v>5120.05</v>
       </c>
       <c r="O403" t="n">
-        <v>34425</v>
+        <v>240642.35</v>
       </c>
       <c r="P403" t="n">
-        <v>14900</v>
+        <v>5700</v>
       </c>
       <c r="Q403" t="n">
-        <v>44700</v>
+        <v>267900</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>FG045</t>
+          <t>FG046</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>HELICPTERO DIDACTICO BOLSA BP1235513</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I404" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>CARRO DINOSAURIO JD1899-108A</t>
         </is>
       </c>
       <c r="J404" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="K404" t="n">
         <v>0</v>
@@ -18966,34 +18956,44 @@
         <v>0</v>
       </c>
       <c r="M404" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="N404" t="n">
-        <v>5120.05</v>
+        <v>3885.95</v>
       </c>
       <c r="O404" t="n">
-        <v>240642.35</v>
+        <v>3885.95</v>
       </c>
       <c r="P404" t="n">
-        <v>5700</v>
+        <v>6700</v>
       </c>
       <c r="Q404" t="n">
-        <v>267900</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>FG046</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO JD1899-108A</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J405" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
@@ -19002,35 +19002,35 @@
         <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="N405" t="n">
-        <v>3885.95</v>
+        <v>1952.66</v>
       </c>
       <c r="O405" t="n">
-        <v>3885.95</v>
+        <v>123017.58</v>
       </c>
       <c r="P405" t="n">
-        <v>6700</v>
+        <v>3500</v>
       </c>
       <c r="Q405" t="n">
-        <v>6700</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG055</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>FICHAS DIDACTICAS CARRITO 2263</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -19039,7 +19039,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
@@ -19048,35 +19048,35 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="N406" t="n">
-        <v>1952.66</v>
+        <v>12575.25</v>
       </c>
       <c r="O406" t="n">
-        <v>123017.58</v>
+        <v>301806</v>
       </c>
       <c r="P406" t="n">
-        <v>3500</v>
+        <v>17900</v>
       </c>
       <c r="Q406" t="n">
-        <v>220500</v>
+        <v>429600</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>FG055</t>
+          <t>FG067</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>FICHAS DIDACTICAS CARRITO 2263</t>
+          <t>COCINA BOLSA 7003-1</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -19085,7 +19085,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
@@ -19094,30 +19094,30 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N407" t="n">
-        <v>12575.25</v>
+        <v>6270.21</v>
       </c>
       <c r="O407" t="n">
-        <v>301806</v>
+        <v>125404.2</v>
       </c>
       <c r="P407" t="n">
-        <v>17900</v>
+        <v>8900</v>
       </c>
       <c r="Q407" t="n">
-        <v>429600</v>
+        <v>178000</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>FG067</t>
+          <t>FG08</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>COCINA BOLSA 7003-1</t>
+          <t>JUEGO DOCTOR MALETA NIÑO 118-88A</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
@@ -19140,35 +19140,35 @@
         <v>0</v>
       </c>
       <c r="M408" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N408" t="n">
-        <v>6270.21</v>
+        <v>7625.7242857143</v>
       </c>
       <c r="O408" t="n">
-        <v>125404.2</v>
+        <v>76257.24285714301</v>
       </c>
       <c r="P408" t="n">
-        <v>8900</v>
+        <v>29900</v>
       </c>
       <c r="Q408" t="n">
-        <v>178000</v>
+        <v>299000</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>FG08</t>
+          <t>FG081</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>JUEGO DOCTOR MALETA NIÑO 118-88A</t>
+          <t>CARRO LLANTON BOLSA THUNDER 6969-44</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K409" t="n">
         <v>0</v>
@@ -19186,35 +19186,35 @@
         <v>0</v>
       </c>
       <c r="M409" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N409" t="n">
-        <v>7625.7242857143</v>
+        <v>9726.98</v>
       </c>
       <c r="O409" t="n">
-        <v>76257.24285714301</v>
+        <v>175085.64</v>
       </c>
       <c r="P409" t="n">
-        <v>29900</v>
+        <v>12900</v>
       </c>
       <c r="Q409" t="n">
-        <v>299000</v>
+        <v>232200</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>FG081</t>
+          <t>FG084</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>CARRO LLANTON BOLSA THUNDER 6969-44</t>
+          <t>BEBE BAÑERA 9431FH7</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -19223,7 +19223,7 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
@@ -19232,35 +19232,35 @@
         <v>0</v>
       </c>
       <c r="M410" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N410" t="n">
-        <v>9726.98</v>
+        <v>9398.26</v>
       </c>
       <c r="O410" t="n">
-        <v>175085.64</v>
+        <v>9398.26</v>
       </c>
       <c r="P410" t="n">
-        <v>12900</v>
+        <v>9900</v>
       </c>
       <c r="Q410" t="n">
-        <v>232200</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>FG084</t>
+          <t>FG089</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>BEBE BAÑERA 9431FH7</t>
+          <t>MULA EN BOLSA CON CARROS 919-113</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -19269,7 +19269,7 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
@@ -19278,35 +19278,35 @@
         <v>0</v>
       </c>
       <c r="M411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N411" t="n">
-        <v>9398.26</v>
+        <v>13958.03</v>
       </c>
       <c r="O411" t="n">
-        <v>9398.26</v>
+        <v>27916.06</v>
       </c>
       <c r="P411" t="n">
-        <v>9900</v>
+        <v>14900</v>
       </c>
       <c r="Q411" t="n">
-        <v>9900</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>FG089</t>
+          <t>FG092</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>MULA EN BOLSA CON CARROS 919-113</t>
+          <t>BLISTER  TETERA SJ377-1</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
@@ -19324,35 +19324,35 @@
         <v>0</v>
       </c>
       <c r="M412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N412" t="n">
-        <v>13958.03</v>
+        <v>9855.0380769231</v>
       </c>
       <c r="O412" t="n">
-        <v>27916.06</v>
+        <v>29565.1142307693</v>
       </c>
       <c r="P412" t="n">
-        <v>14900</v>
+        <v>15500</v>
       </c>
       <c r="Q412" t="n">
-        <v>29800</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>FG092</t>
+          <t>FP-315-ELEFANTE</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>BLISTER  TETERA SJ377-1</t>
+          <t>PELUCHE ELEFANTE  48CM</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="J413" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K413" t="n">
         <v>0</v>
@@ -19370,35 +19370,35 @@
         <v>0</v>
       </c>
       <c r="M413" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N413" t="n">
-        <v>9855.0380769231</v>
+        <v>29250</v>
       </c>
       <c r="O413" t="n">
-        <v>29565.1142307693</v>
+        <v>29250</v>
       </c>
       <c r="P413" t="n">
-        <v>15500</v>
+        <v>36900</v>
       </c>
       <c r="Q413" t="n">
-        <v>46500</v>
+        <v>36900</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>FP-315-ELEFANTE</t>
+          <t>FP-339</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>PELUCHE ELEFANTE  48CM</t>
+          <t>PELUCHE CIGUEÑA CON HUEVITOS 25CM FP-339</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -19407,7 +19407,7 @@
         </is>
       </c>
       <c r="J414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K414" t="n">
         <v>0</v>
@@ -19416,30 +19416,30 @@
         <v>0</v>
       </c>
       <c r="M414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N414" t="n">
-        <v>29250</v>
+        <v>21150</v>
       </c>
       <c r="O414" t="n">
-        <v>29250</v>
+        <v>63450</v>
       </c>
       <c r="P414" t="n">
-        <v>36900</v>
+        <v>26500</v>
       </c>
       <c r="Q414" t="n">
-        <v>36900</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>FP-339</t>
+          <t>J-138</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>PELUCHE CIGUEÑA CON HUEVITOS 25CM FP-339</t>
+          <t>PERRO CAMINA J-138</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="J415" t="n">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="K415" t="n">
         <v>0</v>
@@ -19462,30 +19462,30 @@
         <v>0</v>
       </c>
       <c r="M415" t="n">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="N415" t="n">
-        <v>21150</v>
+        <v>6160</v>
       </c>
       <c r="O415" t="n">
-        <v>63450</v>
+        <v>1774080</v>
       </c>
       <c r="P415" t="n">
-        <v>26500</v>
+        <v>7500</v>
       </c>
       <c r="Q415" t="n">
-        <v>79500</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>J-138</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>PERRO CAMINA J-138</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="J416" t="n">
-        <v>288</v>
+        <v>646</v>
       </c>
       <c r="K416" t="n">
         <v>0</v>
@@ -19508,30 +19508,30 @@
         <v>0</v>
       </c>
       <c r="M416" t="n">
-        <v>288</v>
+        <v>646</v>
       </c>
       <c r="N416" t="n">
-        <v>6160</v>
+        <v>9240</v>
       </c>
       <c r="O416" t="n">
-        <v>1774080</v>
+        <v>5969040</v>
       </c>
       <c r="P416" t="n">
-        <v>7500</v>
+        <v>11500</v>
       </c>
       <c r="Q416" t="n">
-        <v>2160000</v>
+        <v>7429000</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>J-582</t>
+          <t>LP089</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>SET DE BICHOS EN BOLSA 714K-1</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -19545,7 +19545,7 @@
         </is>
       </c>
       <c r="J417" t="n">
-        <v>646</v>
+        <v>25</v>
       </c>
       <c r="K417" t="n">
         <v>0</v>
@@ -19554,30 +19554,30 @@
         <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>646</v>
+        <v>25</v>
       </c>
       <c r="N417" t="n">
-        <v>9240</v>
+        <v>10320</v>
       </c>
       <c r="O417" t="n">
-        <v>5969040</v>
+        <v>258000</v>
       </c>
       <c r="P417" t="n">
-        <v>11500</v>
+        <v>12900</v>
       </c>
       <c r="Q417" t="n">
-        <v>7429000</v>
+        <v>322500</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>LP089</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SET DE BICHOS EN BOLSA 714K-1</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="J418" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K418" t="n">
         <v>0</v>
@@ -19600,35 +19600,35 @@
         <v>0</v>
       </c>
       <c r="M418" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="N418" t="n">
-        <v>10320</v>
+        <v>415.07</v>
       </c>
       <c r="O418" t="n">
-        <v>258000</v>
+        <v>5395.91</v>
       </c>
       <c r="P418" t="n">
-        <v>12900</v>
+        <v>2900</v>
       </c>
       <c r="Q418" t="n">
-        <v>322500</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>MFQ01</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>PELUCHE ERIZO 55CM 23FP-029</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -19637,7 +19637,7 @@
         </is>
       </c>
       <c r="J419" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K419" t="n">
         <v>0</v>
@@ -19646,44 +19646,34 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N419" t="n">
-        <v>415.07</v>
+        <v>17885.0975</v>
       </c>
       <c r="O419" t="n">
-        <v>5395.91</v>
+        <v>71540.39</v>
       </c>
       <c r="P419" t="n">
-        <v>2900</v>
+        <v>46500</v>
       </c>
       <c r="Q419" t="n">
-        <v>37700</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>MFQ01</t>
+          <t>MFQ11</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>PELUCHE ERIZO 55CM 23FP-029</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
         </is>
       </c>
       <c r="J420" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
@@ -19692,34 +19682,34 @@
         <v>0</v>
       </c>
       <c r="M420" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N420" t="n">
-        <v>17885.0975</v>
+        <v>10436.368888889</v>
       </c>
       <c r="O420" t="n">
-        <v>71540.39</v>
+        <v>93927.320000001</v>
       </c>
       <c r="P420" t="n">
-        <v>46500</v>
+        <v>25900</v>
       </c>
       <c r="Q420" t="n">
-        <v>186000</v>
+        <v>233100</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>MFQ11</t>
+          <t>MFQ12</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
+          <t>PELUCHE DINOSAURIO PK FP-166</t>
         </is>
       </c>
       <c r="J421" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
@@ -19728,34 +19718,49 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N421" t="n">
-        <v>10436.368888889</v>
+        <v>8736.825000000001</v>
       </c>
       <c r="O421" t="n">
-        <v>93927.320000001</v>
+        <v>17473.65</v>
       </c>
       <c r="P421" t="n">
-        <v>25900</v>
+        <v>26500</v>
       </c>
       <c r="Q421" t="n">
-        <v>233100</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>MFQ12</t>
+          <t>MG033</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>MG18880</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK FP-166</t>
+          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J422" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
@@ -19764,40 +19769,40 @@
         <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N422" t="n">
-        <v>8736.825000000001</v>
+        <v>1783.57</v>
       </c>
       <c r="O422" t="n">
-        <v>17473.65</v>
+        <v>21402.84</v>
       </c>
       <c r="P422" t="n">
-        <v>26500</v>
+        <v>7800</v>
       </c>
       <c r="Q422" t="n">
-        <v>53000</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MG033</t>
+          <t>MG045</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>MG18880</t>
+          <t>PT20032</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
+          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -19806,7 +19811,7 @@
         </is>
       </c>
       <c r="J423" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K423" t="n">
         <v>0</v>
@@ -19815,40 +19820,35 @@
         <v>0</v>
       </c>
       <c r="M423" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N423" t="n">
-        <v>1783.57</v>
+        <v>6000</v>
       </c>
       <c r="O423" t="n">
-        <v>21402.84</v>
+        <v>210000</v>
       </c>
       <c r="P423" t="n">
-        <v>7800</v>
+        <v>7500</v>
       </c>
       <c r="Q423" t="n">
-        <v>93600</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MG045</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>PT20032</t>
+          <t>MG090</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
+          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
@@ -19866,35 +19866,40 @@
         <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="N424" t="n">
-        <v>6000</v>
+        <v>1462.04</v>
       </c>
       <c r="O424" t="n">
-        <v>210000</v>
+        <v>4386.12</v>
       </c>
       <c r="P424" t="n">
-        <v>7500</v>
+        <v>3800</v>
       </c>
       <c r="Q424" t="n">
-        <v>262500</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>MG090</t>
+          <t>MG093</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>mg26016</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
+          <t>CARRO BASURA BOLSA MG26016</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -19903,7 +19908,7 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
@@ -19912,40 +19917,35 @@
         <v>0</v>
       </c>
       <c r="M425" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="N425" t="n">
-        <v>1462.04</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="O425" t="n">
-        <v>4386.12</v>
+        <v>22349.72</v>
       </c>
       <c r="P425" t="n">
-        <v>3800</v>
+        <v>17800</v>
       </c>
       <c r="Q425" t="n">
-        <v>11400</v>
+        <v>516200</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MG093</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>mg26016</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>CARRO BASURA BOLSA MG26016</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -19954,7 +19954,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -19963,35 +19963,35 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N426" t="n">
-        <v>770.6799999999999</v>
+        <v>1482.84</v>
       </c>
       <c r="O426" t="n">
-        <v>22349.72</v>
+        <v>40036.68</v>
       </c>
       <c r="P426" t="n">
-        <v>17800</v>
+        <v>6500</v>
       </c>
       <c r="Q426" t="n">
-        <v>516200</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG21714</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -20000,7 +20000,7 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
@@ -20009,35 +20009,35 @@
         <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="N427" t="n">
-        <v>1482.84</v>
+        <v>576.58</v>
       </c>
       <c r="O427" t="n">
-        <v>40036.68</v>
+        <v>33441.64</v>
       </c>
       <c r="P427" t="n">
-        <v>6500</v>
+        <v>5900</v>
       </c>
       <c r="Q427" t="n">
-        <v>175500</v>
+        <v>342200</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MG21714</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -20046,7 +20046,7 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
@@ -20055,35 +20055,40 @@
         <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N428" t="n">
-        <v>576.58</v>
+        <v>1129.14</v>
       </c>
       <c r="O428" t="n">
-        <v>33441.64</v>
+        <v>68877.54000000001</v>
       </c>
       <c r="P428" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q428" t="n">
-        <v>342200</v>
+        <v>420900</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>MG22435</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -20092,7 +20097,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -20101,40 +20106,35 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="N429" t="n">
-        <v>1129.14</v>
+        <v>1236.3</v>
       </c>
       <c r="O429" t="n">
-        <v>68877.54000000001</v>
+        <v>279403.8</v>
       </c>
       <c r="P429" t="n">
-        <v>6900</v>
+        <v>2300</v>
       </c>
       <c r="Q429" t="n">
-        <v>420900</v>
+        <v>519800</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MG22435</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>MG22435</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -20143,7 +20143,7 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="K430" t="n">
         <v>0</v>
@@ -20152,35 +20152,35 @@
         <v>0</v>
       </c>
       <c r="M430" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="N430" t="n">
-        <v>1236.3</v>
+        <v>8174.05</v>
       </c>
       <c r="O430" t="n">
-        <v>279403.8</v>
+        <v>16348.1</v>
       </c>
       <c r="P430" t="n">
-        <v>2300</v>
+        <v>8900</v>
       </c>
       <c r="Q430" t="n">
-        <v>519800</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -20189,7 +20189,7 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
@@ -20198,35 +20198,35 @@
         <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N431" t="n">
-        <v>8174.05</v>
+        <v>11433.53</v>
       </c>
       <c r="O431" t="n">
-        <v>16348.1</v>
+        <v>45734.12</v>
       </c>
       <c r="P431" t="n">
-        <v>8900</v>
+        <v>15000</v>
       </c>
       <c r="Q431" t="n">
-        <v>17800</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG26011</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>CAMION DE BOMBEROS MG26011</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -20235,7 +20235,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -20244,30 +20244,30 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N432" t="n">
-        <v>11433.53</v>
+        <v>5920.69</v>
       </c>
       <c r="O432" t="n">
-        <v>45734.12</v>
+        <v>29603.45</v>
       </c>
       <c r="P432" t="n">
-        <v>15000</v>
+        <v>11900</v>
       </c>
       <c r="Q432" t="n">
-        <v>60000</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>MG26011</t>
+          <t>MG26196</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>CAMION DE BOMBEROS MG26011</t>
+          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K433" t="n">
         <v>0</v>
@@ -20290,30 +20290,30 @@
         <v>0</v>
       </c>
       <c r="M433" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N433" t="n">
-        <v>5920.69</v>
+        <v>6272.36</v>
       </c>
       <c r="O433" t="n">
-        <v>29603.45</v>
+        <v>94085.39999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>11900</v>
+        <v>10500</v>
       </c>
       <c r="Q433" t="n">
-        <v>59500</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MG26196</t>
+          <t>MG27332</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
+          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
@@ -20336,30 +20336,30 @@
         <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N434" t="n">
-        <v>6272.36</v>
+        <v>6750.7</v>
       </c>
       <c r="O434" t="n">
-        <v>94085.39999999999</v>
+        <v>135014</v>
       </c>
       <c r="P434" t="n">
-        <v>10500</v>
+        <v>22500</v>
       </c>
       <c r="Q434" t="n">
-        <v>157500</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>MG27332</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K435" t="n">
         <v>0</v>
@@ -20382,35 +20382,35 @@
         <v>0</v>
       </c>
       <c r="M435" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N435" t="n">
-        <v>6750.7</v>
+        <v>9046.99</v>
       </c>
       <c r="O435" t="n">
-        <v>135014</v>
+        <v>63328.93</v>
       </c>
       <c r="P435" t="n">
         <v>22500</v>
       </c>
       <c r="Q435" t="n">
-        <v>450000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -20419,7 +20419,7 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
@@ -20428,35 +20428,40 @@
         <v>0</v>
       </c>
       <c r="M436" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="N436" t="n">
-        <v>9046.99</v>
+        <v>1319.3609259259</v>
       </c>
       <c r="O436" t="n">
-        <v>63328.93</v>
+        <v>50135.7151851842</v>
       </c>
       <c r="P436" t="n">
-        <v>22500</v>
+        <v>3500</v>
       </c>
       <c r="Q436" t="n">
-        <v>157500</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG32342</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>MG32342</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -20465,7 +20470,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -20474,40 +20479,35 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="N437" t="n">
-        <v>1319.3609259259</v>
+        <v>1161.6</v>
       </c>
       <c r="O437" t="n">
-        <v>50135.7151851842</v>
+        <v>20908.8</v>
       </c>
       <c r="P437" t="n">
-        <v>3500</v>
+        <v>24500</v>
       </c>
       <c r="Q437" t="n">
-        <v>133000</v>
+        <v>441000</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>MG32342</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>MG32342</t>
+          <t>MG32594</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
+          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="J438" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K438" t="n">
         <v>0</v>
@@ -20525,35 +20525,40 @@
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="N438" t="n">
-        <v>1161.6</v>
+        <v>3088.1452173913</v>
       </c>
       <c r="O438" t="n">
-        <v>20908.8</v>
+        <v>111173.2278260868</v>
       </c>
       <c r="P438" t="n">
-        <v>24500</v>
+        <v>8500</v>
       </c>
       <c r="Q438" t="n">
-        <v>441000</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>MG32594</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -20562,7 +20567,7 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
@@ -20571,40 +20576,35 @@
         <v>0</v>
       </c>
       <c r="M439" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="N439" t="n">
-        <v>3088.1452173913</v>
+        <v>751.45</v>
       </c>
       <c r="O439" t="n">
-        <v>111173.2278260868</v>
+        <v>2254.35</v>
       </c>
       <c r="P439" t="n">
-        <v>8500</v>
+        <v>2500</v>
       </c>
       <c r="Q439" t="n">
-        <v>306000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -20613,7 +20613,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -20622,35 +20622,35 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="N440" t="n">
-        <v>751.45</v>
+        <v>571.87</v>
       </c>
       <c r="O440" t="n">
-        <v>2254.35</v>
+        <v>86924.24000000001</v>
       </c>
       <c r="P440" t="n">
         <v>2500</v>
       </c>
       <c r="Q440" t="n">
-        <v>7500</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40226</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>ATARY COCODRILO MG40226</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -20659,7 +20659,7 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
@@ -20668,30 +20668,35 @@
         <v>0</v>
       </c>
       <c r="M441" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="N441" t="n">
-        <v>571.87</v>
+        <v>310.41666666667</v>
       </c>
       <c r="O441" t="n">
-        <v>86924.24000000001</v>
+        <v>310.41666666667</v>
       </c>
       <c r="P441" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="Q441" t="n">
-        <v>380000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>MG40226</t>
+          <t>MG40243</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>MG40243</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>ATARY COCODRILO MG40226</t>
+          <t>ATARY DINOSAURIO MG40243</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -20705,7 +20710,7 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
@@ -20714,40 +20719,35 @@
         <v>0</v>
       </c>
       <c r="M442" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N442" t="n">
-        <v>310.41666666667</v>
+        <v>520.674</v>
       </c>
       <c r="O442" t="n">
-        <v>310.41666666667</v>
+        <v>4165.392</v>
       </c>
       <c r="P442" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="Q442" t="n">
-        <v>1800</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MG40243</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>MG40243</t>
+          <t>MG40259</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>ATARY DINOSAURIO MG40243</t>
+          <t>CARRO JET DESTAPADO MG40259</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -20756,7 +20756,7 @@
         </is>
       </c>
       <c r="J443" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K443" t="n">
         <v>0</v>
@@ -20765,35 +20765,40 @@
         <v>0</v>
       </c>
       <c r="M443" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N443" t="n">
-        <v>520.674</v>
+        <v>1153.41</v>
       </c>
       <c r="O443" t="n">
-        <v>4165.392</v>
+        <v>2306.82</v>
       </c>
       <c r="P443" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="Q443" t="n">
-        <v>16000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MG40259</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>CARRO JET DESTAPADO MG40259</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -20802,7 +20807,7 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
@@ -20811,35 +20816,30 @@
         <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="N444" t="n">
-        <v>1153.41</v>
+        <v>2432.1356790123</v>
       </c>
       <c r="O444" t="n">
-        <v>2306.82</v>
+        <v>102149.6985185166</v>
       </c>
       <c r="P444" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="Q444" t="n">
-        <v>8000</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG40327</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>BLISTER PESCA STD  MG40327</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -20862,35 +20862,35 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="N445" t="n">
-        <v>2432.1356790123</v>
+        <v>449.63</v>
       </c>
       <c r="O445" t="n">
-        <v>102149.6985185166</v>
+        <v>449.63</v>
       </c>
       <c r="P445" t="n">
-        <v>4500</v>
+        <v>5100</v>
       </c>
       <c r="Q445" t="n">
-        <v>189000</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MG40327</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>BLISTER PESCA STD  MG40327</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -20899,7 +20899,7 @@
         </is>
       </c>
       <c r="J446" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="K446" t="n">
         <v>0</v>
@@ -20908,30 +20908,30 @@
         <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="N446" t="n">
-        <v>449.63</v>
+        <v>227.41614285714</v>
       </c>
       <c r="O446" t="n">
-        <v>449.63</v>
+        <v>53442.79357142789</v>
       </c>
       <c r="P446" t="n">
-        <v>5100</v>
+        <v>1200</v>
       </c>
       <c r="Q446" t="n">
-        <v>5100</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40415</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>TELEFONO AVION MG40415</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="J447" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="K447" t="n">
         <v>0</v>
@@ -20954,35 +20954,35 @@
         <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="N447" t="n">
-        <v>227.41614285714</v>
+        <v>13308.19</v>
       </c>
       <c r="O447" t="n">
-        <v>53442.79357142789</v>
+        <v>26616.38</v>
       </c>
       <c r="P447" t="n">
-        <v>1200</v>
+        <v>34600</v>
       </c>
       <c r="Q447" t="n">
-        <v>282000</v>
+        <v>69200</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MG40415</t>
+          <t>MG40570</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>TELEFONO AVION MG40415</t>
+          <t>REGISTRADORA SENCILLA MG40570</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -20991,7 +20991,7 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
@@ -21000,35 +21000,35 @@
         <v>0</v>
       </c>
       <c r="M448" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N448" t="n">
-        <v>13308.19</v>
+        <v>8735.540000000001</v>
       </c>
       <c r="O448" t="n">
-        <v>26616.38</v>
+        <v>61148.78000000001</v>
       </c>
       <c r="P448" t="n">
-        <v>34600</v>
+        <v>29900</v>
       </c>
       <c r="Q448" t="n">
-        <v>69200</v>
+        <v>209300</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MG40570</t>
+          <t>MG40805</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>REGISTRADORA SENCILLA MG40570</t>
+          <t>LANZA DARDOS HERO GDE MG40805</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -21037,7 +21037,7 @@
         </is>
       </c>
       <c r="J449" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K449" t="n">
         <v>0</v>
@@ -21046,35 +21046,35 @@
         <v>0</v>
       </c>
       <c r="M449" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N449" t="n">
-        <v>8735.540000000001</v>
+        <v>22654.34</v>
       </c>
       <c r="O449" t="n">
-        <v>61148.78000000001</v>
+        <v>249197.74</v>
       </c>
       <c r="P449" t="n">
-        <v>29900</v>
+        <v>58900</v>
       </c>
       <c r="Q449" t="n">
-        <v>209300</v>
+        <v>647900</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MG40805</t>
+          <t>MG41038</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>LANZA DARDOS HERO GDE MG40805</t>
+          <t>VOLQUETA SENCILLA MED MG41038</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -21083,7 +21083,7 @@
         </is>
       </c>
       <c r="J450" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K450" t="n">
         <v>0</v>
@@ -21092,35 +21092,35 @@
         <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N450" t="n">
-        <v>22654.34</v>
+        <v>4962.04</v>
       </c>
       <c r="O450" t="n">
-        <v>249197.74</v>
+        <v>9924.08</v>
       </c>
       <c r="P450" t="n">
-        <v>58900</v>
+        <v>12900</v>
       </c>
       <c r="Q450" t="n">
-        <v>647900</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>MG41038</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>VOLQUETA SENCILLA MED MG41038</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="J451" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K451" t="n">
         <v>0</v>
@@ -21138,35 +21138,35 @@
         <v>0</v>
       </c>
       <c r="M451" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N451" t="n">
-        <v>4962.04</v>
+        <v>25110.1</v>
       </c>
       <c r="O451" t="n">
-        <v>9924.08</v>
+        <v>326431.3</v>
       </c>
       <c r="P451" t="n">
-        <v>12900</v>
+        <v>27900</v>
       </c>
       <c r="Q451" t="n">
-        <v>25800</v>
+        <v>362700</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MG41588</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
+          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="J452" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K452" t="n">
         <v>0</v>
@@ -21184,30 +21184,30 @@
         <v>0</v>
       </c>
       <c r="M452" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N452" t="n">
-        <v>25110.1</v>
+        <v>5422.51</v>
       </c>
       <c r="O452" t="n">
-        <v>326431.3</v>
+        <v>32535.06</v>
       </c>
       <c r="P452" t="n">
-        <v>27900</v>
+        <v>19900</v>
       </c>
       <c r="Q452" t="n">
-        <v>362700</v>
+        <v>119400</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>MG41588</t>
+          <t>MG41589</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
+          <t>MUÑECA ODONTOLOGA MG41589</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="J453" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
@@ -21230,35 +21230,35 @@
         <v>0</v>
       </c>
       <c r="M453" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N453" t="n">
-        <v>5422.51</v>
+        <v>5103.23</v>
       </c>
       <c r="O453" t="n">
-        <v>32535.06</v>
+        <v>20412.92</v>
       </c>
       <c r="P453" t="n">
         <v>19900</v>
       </c>
       <c r="Q453" t="n">
-        <v>119400</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>MG41589</t>
+          <t>MJC-558</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>MUÑECA ODONTOLOGA MG41589</t>
+          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -21267,7 +21267,7 @@
         </is>
       </c>
       <c r="J454" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K454" t="n">
         <v>0</v>
@@ -21276,30 +21276,30 @@
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N454" t="n">
-        <v>5103.23</v>
+        <v>40500</v>
       </c>
       <c r="O454" t="n">
-        <v>20412.92</v>
+        <v>729000</v>
       </c>
       <c r="P454" t="n">
-        <v>19900</v>
+        <v>48600</v>
       </c>
       <c r="Q454" t="n">
-        <v>79600</v>
+        <v>874800</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>MJC-558</t>
+          <t>MJC-558-1</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="J455" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K455" t="n">
         <v>0</v>
@@ -21322,30 +21322,33 @@
         <v>0</v>
       </c>
       <c r="M455" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N455" t="n">
         <v>40500</v>
       </c>
       <c r="O455" t="n">
-        <v>729000</v>
+        <v>324000</v>
       </c>
       <c r="P455" t="n">
         <v>48600</v>
       </c>
       <c r="Q455" t="n">
-        <v>874800</v>
+        <v>388800</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>MJC-558-1</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -21355,11 +21358,11 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J456" t="n">
-        <v>8</v>
+        <v>582</v>
       </c>
       <c r="K456" t="n">
         <v>0</v>
@@ -21368,33 +21371,30 @@
         <v>0</v>
       </c>
       <c r="M456" t="n">
-        <v>8</v>
+        <v>582</v>
       </c>
       <c r="N456" t="n">
-        <v>40500</v>
+        <v>2539.5716651076</v>
       </c>
       <c r="O456" t="n">
-        <v>324000</v>
+        <v>1478030.709092623</v>
       </c>
       <c r="P456" t="n">
-        <v>48600</v>
+        <v>2900</v>
       </c>
       <c r="Q456" t="n">
-        <v>388800</v>
+        <v>1687800</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B457" t="n">
-        <v>7700154271143</v>
+          <t>MT4690</t>
+        </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>BALDE CASTILLO PQÑ MT4690</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -21404,11 +21404,11 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J457" t="n">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="K457" t="n">
         <v>0</v>
@@ -21417,30 +21417,30 @@
         <v>0</v>
       </c>
       <c r="M457" t="n">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="N457" t="n">
-        <v>2539.5716573557</v>
+        <v>4687.9745841035</v>
       </c>
       <c r="O457" t="n">
-        <v>1478030.704581018</v>
+        <v>2629953.741682063</v>
       </c>
       <c r="P457" t="n">
-        <v>2900</v>
+        <v>5500</v>
       </c>
       <c r="Q457" t="n">
-        <v>1687800</v>
+        <v>3085500</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>MT4690</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>BALDE CASTILLO PQÑ MT4690</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -21454,7 +21454,7 @@
         </is>
       </c>
       <c r="J458" t="n">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="K458" t="n">
         <v>0</v>
@@ -21463,35 +21463,35 @@
         <v>0</v>
       </c>
       <c r="M458" t="n">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="N458" t="n">
-        <v>4687.9745421245</v>
+        <v>4171.6686137441</v>
       </c>
       <c r="O458" t="n">
-        <v>2629953.718131844</v>
+        <v>333733.489099528</v>
       </c>
       <c r="P458" t="n">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="Q458" t="n">
-        <v>3085500</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>PT08</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>ALCANCIA PEQUEÑA PP002</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -21512,32 +21512,32 @@
         <v>80</v>
       </c>
       <c r="N459" t="n">
-        <v>4171.668620283</v>
+        <v>436.24</v>
       </c>
       <c r="O459" t="n">
-        <v>333733.48962264</v>
+        <v>34899.2</v>
       </c>
       <c r="P459" t="n">
-        <v>5000</v>
+        <v>550</v>
       </c>
       <c r="Q459" t="n">
-        <v>400000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>PT08</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>ALCANCIA PEQUEÑA PP002</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -21546,7 +21546,7 @@
         </is>
       </c>
       <c r="J460" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="K460" t="n">
         <v>0</v>
@@ -21555,35 +21555,40 @@
         <v>0</v>
       </c>
       <c r="M460" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="N460" t="n">
-        <v>436.24</v>
+        <v>1950.7</v>
       </c>
       <c r="O460" t="n">
-        <v>34899.2</v>
+        <v>206774.2</v>
       </c>
       <c r="P460" t="n">
-        <v>550</v>
+        <v>7500</v>
       </c>
       <c r="Q460" t="n">
-        <v>44000</v>
+        <v>795000</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>PT15838</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>PT15838</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>LANZADORA DE AGUA PT15838</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -21592,7 +21597,7 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -21601,40 +21606,35 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="N461" t="n">
-        <v>1950.7</v>
+        <v>753.98</v>
       </c>
       <c r="O461" t="n">
-        <v>206774.2</v>
+        <v>753.98</v>
       </c>
       <c r="P461" t="n">
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="Q461" t="n">
-        <v>795000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>PT15838</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>PT15838</t>
+          <t>PT25404</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA PT15838</t>
+          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MONTABLES</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -21655,27 +21655,27 @@
         <v>1</v>
       </c>
       <c r="N462" t="n">
-        <v>753.98</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="O462" t="n">
-        <v>753.98</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="P462" t="n">
-        <v>4000</v>
+        <v>109900</v>
       </c>
       <c r="Q462" t="n">
-        <v>4000</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>PT25404</t>
+          <t>PT25419</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
+          <t>MONOPATIN CAJA LUCES PT25419</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="J463" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K463" t="n">
         <v>0</v>
@@ -21698,30 +21698,30 @@
         <v>0</v>
       </c>
       <c r="M463" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N463" t="n">
-        <v>84538.46000000001</v>
+        <v>87920</v>
       </c>
       <c r="O463" t="n">
-        <v>84538.46000000001</v>
+        <v>527520</v>
       </c>
       <c r="P463" t="n">
         <v>109900</v>
       </c>
       <c r="Q463" t="n">
-        <v>109900</v>
+        <v>659400</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>PT25419</t>
+          <t>PT25420</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>MONOPATIN CAJA LUCES PT25419</t>
+          <t>MONOPATIN  PATO PT25420</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="J464" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K464" t="n">
         <v>0</v>
@@ -21744,35 +21744,35 @@
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N464" t="n">
-        <v>87920</v>
+        <v>15394.79</v>
       </c>
       <c r="O464" t="n">
-        <v>527520</v>
+        <v>169342.69</v>
       </c>
       <c r="P464" t="n">
-        <v>109900</v>
+        <v>99800</v>
       </c>
       <c r="Q464" t="n">
-        <v>659400</v>
+        <v>1097800</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>PT25420</t>
+          <t>PT26747</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>MONOPATIN  PATO PT25420</t>
+          <t>TABLA LABERINTO PT26747</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>MONTABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -21781,7 +21781,7 @@
         </is>
       </c>
       <c r="J465" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K465" t="n">
         <v>0</v>
@@ -21790,30 +21790,30 @@
         <v>0</v>
       </c>
       <c r="M465" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N465" t="n">
-        <v>15394.79</v>
+        <v>2361.5097058824</v>
       </c>
       <c r="O465" t="n">
-        <v>169342.69</v>
+        <v>56676.2329411776</v>
       </c>
       <c r="P465" t="n">
-        <v>99800</v>
+        <v>6200</v>
       </c>
       <c r="Q465" t="n">
-        <v>1097800</v>
+        <v>148800</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>PT26747</t>
+          <t>RL589-28D</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>TABLA LABERINTO PT26747</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -21839,27 +21839,27 @@
         <v>24</v>
       </c>
       <c r="N466" t="n">
-        <v>2361.5097058824</v>
+        <v>7046.7392307692</v>
       </c>
       <c r="O466" t="n">
-        <v>56676.2329411776</v>
+        <v>169121.7415384608</v>
       </c>
       <c r="P466" t="n">
-        <v>6200</v>
+        <v>22900</v>
       </c>
       <c r="Q466" t="n">
-        <v>148800</v>
+        <v>549600</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>RL589-28D</t>
+          <t>RL589-33D</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -21873,7 +21873,7 @@
         </is>
       </c>
       <c r="J467" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K467" t="n">
         <v>0</v>
@@ -21882,35 +21882,35 @@
         <v>0</v>
       </c>
       <c r="M467" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="N467" t="n">
-        <v>7046.7392307692</v>
+        <v>10009.172222222</v>
       </c>
       <c r="O467" t="n">
-        <v>169121.7415384608</v>
+        <v>30027.516666666</v>
       </c>
       <c r="P467" t="n">
         <v>22900</v>
       </c>
       <c r="Q467" t="n">
-        <v>549600</v>
+        <v>68700</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>RL589-33D</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="J468" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K468" t="n">
         <v>0</v>
@@ -21928,35 +21928,35 @@
         <v>0</v>
       </c>
       <c r="M468" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N468" t="n">
-        <v>10009.172222222</v>
+        <v>4091.4</v>
       </c>
       <c r="O468" t="n">
-        <v>30027.516666666</v>
+        <v>36822.6</v>
       </c>
       <c r="P468" t="n">
-        <v>22900</v>
+        <v>10000</v>
       </c>
       <c r="Q468" t="n">
-        <v>68700</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>SEBQ17</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>CUBO MAGICO COLORES X5 SE-19126</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -21965,7 +21965,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="K469" t="n">
         <v>0</v>
@@ -21974,35 +21974,35 @@
         <v>0</v>
       </c>
       <c r="M469" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="N469" t="n">
-        <v>4091.4</v>
+        <v>5148.77</v>
       </c>
       <c r="O469" t="n">
-        <v>36822.6</v>
+        <v>278033.58</v>
       </c>
       <c r="P469" t="n">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="Q469" t="n">
-        <v>90000</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>SEBQ17</t>
+          <t>SEBQ27</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>CUBO MAGICO COLORES X5 SE-19126</t>
+          <t>CELULAR MUÑECO X12 SE1597</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -22011,7 +22011,7 @@
         </is>
       </c>
       <c r="J470" t="n">
-        <v>54</v>
+        <v>451</v>
       </c>
       <c r="K470" t="n">
         <v>0</v>
@@ -22020,30 +22020,30 @@
         <v>0</v>
       </c>
       <c r="M470" t="n">
-        <v>54</v>
+        <v>451</v>
       </c>
       <c r="N470" t="n">
-        <v>5148.77</v>
+        <v>855.85</v>
       </c>
       <c r="O470" t="n">
-        <v>278033.58</v>
+        <v>385988.35</v>
       </c>
       <c r="P470" t="n">
-        <v>10500</v>
+        <v>3500</v>
       </c>
       <c r="Q470" t="n">
-        <v>567000</v>
+        <v>1578500</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>SEBQ27</t>
+          <t>SLT052</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>CELULAR MUÑECO X12 SE1597</t>
+          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -22057,7 +22057,7 @@
         </is>
       </c>
       <c r="J471" t="n">
-        <v>451</v>
+        <v>2</v>
       </c>
       <c r="K471" t="n">
         <v>0</v>
@@ -22066,35 +22066,35 @@
         <v>0</v>
       </c>
       <c r="M471" t="n">
-        <v>451</v>
+        <v>2</v>
       </c>
       <c r="N471" t="n">
-        <v>855.85</v>
+        <v>0</v>
       </c>
       <c r="O471" t="n">
-        <v>385988.35</v>
+        <v>0</v>
       </c>
       <c r="P471" t="n">
-        <v>3500</v>
+        <v>13500</v>
       </c>
       <c r="Q471" t="n">
-        <v>1578500</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>SLT052</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -22103,7 +22103,7 @@
         </is>
       </c>
       <c r="J472" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
@@ -22112,30 +22112,30 @@
         <v>0</v>
       </c>
       <c r="M472" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="N472" t="n">
-        <v>0</v>
+        <v>4550</v>
       </c>
       <c r="O472" t="n">
-        <v>0</v>
+        <v>819000</v>
       </c>
       <c r="P472" t="n">
-        <v>13500</v>
+        <v>5500</v>
       </c>
       <c r="Q472" t="n">
-        <v>27000</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>SLT2641</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>BALON BASQUEBOL # 5 SLT2641</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -22158,30 +22158,30 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="N473" t="n">
-        <v>4550</v>
+        <v>422.91</v>
       </c>
       <c r="O473" t="n">
-        <v>819000</v>
+        <v>3383.28</v>
       </c>
       <c r="P473" t="n">
-        <v>5500</v>
+        <v>12500</v>
       </c>
       <c r="Q473" t="n">
-        <v>990000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>SLT2641</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 5 SLT2641</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -22204,30 +22204,30 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="N474" t="n">
-        <v>422.91</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O474" t="n">
-        <v>3383.28</v>
+        <v>58314.66528688533</v>
       </c>
       <c r="P474" t="n">
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="Q474" t="n">
-        <v>100000</v>
+        <v>2479500</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SLT2642</t>
+          <t>SLT2714</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
+          <t>VENTILADOR MINI SLT2714</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -22241,7 +22241,7 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
@@ -22250,35 +22250,35 @@
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="N475" t="n">
-        <v>341.02143442623</v>
+        <v>4158.2958823529</v>
       </c>
       <c r="O475" t="n">
-        <v>58314.66528688533</v>
+        <v>133065.4682352928</v>
       </c>
       <c r="P475" t="n">
-        <v>14500</v>
+        <v>13800</v>
       </c>
       <c r="Q475" t="n">
-        <v>2479500</v>
+        <v>441600</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>SLT2714</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>VENTILADOR MINI SLT2714</t>
+          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -22287,7 +22287,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -22296,30 +22296,30 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="N476" t="n">
-        <v>4158.2958823529</v>
+        <v>22230.77</v>
       </c>
       <c r="O476" t="n">
-        <v>133065.4682352928</v>
+        <v>111153.85</v>
       </c>
       <c r="P476" t="n">
-        <v>13800</v>
+        <v>28900</v>
       </c>
       <c r="Q476" t="n">
-        <v>441600</v>
+        <v>144500</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T032</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -22333,7 +22333,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -22342,30 +22342,30 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N477" t="n">
-        <v>22230.77</v>
+        <v>33200</v>
       </c>
       <c r="O477" t="n">
-        <v>111153.85</v>
+        <v>33200</v>
       </c>
       <c r="P477" t="n">
-        <v>28900</v>
+        <v>41500</v>
       </c>
       <c r="Q477" t="n">
-        <v>144500</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T038</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
+          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -22391,32 +22391,32 @@
         <v>1</v>
       </c>
       <c r="N478" t="n">
-        <v>33200</v>
+        <v>4962.04</v>
       </c>
       <c r="O478" t="n">
-        <v>33200</v>
+        <v>4962.04</v>
       </c>
       <c r="P478" t="n">
-        <v>41500</v>
+        <v>12900</v>
       </c>
       <c r="Q478" t="n">
-        <v>41500</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>T038</t>
+          <t>T046</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
+          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -22425,7 +22425,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -22434,35 +22434,35 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N479" t="n">
-        <v>4962.04</v>
+        <v>22802.484</v>
       </c>
       <c r="O479" t="n">
-        <v>4962.04</v>
+        <v>114012.42</v>
       </c>
       <c r="P479" t="n">
-        <v>12900</v>
+        <v>41500</v>
       </c>
       <c r="Q479" t="n">
-        <v>12900</v>
+        <v>207500</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>T046</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -22471,7 +22471,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="K480" t="n">
         <v>0</v>
@@ -22480,35 +22480,35 @@
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N480" t="n">
-        <v>22802.484</v>
+        <v>12392.16</v>
       </c>
       <c r="O480" t="n">
-        <v>114012.42</v>
+        <v>557647.2</v>
       </c>
       <c r="P480" t="n">
-        <v>41500</v>
+        <v>15900</v>
       </c>
       <c r="Q480" t="n">
-        <v>207500</v>
+        <v>715500</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -22517,7 +22517,7 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
@@ -22526,35 +22526,35 @@
         <v>0</v>
       </c>
       <c r="M481" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="N481" t="n">
-        <v>12392.16</v>
+        <v>24882.58</v>
       </c>
       <c r="O481" t="n">
-        <v>557647.2</v>
+        <v>174178.06</v>
       </c>
       <c r="P481" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q481" t="n">
-        <v>715500</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T066</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -22563,7 +22563,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
@@ -22572,30 +22572,30 @@
         <v>0</v>
       </c>
       <c r="M482" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N482" t="n">
-        <v>24882.58</v>
+        <v>16576.2</v>
       </c>
       <c r="O482" t="n">
-        <v>174178.06</v>
+        <v>16576.2</v>
       </c>
       <c r="P482" t="n">
-        <v>31500</v>
+        <v>25900</v>
       </c>
       <c r="Q482" t="n">
-        <v>220500</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>T066</t>
+          <t>T067</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
+          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -22621,27 +22621,27 @@
         <v>1</v>
       </c>
       <c r="N483" t="n">
-        <v>16576.2</v>
+        <v>47600</v>
       </c>
       <c r="O483" t="n">
-        <v>16576.2</v>
+        <v>47600</v>
       </c>
       <c r="P483" t="n">
-        <v>25900</v>
+        <v>59500</v>
       </c>
       <c r="Q483" t="n">
-        <v>25900</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>T067</t>
+          <t>T073</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
+          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -22664,30 +22664,30 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N484" t="n">
-        <v>47600</v>
+        <v>6102.9</v>
       </c>
       <c r="O484" t="n">
-        <v>47600</v>
+        <v>12205.8</v>
       </c>
       <c r="P484" t="n">
-        <v>59500</v>
+        <v>11900</v>
       </c>
       <c r="Q484" t="n">
-        <v>59500</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>T073</t>
+          <t>T079</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
+          <t>PELUCHE 15CM BQ-15</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -22701,7 +22701,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -22710,30 +22710,30 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="N485" t="n">
-        <v>6102.9</v>
+        <v>525.33</v>
       </c>
       <c r="O485" t="n">
-        <v>12205.8</v>
+        <v>12082.59</v>
       </c>
       <c r="P485" t="n">
-        <v>11900</v>
+        <v>5900</v>
       </c>
       <c r="Q485" t="n">
-        <v>23800</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>T079</t>
+          <t>T089</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>PELUCHE 15CM BQ-15</t>
+          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -22756,30 +22756,30 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N486" t="n">
-        <v>525.33</v>
+        <v>8580.75</v>
       </c>
       <c r="O486" t="n">
-        <v>12082.59</v>
+        <v>17161.5</v>
       </c>
       <c r="P486" t="n">
-        <v>5900</v>
+        <v>42900</v>
       </c>
       <c r="Q486" t="n">
-        <v>135700</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>T089</t>
+          <t>T098</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
+          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -22793,7 +22793,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -22802,30 +22802,30 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N487" t="n">
-        <v>8580.75</v>
+        <v>14308.02</v>
       </c>
       <c r="O487" t="n">
-        <v>17161.5</v>
+        <v>14308.02</v>
       </c>
       <c r="P487" t="n">
-        <v>42900</v>
+        <v>27900</v>
       </c>
       <c r="Q487" t="n">
-        <v>85800</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>T098</t>
+          <t>T099</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -22839,7 +22839,7 @@
         </is>
       </c>
       <c r="J488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K488" t="n">
         <v>0</v>
@@ -22848,30 +22848,30 @@
         <v>0</v>
       </c>
       <c r="M488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N488" t="n">
-        <v>14308.02</v>
+        <v>8538.8633333333</v>
       </c>
       <c r="O488" t="n">
-        <v>14308.02</v>
+        <v>17077.7266666666</v>
       </c>
       <c r="P488" t="n">
-        <v>27900</v>
+        <v>18500</v>
       </c>
       <c r="Q488" t="n">
-        <v>27900</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>T099</t>
+          <t>T103</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
+          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -22894,30 +22894,30 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N489" t="n">
-        <v>8538.8633333333</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O489" t="n">
-        <v>17077.7266666666</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="P489" t="n">
-        <v>18500</v>
+        <v>25900</v>
       </c>
       <c r="Q489" t="n">
-        <v>37000</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>T103</t>
+          <t>T117</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
+          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -22931,7 +22931,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
@@ -22940,30 +22940,30 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N490" t="n">
-        <v>9962.040000000001</v>
+        <v>14577.42</v>
       </c>
       <c r="O490" t="n">
-        <v>9962.040000000001</v>
+        <v>29154.84</v>
       </c>
       <c r="P490" t="n">
-        <v>25900</v>
+        <v>37900</v>
       </c>
       <c r="Q490" t="n">
-        <v>25900</v>
+        <v>75800</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>T117</t>
+          <t>T121</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
+          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -22977,7 +22977,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -22986,30 +22986,30 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N491" t="n">
-        <v>14577.42</v>
+        <v>13000.5</v>
       </c>
       <c r="O491" t="n">
-        <v>29154.84</v>
+        <v>13000.5</v>
       </c>
       <c r="P491" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="Q491" t="n">
-        <v>75800</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>T121</t>
+          <t>T135</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
+          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -23023,7 +23023,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -23032,30 +23032,30 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N492" t="n">
-        <v>13000.5</v>
+        <v>7115.88</v>
       </c>
       <c r="O492" t="n">
-        <v>13000.5</v>
+        <v>35579.4</v>
       </c>
       <c r="P492" t="n">
-        <v>32500</v>
+        <v>18500</v>
       </c>
       <c r="Q492" t="n">
-        <v>32500</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>T135</t>
+          <t>T136</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
+          <t>BOLSO PELUCHE ANIMALES P01-30</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -23069,7 +23069,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -23078,30 +23078,30 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N493" t="n">
-        <v>7115.88</v>
+        <v>7886.43</v>
       </c>
       <c r="O493" t="n">
-        <v>35579.4</v>
+        <v>31545.72</v>
       </c>
       <c r="P493" t="n">
-        <v>18500</v>
+        <v>34500</v>
       </c>
       <c r="Q493" t="n">
-        <v>92500</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>T136</t>
+          <t>T143</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>BOLSO PELUCHE ANIMALES P01-30</t>
+          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="J494" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
@@ -23124,30 +23124,30 @@
         <v>0</v>
       </c>
       <c r="M494" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N494" t="n">
-        <v>7886.43</v>
+        <v>23920</v>
       </c>
       <c r="O494" t="n">
-        <v>31545.72</v>
+        <v>23920</v>
       </c>
       <c r="P494" t="n">
-        <v>34500</v>
+        <v>29900</v>
       </c>
       <c r="Q494" t="n">
-        <v>138000</v>
+        <v>29900</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>T143</t>
+          <t>T157</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
+          <t>PELUCHE CONEJO 30CM ANA-28</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="J495" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K495" t="n">
         <v>0</v>
@@ -23170,30 +23170,30 @@
         <v>0</v>
       </c>
       <c r="M495" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N495" t="n">
-        <v>23920</v>
+        <v>11472.4</v>
       </c>
       <c r="O495" t="n">
-        <v>23920</v>
+        <v>34417.2</v>
       </c>
       <c r="P495" t="n">
-        <v>29900</v>
+        <v>23900</v>
       </c>
       <c r="Q495" t="n">
-        <v>29900</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>T157</t>
+          <t>T158</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>PELUCHE CONEJO 30CM ANA-28</t>
+          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -23207,7 +23207,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -23216,30 +23216,30 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N496" t="n">
-        <v>11472.4</v>
+        <v>10577.42</v>
       </c>
       <c r="O496" t="n">
-        <v>34417.2</v>
+        <v>105774.2</v>
       </c>
       <c r="P496" t="n">
-        <v>23900</v>
+        <v>27500</v>
       </c>
       <c r="Q496" t="n">
-        <v>71700</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>T158</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -23253,7 +23253,7 @@
         </is>
       </c>
       <c r="J497" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -23262,30 +23262,30 @@
         <v>0</v>
       </c>
       <c r="M497" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N497" t="n">
-        <v>10577.42</v>
+        <v>5186.45</v>
       </c>
       <c r="O497" t="n">
-        <v>105774.2</v>
+        <v>103729</v>
       </c>
       <c r="P497" t="n">
-        <v>27500</v>
+        <v>7200</v>
       </c>
       <c r="Q497" t="n">
-        <v>275000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T171</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -23299,7 +23299,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -23308,44 +23308,34 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N498" t="n">
-        <v>5186.45</v>
+        <v>14832.4</v>
       </c>
       <c r="O498" t="n">
-        <v>103729</v>
+        <v>14832.4</v>
       </c>
       <c r="P498" t="n">
-        <v>7200</v>
+        <v>30900</v>
       </c>
       <c r="Q498" t="n">
-        <v>144000</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>T171</t>
+          <t>T172</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I499" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
         </is>
       </c>
       <c r="J499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -23354,34 +23344,44 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N499" t="n">
-        <v>14832.4</v>
+        <v>4462.14</v>
       </c>
       <c r="O499" t="n">
-        <v>14832.4</v>
+        <v>8924.280000000001</v>
       </c>
       <c r="P499" t="n">
-        <v>30900</v>
+        <v>14500</v>
       </c>
       <c r="Q499" t="n">
-        <v>30900</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>T172</t>
+          <t>T175</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
+          <t>PELUCHE BOWSER 35CM KUP-35</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J500" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -23390,30 +23390,30 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N500" t="n">
-        <v>4462.14</v>
+        <v>4614.22</v>
       </c>
       <c r="O500" t="n">
-        <v>8924.280000000001</v>
+        <v>32299.54</v>
       </c>
       <c r="P500" t="n">
-        <v>14500</v>
+        <v>51900</v>
       </c>
       <c r="Q500" t="n">
-        <v>29000</v>
+        <v>363300</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>T175</t>
+          <t>T181</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>PELUCHE BOWSER 35CM KUP-35</t>
+          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -23427,7 +23427,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -23436,30 +23436,30 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N501" t="n">
-        <v>4614.22</v>
+        <v>11692.75</v>
       </c>
       <c r="O501" t="n">
-        <v>32299.54</v>
+        <v>23385.5</v>
       </c>
       <c r="P501" t="n">
-        <v>51900</v>
+        <v>28500</v>
       </c>
       <c r="Q501" t="n">
-        <v>363300</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>T181</t>
+          <t>T182</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
+          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -23473,7 +23473,7 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
@@ -23482,30 +23482,30 @@
         <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N502" t="n">
-        <v>11692.75</v>
+        <v>5600.5</v>
       </c>
       <c r="O502" t="n">
-        <v>23385.5</v>
+        <v>5600.5</v>
       </c>
       <c r="P502" t="n">
-        <v>28500</v>
+        <v>14000</v>
       </c>
       <c r="Q502" t="n">
-        <v>57000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>T182</t>
+          <t>T185</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
+          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -23519,7 +23519,7 @@
         </is>
       </c>
       <c r="J503" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
@@ -23528,30 +23528,30 @@
         <v>0</v>
       </c>
       <c r="M503" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N503" t="n">
-        <v>5600.5</v>
+        <v>9160.5</v>
       </c>
       <c r="O503" t="n">
-        <v>5600.5</v>
+        <v>45802.5</v>
       </c>
       <c r="P503" t="n">
-        <v>14000</v>
+        <v>22900</v>
       </c>
       <c r="Q503" t="n">
-        <v>14000</v>
+        <v>114500</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>T185</t>
+          <t>T195</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
+          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -23574,30 +23574,30 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N504" t="n">
-        <v>9160.5</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="O504" t="n">
-        <v>45802.5</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="P504" t="n">
-        <v>22900</v>
+        <v>23900</v>
       </c>
       <c r="Q504" t="n">
-        <v>114500</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>T195</t>
+          <t>T201-LJ</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
+          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -23620,35 +23620,35 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N505" t="n">
-        <v>9192.809999999999</v>
+        <v>35000</v>
       </c>
       <c r="O505" t="n">
-        <v>9192.809999999999</v>
+        <v>70000</v>
       </c>
       <c r="P505" t="n">
-        <v>23900</v>
+        <v>45500</v>
       </c>
       <c r="Q505" t="n">
-        <v>23900</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>T201-LJ</t>
+          <t>T203</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
+          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -23657,7 +23657,7 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
@@ -23666,30 +23666,30 @@
         <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N506" t="n">
-        <v>35000</v>
+        <v>11885.11</v>
       </c>
       <c r="O506" t="n">
-        <v>70000</v>
+        <v>11885.11</v>
       </c>
       <c r="P506" t="n">
-        <v>45500</v>
+        <v>30900</v>
       </c>
       <c r="Q506" t="n">
-        <v>91000</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>T203</t>
+          <t>T206</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
+          <t>PELUCHE PATO 30CM HJE-30</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -23703,7 +23703,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -23712,35 +23712,35 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N507" t="n">
-        <v>11885.11</v>
+        <v>31120</v>
       </c>
       <c r="O507" t="n">
-        <v>11885.11</v>
+        <v>62240</v>
       </c>
       <c r="P507" t="n">
-        <v>30900</v>
+        <v>38900</v>
       </c>
       <c r="Q507" t="n">
-        <v>30900</v>
+        <v>77800</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>T206</t>
+          <t>T207</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM HJE-30</t>
+          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -23761,27 +23761,27 @@
         <v>2</v>
       </c>
       <c r="N508" t="n">
-        <v>31120</v>
+        <v>7520.71</v>
       </c>
       <c r="O508" t="n">
-        <v>62240</v>
+        <v>15041.42</v>
       </c>
       <c r="P508" t="n">
-        <v>38900</v>
+        <v>32900</v>
       </c>
       <c r="Q508" t="n">
-        <v>77800</v>
+        <v>65800</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>T207</t>
+          <t>T211</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
+          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -23807,27 +23807,27 @@
         <v>2</v>
       </c>
       <c r="N509" t="n">
-        <v>7520.71</v>
+        <v>16500.5</v>
       </c>
       <c r="O509" t="n">
-        <v>15041.42</v>
+        <v>33001</v>
       </c>
       <c r="P509" t="n">
-        <v>32900</v>
+        <v>42900</v>
       </c>
       <c r="Q509" t="n">
-        <v>65800</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>T211</t>
+          <t>T213</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
+          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -23841,7 +23841,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23850,30 +23850,30 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N510" t="n">
-        <v>16500.5</v>
+        <v>16220.2125</v>
       </c>
       <c r="O510" t="n">
-        <v>33001</v>
+        <v>64880.85</v>
       </c>
       <c r="P510" t="n">
-        <v>42900</v>
+        <v>36900</v>
       </c>
       <c r="Q510" t="n">
-        <v>85800</v>
+        <v>147600</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>T213</t>
+          <t>T214</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
+          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23896,30 +23896,30 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N511" t="n">
-        <v>16220.2125</v>
+        <v>11885.11</v>
       </c>
       <c r="O511" t="n">
-        <v>64880.85</v>
+        <v>11885.11</v>
       </c>
       <c r="P511" t="n">
-        <v>36900</v>
+        <v>30900</v>
       </c>
       <c r="Q511" t="n">
-        <v>147600</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>T214</t>
+          <t>T216</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
+          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -23933,7 +23933,7 @@
         </is>
       </c>
       <c r="J512" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -23942,30 +23942,30 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N512" t="n">
-        <v>11885.11</v>
+        <v>14760.5</v>
       </c>
       <c r="O512" t="n">
-        <v>11885.11</v>
+        <v>73802.5</v>
       </c>
       <c r="P512" t="n">
-        <v>30900</v>
+        <v>36900</v>
       </c>
       <c r="Q512" t="n">
-        <v>30900</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>T216</t>
+          <t>T217</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
+          <t>PELUCHE GATO TELA 30CM BQM-30</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -23979,7 +23979,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -23988,44 +23988,34 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N513" t="n">
-        <v>14760.5</v>
+        <v>8462.040000000001</v>
       </c>
       <c r="O513" t="n">
-        <v>73802.5</v>
+        <v>50772.24000000001</v>
       </c>
       <c r="P513" t="n">
-        <v>36900</v>
+        <v>22000</v>
       </c>
       <c r="Q513" t="n">
-        <v>184500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>T217</t>
+          <t>T222</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>PELUCHE GATO TELA 30CM BQM-30</t>
-        </is>
-      </c>
-      <c r="E514" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I514" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
         </is>
       </c>
       <c r="J514" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -24034,30 +24024,40 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N514" t="n">
-        <v>8462.040000000001</v>
+        <v>23461.54</v>
       </c>
       <c r="O514" t="n">
-        <v>50772.24000000001</v>
+        <v>23461.54</v>
       </c>
       <c r="P514" t="n">
-        <v>22000</v>
+        <v>30500</v>
       </c>
       <c r="Q514" t="n">
-        <v>132000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>T222</t>
+          <t>T229</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
+          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J515" t="n">
@@ -24073,27 +24073,27 @@
         <v>1</v>
       </c>
       <c r="N515" t="n">
-        <v>23461.54</v>
+        <v>18600.5</v>
       </c>
       <c r="O515" t="n">
-        <v>23461.54</v>
+        <v>18600.5</v>
       </c>
       <c r="P515" t="n">
-        <v>30500</v>
+        <v>46500</v>
       </c>
       <c r="Q515" t="n">
-        <v>30500</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>T229</t>
+          <t>T243</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
+          <t>PELUCHE GATO 40CM DX-60</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -24119,27 +24119,27 @@
         <v>1</v>
       </c>
       <c r="N516" t="n">
-        <v>18600.5</v>
+        <v>26000</v>
       </c>
       <c r="O516" t="n">
-        <v>18600.5</v>
+        <v>26000</v>
       </c>
       <c r="P516" t="n">
-        <v>46500</v>
+        <v>32500</v>
       </c>
       <c r="Q516" t="n">
-        <v>46500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>T243</t>
+          <t>T244</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>PELUCHE GATO 40CM DX-60</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -24153,7 +24153,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -24162,30 +24162,30 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N517" t="n">
-        <v>26000</v>
+        <v>7400.5</v>
       </c>
       <c r="O517" t="n">
-        <v>26000</v>
+        <v>22201.5</v>
       </c>
       <c r="P517" t="n">
-        <v>32500</v>
+        <v>18500</v>
       </c>
       <c r="Q517" t="n">
-        <v>32500</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>T244</t>
+          <t>T245</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
+          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -24199,7 +24199,7 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -24208,30 +24208,30 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N518" t="n">
-        <v>7400.5</v>
+        <v>25200</v>
       </c>
       <c r="O518" t="n">
-        <v>22201.5</v>
+        <v>25200</v>
       </c>
       <c r="P518" t="n">
-        <v>18500</v>
+        <v>31500</v>
       </c>
       <c r="Q518" t="n">
-        <v>55500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>T245</t>
+          <t>T247</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
+          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="J519" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -24254,30 +24254,30 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N519" t="n">
-        <v>25200</v>
+        <v>8667.34</v>
       </c>
       <c r="O519" t="n">
-        <v>25200</v>
+        <v>34669.36</v>
       </c>
       <c r="P519" t="n">
-        <v>31500</v>
+        <v>32500</v>
       </c>
       <c r="Q519" t="n">
-        <v>31500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>T247</t>
+          <t>T248</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
+          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -24291,7 +24291,7 @@
         </is>
       </c>
       <c r="J520" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -24300,30 +24300,30 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N520" t="n">
-        <v>8667.34</v>
+        <v>40720</v>
       </c>
       <c r="O520" t="n">
-        <v>34669.36</v>
+        <v>81440</v>
       </c>
       <c r="P520" t="n">
-        <v>32500</v>
+        <v>50900</v>
       </c>
       <c r="Q520" t="n">
-        <v>130000</v>
+        <v>101800</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>T248</t>
+          <t>T250</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
+          <t>PELUCHE MAGO 40CM PCO-40</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -24337,7 +24337,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -24346,30 +24346,30 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N521" t="n">
-        <v>40720</v>
+        <v>29520</v>
       </c>
       <c r="O521" t="n">
-        <v>81440</v>
+        <v>88560</v>
       </c>
       <c r="P521" t="n">
-        <v>50900</v>
+        <v>36900</v>
       </c>
       <c r="Q521" t="n">
-        <v>101800</v>
+        <v>110700</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>T250</t>
+          <t>T272</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO 40CM PCO-40</t>
+          <t>PELUCHE BUHO 40CM MTY-40</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -24383,7 +24383,7 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
@@ -24392,30 +24392,30 @@
         <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N522" t="n">
-        <v>29520</v>
+        <v>12500.5</v>
       </c>
       <c r="O522" t="n">
-        <v>88560</v>
+        <v>12500.5</v>
       </c>
       <c r="P522" t="n">
-        <v>36900</v>
+        <v>32500</v>
       </c>
       <c r="Q522" t="n">
-        <v>110700</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>T272</t>
+          <t>T273</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>PELUCHE BUHO 40CM MTY-40</t>
+          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -24441,37 +24441,27 @@
         <v>1</v>
       </c>
       <c r="N523" t="n">
-        <v>12500.5</v>
+        <v>13808.19</v>
       </c>
       <c r="O523" t="n">
-        <v>12500.5</v>
+        <v>13808.19</v>
       </c>
       <c r="P523" t="n">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="Q523" t="n">
-        <v>32500</v>
+        <v>35900</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>T273</t>
+          <t>T300</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
-        </is>
-      </c>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I524" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
         </is>
       </c>
       <c r="J524" t="n">
@@ -24487,31 +24477,31 @@
         <v>1</v>
       </c>
       <c r="N524" t="n">
-        <v>13808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="O524" t="n">
-        <v>13808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="P524" t="n">
-        <v>35900</v>
+        <v>30500</v>
       </c>
       <c r="Q524" t="n">
-        <v>35900</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>T300</t>
+          <t>T334</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
+          <t>PELUCHE DIGIMON 20CM MD-20</t>
         </is>
       </c>
       <c r="J525" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -24520,44 +24510,34 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N525" t="n">
-        <v>13686.31</v>
+        <v>7571.81</v>
       </c>
       <c r="O525" t="n">
-        <v>13686.31</v>
+        <v>45430.86</v>
       </c>
       <c r="P525" t="n">
-        <v>30500</v>
+        <v>15900</v>
       </c>
       <c r="Q525" t="n">
-        <v>30500</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>T308</t>
+          <t>T336</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMAL ACOSTADO DISFRAZ 25CM DT230918-25</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I526" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
         </is>
       </c>
       <c r="J526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24566,34 +24546,44 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N526" t="n">
-        <v>4808.19</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O526" t="n">
-        <v>4808.19</v>
+        <v>19924.08</v>
       </c>
       <c r="P526" t="n">
-        <v>12500</v>
+        <v>25900</v>
       </c>
       <c r="Q526" t="n">
-        <v>12500</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>T334</t>
+          <t>T345</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>PELUCHE DIGIMON 20CM MD-20</t>
+          <t>PELUCHE ADVNG 20CM ESP-20</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J527" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24602,34 +24592,39 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N527" t="n">
-        <v>7571.81</v>
+        <v>1250.88</v>
       </c>
       <c r="O527" t="n">
-        <v>45430.86</v>
+        <v>3752.64</v>
       </c>
       <c r="P527" t="n">
-        <v>15900</v>
+        <v>12500</v>
       </c>
       <c r="Q527" t="n">
-        <v>95400</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>T336</t>
+          <t>T352</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
+          <t>NINJA T352</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J528" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24638,30 +24633,30 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N528" t="n">
-        <v>9962.040000000001</v>
+        <v>5192.31</v>
       </c>
       <c r="O528" t="n">
-        <v>19924.08</v>
+        <v>5192.31</v>
       </c>
       <c r="P528" t="n">
-        <v>25900</v>
+        <v>13500</v>
       </c>
       <c r="Q528" t="n">
-        <v>51800</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>T345</t>
+          <t>TB058</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>PELUCHE ADVNG 20CM ESP-20</t>
+          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -24687,27 +24682,32 @@
         <v>3</v>
       </c>
       <c r="N529" t="n">
-        <v>1250.88</v>
+        <v>17159.86</v>
       </c>
       <c r="O529" t="n">
-        <v>3752.64</v>
+        <v>51479.58</v>
       </c>
       <c r="P529" t="n">
-        <v>12500</v>
+        <v>21900</v>
       </c>
       <c r="Q529" t="n">
-        <v>37500</v>
+        <v>65700</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>T352</t>
+          <t>TO-030</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>NINJA T352</t>
+          <t>COJIN ANIMALES 40CM DWKD-40</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -24728,32 +24728,32 @@
         <v>1</v>
       </c>
       <c r="N530" t="n">
-        <v>5192.31</v>
+        <v>18384.62</v>
       </c>
       <c r="O530" t="n">
-        <v>5192.31</v>
+        <v>18384.62</v>
       </c>
       <c r="P530" t="n">
-        <v>13500</v>
+        <v>23900</v>
       </c>
       <c r="Q530" t="n">
-        <v>13500</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>TB058</t>
+          <t>TO-038</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
+          <t>COJIN ANIMAL 30CM DXS-25</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -24762,7 +24762,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24771,30 +24771,30 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N531" t="n">
-        <v>17159.86</v>
+        <v>14800</v>
       </c>
       <c r="O531" t="n">
-        <v>51479.58</v>
+        <v>14800</v>
       </c>
       <c r="P531" t="n">
-        <v>21900</v>
+        <v>18500</v>
       </c>
       <c r="Q531" t="n">
-        <v>65700</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>TO-030</t>
+          <t>TO-041</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>COJIN ANIMALES 40CM DWKD-40</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -24808,7 +24808,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24817,110 +24817,18 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N532" t="n">
-        <v>18384.62</v>
+        <v>2372.36</v>
       </c>
       <c r="O532" t="n">
-        <v>18384.62</v>
+        <v>21351.24</v>
       </c>
       <c r="P532" t="n">
-        <v>23900</v>
+        <v>41500</v>
       </c>
       <c r="Q532" t="n">
-        <v>23900</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>TO-038</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>COJIN ANIMAL 30CM DXS-25</t>
-        </is>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I533" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J533" t="n">
-        <v>1</v>
-      </c>
-      <c r="K533" t="n">
-        <v>0</v>
-      </c>
-      <c r="L533" t="n">
-        <v>0</v>
-      </c>
-      <c r="M533" t="n">
-        <v>1</v>
-      </c>
-      <c r="N533" t="n">
-        <v>14800</v>
-      </c>
-      <c r="O533" t="n">
-        <v>14800</v>
-      </c>
-      <c r="P533" t="n">
-        <v>18500</v>
-      </c>
-      <c r="Q533" t="n">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>TO-041</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88</t>
-        </is>
-      </c>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I534" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J534" t="n">
-        <v>9</v>
-      </c>
-      <c r="K534" t="n">
-        <v>0</v>
-      </c>
-      <c r="L534" t="n">
-        <v>0</v>
-      </c>
-      <c r="M534" t="n">
-        <v>9</v>
-      </c>
-      <c r="N534" t="n">
-        <v>2372.36</v>
-      </c>
-      <c r="O534" t="n">
-        <v>21351.24</v>
-      </c>
-      <c r="P534" t="n">
-        <v>41500</v>
-      </c>
-      <c r="Q534" t="n">
         <v>373500</v>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -634,10 +634,10 @@
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O6" t="n">
-        <v>325408.695652176</v>
+        <v>324000</v>
       </c>
       <c r="P6" t="n">
         <v>30000</v>
@@ -3541,10 +3541,10 @@
         <v>1352</v>
       </c>
       <c r="N73" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O73" t="n">
-        <v>7063671.013010092</v>
+        <v>7053243.38320524</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -4105,10 +4105,10 @@
         <v>275</v>
       </c>
       <c r="N85" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O85" t="n">
-        <v>4078638.123704925</v>
+        <v>4076154.17824505</v>
       </c>
       <c r="P85" t="n">
         <v>24900</v>
@@ -4957,10 +4957,10 @@
         <v>11</v>
       </c>
       <c r="N104" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O104" t="n">
-        <v>131549.729857821</v>
+        <v>131135.4</v>
       </c>
       <c r="P104" t="n">
         <v>19900</v>
@@ -6106,10 +6106,10 @@
         <v>6</v>
       </c>
       <c r="N130" t="n">
-        <v>39703.055555556</v>
+        <v>38630</v>
       </c>
       <c r="O130" t="n">
-        <v>238218.333333336</v>
+        <v>231780</v>
       </c>
       <c r="P130" t="n">
         <v>46500</v>
@@ -6439,10 +6439,10 @@
         <v>4</v>
       </c>
       <c r="N138" t="n">
-        <v>11594.699548023</v>
+        <v>11562.038418079</v>
       </c>
       <c r="O138" t="n">
-        <v>46378.798192092</v>
+        <v>46248.153672316</v>
       </c>
       <c r="P138" t="n">
         <v>18500</v>
@@ -6785,10 +6785,10 @@
         <v>16</v>
       </c>
       <c r="N146" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O146" t="n">
-        <v>432176.654970768</v>
+        <v>429664</v>
       </c>
       <c r="P146" t="n">
         <v>43900</v>
@@ -7123,10 +7123,10 @@
         <v>13</v>
       </c>
       <c r="N154" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O154" t="n">
-        <v>170034.335433963</v>
+        <v>168760.67</v>
       </c>
       <c r="P154" t="n">
         <v>21900</v>
@@ -8610,10 +8610,10 @@
         <v>344</v>
       </c>
       <c r="N186" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O186" t="n">
-        <v>5890525.723793712</v>
+        <v>5874140.394476832</v>
       </c>
       <c r="P186" t="n">
         <v>27500</v>
@@ -8656,10 +8656,10 @@
         <v>4</v>
       </c>
       <c r="N187" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O187" t="n">
-        <v>69303.95092024399</v>
+        <v>68672</v>
       </c>
       <c r="P187" t="n">
         <v>27900</v>
@@ -12268,10 +12268,10 @@
         <v>63</v>
       </c>
       <c r="N264" t="n">
-        <v>10639.697586207</v>
+        <v>10548.76</v>
       </c>
       <c r="O264" t="n">
-        <v>670300.947931041</v>
+        <v>664571.88</v>
       </c>
       <c r="P264" t="n">
         <v>35900</v>
@@ -15014,10 +15014,10 @@
         <v>214</v>
       </c>
       <c r="N321" t="n">
-        <v>2830.7108053691</v>
+        <v>2356.29</v>
       </c>
       <c r="O321" t="n">
-        <v>605772.1123489874</v>
+        <v>504246.06</v>
       </c>
       <c r="P321" t="n">
         <v>6500</v>
